--- a/research/traditional_assets/database/data/netherlands/netherlands_entertainment.xlsx
+++ b/research/traditional_assets/database/data/netherlands/netherlands_entertainment.xlsx
@@ -353,7 +353,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AQ3"/>
+  <dimension ref="A1:AQ4"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -581,52 +581,55 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
           <t>Entertainment</t>
         </is>
+      </c>
+      <c r="D2">
+        <v>-0.053</v>
       </c>
       <c r="F2">
         <v>0.156</v>
       </c>
       <c r="G2">
-        <v>0.1354443442296598</v>
+        <v>0.1305324105632052</v>
       </c>
       <c r="H2">
-        <v>0.1354443442296598</v>
+        <v>0.1305324105632052</v>
       </c>
       <c r="I2">
-        <v>0.1473969886811463</v>
+        <v>0.1377819835280721</v>
       </c>
       <c r="J2">
-        <v>0.1075348287416128</v>
+        <v>0.1191510484142507</v>
       </c>
       <c r="K2">
-        <v>1658.6</v>
+        <v>1648.2</v>
       </c>
       <c r="L2">
-        <v>0.1347699258139743</v>
+        <v>0.1321763955828929</v>
       </c>
       <c r="M2">
-        <v>997.5</v>
+        <v>997.979</v>
       </c>
       <c r="N2">
-        <v>0.02130918505985798</v>
+        <v>0.02123707501016124</v>
       </c>
       <c r="O2">
-        <v>0.601410828409502</v>
+        <v>0.6054962989928407</v>
       </c>
       <c r="P2">
-        <v>997.5</v>
+        <v>997.979</v>
       </c>
       <c r="Q2">
-        <v>0.02130918505985798</v>
+        <v>0.02123707501016124</v>
       </c>
       <c r="R2">
-        <v>0.601410828409502</v>
+        <v>0.6054962989928407</v>
       </c>
       <c r="S2">
         <v>0</v>
@@ -635,73 +638,73 @@
         <v>0</v>
       </c>
       <c r="U2">
-        <v>469.3</v>
+        <v>506.4</v>
       </c>
       <c r="V2">
-        <v>0.01002546420911414</v>
+        <v>0.01077623355315658</v>
       </c>
       <c r="W2">
-        <v>0.5941608454236074</v>
+        <v>0.2769487928240763</v>
       </c>
       <c r="X2">
-        <v>0.09258364558085422</v>
+        <v>0.1017427710103605</v>
       </c>
       <c r="Y2">
-        <v>0.5015771998427532</v>
+        <v>0.1752060218137157</v>
       </c>
       <c r="Z2">
-        <v>3.099584435209671</v>
+        <v>2.87917340106211</v>
       </c>
       <c r="AA2">
-        <v>0.3333132814104405</v>
+        <v>0.03364693196735619</v>
       </c>
       <c r="AB2">
-        <v>0.0887193217172273</v>
+        <v>0.08647642493431196</v>
       </c>
       <c r="AC2">
-        <v>0.2445939596932132</v>
+        <v>-0.05282949296695577</v>
       </c>
       <c r="AD2">
-        <v>3859.4</v>
+        <v>3976.4</v>
       </c>
       <c r="AE2">
         <v>0</v>
       </c>
       <c r="AF2">
-        <v>3859.4</v>
+        <v>3976.4</v>
       </c>
       <c r="AG2">
-        <v>3390.1</v>
+        <v>3470</v>
       </c>
       <c r="AH2">
-        <v>0.07616705677104096</v>
+        <v>0.07801650817070084</v>
       </c>
       <c r="AI2">
-        <v>0.5092564491654021</v>
+        <v>0.5009259142615992</v>
       </c>
       <c r="AJ2">
-        <v>0.06753066180088405</v>
+        <v>0.06876420614993767</v>
       </c>
       <c r="AK2">
-        <v>0.4768609688853879</v>
+        <v>0.4669187399921956</v>
       </c>
       <c r="AL2">
-        <v>117.9</v>
+        <v>125.7</v>
       </c>
       <c r="AM2">
-        <v>94.30000000000001</v>
+        <v>91.7</v>
       </c>
       <c r="AN2">
-        <v>2.020205192629816</v>
+        <v>2.125053441641727</v>
       </c>
       <c r="AO2">
-        <v>15.38592027141645</v>
+        <v>13.66825775656324</v>
       </c>
       <c r="AP2">
-        <v>1.774549832495812</v>
+        <v>1.854424967935015</v>
       </c>
       <c r="AQ2">
-        <v>19.23647932131495</v>
+        <v>18.7360959651036</v>
       </c>
     </row>
     <row r="3">
@@ -775,10 +778,10 @@
         <v>0.5941608454236074</v>
       </c>
       <c r="X3">
-        <v>0.09258364558085422</v>
+        <v>0.0925535678563045</v>
       </c>
       <c r="Y3">
-        <v>0.5015771998427532</v>
+        <v>0.5016072775673028</v>
       </c>
       <c r="Z3">
         <v>3.099584435209671</v>
@@ -787,10 +790,10 @@
         <v>0.3333132814104405</v>
       </c>
       <c r="AB3">
-        <v>0.0887193217172273</v>
+        <v>0.0886915349244309</v>
       </c>
       <c r="AC3">
-        <v>0.2445939596932132</v>
+        <v>0.2446217464860097</v>
       </c>
       <c r="AD3">
         <v>3859.4</v>
@@ -833,6 +836,137 @@
       </c>
       <c r="AQ3">
         <v>19.23647932131495</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Netherlands</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>AFC Ajax NV (ENXTAM:AJAX)</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Entertainment</t>
+        </is>
+      </c>
+      <c r="D4">
+        <v>-0.053</v>
+      </c>
+      <c r="G4">
+        <v>-0.2407862407862408</v>
+      </c>
+      <c r="H4">
+        <v>-0.2407862407862408</v>
+      </c>
+      <c r="I4">
+        <v>-0.5890663390663391</v>
+      </c>
+      <c r="J4">
+        <v>-0.5890663390663391</v>
+      </c>
+      <c r="K4">
+        <v>-10.4</v>
+      </c>
+      <c r="L4">
+        <v>-0.06388206388206388</v>
+      </c>
+      <c r="M4">
+        <v>0.479</v>
+      </c>
+      <c r="N4">
+        <v>0.002639118457300276</v>
+      </c>
+      <c r="O4">
+        <v>-0.04605769230769231</v>
+      </c>
+      <c r="P4">
+        <v>0.479</v>
+      </c>
+      <c r="Q4">
+        <v>0.002639118457300276</v>
+      </c>
+      <c r="R4">
+        <v>-0.04605769230769231</v>
+      </c>
+      <c r="S4">
+        <v>0</v>
+      </c>
+      <c r="T4">
+        <v>0</v>
+      </c>
+      <c r="U4">
+        <v>37.1</v>
+      </c>
+      <c r="V4">
+        <v>0.2044077134986226</v>
+      </c>
+      <c r="W4">
+        <v>-0.0402632597754549</v>
+      </c>
+      <c r="X4">
+        <v>0.1109319741644166</v>
+      </c>
+      <c r="Y4">
+        <v>-0.1511952339398715</v>
+      </c>
+      <c r="Z4">
+        <v>0.4515950069348128</v>
+      </c>
+      <c r="AA4">
+        <v>-0.2660194174757282</v>
+      </c>
+      <c r="AB4">
+        <v>0.08426131494419301</v>
+      </c>
+      <c r="AC4">
+        <v>-0.3502807324199212</v>
+      </c>
+      <c r="AD4">
+        <v>117</v>
+      </c>
+      <c r="AE4">
+        <v>0</v>
+      </c>
+      <c r="AF4">
+        <v>117</v>
+      </c>
+      <c r="AG4">
+        <v>79.90000000000001</v>
+      </c>
+      <c r="AH4">
+        <v>0.3919597989949749</v>
+      </c>
+      <c r="AI4">
+        <v>0.3253615127919911</v>
+      </c>
+      <c r="AJ4">
+        <v>0.3056618209640398</v>
+      </c>
+      <c r="AK4">
+        <v>0.2477519379844961</v>
+      </c>
+      <c r="AL4">
+        <v>7.8</v>
+      </c>
+      <c r="AM4">
+        <v>-2.600000000000001</v>
+      </c>
+      <c r="AN4">
+        <v>-2.98469387755102</v>
+      </c>
+      <c r="AO4">
+        <v>-12.2948717948718</v>
+      </c>
+      <c r="AP4">
+        <v>-2.038265306122449</v>
+      </c>
+      <c r="AQ4">
+        <v>36.88461538461538</v>
       </c>
     </row>
   </sheetData>
@@ -1127,49 +1261,49 @@
         <v>13.6047497879559</v>
       </c>
       <c r="F2">
-        <v>3.03739082413973</v>
+        <v>3.01281880357707</v>
       </c>
       <c r="G2">
         <v>2.02020519262982</v>
       </c>
       <c r="H2">
-        <v>4.77420226130653</v>
+        <v>5.03943572026801</v>
       </c>
       <c r="I2">
         <v>0.07616705677104101</v>
       </c>
       <c r="J2">
-        <v>0.18</v>
+        <v>0.19</v>
       </c>
       <c r="K2">
         <v>46810.8</v>
       </c>
       <c r="L2">
-        <v>43230.9999519045</v>
+        <v>43368.1852427251</v>
       </c>
       <c r="M2">
         <v>50200.9</v>
       </c>
       <c r="N2">
-        <v>51882.3359519045</v>
+        <v>52526.2232427251</v>
       </c>
       <c r="O2">
         <v>3859.4</v>
       </c>
       <c r="P2">
-        <v>9120.636</v>
+        <v>9627.338</v>
       </c>
       <c r="Q2">
-        <v>0.0887193217172273</v>
+        <v>0.0886915349244309</v>
       </c>
       <c r="R2">
-        <v>0.0873283648676051</v>
+        <v>0.08679273701133811</v>
       </c>
       <c r="S2">
         <v>0.0418488</v>
       </c>
       <c r="T2">
-        <v>0.0429618</v>
+        <v>0.0410326</v>
       </c>
       <c r="U2" t="inlineStr">
         <is>
@@ -1182,16 +1316,16 @@
         </is>
       </c>
       <c r="W2">
-        <v>0.0925836455808542</v>
+        <v>0.0925535678563045</v>
       </c>
       <c r="X2">
-        <v>0.0970673669117135</v>
+        <v>0.09752659631029389</v>
       </c>
       <c r="Y2">
         <v>1.07975907289387</v>
       </c>
       <c r="Z2">
-        <v>1.18324264556578</v>
+        <v>1.19460961455644</v>
       </c>
       <c r="AA2">
         <v>3859.4</v>
@@ -1224,7 +1358,7 @@
         <v>46810.8</v>
       </c>
       <c r="AK2">
-        <v>0.043327855959079</v>
+        <v>0.0433</v>
       </c>
       <c r="AL2" t="inlineStr">
         <is>
@@ -1412,13 +1546,13 @@
         <v>0</v>
       </c>
       <c r="B2">
-        <v>0.08988662367088077</v>
+        <v>0.08985827989162551</v>
       </c>
       <c r="C2">
-        <v>49341.00752015338</v>
+        <v>49340.7870595104</v>
       </c>
       <c r="D2">
-        <v>48871.70752015338</v>
+        <v>48871.48705951039</v>
       </c>
       <c r="E2">
         <v>-3859.4</v>
@@ -1463,19 +1597,19 @@
         <v>0</v>
       </c>
       <c r="S2">
-        <v>0.08988662367088077</v>
+        <v>0.08985827989162551</v>
       </c>
       <c r="T2">
         <v>1.017512237681883</v>
       </c>
       <c r="U2">
-        <v>0.0517</v>
+        <v>0.0503</v>
       </c>
       <c r="V2">
         <v>0.258</v>
       </c>
       <c r="W2">
-        <v>0.0383614</v>
+        <v>0.0373226</v>
       </c>
       <c r="X2" t="inlineStr">
         <is>
@@ -1494,13 +1628,13 @@
         <v>0.01</v>
       </c>
       <c r="B3">
-        <v>0.0896984941818099</v>
+        <v>0.08965983552950513</v>
       </c>
       <c r="C3">
-        <v>49043.74799733059</v>
+        <v>49055.20470025494</v>
       </c>
       <c r="D3">
-        <v>49081.14999733058</v>
+        <v>49092.60670025494</v>
       </c>
       <c r="E3">
         <v>-3352.698</v>
@@ -1527,37 +1661,37 @@
         <v>1604</v>
       </c>
       <c r="M3">
-        <v>26.1964934</v>
+        <v>25.4871106</v>
       </c>
       <c r="N3">
-        <v>1577.8035066</v>
+        <v>1578.5128894</v>
       </c>
       <c r="O3">
-        <v>407.0733047028</v>
+        <v>407.2563254652</v>
       </c>
       <c r="P3">
-        <v>1170.7302018972</v>
+        <v>1171.2565639348</v>
       </c>
       <c r="Q3">
-        <v>1477.1302018972</v>
+        <v>1477.6565639348</v>
       </c>
       <c r="R3">
         <v>0.0101010101010101</v>
       </c>
       <c r="S3">
-        <v>0.09021705068869687</v>
+        <v>0.09018849447424759</v>
       </c>
       <c r="T3">
         <v>1.025138440513801</v>
       </c>
       <c r="U3">
-        <v>0.0517</v>
+        <v>0.0503</v>
       </c>
       <c r="V3">
         <v>0.258</v>
       </c>
       <c r="W3">
-        <v>0.0383614</v>
+        <v>0.0373226</v>
       </c>
       <c r="X3" t="inlineStr">
         <is>
@@ -1565,7 +1699,7 @@
         </is>
       </c>
       <c r="Y3">
-        <v>61.22956899261943</v>
+        <v>62.93377170811979</v>
       </c>
       <c r="Z3">
         <v>0</v>
@@ -1576,13 +1710,13 @@
         <v>0.02</v>
       </c>
       <c r="B4">
-        <v>0.08951036469273903</v>
+        <v>0.08946139116738472</v>
       </c>
       <c r="C4">
-        <v>48748.29135611257</v>
+        <v>48771.63235235676</v>
       </c>
       <c r="D4">
-        <v>49292.39535611257</v>
+        <v>49315.73635235676</v>
       </c>
       <c r="E4">
         <v>-2845.996</v>
@@ -1609,37 +1743,37 @@
         <v>1604</v>
       </c>
       <c r="M4">
-        <v>52.39298680000001</v>
+        <v>50.9742212</v>
       </c>
       <c r="N4">
-        <v>1551.6070132</v>
+        <v>1553.0257788</v>
       </c>
       <c r="O4">
-        <v>400.3146094056</v>
+        <v>400.6806509304</v>
       </c>
       <c r="P4">
-        <v>1151.2924037944</v>
+        <v>1152.3451278696</v>
       </c>
       <c r="Q4">
-        <v>1457.6924037944</v>
+        <v>1458.7451278696</v>
       </c>
       <c r="R4">
         <v>0.02040816326530612</v>
       </c>
       <c r="S4">
-        <v>0.09055422111503983</v>
+        <v>0.09052544812998442</v>
       </c>
       <c r="T4">
         <v>1.032920280138208</v>
       </c>
       <c r="U4">
-        <v>0.0517</v>
+        <v>0.0503</v>
       </c>
       <c r="V4">
         <v>0.258</v>
       </c>
       <c r="W4">
-        <v>0.0383614</v>
+        <v>0.0373226</v>
       </c>
       <c r="X4" t="inlineStr">
         <is>
@@ -1647,7 +1781,7 @@
         </is>
       </c>
       <c r="Y4">
-        <v>30.61478449630972</v>
+        <v>31.46688585405989</v>
       </c>
       <c r="Z4">
         <v>0</v>
@@ -1658,13 +1792,13 @@
         <v>0.03</v>
       </c>
       <c r="B5">
-        <v>0.08932223520366814</v>
+        <v>0.08926294680526432</v>
       </c>
       <c r="C5">
-        <v>48454.6609759416</v>
+        <v>48490.09754791736</v>
       </c>
       <c r="D5">
-        <v>49505.4669759416</v>
+        <v>49540.90354791736</v>
       </c>
       <c r="E5">
         <v>-2339.294</v>
@@ -1691,37 +1825,37 @@
         <v>1604</v>
       </c>
       <c r="M5">
-        <v>78.58948020000001</v>
+        <v>76.4613318</v>
       </c>
       <c r="N5">
-        <v>1525.4105198</v>
+        <v>1527.5386682</v>
       </c>
       <c r="O5">
-        <v>393.5559141084</v>
+        <v>394.1049763956</v>
       </c>
       <c r="P5">
-        <v>1131.8546056916</v>
+        <v>1133.4336918044</v>
       </c>
       <c r="Q5">
-        <v>1438.2546056916</v>
+        <v>1439.8336918044</v>
       </c>
       <c r="R5">
         <v>0.03092783505154639</v>
       </c>
       <c r="S5">
-        <v>0.09089834350893623</v>
+        <v>0.09086934928377766</v>
       </c>
       <c r="T5">
         <v>1.040862570064149</v>
       </c>
       <c r="U5">
-        <v>0.0517</v>
+        <v>0.0503</v>
       </c>
       <c r="V5">
         <v>0.258</v>
       </c>
       <c r="W5">
-        <v>0.0383614</v>
+        <v>0.0373226</v>
       </c>
       <c r="X5" t="inlineStr">
         <is>
@@ -1729,7 +1863,7 @@
         </is>
       </c>
       <c r="Y5">
-        <v>20.40985633087315</v>
+        <v>20.9779239027066</v>
       </c>
       <c r="Z5">
         <v>0</v>
@@ -1740,13 +1874,13 @@
         <v>0.04</v>
       </c>
       <c r="B6">
-        <v>0.08913410571459729</v>
+        <v>0.08906450244314394</v>
       </c>
       <c r="C6">
-        <v>48162.88064225535</v>
+        <v>48210.62832417207</v>
       </c>
       <c r="D6">
-        <v>49720.38864225535</v>
+        <v>49768.13632417206</v>
       </c>
       <c r="E6">
         <v>-1832.592</v>
@@ -1773,37 +1907,37 @@
         <v>1604</v>
       </c>
       <c r="M6">
-        <v>104.7859736</v>
+        <v>101.9484424</v>
       </c>
       <c r="N6">
-        <v>1499.2140264</v>
+        <v>1502.0515576</v>
       </c>
       <c r="O6">
-        <v>386.7972188112</v>
+        <v>387.5293018608</v>
       </c>
       <c r="P6">
-        <v>1112.4168075888</v>
+        <v>1114.5222557392</v>
       </c>
       <c r="Q6">
-        <v>1418.8168075888</v>
+        <v>1420.9222557392</v>
       </c>
       <c r="R6">
         <v>0.04166666666666667</v>
       </c>
       <c r="S6">
-        <v>0.09124963511937217</v>
+        <v>0.09122041504494161</v>
       </c>
       <c r="T6">
         <v>1.048970324363548</v>
       </c>
       <c r="U6">
-        <v>0.0517</v>
+        <v>0.0503</v>
       </c>
       <c r="V6">
         <v>0.258</v>
       </c>
       <c r="W6">
-        <v>0.0383614</v>
+        <v>0.0373226</v>
       </c>
       <c r="X6" t="inlineStr">
         <is>
@@ -1811,7 +1945,7 @@
         </is>
       </c>
       <c r="Y6">
-        <v>15.30739224815486</v>
+        <v>15.73344292702995</v>
       </c>
       <c r="Z6">
         <v>0</v>
@@ -1822,13 +1956,13 @@
         <v>0.05</v>
       </c>
       <c r="B7">
-        <v>0.0889459762255264</v>
+        <v>0.08886605808102353</v>
       </c>
       <c r="C7">
-        <v>47872.97455533843</v>
+        <v>47933.25323512805</v>
       </c>
       <c r="D7">
-        <v>49937.18455533843</v>
+        <v>49997.46323512805</v>
       </c>
       <c r="E7">
         <v>-1325.89</v>
@@ -1855,37 +1989,37 @@
         <v>1604</v>
       </c>
       <c r="M7">
-        <v>130.982467</v>
+        <v>127.435553</v>
       </c>
       <c r="N7">
-        <v>1473.017533</v>
+        <v>1476.564447</v>
       </c>
       <c r="O7">
-        <v>380.038523514</v>
+        <v>380.953627326</v>
       </c>
       <c r="P7">
-        <v>1092.979009486</v>
+        <v>1095.610819674</v>
       </c>
       <c r="Q7">
-        <v>1399.379009486</v>
+        <v>1402.010819674</v>
       </c>
       <c r="R7">
         <v>0.05263157894736843</v>
       </c>
       <c r="S7">
-        <v>0.09160832234265938</v>
+        <v>0.09157887166423531</v>
       </c>
       <c r="T7">
         <v>1.057248768227144</v>
       </c>
       <c r="U7">
-        <v>0.0517</v>
+        <v>0.0503</v>
       </c>
       <c r="V7">
         <v>0.258</v>
       </c>
       <c r="W7">
-        <v>0.0383614</v>
+        <v>0.0373226</v>
       </c>
       <c r="X7" t="inlineStr">
         <is>
@@ -1893,7 +2027,7 @@
         </is>
       </c>
       <c r="Y7">
-        <v>12.24591379852389</v>
+        <v>12.58675434162396</v>
       </c>
       <c r="Z7">
         <v>0</v>
@@ -1904,13 +2038,13 @@
         <v>0.06</v>
       </c>
       <c r="B8">
-        <v>0.08875784673645552</v>
+        <v>0.08866761371890315</v>
       </c>
       <c r="C8">
-        <v>47584.96733940593</v>
+        <v>47658.00136352549</v>
       </c>
       <c r="D8">
-        <v>50155.87933940592</v>
+        <v>50228.91336352549</v>
       </c>
       <c r="E8">
         <v>-819.1880000000001</v>
@@ -1937,37 +2071,37 @@
         <v>1604</v>
       </c>
       <c r="M8">
-        <v>157.1789604</v>
+        <v>152.9226636</v>
       </c>
       <c r="N8">
-        <v>1446.8210396</v>
+        <v>1451.0773364</v>
       </c>
       <c r="O8">
-        <v>373.2798282168</v>
+        <v>374.3779527912</v>
       </c>
       <c r="P8">
-        <v>1073.5412113832</v>
+        <v>1076.6993836088</v>
       </c>
       <c r="Q8">
-        <v>1379.9412113832</v>
+        <v>1383.0993836088</v>
       </c>
       <c r="R8">
         <v>0.06382978723404255</v>
       </c>
       <c r="S8">
-        <v>0.09197464120899525</v>
+        <v>0.09194495502010974</v>
       </c>
       <c r="T8">
         <v>1.06570334919422</v>
       </c>
       <c r="U8">
-        <v>0.0517</v>
+        <v>0.0503</v>
       </c>
       <c r="V8">
         <v>0.258</v>
       </c>
       <c r="W8">
-        <v>0.0383614</v>
+        <v>0.0373226</v>
       </c>
       <c r="X8" t="inlineStr">
         <is>
@@ -1975,7 +2109,7 @@
         </is>
       </c>
       <c r="Y8">
-        <v>10.20492816543657</v>
+        <v>10.4889619513533</v>
       </c>
       <c r="Z8">
         <v>0</v>
@@ -1986,13 +2120,13 @@
         <v>0.07000000000000001</v>
       </c>
       <c r="B9">
-        <v>0.08856971724738466</v>
+        <v>0.08846916935678274</v>
       </c>
       <c r="C9">
-        <v>47298.88405192732</v>
+        <v>47384.90233313291</v>
       </c>
       <c r="D9">
-        <v>50376.49805192732</v>
+        <v>50462.5163331329</v>
       </c>
       <c r="E9">
         <v>-312.4859999999994</v>
@@ -2019,37 +2153,37 @@
         <v>1604</v>
       </c>
       <c r="M9">
-        <v>183.3754538</v>
+        <v>178.4097742</v>
       </c>
       <c r="N9">
-        <v>1420.6245462</v>
+        <v>1425.5902258</v>
       </c>
       <c r="O9">
-        <v>366.5211329196</v>
+        <v>367.8022782564</v>
       </c>
       <c r="P9">
-        <v>1054.1034132804</v>
+        <v>1057.7879475436</v>
       </c>
       <c r="Q9">
-        <v>1360.5034132804</v>
+        <v>1364.1879475436</v>
       </c>
       <c r="R9">
         <v>0.07526881720430109</v>
       </c>
       <c r="S9">
-        <v>0.09234883790041362</v>
+        <v>0.09231891113632554</v>
       </c>
       <c r="T9">
         <v>1.074339749106826</v>
       </c>
       <c r="U9">
-        <v>0.0517</v>
+        <v>0.0503</v>
       </c>
       <c r="V9">
         <v>0.258</v>
       </c>
       <c r="W9">
-        <v>0.0383614</v>
+        <v>0.0373226</v>
       </c>
       <c r="X9" t="inlineStr">
         <is>
@@ -2057,7 +2191,7 @@
         </is>
       </c>
       <c r="Y9">
-        <v>8.74708128465992</v>
+        <v>8.990538815445685</v>
       </c>
       <c r="Z9">
         <v>0</v>
@@ -2068,13 +2202,13 @@
         <v>0.08</v>
       </c>
       <c r="B10">
-        <v>0.08844688375831379</v>
+        <v>0.08835976499466237</v>
       </c>
       <c r="C10">
-        <v>46937.27872670333</v>
+        <v>47007.91955059351</v>
       </c>
       <c r="D10">
-        <v>50521.59472670333</v>
+        <v>50592.23555059351</v>
       </c>
       <c r="E10">
         <v>194.2160000000003</v>
@@ -2101,37 +2235,37 @@
         <v>1604</v>
       </c>
       <c r="M10">
-        <v>214.0309248</v>
+        <v>209.9773088</v>
       </c>
       <c r="N10">
-        <v>1389.9690752</v>
+        <v>1394.0226912</v>
       </c>
       <c r="O10">
-        <v>358.6120214016</v>
+        <v>359.6578543296</v>
       </c>
       <c r="P10">
-        <v>1031.3570537984</v>
+        <v>1034.3648368704</v>
       </c>
       <c r="Q10">
-        <v>1337.7570537984</v>
+        <v>1340.7648368704</v>
       </c>
       <c r="R10">
         <v>0.08695652173913043</v>
       </c>
       <c r="S10">
-        <v>0.09273116930251499</v>
+        <v>0.09270099673332866</v>
       </c>
       <c r="T10">
         <v>1.083163896843618</v>
       </c>
       <c r="U10">
-        <v>0.0528</v>
+        <v>0.0518</v>
       </c>
       <c r="V10">
         <v>0.258</v>
       </c>
       <c r="W10">
-        <v>0.0391776</v>
+        <v>0.0384356</v>
       </c>
       <c r="X10" t="inlineStr">
         <is>
@@ -2139,7 +2273,7 @@
         </is>
       </c>
       <c r="Y10">
-        <v>7.494244121492484</v>
+        <v>7.638920648934423</v>
       </c>
       <c r="Z10">
         <v>0</v>
@@ -2150,13 +2284,13 @@
         <v>0.09</v>
       </c>
       <c r="B11">
-        <v>0.08841383226924293</v>
+        <v>0.08817245063254198</v>
       </c>
       <c r="C11">
-        <v>46469.76151359134</v>
+        <v>46724.86881902231</v>
       </c>
       <c r="D11">
-        <v>50560.77951359134</v>
+        <v>50815.88681902231</v>
       </c>
       <c r="E11">
         <v>700.9180000000001</v>
@@ -2183,45 +2317,45 @@
         <v>1604</v>
       </c>
       <c r="M11">
-        <v>250.81749</v>
+        <v>236.2244724</v>
       </c>
       <c r="N11">
-        <v>1353.18251</v>
+        <v>1367.7755276</v>
       </c>
       <c r="O11">
-        <v>349.1210875800001</v>
+        <v>352.8860861208</v>
       </c>
       <c r="P11">
-        <v>1004.06142242</v>
+        <v>1014.8894414792</v>
       </c>
       <c r="Q11">
-        <v>1310.46142242</v>
+        <v>1321.2894414792</v>
       </c>
       <c r="R11">
         <v>0.0989010989010989</v>
       </c>
       <c r="S11">
-        <v>0.09312190359257463</v>
+        <v>0.09309147981598019</v>
       </c>
       <c r="T11">
         <v>1.092181981893307</v>
       </c>
       <c r="U11">
-        <v>0.055</v>
+        <v>0.0518</v>
       </c>
       <c r="V11">
         <v>0.258</v>
       </c>
       <c r="W11">
-        <v>0.04081</v>
+        <v>0.0384356</v>
       </c>
       <c r="X11" t="inlineStr">
         <is>
-          <t>A1/A+</t>
+          <t>Aa2/AA</t>
         </is>
       </c>
       <c r="Y11">
-        <v>6.39508831700692</v>
+        <v>6.790151687941711</v>
       </c>
       <c r="Z11">
         <v>0</v>
@@ -2232,13 +2366,13 @@
         <v>0.1</v>
       </c>
       <c r="B12">
-        <v>0.08825018878017205</v>
+        <v>0.08811127627042156</v>
       </c>
       <c r="C12">
-        <v>46157.96894998029</v>
+        <v>46291.63729157126</v>
       </c>
       <c r="D12">
-        <v>50755.68894998029</v>
+        <v>50889.35729157125</v>
       </c>
       <c r="E12">
         <v>1207.62</v>
@@ -2265,37 +2399,37 @@
         <v>1604</v>
       </c>
       <c r="M12">
-        <v>278.6861</v>
+        <v>271.08557</v>
       </c>
       <c r="N12">
-        <v>1325.3139</v>
+        <v>1332.91443</v>
       </c>
       <c r="O12">
-        <v>341.9309862000001</v>
+        <v>343.89192294</v>
       </c>
       <c r="P12">
-        <v>983.3829138000001</v>
+        <v>989.02250706</v>
       </c>
       <c r="Q12">
-        <v>1289.7829138</v>
+        <v>1295.42250706</v>
       </c>
       <c r="R12">
         <v>0.1111111111111111</v>
       </c>
       <c r="S12">
-        <v>0.09352132086685783</v>
+        <v>0.09349064030046841</v>
       </c>
       <c r="T12">
         <v>1.101400468832989</v>
       </c>
       <c r="U12">
-        <v>0.055</v>
+        <v>0.0535</v>
       </c>
       <c r="V12">
         <v>0.258</v>
       </c>
       <c r="W12">
-        <v>0.04081</v>
+        <v>0.039697</v>
       </c>
       <c r="X12" t="inlineStr">
         <is>
@@ -2303,7 +2437,7 @@
         </is>
       </c>
       <c r="Y12">
-        <v>5.755579485306228</v>
+        <v>5.91695087274472</v>
       </c>
       <c r="Z12">
         <v>0</v>
@@ -2314,13 +2448,13 @@
         <v>0.11</v>
       </c>
       <c r="B13">
-        <v>0.08820897529110117</v>
+        <v>0.08800187190830119</v>
       </c>
       <c r="C13">
-        <v>45700.59186333805</v>
+        <v>45916.86113801942</v>
       </c>
       <c r="D13">
-        <v>50805.01386333805</v>
+        <v>51021.28313801942</v>
       </c>
       <c r="E13">
         <v>1714.322000000001</v>
@@ -2347,37 +2481,37 @@
         <v>1604</v>
       </c>
       <c r="M13">
-        <v>314.915293</v>
+        <v>302.6531046000001</v>
       </c>
       <c r="N13">
-        <v>1289.084707</v>
+        <v>1301.3468954</v>
       </c>
       <c r="O13">
-        <v>332.583854406</v>
+        <v>335.7474990132</v>
       </c>
       <c r="P13">
-        <v>956.500852594</v>
+        <v>965.5993963868</v>
       </c>
       <c r="Q13">
-        <v>1262.900852594</v>
+        <v>1271.9993963868</v>
       </c>
       <c r="R13">
         <v>0.1235955056179775</v>
       </c>
       <c r="S13">
-        <v>0.09392971381022602</v>
+        <v>0.09389877068348448</v>
       </c>
       <c r="T13">
         <v>1.110826112782551</v>
       </c>
       <c r="U13">
-        <v>0.0565</v>
+        <v>0.0543</v>
       </c>
       <c r="V13">
         <v>0.258</v>
       </c>
       <c r="W13">
-        <v>0.041923</v>
+        <v>0.0402906</v>
       </c>
       <c r="X13" t="inlineStr">
         <is>
@@ -2385,7 +2519,7 @@
         </is>
       </c>
       <c r="Y13">
-        <v>5.093433172837369</v>
+        <v>5.299796947795789</v>
       </c>
       <c r="Z13">
         <v>0</v>
@@ -2396,13 +2530,13 @@
         <v>0.12</v>
       </c>
       <c r="B14">
-        <v>0.08805646180203031</v>
+        <v>0.0878331075461808</v>
       </c>
       <c r="C14">
-        <v>45377.25708331242</v>
+        <v>45615.01133206412</v>
       </c>
       <c r="D14">
-        <v>50988.38108331242</v>
+        <v>51226.13533206411</v>
       </c>
       <c r="E14">
         <v>2221.024</v>
@@ -2429,37 +2563,37 @@
         <v>1604</v>
       </c>
       <c r="M14">
-        <v>343.543956</v>
+        <v>330.1670232</v>
       </c>
       <c r="N14">
-        <v>1260.456044</v>
+        <v>1273.8329768</v>
       </c>
       <c r="O14">
-        <v>325.197659352</v>
+        <v>328.6489080144</v>
       </c>
       <c r="P14">
-        <v>935.2583846479999</v>
+        <v>945.1840687855999</v>
       </c>
       <c r="Q14">
-        <v>1241.658384648</v>
+        <v>1251.5840687856</v>
       </c>
       <c r="R14">
         <v>0.1363636363636364</v>
       </c>
       <c r="S14">
-        <v>0.09434738841139807</v>
+        <v>0.09431617675702364</v>
       </c>
       <c r="T14">
         <v>1.120465975912786</v>
       </c>
       <c r="U14">
-        <v>0.0565</v>
+        <v>0.0543</v>
       </c>
       <c r="V14">
         <v>0.258</v>
       </c>
       <c r="W14">
-        <v>0.041923</v>
+        <v>0.0402906</v>
       </c>
       <c r="X14" t="inlineStr">
         <is>
@@ -2467,7 +2601,7 @@
         </is>
       </c>
       <c r="Y14">
-        <v>4.668980408434256</v>
+        <v>4.85814720214614</v>
       </c>
       <c r="Z14">
         <v>0</v>
@@ -2478,13 +2612,13 @@
         <v>0.13</v>
       </c>
       <c r="B15">
-        <v>0.08790394831295942</v>
+        <v>0.0876643431840604</v>
       </c>
       <c r="C15">
-        <v>45055.25072855903</v>
+        <v>45314.81313448136</v>
       </c>
       <c r="D15">
-        <v>51173.07672855903</v>
+        <v>51432.63913448136</v>
       </c>
       <c r="E15">
         <v>2727.726000000001</v>
@@ -2511,37 +2645,37 @@
         <v>1604</v>
       </c>
       <c r="M15">
-        <v>372.1726190000001</v>
+        <v>357.6809418000001</v>
       </c>
       <c r="N15">
-        <v>1231.827381</v>
+        <v>1246.3190582</v>
       </c>
       <c r="O15">
-        <v>317.811464298</v>
+        <v>321.5503170156</v>
       </c>
       <c r="P15">
-        <v>914.015916702</v>
+        <v>924.7687411843999</v>
       </c>
       <c r="Q15">
-        <v>1220.415916702</v>
+        <v>1231.1687411844</v>
       </c>
       <c r="R15">
         <v>0.1494252873563219</v>
       </c>
       <c r="S15">
-        <v>0.09477466472753956</v>
+        <v>0.09474317837248322</v>
       </c>
       <c r="T15">
         <v>1.130327445091991</v>
       </c>
       <c r="U15">
-        <v>0.0565</v>
+        <v>0.0543</v>
       </c>
       <c r="V15">
         <v>0.258</v>
       </c>
       <c r="W15">
-        <v>0.041923</v>
+        <v>0.0402906</v>
       </c>
       <c r="X15" t="inlineStr">
         <is>
@@ -2549,7 +2683,7 @@
         </is>
       </c>
       <c r="Y15">
-        <v>4.309828069323927</v>
+        <v>4.484443571211822</v>
       </c>
       <c r="Z15">
         <v>0</v>
@@ -2560,13 +2694,13 @@
         <v>0.14</v>
       </c>
       <c r="B16">
-        <v>0.08789686682388854</v>
+        <v>0.08759945882194001</v>
       </c>
       <c r="C16">
-        <v>44557.15700777117</v>
+        <v>44887.94886627175</v>
       </c>
       <c r="D16">
-        <v>51181.68500777116</v>
+        <v>51512.47686627175</v>
       </c>
       <c r="E16">
         <v>3234.428000000001</v>
@@ -2593,37 +2727,37 @@
         <v>1604</v>
       </c>
       <c r="M16">
-        <v>410.7326412000001</v>
+        <v>392.2886884000001</v>
       </c>
       <c r="N16">
-        <v>1193.2673588</v>
+        <v>1211.7113116</v>
       </c>
       <c r="O16">
-        <v>307.8629785703999</v>
+        <v>312.6215183928</v>
       </c>
       <c r="P16">
-        <v>885.4043802295998</v>
+        <v>899.0897932072</v>
       </c>
       <c r="Q16">
-        <v>1191.8043802296</v>
+        <v>1205.4897932072</v>
       </c>
       <c r="R16">
         <v>0.1627906976744186</v>
       </c>
       <c r="S16">
-        <v>0.095211877702196</v>
+        <v>0.09518011025806977</v>
       </c>
       <c r="T16">
         <v>1.140418250763736</v>
       </c>
       <c r="U16">
-        <v>0.0579</v>
+        <v>0.0553</v>
       </c>
       <c r="V16">
         <v>0.258</v>
       </c>
       <c r="W16">
-        <v>0.0429618</v>
+        <v>0.0410326</v>
       </c>
       <c r="X16" t="inlineStr">
         <is>
@@ -2631,7 +2765,7 @@
         </is>
       </c>
       <c r="Y16">
-        <v>3.905216773893936</v>
+        <v>4.088825519140306</v>
       </c>
       <c r="Z16">
         <v>0</v>
@@ -2642,13 +2776,13 @@
         <v>0.15</v>
       </c>
       <c r="B17">
-        <v>0.08775474133481767</v>
+        <v>0.0874381144598196</v>
       </c>
       <c r="C17">
-        <v>44223.83760486906</v>
+        <v>44580.85359268227</v>
       </c>
       <c r="D17">
-        <v>51355.06760486906</v>
+        <v>51712.08359268226</v>
       </c>
       <c r="E17">
         <v>3741.130000000001</v>
@@ -2675,37 +2809,37 @@
         <v>1604</v>
       </c>
       <c r="M17">
-        <v>440.070687</v>
+        <v>420.309309</v>
       </c>
       <c r="N17">
-        <v>1163.929313</v>
+        <v>1183.690691</v>
       </c>
       <c r="O17">
-        <v>300.2937627540001</v>
+        <v>305.392198278</v>
       </c>
       <c r="P17">
-        <v>863.6355502460001</v>
+        <v>878.298492722</v>
       </c>
       <c r="Q17">
-        <v>1170.035550246</v>
+        <v>1184.698492722</v>
       </c>
       <c r="R17">
         <v>0.1764705882352941</v>
       </c>
       <c r="S17">
-        <v>0.09565937804096197</v>
+        <v>0.09562732289390542</v>
       </c>
       <c r="T17">
         <v>1.150746487157169</v>
       </c>
       <c r="U17">
-        <v>0.0579</v>
+        <v>0.0553</v>
       </c>
       <c r="V17">
         <v>0.258</v>
       </c>
       <c r="W17">
-        <v>0.0429618</v>
+        <v>0.0410326</v>
       </c>
       <c r="X17" t="inlineStr">
         <is>
@@ -2713,7 +2847,7 @@
         </is>
       </c>
       <c r="Y17">
-        <v>3.644868988967675</v>
+        <v>3.816237151197619</v>
       </c>
       <c r="Z17">
         <v>0</v>
@@ -2724,13 +2858,13 @@
         <v>0.16</v>
       </c>
       <c r="B18">
-        <v>0.0876126158457468</v>
+        <v>0.08727677009769921</v>
       </c>
       <c r="C18">
-        <v>43891.69689341739</v>
+        <v>44275.31125679121</v>
       </c>
       <c r="D18">
-        <v>51529.62889341739</v>
+        <v>51913.24325679121</v>
       </c>
       <c r="E18">
         <v>4247.832</v>
@@ -2757,37 +2891,37 @@
         <v>1604</v>
       </c>
       <c r="M18">
-        <v>469.4087328000001</v>
+        <v>448.3299296000001</v>
       </c>
       <c r="N18">
-        <v>1134.5912672</v>
+        <v>1155.6700704</v>
       </c>
       <c r="O18">
-        <v>292.7245469376</v>
+        <v>298.1628781632</v>
       </c>
       <c r="P18">
-        <v>841.8667202623999</v>
+        <v>857.5071922367999</v>
       </c>
       <c r="Q18">
-        <v>1148.2667202624</v>
+        <v>1163.9071922368</v>
       </c>
       <c r="R18">
         <v>0.1904761904761905</v>
       </c>
       <c r="S18">
-        <v>0.09611753314969858</v>
+        <v>0.09608518344964193</v>
       </c>
       <c r="T18">
         <v>1.161320633940922</v>
       </c>
       <c r="U18">
-        <v>0.0579</v>
+        <v>0.0553</v>
       </c>
       <c r="V18">
         <v>0.258</v>
       </c>
       <c r="W18">
-        <v>0.0429618</v>
+        <v>0.0410326</v>
       </c>
       <c r="X18" t="inlineStr">
         <is>
@@ -2795,7 +2929,7 @@
         </is>
       </c>
       <c r="Y18">
-        <v>3.417064677157195</v>
+        <v>3.577722329247768</v>
       </c>
       <c r="Z18">
         <v>0</v>
@@ -2806,13 +2940,13 @@
         <v>0.17</v>
       </c>
       <c r="B19">
-        <v>0.08747049035667594</v>
+        <v>0.08711542573557882</v>
       </c>
       <c r="C19">
-        <v>43560.74693390048</v>
+        <v>43971.34005212355</v>
       </c>
       <c r="D19">
-        <v>51705.38093390048</v>
+        <v>52115.97405212354</v>
       </c>
       <c r="E19">
         <v>4754.534000000001</v>
@@ -2839,37 +2973,37 @@
         <v>1604</v>
       </c>
       <c r="M19">
-        <v>498.7467786000001</v>
+        <v>476.3505502000001</v>
       </c>
       <c r="N19">
-        <v>1105.2532214</v>
+        <v>1127.6494498</v>
       </c>
       <c r="O19">
-        <v>285.1553311211999</v>
+        <v>290.9335580484</v>
       </c>
       <c r="P19">
-        <v>820.0978902787999</v>
+        <v>836.7158917515999</v>
       </c>
       <c r="Q19">
-        <v>1126.4978902788</v>
+        <v>1143.1158917516</v>
       </c>
       <c r="R19">
         <v>0.2048192771084338</v>
       </c>
       <c r="S19">
-        <v>0.09658672814057342</v>
+        <v>0.096554076789854</v>
       </c>
       <c r="T19">
         <v>1.172149579442356</v>
       </c>
       <c r="U19">
-        <v>0.0579</v>
+        <v>0.0553</v>
       </c>
       <c r="V19">
         <v>0.258</v>
       </c>
       <c r="W19">
-        <v>0.0429618</v>
+        <v>0.0410326</v>
       </c>
       <c r="X19" t="inlineStr">
         <is>
@@ -2877,7 +3011,7 @@
         </is>
       </c>
       <c r="Y19">
-        <v>3.216060872618536</v>
+        <v>3.367268074586134</v>
       </c>
       <c r="Z19">
         <v>0</v>
@@ -2888,13 +3022,13 @@
         <v>0.18</v>
       </c>
       <c r="B20">
-        <v>0.08732836486760506</v>
+        <v>0.08695408137345843</v>
       </c>
       <c r="C20">
-        <v>43230.99995190455</v>
+        <v>43668.95845751463</v>
       </c>
       <c r="D20">
-        <v>51882.33595190454</v>
+        <v>52320.29445751462</v>
       </c>
       <c r="E20">
         <v>5261.236000000001</v>
@@ -2921,37 +3055,37 @@
         <v>1604</v>
       </c>
       <c r="M20">
-        <v>528.0848244</v>
+        <v>504.3711708</v>
       </c>
       <c r="N20">
-        <v>1075.9151756</v>
+        <v>1099.6288292</v>
       </c>
       <c r="O20">
-        <v>277.5861153048</v>
+        <v>283.7042379336</v>
       </c>
       <c r="P20">
-        <v>798.3290602952001</v>
+        <v>815.9245912663999</v>
       </c>
       <c r="Q20">
-        <v>1104.7290602952</v>
+        <v>1122.3245912664</v>
       </c>
       <c r="R20">
         <v>0.2195121951219512</v>
       </c>
       <c r="S20">
-        <v>0.09706736691171348</v>
+        <v>0.09703440655299808</v>
       </c>
       <c r="T20">
         <v>1.183242645565775</v>
       </c>
       <c r="U20">
-        <v>0.0579</v>
+        <v>0.0553</v>
       </c>
       <c r="V20">
         <v>0.258</v>
       </c>
       <c r="W20">
-        <v>0.0429618</v>
+        <v>0.0410326</v>
       </c>
       <c r="X20" t="inlineStr">
         <is>
@@ -2959,7 +3093,7 @@
         </is>
       </c>
       <c r="Y20">
-        <v>3.037390824139729</v>
+        <v>3.180197625998016</v>
       </c>
       <c r="Z20">
         <v>0</v>
@@ -2970,13 +3104,13 @@
         <v>0.19</v>
       </c>
       <c r="B21">
-        <v>0.08755278737853418</v>
+        <v>0.08679273701133805</v>
       </c>
       <c r="C21">
-        <v>42445.4288071542</v>
+        <v>43368.18524272512</v>
       </c>
       <c r="D21">
-        <v>51603.4668071542</v>
+        <v>52526.22324272512</v>
       </c>
       <c r="E21">
         <v>5767.938000000002</v>
@@ -3003,45 +3137,45 @@
         <v>1604</v>
       </c>
       <c r="M21">
-        <v>582.4539490000001</v>
+        <v>532.3917914000001</v>
       </c>
       <c r="N21">
-        <v>1021.546051</v>
+        <v>1071.6082086</v>
       </c>
       <c r="O21">
-        <v>263.558881158</v>
+        <v>276.4749178188</v>
       </c>
       <c r="P21">
-        <v>757.987169842</v>
+        <v>795.1332907811999</v>
       </c>
       <c r="Q21">
-        <v>1064.387169842</v>
+        <v>1101.5332907812</v>
       </c>
       <c r="R21">
         <v>0.2345679012345679</v>
       </c>
       <c r="S21">
-        <v>0.09755987330683233</v>
+        <v>0.09752659631029387</v>
       </c>
       <c r="T21">
         <v>1.19460961455644</v>
       </c>
       <c r="U21">
-        <v>0.0605</v>
+        <v>0.0553</v>
       </c>
       <c r="V21">
         <v>0.258</v>
       </c>
       <c r="W21">
-        <v>0.044891</v>
+        <v>0.0410326</v>
       </c>
       <c r="X21" t="inlineStr">
         <is>
-          <t>Baa2/BBB</t>
+          <t>A3/A-</t>
         </is>
       </c>
       <c r="Y21">
-        <v>2.753865782443171</v>
+        <v>3.012818803577067</v>
       </c>
       <c r="Z21">
         <v>0</v>
@@ -3052,13 +3186,13 @@
         <v>0.2</v>
       </c>
       <c r="B22">
-        <v>0.08742995388946334</v>
+        <v>0.08700239264921765</v>
       </c>
       <c r="C22">
-        <v>42090.98817868742</v>
+        <v>42594.20704512379</v>
       </c>
       <c r="D22">
-        <v>51755.72817868742</v>
+        <v>52258.94704512379</v>
       </c>
       <c r="E22">
         <v>6274.640000000001</v>
@@ -3085,37 +3219,37 @@
         <v>1604</v>
       </c>
       <c r="M22">
-        <v>613.10942</v>
+        <v>585.7475120000001</v>
       </c>
       <c r="N22">
-        <v>990.89058</v>
+        <v>1018.252488</v>
       </c>
       <c r="O22">
-        <v>255.64976964</v>
+        <v>262.709141904</v>
       </c>
       <c r="P22">
-        <v>735.24081036</v>
+        <v>755.5433460959998</v>
       </c>
       <c r="Q22">
-        <v>1041.64081036</v>
+        <v>1061.943346096</v>
       </c>
       <c r="R22">
         <v>0.25</v>
       </c>
       <c r="S22">
-        <v>0.09806469236182916</v>
+        <v>0.09803109081152205</v>
       </c>
       <c r="T22">
         <v>1.206260757771872</v>
       </c>
       <c r="U22">
-        <v>0.0605</v>
+        <v>0.0578</v>
       </c>
       <c r="V22">
         <v>0.258</v>
       </c>
       <c r="W22">
-        <v>0.044891</v>
+        <v>0.0428876</v>
       </c>
       <c r="X22" t="inlineStr">
         <is>
@@ -3123,7 +3257,7 @@
         </is>
       </c>
       <c r="Y22">
-        <v>2.616172493321013</v>
+        <v>2.738381243009018</v>
       </c>
       <c r="Z22">
         <v>0</v>
@@ -3134,13 +3268,13 @@
         <v>0.21</v>
       </c>
       <c r="B23">
-        <v>0.08772783440039245</v>
+        <v>0.08685959828709724</v>
       </c>
       <c r="C23">
-        <v>41216.58240924992</v>
+        <v>42269.24776350634</v>
       </c>
       <c r="D23">
-        <v>51388.02440924992</v>
+        <v>52440.68976350634</v>
       </c>
       <c r="E23">
         <v>6781.342000000001</v>
@@ -3167,45 +3301,45 @@
         <v>1604</v>
       </c>
       <c r="M23">
-        <v>672.4948944</v>
+        <v>615.0348876</v>
       </c>
       <c r="N23">
-        <v>931.5051056</v>
+        <v>988.9651124</v>
       </c>
       <c r="O23">
-        <v>240.3283172448</v>
+        <v>255.1529989992</v>
       </c>
       <c r="P23">
-        <v>691.1767883552</v>
+        <v>733.8121134007999</v>
       </c>
       <c r="Q23">
-        <v>997.5767883551999</v>
+        <v>1040.2121134008</v>
       </c>
       <c r="R23">
         <v>0.2658227848101266</v>
       </c>
       <c r="S23">
-        <v>0.09858229164606638</v>
+        <v>0.09854835732543954</v>
       </c>
       <c r="T23">
         <v>1.218206866638327</v>
       </c>
       <c r="U23">
-        <v>0.06320000000000001</v>
+        <v>0.0578</v>
       </c>
       <c r="V23">
         <v>0.258</v>
       </c>
       <c r="W23">
-        <v>0.0468944</v>
+        <v>0.0428876</v>
       </c>
       <c r="X23" t="inlineStr">
         <is>
-          <t>Ba1/BB+</t>
+          <t>Baa2/BBB</t>
         </is>
       </c>
       <c r="Y23">
-        <v>2.385148219498512</v>
+        <v>2.607982136199065</v>
       </c>
       <c r="Z23">
         <v>0</v>
@@ -3216,13 +3350,13 @@
         <v>0.22</v>
       </c>
       <c r="B24">
-        <v>0.08762503491132158</v>
+        <v>0.08728814392497684</v>
       </c>
       <c r="C24">
-        <v>40836.1842525063</v>
+        <v>41220.86742556511</v>
       </c>
       <c r="D24">
-        <v>51514.3282525063</v>
+        <v>51899.01142556511</v>
       </c>
       <c r="E24">
         <v>7288.044000000002</v>
@@ -3249,37 +3383,37 @@
         <v>1604</v>
       </c>
       <c r="M24">
-        <v>704.5184608000002</v>
+        <v>683.3383172000001</v>
       </c>
       <c r="N24">
-        <v>899.4815391999998</v>
+        <v>920.6616827999999</v>
       </c>
       <c r="O24">
-        <v>232.0662371136</v>
+        <v>237.5307141624</v>
       </c>
       <c r="P24">
-        <v>667.4153020863998</v>
+        <v>683.1309686375998</v>
       </c>
       <c r="Q24">
-        <v>973.8153020863998</v>
+        <v>989.5309686375998</v>
       </c>
       <c r="R24">
         <v>0.282051282051282</v>
       </c>
       <c r="S24">
-        <v>0.09911316270682252</v>
+        <v>0.09907888708330365</v>
       </c>
       <c r="T24">
         <v>1.230459285988537</v>
       </c>
       <c r="U24">
-        <v>0.06320000000000001</v>
+        <v>0.0613</v>
       </c>
       <c r="V24">
         <v>0.258</v>
       </c>
       <c r="W24">
-        <v>0.0468944</v>
+        <v>0.0454846</v>
       </c>
       <c r="X24" t="inlineStr">
         <is>
@@ -3287,7 +3421,7 @@
         </is>
       </c>
       <c r="Y24">
-        <v>2.276732391339488</v>
+        <v>2.347299953224399</v>
       </c>
       <c r="Z24">
         <v>0</v>
@@ -3298,13 +3432,13 @@
         <v>0.23</v>
       </c>
       <c r="B25">
-        <v>0.08832433742225071</v>
+        <v>0.08764916756285646</v>
       </c>
       <c r="C25">
-        <v>39482.34150253767</v>
+        <v>40266.44397736496</v>
       </c>
       <c r="D25">
-        <v>50667.18750253766</v>
+        <v>51451.28997736496</v>
       </c>
       <c r="E25">
         <v>7794.746000000001</v>
@@ -3331,37 +3465,37 @@
         <v>1604</v>
       </c>
       <c r="M25">
-        <v>791.3165134000001</v>
+        <v>747.0307586000001</v>
       </c>
       <c r="N25">
-        <v>812.6834865999999</v>
+        <v>856.9692413999999</v>
       </c>
       <c r="O25">
-        <v>209.6723395428</v>
+        <v>221.0980642812</v>
       </c>
       <c r="P25">
-        <v>603.0111470571999</v>
+        <v>635.8711771187999</v>
       </c>
       <c r="Q25">
-        <v>909.4111470571999</v>
+        <v>942.2711771187999</v>
       </c>
       <c r="R25">
         <v>0.2987012987012987</v>
       </c>
       <c r="S25">
-        <v>0.09965782262629962</v>
+        <v>0.09962319683487852</v>
       </c>
       <c r="T25">
         <v>1.243029949997194</v>
       </c>
       <c r="U25">
-        <v>0.0679</v>
+        <v>0.0641</v>
       </c>
       <c r="V25">
         <v>0.258</v>
       </c>
       <c r="W25">
-        <v>0.0503818</v>
+        <v>0.04756220000000001</v>
       </c>
       <c r="X25" t="inlineStr">
         <is>
@@ -3369,7 +3503,7 @@
         </is>
       </c>
       <c r="Y25">
-        <v>2.027001803751313</v>
+        <v>2.147167277296632</v>
       </c>
       <c r="Z25">
         <v>0</v>
@@ -3380,13 +3514,13 @@
         <v>0.24</v>
       </c>
       <c r="B26">
-        <v>0.09074953193317983</v>
+        <v>0.08755311920073608</v>
       </c>
       <c r="C26">
-        <v>36241.95619749155</v>
+        <v>39878.09989231612</v>
       </c>
       <c r="D26">
-        <v>47933.50419749154</v>
+        <v>51569.64789231612</v>
       </c>
       <c r="E26">
         <v>8301.448</v>
@@ -3413,45 +3547,45 @@
         <v>1604</v>
       </c>
       <c r="M26">
-        <v>995.9734512</v>
+        <v>779.5103568000001</v>
       </c>
       <c r="N26">
-        <v>608.0265488</v>
+        <v>824.4896431999999</v>
       </c>
       <c r="O26">
-        <v>156.8708495904</v>
+        <v>212.7183279456</v>
       </c>
       <c r="P26">
-        <v>451.1556992096</v>
+        <v>611.7713152544</v>
       </c>
       <c r="Q26">
-        <v>757.5556992096</v>
+        <v>918.1713152543999</v>
       </c>
       <c r="R26">
         <v>0.3157894736842105</v>
       </c>
       <c r="S26">
-        <v>0.1002168157015524</v>
+        <v>0.1001818305272843</v>
       </c>
       <c r="T26">
         <v>1.255931420953448</v>
       </c>
       <c r="U26">
-        <v>0.0819</v>
+        <v>0.0641</v>
       </c>
       <c r="V26">
         <v>0.258</v>
       </c>
       <c r="W26">
-        <v>0.0607698</v>
+        <v>0.04756220000000001</v>
       </c>
       <c r="X26" t="inlineStr">
         <is>
-          <t>B2/B</t>
+          <t>Ba2/BB</t>
         </is>
       </c>
       <c r="Y26">
-        <v>1.610484695216944</v>
+        <v>2.05770197407594</v>
       </c>
       <c r="Z26">
         <v>0</v>
@@ -3462,13 +3596,13 @@
         <v>0.25</v>
       </c>
       <c r="B27">
-        <v>0.09078548644410896</v>
+        <v>0.08890397083861568</v>
       </c>
       <c r="C27">
-        <v>35696.94349248936</v>
+        <v>37755.23720074011</v>
       </c>
       <c r="D27">
-        <v>47895.19349248936</v>
+        <v>49953.48720074011</v>
       </c>
       <c r="E27">
         <v>8808.150000000001</v>
@@ -3495,45 +3629,45 @@
         <v>1604</v>
       </c>
       <c r="M27">
-        <v>1037.472345</v>
+        <v>910.7968450000002</v>
       </c>
       <c r="N27">
-        <v>566.5276549999999</v>
+        <v>693.2031549999998</v>
       </c>
       <c r="O27">
-        <v>146.16413499</v>
+        <v>178.8464139899999</v>
       </c>
       <c r="P27">
-        <v>420.3635200099999</v>
+        <v>514.3567410099998</v>
       </c>
       <c r="Q27">
-        <v>726.7635200099999</v>
+        <v>820.7567410099998</v>
       </c>
       <c r="R27">
         <v>0.3333333333333333</v>
       </c>
       <c r="S27">
-        <v>0.1007907152588119</v>
+        <v>0.1007553611181542</v>
       </c>
       <c r="T27">
         <v>1.269176931135202</v>
       </c>
       <c r="U27">
-        <v>0.0819</v>
+        <v>0.07190000000000001</v>
       </c>
       <c r="V27">
         <v>0.258</v>
       </c>
       <c r="W27">
-        <v>0.0607698</v>
+        <v>0.0533498</v>
       </c>
       <c r="X27" t="inlineStr">
         <is>
-          <t>B2/B</t>
+          <t>B1/B+</t>
         </is>
       </c>
       <c r="Y27">
-        <v>1.546065307408266</v>
+        <v>1.761095252805799</v>
       </c>
       <c r="Z27">
         <v>0</v>
@@ -3544,13 +3678,13 @@
         <v>0.26</v>
       </c>
       <c r="B28">
-        <v>0.1010947854052503</v>
+        <v>0.08961818647649528</v>
       </c>
       <c r="C28">
-        <v>26260.54107142761</v>
+        <v>36434.31707364977</v>
       </c>
       <c r="D28">
-        <v>38965.49307142761</v>
+        <v>49139.26907364977</v>
       </c>
       <c r="E28">
         <v>9314.852000000003</v>
@@ -3577,45 +3711,45 @@
         <v>1604</v>
       </c>
       <c r="M28">
-        <v>1724.5095868</v>
+        <v>998.6083016000002</v>
       </c>
       <c r="N28">
-        <v>-120.5095868000001</v>
+        <v>605.3916983999998</v>
       </c>
       <c r="O28">
-        <v>-31.09147339440002</v>
+        <v>156.1910581872</v>
       </c>
       <c r="P28">
-        <v>-89.41811340560005</v>
+        <v>449.2006402127998</v>
       </c>
       <c r="Q28">
-        <v>216.9818865943999</v>
+        <v>755.6006402127998</v>
       </c>
       <c r="R28">
         <v>0.3513513513513514</v>
       </c>
       <c r="S28">
-        <v>0.1016593955336484</v>
+        <v>0.1013443925358044</v>
       </c>
       <c r="T28">
-        <v>1.28922593322884</v>
+        <v>1.282780428078624</v>
       </c>
       <c r="U28">
-        <v>0.1309</v>
+        <v>0.07580000000000001</v>
       </c>
       <c r="V28">
-        <v>0.2399708318049462</v>
+        <v>0.258</v>
       </c>
       <c r="W28">
-        <v>0.09948781811673253</v>
+        <v>0.0562436</v>
       </c>
       <c r="X28" t="inlineStr">
         <is>
-          <t>Caa/CCC</t>
+          <t>B2/B</t>
         </is>
       </c>
       <c r="Y28">
-        <v>0.9301195031199463</v>
+        <v>1.606235395229564</v>
       </c>
       <c r="Z28">
         <v>0</v>
@@ -3626,13 +3760,13 @@
         <v>0.27</v>
       </c>
       <c r="B29">
-        <v>0.1019457854052503</v>
+        <v>0.08960895211437488</v>
       </c>
       <c r="C29">
-        <v>25163.24025150826</v>
+        <v>35937.97299784237</v>
       </c>
       <c r="D29">
-        <v>38374.89425150826</v>
+        <v>49149.62699784237</v>
       </c>
       <c r="E29">
         <v>9821.554000000002</v>
@@ -3659,45 +3793,45 @@
         <v>1604</v>
       </c>
       <c r="M29">
-        <v>1790.8368786</v>
+        <v>1037.0163132</v>
       </c>
       <c r="N29">
-        <v>-186.8368786000001</v>
+        <v>566.9836867999998</v>
       </c>
       <c r="O29">
-        <v>-48.20391467880003</v>
+        <v>146.2817911943999</v>
       </c>
       <c r="P29">
-        <v>-138.6329639212001</v>
+        <v>420.7018956055998</v>
       </c>
       <c r="Q29">
-        <v>167.7670360787999</v>
+        <v>727.1018956055998</v>
       </c>
       <c r="R29">
         <v>0.3698630136986302</v>
       </c>
       <c r="S29">
-        <v>0.1024245927327395</v>
+        <v>0.1019495618005135</v>
       </c>
       <c r="T29">
-        <v>1.306886562451153</v>
+        <v>1.296756623568442</v>
       </c>
       <c r="U29">
-        <v>0.1309</v>
+        <v>0.07580000000000001</v>
       </c>
       <c r="V29">
-        <v>0.2310830232195778</v>
+        <v>0.258</v>
       </c>
       <c r="W29">
-        <v>0.1006512322605573</v>
+        <v>0.0562436</v>
       </c>
       <c r="X29" t="inlineStr">
         <is>
-          <t>Caa/CCC</t>
+          <t>B2/B</t>
         </is>
       </c>
       <c r="Y29">
-        <v>0.8956706326340224</v>
+        <v>1.546745195406247</v>
       </c>
       <c r="Z29">
         <v>0</v>
@@ -3708,13 +3842,13 @@
         <v>0.28</v>
       </c>
       <c r="B30">
-        <v>0.1027967854052503</v>
+        <v>0.09254990975225449</v>
       </c>
       <c r="C30">
-        <v>24083.57549973482</v>
+        <v>32339.35121266529</v>
       </c>
       <c r="D30">
-        <v>37801.93149973482</v>
+        <v>46057.70721266529</v>
       </c>
       <c r="E30">
         <v>10328.256</v>
@@ -3741,45 +3875,45 @@
         <v>1604</v>
       </c>
       <c r="M30">
-        <v>1857.1641704</v>
+        <v>1276.88904</v>
       </c>
       <c r="N30">
-        <v>-253.1641704000001</v>
+        <v>327.1109599999997</v>
       </c>
       <c r="O30">
-        <v>-65.31635596320002</v>
+        <v>84.39462767999994</v>
       </c>
       <c r="P30">
-        <v>-187.8478144368001</v>
+        <v>242.7163323199998</v>
       </c>
       <c r="Q30">
-        <v>118.5521855631999</v>
+        <v>549.1163323199999</v>
       </c>
       <c r="R30">
         <v>0.388888888888889</v>
       </c>
       <c r="S30">
-        <v>0.1032110454095831</v>
+        <v>0.1025715413225757</v>
       </c>
       <c r="T30">
-        <v>1.325037764707419</v>
+        <v>1.311121046710755</v>
       </c>
       <c r="U30">
-        <v>0.1309</v>
+        <v>0.09</v>
       </c>
       <c r="V30">
-        <v>0.2228300581045929</v>
+        <v>0.258</v>
       </c>
       <c r="W30">
-        <v>0.1017315453941088</v>
+        <v>0.06677999999999999</v>
       </c>
       <c r="X30" t="inlineStr">
         <is>
-          <t>Caa/CCC</t>
+          <t>B3/B-</t>
         </is>
       </c>
       <c r="Y30">
-        <v>0.8636823957542359</v>
+        <v>1.256178062269216</v>
       </c>
       <c r="Z30">
         <v>0</v>
@@ -3790,13 +3924,13 @@
         <v>0.29</v>
       </c>
       <c r="B31">
-        <v>0.1036477854052503</v>
+        <v>0.09976912151960576</v>
       </c>
       <c r="C31">
-        <v>23020.76848238778</v>
+        <v>25671.7125043273</v>
       </c>
       <c r="D31">
-        <v>37245.82648238778</v>
+        <v>39896.7705043273</v>
       </c>
       <c r="E31">
         <v>10834.958</v>
@@ -3823,37 +3957,37 @@
         <v>1604</v>
       </c>
       <c r="M31">
-        <v>1923.4914622</v>
+        <v>1742.7508588</v>
       </c>
       <c r="N31">
-        <v>-319.4914621999999</v>
+        <v>-138.7508588000003</v>
       </c>
       <c r="O31">
-        <v>-82.42879724759997</v>
+        <v>-35.79772157040008</v>
       </c>
       <c r="P31">
-        <v>-237.0626649523999</v>
+        <v>-102.9531372296002</v>
       </c>
       <c r="Q31">
-        <v>69.33733504760005</v>
+        <v>203.4468627703998</v>
       </c>
       <c r="R31">
         <v>0.4084507042253521</v>
       </c>
       <c r="S31">
-        <v>0.1040196516829575</v>
+        <v>0.1035806884637399</v>
       </c>
       <c r="T31">
-        <v>1.343700268435693</v>
+        <v>1.33442698530577</v>
       </c>
       <c r="U31">
-        <v>0.1309</v>
+        <v>0.1186</v>
       </c>
       <c r="V31">
-        <v>0.2151462629975379</v>
+        <v>0.2374590710487159</v>
       </c>
       <c r="W31">
-        <v>0.1027373541736223</v>
+        <v>0.09043735417362231</v>
       </c>
       <c r="X31" t="inlineStr">
         <is>
@@ -3861,7 +3995,7 @@
         </is>
       </c>
       <c r="Y31">
-        <v>0.8339002441765037</v>
+        <v>0.9203839963128525</v>
       </c>
       <c r="Z31">
         <v>0</v>
@@ -3872,13 +4006,13 @@
         <v>0.3</v>
       </c>
       <c r="B32">
-        <v>0.1044987854052503</v>
+        <v>0.1004971215196058</v>
       </c>
       <c r="C32">
-        <v>21974.08600208168</v>
+        <v>24633.99811975895</v>
       </c>
       <c r="D32">
-        <v>36705.84600208168</v>
+        <v>39365.75811975895</v>
       </c>
       <c r="E32">
         <v>11341.66</v>
@@ -3905,37 +4039,37 @@
         <v>1604</v>
       </c>
       <c r="M32">
-        <v>1989.818754</v>
+        <v>1802.845716</v>
       </c>
       <c r="N32">
-        <v>-385.8187539999999</v>
+        <v>-198.8457160000003</v>
       </c>
       <c r="O32">
-        <v>-99.54123853199998</v>
+        <v>-51.30219472800007</v>
       </c>
       <c r="P32">
-        <v>-286.2775154679999</v>
+        <v>-147.5435212720002</v>
       </c>
       <c r="Q32">
-        <v>20.12248453200004</v>
+        <v>158.8564787279998</v>
       </c>
       <c r="R32">
         <v>0.4285714285714286</v>
       </c>
       <c r="S32">
-        <v>0.104851360992714</v>
+        <v>0.1044061268703647</v>
       </c>
       <c r="T32">
-        <v>1.362895986556203</v>
+        <v>1.353490227952996</v>
       </c>
       <c r="U32">
-        <v>0.1309</v>
+        <v>0.1186</v>
       </c>
       <c r="V32">
-        <v>0.20797472089762</v>
+        <v>0.2295437686804254</v>
       </c>
       <c r="W32">
-        <v>0.1036761090345015</v>
+        <v>0.09137610903450157</v>
       </c>
       <c r="X32" t="inlineStr">
         <is>
@@ -3943,7 +4077,7 @@
         </is>
       </c>
       <c r="Y32">
-        <v>0.8061035693706202</v>
+        <v>0.8897045297690908</v>
       </c>
       <c r="Z32">
         <v>0</v>
@@ -3954,13 +4088,13 @@
         <v>0.31</v>
       </c>
       <c r="B33">
-        <v>0.1327509539217507</v>
+        <v>0.1012251215196058</v>
       </c>
       <c r="C33">
-        <v>9540.893261971281</v>
+        <v>23610.23325863294</v>
       </c>
       <c r="D33">
-        <v>24779.35526197128</v>
+        <v>38848.69525863294</v>
       </c>
       <c r="E33">
         <v>11848.362</v>
@@ -3987,45 +4121,45 @@
         <v>1604</v>
       </c>
       <c r="M33">
-        <v>3389.735039600001</v>
+        <v>1862.9405732</v>
       </c>
       <c r="N33">
-        <v>-1785.735039600001</v>
+        <v>-258.9405732000002</v>
       </c>
       <c r="O33">
-        <v>-460.7196402168001</v>
+        <v>-66.80666788560006</v>
       </c>
       <c r="P33">
-        <v>-1325.0153993832</v>
+        <v>-192.1339053144002</v>
       </c>
       <c r="Q33">
-        <v>-1018.6153993832</v>
+        <v>114.2660946855998</v>
       </c>
       <c r="R33">
         <v>0.4492753623188406</v>
       </c>
       <c r="S33">
-        <v>0.1072755379875365</v>
+        <v>0.1052554910279062</v>
       </c>
       <c r="T33">
-        <v>1.418845604675133</v>
+        <v>1.373106028358112</v>
       </c>
       <c r="U33">
-        <v>0.2158</v>
+        <v>0.1186</v>
       </c>
       <c r="V33">
-        <v>0.1220838782870868</v>
+        <v>0.2221391309810569</v>
       </c>
       <c r="W33">
-        <v>0.1894542990656467</v>
+        <v>0.09225429906564667</v>
       </c>
       <c r="X33" t="inlineStr">
         <is>
-          <t>C2/C</t>
+          <t>Caa/CCC</t>
         </is>
       </c>
       <c r="Y33">
-        <v>0.4731933266941351</v>
+        <v>0.8610043836475072</v>
       </c>
       <c r="Z33">
         <v>0</v>
@@ -4036,13 +4170,13 @@
         <v>0.32</v>
       </c>
       <c r="B34">
-        <v>0.1344509539217507</v>
+        <v>0.1019531215196058</v>
       </c>
       <c r="C34">
-        <v>8559.01415352716</v>
+        <v>22599.87537303074</v>
       </c>
       <c r="D34">
-        <v>24304.17815352716</v>
+        <v>38345.03937303074</v>
       </c>
       <c r="E34">
         <v>12355.064</v>
@@ -4069,45 +4203,45 @@
         <v>1604</v>
       </c>
       <c r="M34">
-        <v>3499.0813312</v>
+        <v>1923.0354304</v>
       </c>
       <c r="N34">
-        <v>-1895.0813312</v>
+        <v>-319.0354304000005</v>
       </c>
       <c r="O34">
-        <v>-488.9309834496001</v>
+        <v>-82.31114104320012</v>
       </c>
       <c r="P34">
-        <v>-1406.1503477504</v>
+        <v>-236.7242893568003</v>
       </c>
       <c r="Q34">
-        <v>-1099.7503477504</v>
+        <v>69.67571064319964</v>
       </c>
       <c r="R34">
         <v>0.4705882352941177</v>
       </c>
       <c r="S34">
-        <v>0.108179590016765</v>
+        <v>0.106129836484199</v>
       </c>
       <c r="T34">
-        <v>1.439710981214473</v>
+        <v>1.39329876406926</v>
       </c>
       <c r="U34">
-        <v>0.2158</v>
+        <v>0.1186</v>
       </c>
       <c r="V34">
-        <v>0.1182687570906154</v>
+        <v>0.2151972831378988</v>
       </c>
       <c r="W34">
-        <v>0.1902776022198452</v>
+        <v>0.09307760221984522</v>
       </c>
       <c r="X34" t="inlineStr">
         <is>
-          <t>C2/C</t>
+          <t>Caa/CCC</t>
         </is>
       </c>
       <c r="Y34">
-        <v>0.4584060352349434</v>
+        <v>0.8340979966585225</v>
       </c>
       <c r="Z34">
         <v>0</v>
@@ -4118,13 +4252,13 @@
         <v>0.33</v>
       </c>
       <c r="B35">
-        <v>0.1361509539217507</v>
+        <v>0.1026811215196058</v>
       </c>
       <c r="C35">
-        <v>7595.016451959033</v>
+        <v>21602.4096904978</v>
       </c>
       <c r="D35">
-        <v>23846.88245195903</v>
+        <v>37854.27569049779</v>
       </c>
       <c r="E35">
         <v>12861.766</v>
@@ -4151,45 +4285,45 @@
         <v>1604</v>
       </c>
       <c r="M35">
-        <v>3608.4276228</v>
+        <v>1983.1302876</v>
       </c>
       <c r="N35">
-        <v>-2004.4276228</v>
+        <v>-379.1302876000002</v>
       </c>
       <c r="O35">
-        <v>-517.1423266824002</v>
+        <v>-97.81561420080006</v>
       </c>
       <c r="P35">
-        <v>-1487.2852961176</v>
+        <v>-281.3146733992002</v>
       </c>
       <c r="Q35">
-        <v>-1180.8852961176</v>
+        <v>25.08532660079982</v>
       </c>
       <c r="R35">
         <v>0.4925373134328359</v>
       </c>
       <c r="S35">
-        <v>0.1091106286737316</v>
+        <v>0.1070302818048587</v>
       </c>
       <c r="T35">
-        <v>1.461199204814689</v>
+        <v>1.414094268010593</v>
       </c>
       <c r="U35">
-        <v>0.2158</v>
+        <v>0.1186</v>
       </c>
       <c r="V35">
-        <v>0.1146848553605967</v>
+        <v>0.2086761533458413</v>
       </c>
       <c r="W35">
-        <v>0.1910510082131832</v>
+        <v>0.09385100821318322</v>
       </c>
       <c r="X35" t="inlineStr">
         <is>
-          <t>C2/C</t>
+          <t>Caa/CCC</t>
         </is>
       </c>
       <c r="Y35">
-        <v>0.4445149432581269</v>
+        <v>0.8088222997900826</v>
       </c>
       <c r="Z35">
         <v>0</v>
@@ -4200,13 +4334,13 @@
         <v>0.34</v>
       </c>
       <c r="B36">
-        <v>0.1378509539217507</v>
+        <v>0.1325991238451577</v>
       </c>
       <c r="C36">
-        <v>6647.909454061981</v>
+        <v>8048.060917464394</v>
       </c>
       <c r="D36">
-        <v>23406.47745406198</v>
+        <v>24806.6289174644</v>
       </c>
       <c r="E36">
         <v>13368.468</v>
@@ -4233,37 +4367,37 @@
         <v>1604</v>
       </c>
       <c r="M36">
-        <v>3717.773914400001</v>
+        <v>3459.355894400001</v>
       </c>
       <c r="N36">
-        <v>-2113.773914400001</v>
+        <v>-1855.355894400001</v>
       </c>
       <c r="O36">
-        <v>-545.3536699152002</v>
+        <v>-478.6818207552001</v>
       </c>
       <c r="P36">
-        <v>-1568.420244484801</v>
+        <v>-1376.674073644801</v>
       </c>
       <c r="Q36">
-        <v>-1262.020244484801</v>
+        <v>-1070.2740736448</v>
       </c>
       <c r="R36">
         <v>0.5151515151515152</v>
       </c>
       <c r="S36">
-        <v>0.1100698806233336</v>
+        <v>0.1098398350527383</v>
       </c>
       <c r="T36">
-        <v>1.483338586705821</v>
+        <v>1.478980024312662</v>
       </c>
       <c r="U36">
-        <v>0.2158</v>
+        <v>0.2008</v>
       </c>
       <c r="V36">
-        <v>0.1113117713794027</v>
+        <v>0.1196268937434019</v>
       </c>
       <c r="W36">
-        <v>0.1917789197363249</v>
+        <v>0.1767789197363249</v>
       </c>
       <c r="X36" t="inlineStr">
         <is>
@@ -4271,7 +4405,7 @@
         </is>
       </c>
       <c r="Y36">
-        <v>0.4314409743387703</v>
+        <v>0.4636701307883796</v>
       </c>
       <c r="Z36">
         <v>0</v>
@@ -4282,13 +4416,13 @@
         <v>0.35</v>
       </c>
       <c r="B37">
-        <v>0.1395509539217507</v>
+        <v>0.1341491238451577</v>
       </c>
       <c r="C37">
-        <v>5716.774314905695</v>
+        <v>7106.150585467141</v>
       </c>
       <c r="D37">
-        <v>22982.0443149057</v>
+        <v>24371.42058546715</v>
       </c>
       <c r="E37">
         <v>13875.17</v>
@@ -4315,37 +4449,37 @@
         <v>1604</v>
       </c>
       <c r="M37">
-        <v>3827.120206000001</v>
+        <v>3561.101656000001</v>
       </c>
       <c r="N37">
-        <v>-2223.120206000001</v>
+        <v>-1957.101656000001</v>
       </c>
       <c r="O37">
-        <v>-573.5650131480003</v>
+        <v>-504.9322272480002</v>
       </c>
       <c r="P37">
-        <v>-1649.555192852001</v>
+        <v>-1452.169428752001</v>
       </c>
       <c r="Q37">
-        <v>-1343.155192852001</v>
+        <v>-1145.769428752001</v>
       </c>
       <c r="R37">
         <v>0.5384615384615385</v>
       </c>
       <c r="S37">
-        <v>0.1110586480175388</v>
+        <v>0.1108250632843188</v>
       </c>
       <c r="T37">
-        <v>1.506159180347449</v>
+        <v>1.501733563148241</v>
       </c>
       <c r="U37">
-        <v>0.2158</v>
+        <v>0.2008</v>
       </c>
       <c r="V37">
-        <v>0.1081314350542769</v>
+        <v>0.1162089824935904</v>
       </c>
       <c r="W37">
-        <v>0.1924652363152871</v>
+        <v>0.177465236315287</v>
       </c>
       <c r="X37" t="inlineStr">
         <is>
@@ -4353,7 +4487,7 @@
         </is>
       </c>
       <c r="Y37">
-        <v>0.4191140893576625</v>
+        <v>0.4504224127658544</v>
       </c>
       <c r="Z37">
         <v>0</v>
@@ -4364,13 +4498,13 @@
         <v>0.36</v>
       </c>
       <c r="B38">
-        <v>0.1412509539217507</v>
+        <v>0.1356991238451577</v>
       </c>
       <c r="C38">
-        <v>4800.757648785449</v>
+        <v>6179.247583591543</v>
       </c>
       <c r="D38">
-        <v>22572.72964878545</v>
+        <v>23951.21958359154</v>
       </c>
       <c r="E38">
         <v>14381.872</v>
@@ -4397,37 +4531,37 @@
         <v>1604</v>
       </c>
       <c r="M38">
-        <v>3936.4664976</v>
+        <v>3662.8474176</v>
       </c>
       <c r="N38">
-        <v>-2332.4664976</v>
+        <v>-2058.8474176</v>
       </c>
       <c r="O38">
-        <v>-601.7763563808002</v>
+        <v>-531.1826337408002</v>
       </c>
       <c r="P38">
-        <v>-1730.6901412192</v>
+        <v>-1527.6647838592</v>
       </c>
       <c r="Q38">
-        <v>-1424.2901412192</v>
+        <v>-1221.2647838592</v>
       </c>
       <c r="R38">
         <v>0.5625</v>
       </c>
       <c r="S38">
-        <v>0.1120783143928128</v>
+        <v>0.1118410798981363</v>
       </c>
       <c r="T38">
-        <v>1.529692917540378</v>
+        <v>1.525198150072432</v>
       </c>
       <c r="U38">
-        <v>0.2158</v>
+        <v>0.2008</v>
       </c>
       <c r="V38">
-        <v>0.105127784080547</v>
+        <v>0.1129809552021018</v>
       </c>
       <c r="W38">
-        <v>0.193113424195418</v>
+        <v>0.178113424195418</v>
       </c>
       <c r="X38" t="inlineStr">
         <is>
@@ -4435,7 +4569,7 @@
         </is>
       </c>
       <c r="Y38">
-        <v>0.4074720313199497</v>
+        <v>0.437910679077914</v>
       </c>
       <c r="Z38">
         <v>0</v>
@@ -4446,13 +4580,13 @@
         <v>0.37</v>
       </c>
       <c r="B39">
-        <v>0.1429509539217507</v>
+        <v>0.1372491238451577</v>
       </c>
       <c r="C39">
-        <v>3899.065802017263</v>
+        <v>5266.588819944176</v>
       </c>
       <c r="D39">
-        <v>22177.73980201727</v>
+        <v>23545.26281994418</v>
       </c>
       <c r="E39">
         <v>14888.574</v>
@@ -4479,37 +4613,37 @@
         <v>1604</v>
       </c>
       <c r="M39">
-        <v>4045.812789200001</v>
+        <v>3764.593179200001</v>
       </c>
       <c r="N39">
-        <v>-2441.812789200001</v>
+        <v>-2160.593179200001</v>
       </c>
       <c r="O39">
-        <v>-629.9876996136002</v>
+        <v>-557.4330402336002</v>
       </c>
       <c r="P39">
-        <v>-1811.825089586401</v>
+        <v>-1603.1601389664</v>
       </c>
       <c r="Q39">
-        <v>-1505.425089586401</v>
+        <v>-1296.760138966401</v>
       </c>
       <c r="R39">
         <v>0.5873015873015873</v>
       </c>
       <c r="S39">
-        <v>0.1131303511292067</v>
+        <v>0.1128893510076306</v>
       </c>
       <c r="T39">
-        <v>1.553973757501336</v>
+        <v>1.549407644518027</v>
       </c>
       <c r="U39">
-        <v>0.2158</v>
+        <v>0.2008</v>
       </c>
       <c r="V39">
-        <v>0.1022864926189106</v>
+        <v>0.1099274158723153</v>
       </c>
       <c r="W39">
-        <v>0.1937265748928391</v>
+        <v>0.1787265748928391</v>
       </c>
       <c r="X39" t="inlineStr">
         <is>
@@ -4517,7 +4651,7 @@
         </is>
       </c>
       <c r="Y39">
-        <v>0.3964592737167077</v>
+        <v>0.4260752553190514</v>
       </c>
       <c r="Z39">
         <v>0</v>
@@ -4528,13 +4662,13 @@
         <v>0.38</v>
       </c>
       <c r="B40">
-        <v>0.1446509539217507</v>
+        <v>0.1387991238451577</v>
       </c>
       <c r="C40">
-        <v>3010.959716698326</v>
+        <v>4367.462075903819</v>
       </c>
       <c r="D40">
-        <v>21796.33571669833</v>
+        <v>23152.83807590382</v>
       </c>
       <c r="E40">
         <v>15395.276</v>
@@ -4561,37 +4695,37 @@
         <v>1604</v>
       </c>
       <c r="M40">
-        <v>4155.159080800001</v>
+        <v>3866.338940800001</v>
       </c>
       <c r="N40">
-        <v>-2551.159080800001</v>
+        <v>-2262.338940800001</v>
       </c>
       <c r="O40">
-        <v>-658.1990428464003</v>
+        <v>-583.6834467264002</v>
       </c>
       <c r="P40">
-        <v>-1892.960037953601</v>
+        <v>-1678.6554940736</v>
       </c>
       <c r="Q40">
-        <v>-1586.560037953601</v>
+        <v>-1372.2554940736</v>
       </c>
       <c r="R40">
         <v>0.6129032258064516</v>
       </c>
       <c r="S40">
-        <v>0.1142163245345165</v>
+        <v>0.1139714373142053</v>
       </c>
       <c r="T40">
-        <v>1.579037850364261</v>
+        <v>1.57439809039735</v>
       </c>
       <c r="U40">
-        <v>0.2158</v>
+        <v>0.2008</v>
       </c>
       <c r="V40">
-        <v>0.0995947428131498</v>
+        <v>0.1070345891388333</v>
       </c>
       <c r="W40">
-        <v>0.1943074545009223</v>
+        <v>0.1793074545009223</v>
       </c>
       <c r="X40" t="inlineStr">
         <is>
@@ -4599,7 +4733,7 @@
         </is>
       </c>
       <c r="Y40">
-        <v>0.3860261349346891</v>
+        <v>0.4148627486001291</v>
       </c>
       <c r="Z40">
         <v>0</v>
@@ -4610,13 +4744,13 @@
         <v>0.39</v>
       </c>
       <c r="B41">
-        <v>0.1463509539217507</v>
+        <v>0.1403491238451577</v>
       </c>
       <c r="C41">
-        <v>2135.75031549334</v>
+        <v>3481.201836142427</v>
       </c>
       <c r="D41">
-        <v>21427.82831549334</v>
+        <v>22773.27983614243</v>
       </c>
       <c r="E41">
         <v>15901.978</v>
@@ -4643,37 +4777,37 @@
         <v>1604</v>
       </c>
       <c r="M41">
-        <v>4264.505372400001</v>
+        <v>3968.0847024</v>
       </c>
       <c r="N41">
-        <v>-2660.505372400001</v>
+        <v>-2364.0847024</v>
       </c>
       <c r="O41">
-        <v>-686.4103860792003</v>
+        <v>-609.9338532192002</v>
       </c>
       <c r="P41">
-        <v>-1974.094986320801</v>
+        <v>-1754.1508491808</v>
       </c>
       <c r="Q41">
-        <v>-1667.694986320801</v>
+        <v>-1447.7508491808</v>
       </c>
       <c r="R41">
         <v>0.639344262295082</v>
       </c>
       <c r="S41">
-        <v>0.1153379036252462</v>
+        <v>0.1150890018603397</v>
       </c>
       <c r="T41">
-        <v>1.604923716763675</v>
+        <v>1.600207895157962</v>
       </c>
       <c r="U41">
-        <v>0.2158</v>
+        <v>0.2008</v>
       </c>
       <c r="V41">
-        <v>0.09704103145896646</v>
+        <v>0.1042901124942478</v>
       </c>
       <c r="W41">
-        <v>0.194858545411155</v>
+        <v>0.179858545411155</v>
       </c>
       <c r="X41" t="inlineStr">
         <is>
@@ -4681,7 +4815,7 @@
         </is>
       </c>
       <c r="Y41">
-        <v>0.3761280289107227</v>
+        <v>0.4042252422257668</v>
       </c>
       <c r="Z41">
         <v>0</v>
@@ -4692,13 +4826,13 @@
         <v>0.4</v>
       </c>
       <c r="B42">
-        <v>0.1480509539217507</v>
+        <v>0.1418991238451577</v>
       </c>
       <c r="C42">
-        <v>1272.794346809438</v>
+        <v>2607.185522196156</v>
       </c>
       <c r="D42">
-        <v>21071.57434680944</v>
+        <v>22405.96552219616</v>
       </c>
       <c r="E42">
         <v>16408.68</v>
@@ -4725,37 +4859,37 @@
         <v>1604</v>
       </c>
       <c r="M42">
-        <v>4373.851664000001</v>
+        <v>4069.830464000001</v>
       </c>
       <c r="N42">
-        <v>-2769.851664000001</v>
+        <v>-2465.830464000001</v>
       </c>
       <c r="O42">
-        <v>-714.6217293120002</v>
+        <v>-636.1842597120002</v>
       </c>
       <c r="P42">
-        <v>-2055.229934688</v>
+        <v>-1829.646204288</v>
       </c>
       <c r="Q42">
-        <v>-1748.829934688</v>
+        <v>-1523.246204288</v>
       </c>
       <c r="R42">
         <v>0.6666666666666667</v>
       </c>
       <c r="S42">
-        <v>0.116496868685667</v>
+        <v>0.1162438185580121</v>
       </c>
       <c r="T42">
-        <v>1.631672445376403</v>
+        <v>1.626878026743928</v>
       </c>
       <c r="U42">
-        <v>0.2158</v>
+        <v>0.2008</v>
       </c>
       <c r="V42">
-        <v>0.09461500567249231</v>
+        <v>0.1016828596818916</v>
       </c>
       <c r="W42">
-        <v>0.1953820817758762</v>
+        <v>0.1803820817758762</v>
       </c>
       <c r="X42" t="inlineStr">
         <is>
@@ -4763,7 +4897,7 @@
         </is>
       </c>
       <c r="Y42">
-        <v>0.3667248281879547</v>
+        <v>0.3941196111701226</v>
       </c>
       <c r="Z42">
         <v>0</v>
@@ -4774,13 +4908,13 @@
         <v>0.41</v>
       </c>
       <c r="B43">
-        <v>0.1497509539217507</v>
+        <v>0.1434491238451577</v>
       </c>
       <c r="C43">
-        <v>421.4906376558974</v>
+        <v>1744.830084747256</v>
       </c>
       <c r="D43">
-        <v>20726.9726376559</v>
+        <v>22050.31208474726</v>
       </c>
       <c r="E43">
         <v>16915.382</v>
@@ -4807,37 +4941,37 @@
         <v>1604</v>
       </c>
       <c r="M43">
-        <v>4483.197955600001</v>
+        <v>4171.576225600001</v>
       </c>
       <c r="N43">
-        <v>-2879.197955600001</v>
+        <v>-2567.576225600001</v>
       </c>
       <c r="O43">
-        <v>-742.8330725448004</v>
+        <v>-662.4346662048002</v>
       </c>
       <c r="P43">
-        <v>-2136.364883055201</v>
+        <v>-1905.141559395201</v>
       </c>
       <c r="Q43">
-        <v>-1829.964883055201</v>
+        <v>-1598.741559395201</v>
       </c>
       <c r="R43">
         <v>0.6949152542372882</v>
       </c>
       <c r="S43">
-        <v>0.1176951206972885</v>
+        <v>0.1174377815844191</v>
       </c>
       <c r="T43">
-        <v>1.659327910552274</v>
+        <v>1.654452230587045</v>
       </c>
       <c r="U43">
-        <v>0.2158</v>
+        <v>0.2008</v>
       </c>
       <c r="V43">
-        <v>0.09230732260730956</v>
+        <v>0.09920278993355282</v>
       </c>
       <c r="W43">
-        <v>0.1958800797813426</v>
+        <v>0.1808800797813426</v>
       </c>
       <c r="X43" t="inlineStr">
         <is>
@@ -4845,7 +4979,7 @@
         </is>
       </c>
       <c r="Y43">
-        <v>0.3577803201833704</v>
+        <v>0.3845069377269489</v>
       </c>
       <c r="Z43">
         <v>0</v>
@@ -4856,13 +4990,13 @@
         <v>0.42</v>
       </c>
       <c r="B44">
-        <v>0.1514509539217507</v>
+        <v>0.1449991238451577</v>
       </c>
       <c r="C44">
-        <v>-418.7232917310539</v>
+        <v>893.5889153821408</v>
       </c>
       <c r="D44">
-        <v>20393.46070826895</v>
+        <v>21705.77291538214</v>
       </c>
       <c r="E44">
         <v>17422.084</v>
@@ -4889,37 +5023,37 @@
         <v>1604</v>
       </c>
       <c r="M44">
-        <v>4592.5442472</v>
+        <v>4273.3219872</v>
       </c>
       <c r="N44">
-        <v>-2988.5442472</v>
+        <v>-2669.3219872</v>
       </c>
       <c r="O44">
-        <v>-771.0444157776001</v>
+        <v>-688.6850726976</v>
       </c>
       <c r="P44">
-        <v>-2217.4998314224</v>
+        <v>-1980.6369145024</v>
       </c>
       <c r="Q44">
-        <v>-1911.0998314224</v>
+        <v>-1674.2369145024</v>
       </c>
       <c r="R44">
         <v>0.7241379310344827</v>
       </c>
       <c r="S44">
-        <v>0.1189346917437935</v>
+        <v>0.1186729157496677</v>
       </c>
       <c r="T44">
-        <v>1.687937012458348</v>
+        <v>1.682977269045443</v>
       </c>
       <c r="U44">
-        <v>0.2158</v>
+        <v>0.2008</v>
       </c>
       <c r="V44">
-        <v>0.09010952921189745</v>
+        <v>0.09684081874465873</v>
       </c>
       <c r="W44">
-        <v>0.1963543635960726</v>
+        <v>0.1813543635960725</v>
       </c>
       <c r="X44" t="inlineStr">
         <is>
@@ -4927,7 +5061,7 @@
         </is>
       </c>
       <c r="Y44">
-        <v>0.3492617411313854</v>
+        <v>0.3753520106382121</v>
       </c>
       <c r="Z44">
         <v>0</v>
@@ -4938,13 +5072,13 @@
         <v>0.43</v>
       </c>
       <c r="B45">
-        <v>0.1531509539217507</v>
+        <v>0.1465491238451577</v>
       </c>
       <c r="C45">
-        <v>-1248.37429160047</v>
+        <v>52.9490434205909</v>
       </c>
       <c r="D45">
-        <v>20070.51170839953</v>
+        <v>21371.83504342059</v>
       </c>
       <c r="E45">
         <v>17928.786</v>
@@ -4971,37 +5105,37 @@
         <v>1604</v>
       </c>
       <c r="M45">
-        <v>4701.890538800001</v>
+        <v>4375.0677488</v>
       </c>
       <c r="N45">
-        <v>-3097.890538800001</v>
+        <v>-2771.0677488</v>
       </c>
       <c r="O45">
-        <v>-799.2557590104003</v>
+        <v>-714.9354791904001</v>
       </c>
       <c r="P45">
-        <v>-2298.634779789601</v>
+        <v>-2056.1322696096</v>
       </c>
       <c r="Q45">
-        <v>-1992.234779789601</v>
+        <v>-1749.7322696096</v>
       </c>
       <c r="R45">
         <v>0.7543859649122806</v>
       </c>
       <c r="S45">
-        <v>0.1202177565112284</v>
+        <v>0.1199513879558022</v>
       </c>
       <c r="T45">
-        <v>1.717549942501477</v>
+        <v>1.71250318604624</v>
       </c>
       <c r="U45">
-        <v>0.2158</v>
+        <v>0.2008</v>
       </c>
       <c r="V45">
-        <v>0.08801395876510912</v>
+        <v>0.09458870668082944</v>
       </c>
       <c r="W45">
-        <v>0.1968065876984895</v>
+        <v>0.1818065876984895</v>
       </c>
       <c r="X45" t="inlineStr">
         <is>
@@ -5009,7 +5143,7 @@
         </is>
       </c>
       <c r="Y45">
-        <v>0.3411393750585625</v>
+        <v>0.366622894111742</v>
       </c>
       <c r="Z45">
         <v>0</v>
@@ -5020,13 +5154,13 @@
         <v>0.44</v>
       </c>
       <c r="B46">
-        <v>0.1548509539217507</v>
+        <v>0.1480991238451577</v>
       </c>
       <c r="C46">
-        <v>-2067.956359836848</v>
+        <v>-777.5714124191945</v>
       </c>
       <c r="D46">
-        <v>19757.63164016316</v>
+        <v>21048.01658758081</v>
       </c>
       <c r="E46">
         <v>18435.488</v>
@@ -5053,37 +5187,37 @@
         <v>1604</v>
       </c>
       <c r="M46">
-        <v>4811.236830400001</v>
+        <v>4476.8135104</v>
       </c>
       <c r="N46">
-        <v>-3207.236830400001</v>
+        <v>-2872.8135104</v>
       </c>
       <c r="O46">
-        <v>-827.4671022432003</v>
+        <v>-741.1858856832001</v>
       </c>
       <c r="P46">
-        <v>-2379.769728156801</v>
+        <v>-2131.6276247168</v>
       </c>
       <c r="Q46">
-        <v>-2073.369728156801</v>
+        <v>-1825.2276247168</v>
       </c>
       <c r="R46">
         <v>0.7857142857142857</v>
       </c>
       <c r="S46">
-        <v>0.1215466450203575</v>
+        <v>0.1212755198835844</v>
       </c>
       <c r="T46">
-        <v>1.748220477189003</v>
+        <v>1.74308360008278</v>
       </c>
       <c r="U46">
-        <v>0.2158</v>
+        <v>0.2008</v>
       </c>
       <c r="V46">
-        <v>0.08601364152044755</v>
+        <v>0.09243896334717423</v>
       </c>
       <c r="W46">
-        <v>0.1972382561598874</v>
+        <v>0.1822382561598874</v>
       </c>
       <c r="X46" t="inlineStr">
         <is>
@@ -5091,7 +5225,7 @@
         </is>
       </c>
       <c r="Y46">
-        <v>0.3333862074435952</v>
+        <v>0.3582905556092024</v>
       </c>
       <c r="Z46">
         <v>0</v>
@@ -5102,13 +5236,13 @@
         <v>0.45</v>
       </c>
       <c r="B47">
-        <v>0.1565509539217507</v>
+        <v>0.1496491238451577</v>
       </c>
       <c r="C47">
-        <v>-2877.933163338839</v>
+        <v>-1598.425564144563</v>
       </c>
       <c r="D47">
-        <v>19454.35683666117</v>
+        <v>20733.86443585544</v>
       </c>
       <c r="E47">
         <v>18942.19</v>
@@ -5135,37 +5269,37 @@
         <v>1604</v>
       </c>
       <c r="M47">
-        <v>4920.583122000001</v>
+        <v>4578.559272000001</v>
       </c>
       <c r="N47">
-        <v>-3316.583122000001</v>
+        <v>-2974.559272000001</v>
       </c>
       <c r="O47">
-        <v>-855.6784454760002</v>
+        <v>-767.4362921760004</v>
       </c>
       <c r="P47">
-        <v>-2460.904676524001</v>
+        <v>-2207.122979824001</v>
       </c>
       <c r="Q47">
-        <v>-2154.504676524001</v>
+        <v>-1900.722979824001</v>
       </c>
       <c r="R47">
         <v>0.8181818181818181</v>
       </c>
       <c r="S47">
-        <v>0.1229238567480004</v>
+        <v>0.1226478020632859</v>
       </c>
       <c r="T47">
-        <v>1.780006304046985</v>
+        <v>1.774776029175194</v>
       </c>
       <c r="U47">
-        <v>0.2158</v>
+        <v>0.2008</v>
       </c>
       <c r="V47">
-        <v>0.08410222726443761</v>
+        <v>0.09038476416168144</v>
       </c>
       <c r="W47">
-        <v>0.1976507393563344</v>
+        <v>0.1826507393563344</v>
       </c>
       <c r="X47" t="inlineStr">
         <is>
@@ -5173,7 +5307,7 @@
         </is>
       </c>
       <c r="Y47">
-        <v>0.3259776250559597</v>
+        <v>0.3503285432623312</v>
       </c>
       <c r="Z47">
         <v>0</v>
@@ -5184,13 +5318,13 @@
         <v>0.46</v>
       </c>
       <c r="B48">
-        <v>0.1582509539217507</v>
+        <v>0.1511991238451577</v>
       </c>
       <c r="C48">
-        <v>-3678.74033069329</v>
+        <v>-2410.039869893793</v>
       </c>
       <c r="D48">
-        <v>19160.25166930671</v>
+        <v>20428.95213010621</v>
       </c>
       <c r="E48">
         <v>19448.892</v>
@@ -5217,37 +5351,37 @@
         <v>1604</v>
       </c>
       <c r="M48">
-        <v>5029.929413600001</v>
+        <v>4680.305033600001</v>
       </c>
       <c r="N48">
-        <v>-3425.929413600001</v>
+        <v>-3076.305033600001</v>
       </c>
       <c r="O48">
-        <v>-883.8897887088002</v>
+        <v>-793.6866986688002</v>
       </c>
       <c r="P48">
-        <v>-2542.039624891201</v>
+        <v>-2282.6183349312</v>
       </c>
       <c r="Q48">
-        <v>-2235.639624891201</v>
+        <v>-1976.2183349312</v>
       </c>
       <c r="R48">
         <v>0.8518518518518519</v>
       </c>
       <c r="S48">
-        <v>0.1243520763174078</v>
+        <v>0.1240709095089023</v>
       </c>
       <c r="T48">
-        <v>1.812969383751559</v>
+        <v>1.807642251937698</v>
       </c>
       <c r="U48">
-        <v>0.2158</v>
+        <v>0.2008</v>
       </c>
       <c r="V48">
-        <v>0.08227391797608027</v>
+        <v>0.0884198779842536</v>
       </c>
       <c r="W48">
-        <v>0.1980452885007619</v>
+        <v>0.1830452885007619</v>
       </c>
       <c r="X48" t="inlineStr">
         <is>
@@ -5255,7 +5389,7 @@
         </is>
       </c>
       <c r="Y48">
-        <v>0.3188911549460476</v>
+        <v>0.3427127053653241</v>
       </c>
       <c r="Z48">
         <v>0</v>
@@ -5266,13 +5400,13 @@
         <v>0.47</v>
       </c>
       <c r="B49">
-        <v>0.1599509539217507</v>
+        <v>0.1527491238451577</v>
       </c>
       <c r="C49">
-        <v>-4470.787539986501</v>
+        <v>-3212.816065391733</v>
       </c>
       <c r="D49">
-        <v>18874.9064600135</v>
+        <v>20132.87793460827</v>
       </c>
       <c r="E49">
         <v>19955.594</v>
@@ -5299,37 +5433,37 @@
         <v>1604</v>
       </c>
       <c r="M49">
-        <v>5139.275705200001</v>
+        <v>4782.050795200001</v>
       </c>
       <c r="N49">
-        <v>-3535.275705200001</v>
+        <v>-3178.050795200001</v>
       </c>
       <c r="O49">
-        <v>-912.1011319416002</v>
+        <v>-819.9371051616002</v>
       </c>
       <c r="P49">
-        <v>-2623.1745732584</v>
+        <v>-2358.1136900384</v>
       </c>
       <c r="Q49">
-        <v>-2316.7745732584</v>
+        <v>-2051.7136900384</v>
       </c>
       <c r="R49">
         <v>0.8867924528301887</v>
       </c>
       <c r="S49">
-        <v>0.125834190964906</v>
+        <v>0.1255477191222778</v>
       </c>
       <c r="T49">
-        <v>1.847176353256305</v>
+        <v>1.841748709521428</v>
       </c>
       <c r="U49">
-        <v>0.2158</v>
+        <v>0.2008</v>
       </c>
       <c r="V49">
-        <v>0.08052340908297219</v>
+        <v>0.08653860398458862</v>
       </c>
       <c r="W49">
-        <v>0.1984230483198946</v>
+        <v>0.1834230483198946</v>
       </c>
       <c r="X49" t="inlineStr">
         <is>
@@ -5337,7 +5471,7 @@
         </is>
       </c>
       <c r="Y49">
-        <v>0.3121062367557061</v>
+        <v>0.3354209456767001</v>
       </c>
       <c r="Z49">
         <v>0</v>
@@ -5348,13 +5482,13 @@
         <v>0.48</v>
       </c>
       <c r="B50">
-        <v>0.1616509539217507</v>
+        <v>0.1542991238451577</v>
       </c>
       <c r="C50">
-        <v>-5254.460422795935</v>
+        <v>-4007.132929850704</v>
       </c>
       <c r="D50">
-        <v>18597.93557720407</v>
+        <v>19845.2630701493</v>
       </c>
       <c r="E50">
         <v>20462.296</v>
@@ -5381,37 +5515,37 @@
         <v>1604</v>
       </c>
       <c r="M50">
-        <v>5248.6219968</v>
+        <v>4883.7965568</v>
       </c>
       <c r="N50">
-        <v>-3644.6219968</v>
+        <v>-3279.7965568</v>
       </c>
       <c r="O50">
-        <v>-940.3124751744001</v>
+        <v>-846.1875116544001</v>
       </c>
       <c r="P50">
-        <v>-2704.309521625601</v>
+        <v>-2433.6090451456</v>
       </c>
       <c r="Q50">
-        <v>-2397.909521625601</v>
+        <v>-2127.2090451456</v>
       </c>
       <c r="R50">
         <v>0.923076923076923</v>
       </c>
       <c r="S50">
-        <v>0.1273733100219235</v>
+        <v>0.1270813291053985</v>
       </c>
       <c r="T50">
-        <v>1.882698975434311</v>
+        <v>1.877166953935302</v>
       </c>
       <c r="U50">
-        <v>0.2158</v>
+        <v>0.2008</v>
       </c>
       <c r="V50">
-        <v>0.07884583806041026</v>
+        <v>0.08473571640157637</v>
       </c>
       <c r="W50">
-        <v>0.1987850681465635</v>
+        <v>0.1837850681465635</v>
       </c>
       <c r="X50" t="inlineStr">
         <is>
@@ -5419,7 +5553,7 @@
         </is>
       </c>
       <c r="Y50">
-        <v>0.3056040234899623</v>
+        <v>0.3284330093084356</v>
       </c>
       <c r="Z50">
         <v>0</v>
@@ -5430,13 +5564,13 @@
         <v>0.49</v>
       </c>
       <c r="B51">
-        <v>0.1633509539217507</v>
+        <v>0.1558491238451577</v>
       </c>
       <c r="C51">
-        <v>-6030.122302970904</v>
+        <v>-4793.34790263922</v>
       </c>
       <c r="D51">
-        <v>18328.9756970291</v>
+        <v>19565.75009736078</v>
       </c>
       <c r="E51">
         <v>20968.998</v>
@@ -5463,37 +5597,37 @@
         <v>1604</v>
       </c>
       <c r="M51">
-        <v>5357.9682884</v>
+        <v>4985.5423184</v>
       </c>
       <c r="N51">
-        <v>-3753.9682884</v>
+        <v>-3381.5423184</v>
       </c>
       <c r="O51">
-        <v>-968.5238184072001</v>
+        <v>-872.4379181472001</v>
       </c>
       <c r="P51">
-        <v>-2785.4444699928</v>
+        <v>-2509.1044002528</v>
       </c>
       <c r="Q51">
-        <v>-2479.0444699928</v>
+        <v>-2202.7044002528</v>
       </c>
       <c r="R51">
         <v>0.9607843137254901</v>
       </c>
       <c r="S51">
-        <v>0.12897278668902</v>
+        <v>0.1286750806564848</v>
       </c>
       <c r="T51">
-        <v>1.919614641619298</v>
+        <v>1.913974149110503</v>
       </c>
       <c r="U51">
-        <v>0.2158</v>
+        <v>0.2008</v>
       </c>
       <c r="V51">
-        <v>0.07723673932448352</v>
+        <v>0.08300641606685033</v>
       </c>
       <c r="W51">
-        <v>0.1991323116537765</v>
+        <v>0.1841323116537765</v>
       </c>
       <c r="X51" t="inlineStr">
         <is>
@@ -5501,7 +5635,7 @@
         </is>
       </c>
       <c r="Y51">
-        <v>0.2993672066840447</v>
+        <v>0.3217302948327532</v>
       </c>
       <c r="Z51">
         <v>0</v>
@@ -5512,13 +5646,13 @@
         <v>0.5</v>
       </c>
       <c r="B52">
-        <v>0.1650509539217507</v>
+        <v>0.1573991238451577</v>
       </c>
       <c r="C52">
-        <v>-6798.115786688471</v>
+        <v>-5571.798565227182</v>
       </c>
       <c r="D52">
-        <v>18067.68421331153</v>
+        <v>19294.00143477282</v>
       </c>
       <c r="E52">
         <v>21475.7</v>
@@ -5545,37 +5679,37 @@
         <v>1604</v>
       </c>
       <c r="M52">
-        <v>5467.314580000001</v>
+        <v>5087.28808</v>
       </c>
       <c r="N52">
-        <v>-3863.314580000001</v>
+        <v>-3483.28808</v>
       </c>
       <c r="O52">
-        <v>-996.7351616400003</v>
+        <v>-898.6883246400001</v>
       </c>
       <c r="P52">
-        <v>-2866.579418360001</v>
+        <v>-2584.59975536</v>
       </c>
       <c r="Q52">
-        <v>-2560.179418360001</v>
+        <v>-2278.19975536</v>
       </c>
       <c r="R52">
         <v>1</v>
       </c>
       <c r="S52">
-        <v>0.1306362424228004</v>
+        <v>0.1303325822696145</v>
       </c>
       <c r="T52">
-        <v>1.958006934451684</v>
+        <v>1.952253632092714</v>
       </c>
       <c r="U52">
-        <v>0.2158</v>
+        <v>0.2008</v>
       </c>
       <c r="V52">
-        <v>0.07569200453799385</v>
+        <v>0.08134628774551331</v>
       </c>
       <c r="W52">
-        <v>0.1994656654207009</v>
+        <v>0.1844656654207009</v>
       </c>
       <c r="X52" t="inlineStr">
         <is>
@@ -5583,7 +5717,7 @@
         </is>
       </c>
       <c r="Y52">
-        <v>0.2933798625503637</v>
+        <v>0.3152956889360982</v>
       </c>
       <c r="Z52">
         <v>0</v>
@@ -5594,13 +5728,13 @@
         <v>0.51</v>
       </c>
       <c r="B53">
-        <v>0.1667509539217507</v>
+        <v>0.1589491238451577</v>
       </c>
       <c r="C53">
-        <v>-7558.764218417335</v>
+        <v>-6342.804001326462</v>
       </c>
       <c r="D53">
-        <v>17813.73778158267</v>
+        <v>19029.69799867354</v>
       </c>
       <c r="E53">
         <v>21982.402</v>
@@ -5627,37 +5761,37 @@
         <v>1604</v>
       </c>
       <c r="M53">
-        <v>5576.660871600001</v>
+        <v>5189.0338416</v>
       </c>
       <c r="N53">
-        <v>-3972.660871600001</v>
+        <v>-3585.0338416</v>
       </c>
       <c r="O53">
-        <v>-1024.9465048728</v>
+        <v>-924.9387311328002</v>
       </c>
       <c r="P53">
-        <v>-2947.714366727201</v>
+        <v>-2660.0951104672</v>
       </c>
       <c r="Q53">
-        <v>-2641.314366727201</v>
+        <v>-2353.6951104672</v>
       </c>
       <c r="R53">
         <v>1.040816326530612</v>
       </c>
       <c r="S53">
-        <v>0.13236759430898</v>
+        <v>0.1320577370098107</v>
       </c>
       <c r="T53">
-        <v>1.997966259644576</v>
+        <v>1.992095542951749</v>
       </c>
       <c r="U53">
-        <v>0.2158</v>
+        <v>0.2008</v>
       </c>
       <c r="V53">
-        <v>0.07420784758626847</v>
+        <v>0.07975126249560129</v>
       </c>
       <c r="W53">
-        <v>0.1997859464908833</v>
+        <v>0.1847859464908833</v>
       </c>
       <c r="X53" t="inlineStr">
         <is>
@@ -5665,7 +5799,7 @@
         </is>
       </c>
       <c r="Y53">
-        <v>0.2876273162258468</v>
+        <v>0.3091134205255864</v>
       </c>
       <c r="Z53">
         <v>0</v>
@@ -5676,13 +5810,13 @@
         <v>0.52</v>
       </c>
       <c r="B54">
-        <v>0.1684509539217507</v>
+        <v>0.1604991238451577</v>
       </c>
       <c r="C54">
-        <v>-8312.373015799523</v>
+        <v>-7106.666046748982</v>
       </c>
       <c r="D54">
-        <v>17566.83098420048</v>
+        <v>18772.53795325102</v>
       </c>
       <c r="E54">
         <v>22489.104</v>
@@ -5709,37 +5843,37 @@
         <v>1604</v>
       </c>
       <c r="M54">
-        <v>5686.007163200002</v>
+        <v>5290.779603200001</v>
       </c>
       <c r="N54">
-        <v>-4082.007163200002</v>
+        <v>-3686.779603200001</v>
       </c>
       <c r="O54">
-        <v>-1053.157848105601</v>
+        <v>-951.1891376256004</v>
       </c>
       <c r="P54">
-        <v>-3028.849315094401</v>
+        <v>-2735.590465574401</v>
       </c>
       <c r="Q54">
-        <v>-2722.449315094401</v>
+        <v>-2429.190465574401</v>
       </c>
       <c r="R54">
         <v>1.083333333333333</v>
       </c>
       <c r="S54">
-        <v>0.1341710858570838</v>
+        <v>0.1338547731975151</v>
       </c>
       <c r="T54">
-        <v>2.039590556720504</v>
+        <v>2.03359753342991</v>
       </c>
       <c r="U54">
-        <v>0.2158</v>
+        <v>0.2008</v>
       </c>
       <c r="V54">
-        <v>0.07278077359422484</v>
+        <v>0.07821758437068586</v>
       </c>
       <c r="W54">
-        <v>0.2000939090583663</v>
+        <v>0.1850939090583663</v>
       </c>
       <c r="X54" t="inlineStr">
         <is>
@@ -5747,7 +5881,7 @@
         </is>
       </c>
       <c r="Y54">
-        <v>0.282096021683042</v>
+        <v>0.303168931669325</v>
       </c>
       <c r="Z54">
         <v>0</v>
@@ -5758,13 +5892,13 @@
         <v>0.53</v>
       </c>
       <c r="B55">
-        <v>0.1701509539217507</v>
+        <v>0.1620491238451577</v>
       </c>
       <c r="C55">
-        <v>-9059.230895037348</v>
+        <v>-7863.670439275367</v>
       </c>
       <c r="D55">
-        <v>17326.67510496265</v>
+        <v>18522.23556072464</v>
       </c>
       <c r="E55">
         <v>22995.806</v>
@@ -5791,37 +5925,37 @@
         <v>1604</v>
       </c>
       <c r="M55">
-        <v>5795.353454800001</v>
+        <v>5392.525364800001</v>
       </c>
       <c r="N55">
-        <v>-4191.353454800001</v>
+        <v>-3788.525364800001</v>
       </c>
       <c r="O55">
-        <v>-1081.3691913384</v>
+        <v>-977.4395441184002</v>
       </c>
       <c r="P55">
-        <v>-3109.984263461601</v>
+        <v>-2811.085820681601</v>
       </c>
       <c r="Q55">
-        <v>-2803.584263461601</v>
+        <v>-2504.6858206816</v>
       </c>
       <c r="R55">
         <v>1.127659574468085</v>
       </c>
       <c r="S55">
-        <v>0.1360513217263834</v>
+        <v>0.1357282790102282</v>
       </c>
       <c r="T55">
-        <v>2.082986100480515</v>
+        <v>2.076865566056078</v>
       </c>
       <c r="U55">
-        <v>0.2158</v>
+        <v>0.2008</v>
       </c>
       <c r="V55">
-        <v>0.07140755145093759</v>
+        <v>0.0767417808919937</v>
       </c>
       <c r="W55">
-        <v>0.2003902503968877</v>
+        <v>0.1853902503968877</v>
       </c>
       <c r="X55" t="inlineStr">
         <is>
@@ -5829,7 +5963,7 @@
         </is>
       </c>
       <c r="Y55">
-        <v>0.2767734552361922</v>
+        <v>0.2974487631472623</v>
       </c>
       <c r="Z55">
         <v>0</v>
@@ -5840,13 +5974,13 @@
         <v>0.54</v>
       </c>
       <c r="B56">
-        <v>0.1718509539217507</v>
+        <v>0.1635991238451577</v>
       </c>
       <c r="C56">
-        <v>-9799.610997122334</v>
+        <v>-8614.08787774383</v>
       </c>
       <c r="D56">
-        <v>17092.99700287767</v>
+        <v>18278.52012225617</v>
       </c>
       <c r="E56">
         <v>23502.508</v>
@@ -5873,37 +6007,37 @@
         <v>1604</v>
       </c>
       <c r="M56">
-        <v>5904.699746400001</v>
+        <v>5494.271126400001</v>
       </c>
       <c r="N56">
-        <v>-4300.699746400001</v>
+        <v>-3890.271126400001</v>
       </c>
       <c r="O56">
-        <v>-1109.5805345712</v>
+        <v>-1003.6899506112</v>
       </c>
       <c r="P56">
-        <v>-3191.119211828801</v>
+        <v>-2886.5811757888</v>
       </c>
       <c r="Q56">
-        <v>-2884.719211828801</v>
+        <v>-2580.1811757888</v>
       </c>
       <c r="R56">
         <v>1.173913043478261</v>
       </c>
       <c r="S56">
-        <v>0.1380133069813048</v>
+        <v>0.1376832415974071</v>
       </c>
       <c r="T56">
-        <v>2.1282684070127</v>
+        <v>2.12201481749208</v>
       </c>
       <c r="U56">
-        <v>0.2158</v>
+        <v>0.2008</v>
       </c>
       <c r="V56">
-        <v>0.07008518938703134</v>
+        <v>0.07532063680140122</v>
       </c>
       <c r="W56">
-        <v>0.2006756161302787</v>
+        <v>0.1856756161302786</v>
       </c>
       <c r="X56" t="inlineStr">
         <is>
@@ -5911,7 +6045,7 @@
         </is>
       </c>
       <c r="Y56">
-        <v>0.2716480208799664</v>
+        <v>0.2919404527186094</v>
       </c>
       <c r="Z56">
         <v>0</v>
@@ -5922,13 +6056,13 @@
         <v>0.55</v>
       </c>
       <c r="B57">
-        <v>0.1735509539217507</v>
+        <v>0.1651491238451577</v>
       </c>
       <c r="C57">
-        <v>-10533.77192414287</v>
+        <v>-9358.174998612034</v>
       </c>
       <c r="D57">
-        <v>16865.53807585713</v>
+        <v>18041.13500138797</v>
       </c>
       <c r="E57">
         <v>24009.21</v>
@@ -5955,37 +6089,37 @@
         <v>1604</v>
       </c>
       <c r="M57">
-        <v>6014.046038000001</v>
+        <v>5596.016888000001</v>
       </c>
       <c r="N57">
-        <v>-4410.046038000001</v>
+        <v>-3992.016888000001</v>
       </c>
       <c r="O57">
-        <v>-1137.791877804</v>
+        <v>-1029.940357104</v>
       </c>
       <c r="P57">
-        <v>-3272.254160196001</v>
+        <v>-2962.076530896001</v>
       </c>
       <c r="Q57">
-        <v>-2965.854160196001</v>
+        <v>-2655.676530896001</v>
       </c>
       <c r="R57">
         <v>1.222222222222223</v>
       </c>
       <c r="S57">
-        <v>0.1400624915808893</v>
+        <v>0.1397250914106828</v>
       </c>
       <c r="T57">
-        <v>2.175563260501872</v>
+        <v>2.169170702325238</v>
       </c>
       <c r="U57">
-        <v>0.2158</v>
+        <v>0.2008</v>
       </c>
       <c r="V57">
-        <v>0.06881091321635804</v>
+        <v>0.07395117067773938</v>
       </c>
       <c r="W57">
-        <v>0.2009506049279099</v>
+        <v>0.1859506049279099</v>
       </c>
       <c r="X57" t="inlineStr">
         <is>
@@ -5993,7 +6127,7 @@
         </is>
       </c>
       <c r="Y57">
-        <v>0.2667089659548761</v>
+        <v>0.2866324444873619</v>
       </c>
       <c r="Z57">
         <v>0</v>
@@ -6004,13 +6138,13 @@
         <v>0.5600000000000001</v>
       </c>
       <c r="B58">
-        <v>0.1752509539217507</v>
+        <v>0.1666991238451577</v>
       </c>
       <c r="C58">
-        <v>-11261.95869393676</v>
+        <v>-10096.17527739829</v>
       </c>
       <c r="D58">
-        <v>16644.05330606325</v>
+        <v>17809.83672260172</v>
       </c>
       <c r="E58">
         <v>24515.912</v>
@@ -6037,37 +6171,37 @@
         <v>1604</v>
       </c>
       <c r="M58">
-        <v>6123.392329600002</v>
+        <v>5697.762649600001</v>
       </c>
       <c r="N58">
-        <v>-4519.392329600002</v>
+        <v>-4093.762649600001</v>
       </c>
       <c r="O58">
-        <v>-1166.003221036801</v>
+        <v>-1056.1907635968</v>
       </c>
       <c r="P58">
-        <v>-3353.389108563201</v>
+        <v>-3037.571886003201</v>
       </c>
       <c r="Q58">
-        <v>-3046.989108563201</v>
+        <v>-2731.171886003201</v>
       </c>
       <c r="R58">
         <v>1.272727272727273</v>
       </c>
       <c r="S58">
-        <v>0.1422048209350005</v>
+        <v>0.1418597525791074</v>
       </c>
       <c r="T58">
-        <v>2.225007880058732</v>
+        <v>2.218470036468993</v>
       </c>
       <c r="U58">
-        <v>0.2158</v>
+        <v>0.2008</v>
       </c>
       <c r="V58">
-        <v>0.06758214690892307</v>
+        <v>0.07263061405849403</v>
       </c>
       <c r="W58">
-        <v>0.2012157726970544</v>
+        <v>0.1862157726970544</v>
       </c>
       <c r="X58" t="inlineStr">
         <is>
@@ -6075,7 +6209,7 @@
         </is>
       </c>
       <c r="Y58">
-        <v>0.2619463058485391</v>
+        <v>0.281514007978659</v>
       </c>
       <c r="Z58">
         <v>0</v>
@@ -6086,13 +6220,13 @@
         <v>0.5700000000000001</v>
       </c>
       <c r="B59">
-        <v>0.1769509539217507</v>
+        <v>0.1682491238451577</v>
       </c>
       <c r="C59">
-        <v>-11984.40362049747</v>
+        <v>-10828.31986165835</v>
       </c>
       <c r="D59">
-        <v>16428.31037950254</v>
+        <v>17584.39413834165</v>
       </c>
       <c r="E59">
         <v>25022.61400000001</v>
@@ -6119,37 +6253,37 @@
         <v>1604</v>
       </c>
       <c r="M59">
-        <v>6232.738621200002</v>
+        <v>5799.508411200001</v>
       </c>
       <c r="N59">
-        <v>-4628.738621200002</v>
+        <v>-4195.508411200001</v>
       </c>
       <c r="O59">
-        <v>-1194.2145642696</v>
+        <v>-1082.4411700896</v>
       </c>
       <c r="P59">
-        <v>-3434.524056930401</v>
+        <v>-3113.067241110401</v>
       </c>
       <c r="Q59">
-        <v>-3128.124056930401</v>
+        <v>-2806.667241110401</v>
       </c>
       <c r="R59">
         <v>1.325581395348838</v>
       </c>
       <c r="S59">
-        <v>0.1444467935148842</v>
+        <v>0.1440937003135052</v>
       </c>
       <c r="T59">
-        <v>2.276752249362424</v>
+        <v>2.270062362898504</v>
       </c>
       <c r="U59">
-        <v>0.2158</v>
+        <v>0.2008</v>
       </c>
       <c r="V59">
-        <v>0.06639649520876653</v>
+        <v>0.0713563927592222</v>
       </c>
       <c r="W59">
-        <v>0.2014716363339482</v>
+        <v>0.1864716363339482</v>
       </c>
       <c r="X59" t="inlineStr">
         <is>
@@ -6157,7 +6291,7 @@
         </is>
       </c>
       <c r="Y59">
-        <v>0.257350756623126</v>
+        <v>0.2765751657334193</v>
       </c>
       <c r="Z59">
         <v>0</v>
@@ -6168,13 +6302,13 @@
         <v>0.58</v>
       </c>
       <c r="B60">
-        <v>0.1786509539217507</v>
+        <v>0.1697991238451577</v>
       </c>
       <c r="C60">
-        <v>-12701.32712678491</v>
+        <v>-11554.82834148852</v>
       </c>
       <c r="D60">
-        <v>16218.08887321509</v>
+        <v>17364.58765851149</v>
       </c>
       <c r="E60">
         <v>25529.316</v>
@@ -6201,37 +6335,37 @@
         <v>1604</v>
       </c>
       <c r="M60">
-        <v>6342.084912800001</v>
+        <v>5901.254172800001</v>
       </c>
       <c r="N60">
-        <v>-4738.084912800001</v>
+        <v>-4297.254172800001</v>
       </c>
       <c r="O60">
-        <v>-1222.4259075024</v>
+        <v>-1108.6915765824</v>
       </c>
       <c r="P60">
-        <v>-3515.659005297601</v>
+        <v>-3188.5625962176</v>
       </c>
       <c r="Q60">
-        <v>-3209.259005297601</v>
+        <v>-2882.1625962176</v>
       </c>
       <c r="R60">
         <v>1.380952380952381</v>
       </c>
       <c r="S60">
-        <v>0.14679552669381</v>
+        <v>0.1464340265114458</v>
       </c>
       <c r="T60">
-        <v>2.330960636252004</v>
+        <v>2.32411146677704</v>
       </c>
       <c r="U60">
-        <v>0.2158</v>
+        <v>0.2008</v>
       </c>
       <c r="V60">
-        <v>0.0652517280499947</v>
+        <v>0.07012611012544251</v>
       </c>
       <c r="W60">
-        <v>0.2017186770868112</v>
+        <v>0.1867186770868112</v>
       </c>
       <c r="X60" t="inlineStr">
         <is>
@@ -6239,7 +6373,7 @@
         </is>
       </c>
       <c r="Y60">
-        <v>0.2529136746123826</v>
+        <v>0.271806628393188</v>
       </c>
       <c r="Z60">
         <v>0</v>
@@ -6250,13 +6384,13 @@
         <v>0.59</v>
       </c>
       <c r="B61">
-        <v>0.1803509539217507</v>
+        <v>0.1713491238451577</v>
       </c>
       <c r="C61">
-        <v>-13412.93849591877</v>
+        <v>-12275.90946295406</v>
       </c>
       <c r="D61">
-        <v>16013.17950408123</v>
+        <v>17150.20853704595</v>
       </c>
       <c r="E61">
         <v>26036.018</v>
@@ -6283,37 +6417,37 @@
         <v>1604</v>
       </c>
       <c r="M61">
-        <v>6451.431204400001</v>
+        <v>6002.999934400001</v>
       </c>
       <c r="N61">
-        <v>-4847.431204400001</v>
+        <v>-4398.999934400001</v>
       </c>
       <c r="O61">
-        <v>-1250.6372507352</v>
+        <v>-1134.9419830752</v>
       </c>
       <c r="P61">
-        <v>-3596.7939536648</v>
+        <v>-3264.0579513248</v>
       </c>
       <c r="Q61">
-        <v>-3290.3939536648</v>
+        <v>-2957.6579513248</v>
       </c>
       <c r="R61">
         <v>1.439024390243902</v>
       </c>
       <c r="S61">
-        <v>0.1492588322229273</v>
+        <v>0.1488885149629445</v>
       </c>
       <c r="T61">
-        <v>2.387813334697175</v>
+        <v>2.380797112308187</v>
       </c>
       <c r="U61">
-        <v>0.2158</v>
+        <v>0.2008</v>
       </c>
       <c r="V61">
-        <v>0.06414576655762191</v>
+        <v>0.06893753198772315</v>
       </c>
       <c r="W61">
-        <v>0.2019573435768652</v>
+        <v>0.1869573435768652</v>
       </c>
       <c r="X61" t="inlineStr">
         <is>
@@ -6321,7 +6455,7 @@
         </is>
       </c>
       <c r="Y61">
-        <v>0.2486270021613253</v>
+        <v>0.2671997363865238</v>
       </c>
       <c r="Z61">
         <v>0</v>
@@ -6332,13 +6466,13 @@
         <v>0.6</v>
       </c>
       <c r="B62">
-        <v>0.1820509539217507</v>
+        <v>0.1728991238451577</v>
       </c>
       <c r="C62">
-        <v>-14119.43656613618</v>
+        <v>-12991.76178931513</v>
       </c>
       <c r="D62">
-        <v>15813.38343386382</v>
+        <v>16941.05821068487</v>
       </c>
       <c r="E62">
         <v>26542.72</v>
@@ -6365,37 +6499,37 @@
         <v>1604</v>
       </c>
       <c r="M62">
-        <v>6560.777496000002</v>
+        <v>6104.745696000001</v>
       </c>
       <c r="N62">
-        <v>-4956.777496000002</v>
+        <v>-4500.745696000001</v>
       </c>
       <c r="O62">
-        <v>-1278.848593968</v>
+        <v>-1161.192389568</v>
       </c>
       <c r="P62">
-        <v>-3677.928902032001</v>
+        <v>-3339.553306432001</v>
       </c>
       <c r="Q62">
-        <v>-3371.528902032001</v>
+        <v>-3033.153306432001</v>
       </c>
       <c r="R62">
         <v>1.5</v>
       </c>
       <c r="S62">
-        <v>0.1518453030285005</v>
+        <v>0.1514657278370181</v>
       </c>
       <c r="T62">
-        <v>2.447508668064604</v>
+        <v>2.440317040115892</v>
       </c>
       <c r="U62">
-        <v>0.2158</v>
+        <v>0.2008</v>
       </c>
       <c r="V62">
-        <v>0.06307667044832821</v>
+        <v>0.0677885731212611</v>
       </c>
       <c r="W62">
-        <v>0.2021880545172508</v>
+        <v>0.1871880545172508</v>
       </c>
       <c r="X62" t="inlineStr">
         <is>
@@ -6403,7 +6537,7 @@
         </is>
       </c>
       <c r="Y62">
-        <v>0.2444832187919698</v>
+        <v>0.2627464074467484</v>
       </c>
       <c r="Z62">
         <v>0</v>
@@ -6414,13 +6548,13 @@
         <v>0.61</v>
       </c>
       <c r="B63">
-        <v>0.1837509539217507</v>
+        <v>0.1744491238451577</v>
       </c>
       <c r="C63">
-        <v>-14821.01037436461</v>
+        <v>-13702.574314453</v>
       </c>
       <c r="D63">
-        <v>15618.51162563539</v>
+        <v>16736.94768554701</v>
       </c>
       <c r="E63">
         <v>27049.422</v>
@@ -6447,37 +6581,37 @@
         <v>1604</v>
       </c>
       <c r="M63">
-        <v>6670.123787600001</v>
+        <v>6206.491457600001</v>
       </c>
       <c r="N63">
-        <v>-5066.123787600001</v>
+        <v>-4602.491457600001</v>
       </c>
       <c r="O63">
-        <v>-1307.059937200801</v>
+        <v>-1187.4427960608</v>
       </c>
       <c r="P63">
-        <v>-3759.063850399201</v>
+        <v>-3415.048661539201</v>
       </c>
       <c r="Q63">
-        <v>-3452.663850399201</v>
+        <v>-3108.648661539201</v>
       </c>
       <c r="R63">
         <v>1.564102564102564</v>
       </c>
       <c r="S63">
-        <v>0.1545644133625646</v>
+        <v>0.1541751054738648</v>
       </c>
       <c r="T63">
-        <v>2.510265300579082</v>
+        <v>2.502889271913736</v>
       </c>
       <c r="U63">
-        <v>0.2158</v>
+        <v>0.2008</v>
       </c>
       <c r="V63">
-        <v>0.06204262667048676</v>
+        <v>0.06667728503730599</v>
       </c>
       <c r="W63">
-        <v>0.202411201164509</v>
+        <v>0.187411201164509</v>
       </c>
       <c r="X63" t="inlineStr">
         <is>
@@ -6485,7 +6619,7 @@
         </is>
       </c>
       <c r="Y63">
-        <v>0.2404752971724293</v>
+        <v>0.2584390892918836</v>
       </c>
       <c r="Z63">
         <v>0</v>
@@ -6496,13 +6630,13 @@
         <v>0.62</v>
       </c>
       <c r="B64">
-        <v>0.1854509539217507</v>
+        <v>0.1759991238451577</v>
       </c>
       <c r="C64">
-        <v>-15517.8397527888</v>
+        <v>-14408.52703247972</v>
       </c>
       <c r="D64">
-        <v>15428.3842472112</v>
+        <v>16537.69696752028</v>
       </c>
       <c r="E64">
         <v>27556.124</v>
@@ -6529,37 +6663,37 @@
         <v>1604</v>
       </c>
       <c r="M64">
-        <v>6779.470079200001</v>
+        <v>6308.2372192</v>
       </c>
       <c r="N64">
-        <v>-5175.470079200001</v>
+        <v>-4704.2372192</v>
       </c>
       <c r="O64">
-        <v>-1335.2712804336</v>
+        <v>-1213.6932025536</v>
       </c>
       <c r="P64">
-        <v>-3840.198798766401</v>
+        <v>-3490.5440166464</v>
       </c>
       <c r="Q64">
-        <v>-3533.798798766401</v>
+        <v>-3184.1440166464</v>
       </c>
       <c r="R64">
         <v>1.631578947368421</v>
       </c>
       <c r="S64">
-        <v>0.1574266347668426</v>
+        <v>0.1570270819337033</v>
       </c>
       <c r="T64">
-        <v>2.576324913752215</v>
+        <v>2.56875477906936</v>
       </c>
       <c r="U64">
-        <v>0.2158</v>
+        <v>0.2008</v>
       </c>
       <c r="V64">
-        <v>0.06104193914354342</v>
+        <v>0.06560184495605913</v>
       </c>
       <c r="W64">
-        <v>0.2026271495328233</v>
+        <v>0.1876271495328233</v>
       </c>
       <c r="X64" t="inlineStr">
         <is>
@@ -6567,7 +6701,7 @@
         </is>
       </c>
       <c r="Y64">
-        <v>0.2365966633470675</v>
+        <v>0.2542707168839501</v>
       </c>
       <c r="Z64">
         <v>0</v>
@@ -6578,13 +6712,13 @@
         <v>0.63</v>
       </c>
       <c r="B65">
-        <v>0.1871509539217507</v>
+        <v>0.1775491238451577</v>
       </c>
       <c r="C65">
-        <v>-16210.09588236885</v>
+        <v>-15109.79146713988</v>
       </c>
       <c r="D65">
-        <v>15242.83011763116</v>
+        <v>16343.13453286013</v>
       </c>
       <c r="E65">
         <v>28062.826</v>
@@ -6611,37 +6745,37 @@
         <v>1604</v>
       </c>
       <c r="M65">
-        <v>6888.816370800001</v>
+        <v>6409.9829808</v>
       </c>
       <c r="N65">
-        <v>-5284.816370800001</v>
+        <v>-4805.9829808</v>
       </c>
       <c r="O65">
-        <v>-1363.4826236664</v>
+        <v>-1239.9436090464</v>
       </c>
       <c r="P65">
-        <v>-3921.333747133601</v>
+        <v>-3566.0393717536</v>
       </c>
       <c r="Q65">
-        <v>-3614.933747133601</v>
+        <v>-3259.6393717536</v>
       </c>
       <c r="R65">
         <v>1.702702702702703</v>
       </c>
       <c r="S65">
-        <v>0.1604435708416222</v>
+        <v>0.1600332192832628</v>
       </c>
       <c r="T65">
-        <v>2.6459553168266</v>
+        <v>2.638180583909072</v>
       </c>
       <c r="U65">
-        <v>0.2158</v>
+        <v>0.2008</v>
       </c>
       <c r="V65">
-        <v>0.0600730194745983</v>
+        <v>0.06456054582977247</v>
       </c>
       <c r="W65">
-        <v>0.2028362423973817</v>
+        <v>0.1878362423973817</v>
       </c>
       <c r="X65" t="inlineStr">
         <is>
@@ -6649,7 +6783,7 @@
         </is>
       </c>
       <c r="Y65">
-        <v>0.232841160754257</v>
+        <v>0.250234673758808</v>
       </c>
       <c r="Z65">
         <v>0</v>
@@ -6660,13 +6794,13 @@
         <v>0.64</v>
       </c>
       <c r="B66">
-        <v>0.1888509539217507</v>
+        <v>0.1790991238451577</v>
       </c>
       <c r="C66">
-        <v>-16897.94180689065</v>
+        <v>-15806.53116427702</v>
       </c>
       <c r="D66">
-        <v>15061.68619310936</v>
+        <v>16153.09683572298</v>
       </c>
       <c r="E66">
         <v>28569.528</v>
@@ -6693,37 +6827,37 @@
         <v>1604</v>
       </c>
       <c r="M66">
-        <v>6998.162662400001</v>
+        <v>6511.728742400001</v>
       </c>
       <c r="N66">
-        <v>-5394.162662400001</v>
+        <v>-4907.728742400001</v>
       </c>
       <c r="O66">
-        <v>-1391.6939668992</v>
+        <v>-1266.1940155392</v>
       </c>
       <c r="P66">
-        <v>-4002.468695500801</v>
+        <v>-3641.5347268608</v>
       </c>
       <c r="Q66">
-        <v>-3696.068695500801</v>
+        <v>-3335.1347268608</v>
       </c>
       <c r="R66">
         <v>1.777777777777778</v>
       </c>
       <c r="S66">
-        <v>0.1636281144761117</v>
+        <v>0.1632063642633535</v>
       </c>
       <c r="T66">
-        <v>2.719454075627339</v>
+        <v>2.711463377906547</v>
       </c>
       <c r="U66">
-        <v>0.2158</v>
+        <v>0.2008</v>
       </c>
       <c r="V66">
-        <v>0.0591343785453077</v>
+        <v>0.06355178730118229</v>
       </c>
       <c r="W66">
-        <v>0.2030388011099226</v>
+        <v>0.1880388011099226</v>
       </c>
       <c r="X66" t="inlineStr">
         <is>
@@ -6731,7 +6865,7 @@
         </is>
       </c>
       <c r="Y66">
-        <v>0.2292030176174716</v>
+        <v>0.2463247569813266</v>
       </c>
       <c r="Z66">
         <v>0</v>
@@ -6742,13 +6876,13 @@
         <v>0.65</v>
       </c>
       <c r="B67">
-        <v>0.1905509539217507</v>
+        <v>0.1806491238451577</v>
       </c>
       <c r="C67">
-        <v>-17581.53291079339</v>
+        <v>-16498.90215033674</v>
       </c>
       <c r="D67">
-        <v>14884.79708920662</v>
+        <v>15967.42784966327</v>
       </c>
       <c r="E67">
         <v>29076.23</v>
@@ -6775,37 +6909,37 @@
         <v>1604</v>
       </c>
       <c r="M67">
-        <v>7107.508954000002</v>
+        <v>6613.474504000001</v>
       </c>
       <c r="N67">
-        <v>-5503.508954000002</v>
+        <v>-5009.474504000001</v>
       </c>
       <c r="O67">
-        <v>-1419.905310132001</v>
+        <v>-1292.444422032</v>
       </c>
       <c r="P67">
-        <v>-4083.603643868001</v>
+        <v>-3717.030081968001</v>
       </c>
       <c r="Q67">
-        <v>-3777.203643868001</v>
+        <v>-3410.630081968</v>
       </c>
       <c r="R67">
         <v>1.857142857142857</v>
       </c>
       <c r="S67">
-        <v>0.166994632032572</v>
+        <v>0.166560831813735</v>
       </c>
       <c r="T67">
-        <v>2.797152763502406</v>
+        <v>2.788933760132448</v>
       </c>
       <c r="U67">
-        <v>0.2158</v>
+        <v>0.2008</v>
       </c>
       <c r="V67">
-        <v>0.05822461887537988</v>
+        <v>0.0625740674965487</v>
       </c>
       <c r="W67">
-        <v>0.203235127246693</v>
+        <v>0.188235127246693</v>
       </c>
       <c r="X67" t="inlineStr">
         <is>
@@ -6813,7 +6947,7 @@
         </is>
       </c>
       <c r="Y67">
-        <v>0.2256768173464336</v>
+        <v>0.2425351453354601</v>
       </c>
       <c r="Z67">
         <v>0</v>
@@ -6824,13 +6958,13 @@
         <v>0.66</v>
       </c>
       <c r="B68">
-        <v>0.1922509539217507</v>
+        <v>0.1821991238451577</v>
       </c>
       <c r="C68">
-        <v>-18261.01736371733</v>
+        <v>-17187.05335960786</v>
       </c>
       <c r="D68">
-        <v>14712.01463628267</v>
+        <v>15785.97864039214</v>
       </c>
       <c r="E68">
         <v>29582.932</v>
@@ -6857,37 +6991,37 @@
         <v>1604</v>
       </c>
       <c r="M68">
-        <v>7216.855245600001</v>
+        <v>6715.220265600001</v>
       </c>
       <c r="N68">
-        <v>-5612.855245600001</v>
+        <v>-5111.220265600001</v>
       </c>
       <c r="O68">
-        <v>-1448.1166533648</v>
+        <v>-1318.6948285248</v>
       </c>
       <c r="P68">
-        <v>-4164.7385922352</v>
+        <v>-3792.525437075201</v>
       </c>
       <c r="Q68">
-        <v>-3858.3385922352</v>
+        <v>-3486.125437075201</v>
       </c>
       <c r="R68">
         <v>1.941176470588236</v>
       </c>
       <c r="S68">
-        <v>0.17055918003353</v>
+        <v>0.1701126209847272</v>
       </c>
       <c r="T68">
-        <v>2.879421962428947</v>
+        <v>2.870961223665755</v>
       </c>
       <c r="U68">
-        <v>0.2158</v>
+        <v>0.2008</v>
       </c>
       <c r="V68">
-        <v>0.05734242768029837</v>
+        <v>0.06162597556478281</v>
       </c>
       <c r="W68">
-        <v>0.2034255041065916</v>
+        <v>0.1884255041065916</v>
       </c>
       <c r="X68" t="inlineStr">
         <is>
@@ -6895,7 +7029,7 @@
         </is>
       </c>
       <c r="Y68">
-        <v>0.2222574716290635</v>
+        <v>0.2388603704061349</v>
       </c>
       <c r="Z68">
         <v>0</v>
@@ -6906,13 +7040,13 @@
         <v>0.67</v>
       </c>
       <c r="B69">
-        <v>0.1939509539217507</v>
+        <v>0.1837491238451577</v>
       </c>
       <c r="C69">
-        <v>-18936.53653444504</v>
+        <v>-17871.12703266084</v>
       </c>
       <c r="D69">
-        <v>14543.19746555497</v>
+        <v>15608.60696733917</v>
       </c>
       <c r="E69">
         <v>30089.63400000001</v>
@@ -6939,37 +7073,37 @@
         <v>1604</v>
       </c>
       <c r="M69">
-        <v>7326.201537200002</v>
+        <v>6816.966027200002</v>
       </c>
       <c r="N69">
-        <v>-5722.201537200002</v>
+        <v>-5212.966027200002</v>
       </c>
       <c r="O69">
-        <v>-1476.327996597601</v>
+        <v>-1344.9452350176</v>
       </c>
       <c r="P69">
-        <v>-4245.873540602402</v>
+        <v>-3868.020792182401</v>
       </c>
       <c r="Q69">
-        <v>-3939.473540602401</v>
+        <v>-3561.620792182401</v>
       </c>
       <c r="R69">
         <v>2.030303030303031</v>
       </c>
       <c r="S69">
-        <v>0.1743397612466673</v>
+        <v>0.1738796701054765</v>
       </c>
       <c r="T69">
-        <v>2.966677173411643</v>
+        <v>2.957960048625324</v>
       </c>
       <c r="U69">
-        <v>0.2158</v>
+        <v>0.2008</v>
       </c>
       <c r="V69">
-        <v>0.05648657055074167</v>
+        <v>0.06070618488471142</v>
       </c>
       <c r="W69">
-        <v>0.20361019807515</v>
+        <v>0.1886101980751499</v>
       </c>
       <c r="X69" t="inlineStr">
         <is>
@@ -6977,7 +7111,7 @@
         </is>
       </c>
       <c r="Y69">
-        <v>0.2189401959331072</v>
+        <v>0.2352952902508194</v>
       </c>
       <c r="Z69">
         <v>0</v>
@@ -6988,13 +7122,13 @@
         <v>0.68</v>
       </c>
       <c r="B70">
-        <v>0.1956509539217507</v>
+        <v>0.1852991238451577</v>
       </c>
       <c r="C70">
-        <v>-19608.22537666663</v>
+        <v>-18551.25908822327</v>
       </c>
       <c r="D70">
-        <v>14378.21062333337</v>
+        <v>15435.17691177674</v>
       </c>
       <c r="E70">
         <v>30596.336</v>
@@ -7021,37 +7155,37 @@
         <v>1604</v>
       </c>
       <c r="M70">
-        <v>7435.547828800001</v>
+        <v>6918.711788800001</v>
       </c>
       <c r="N70">
-        <v>-5831.547828800001</v>
+        <v>-5314.711788800001</v>
       </c>
       <c r="O70">
-        <v>-1504.5393398304</v>
+        <v>-1371.1956415104</v>
       </c>
       <c r="P70">
-        <v>-4327.008488969601</v>
+        <v>-3943.516147289601</v>
       </c>
       <c r="Q70">
-        <v>-4020.608488969601</v>
+        <v>-3637.116147289601</v>
       </c>
       <c r="R70">
         <v>2.125</v>
       </c>
       <c r="S70">
-        <v>0.1783566287856256</v>
+        <v>0.1778821597962727</v>
       </c>
       <c r="T70">
-        <v>3.059385835080756</v>
+        <v>3.050396300144866</v>
       </c>
       <c r="U70">
-        <v>0.2158</v>
+        <v>0.2008</v>
       </c>
       <c r="V70">
-        <v>0.05565588568970136</v>
+        <v>0.05981344687170096</v>
       </c>
       <c r="W70">
-        <v>0.2037894598681625</v>
+        <v>0.1887894598681625</v>
       </c>
       <c r="X70" t="inlineStr">
         <is>
@@ -7059,7 +7193,7 @@
         </is>
       </c>
       <c r="Y70">
-        <v>0.2157204871693851</v>
+        <v>0.2318350653941897</v>
       </c>
       <c r="Z70">
         <v>0</v>
@@ -7070,13 +7204,13 @@
         <v>0.6900000000000001</v>
       </c>
       <c r="B71">
-        <v>0.1973509539217507</v>
+        <v>0.1868491238451577</v>
       </c>
       <c r="C71">
-        <v>-20276.21278878147</v>
+        <v>-19227.57947053607</v>
       </c>
       <c r="D71">
-        <v>14216.92521121854</v>
+        <v>15265.55852946394</v>
       </c>
       <c r="E71">
         <v>31103.03800000001</v>
@@ -7103,37 +7237,37 @@
         <v>1604</v>
       </c>
       <c r="M71">
-        <v>7544.894120400003</v>
+        <v>7020.457550400002</v>
       </c>
       <c r="N71">
-        <v>-5940.894120400003</v>
+        <v>-5416.457550400002</v>
       </c>
       <c r="O71">
-        <v>-1532.750683063201</v>
+        <v>-1397.446048003201</v>
       </c>
       <c r="P71">
-        <v>-4408.143437336802</v>
+        <v>-4019.011502396802</v>
       </c>
       <c r="Q71">
-        <v>-4101.743437336802</v>
+        <v>-3712.611502396802</v>
       </c>
       <c r="R71">
         <v>2.225806451612904</v>
       </c>
       <c r="S71">
-        <v>0.1826326490690329</v>
+        <v>0.1821428746284105</v>
       </c>
       <c r="T71">
-        <v>3.158075700728523</v>
+        <v>3.1487961807947</v>
       </c>
       <c r="U71">
-        <v>0.2158</v>
+        <v>0.2008</v>
       </c>
       <c r="V71">
-        <v>0.05484927865072017</v>
+        <v>0.05894658532283573</v>
       </c>
       <c r="W71">
-        <v>0.2039635256671746</v>
+        <v>0.1889635256671746</v>
       </c>
       <c r="X71" t="inlineStr">
         <is>
@@ -7141,7 +7275,7 @@
         </is>
       </c>
       <c r="Y71">
-        <v>0.2125941032973649</v>
+        <v>0.2284751369102159</v>
       </c>
       <c r="Z71">
         <v>0</v>
@@ -7152,13 +7286,13 @@
         <v>0.7000000000000001</v>
       </c>
       <c r="B72">
-        <v>0.1990509539217507</v>
+        <v>0.1883991238451577</v>
       </c>
       <c r="C72">
-        <v>-20940.62194975231</v>
+        <v>-19900.21247405585</v>
       </c>
       <c r="D72">
-        <v>14059.2180502477</v>
+        <v>15099.62752594416</v>
       </c>
       <c r="E72">
         <v>31609.74000000001</v>
@@ -7185,37 +7319,37 @@
         <v>1604</v>
       </c>
       <c r="M72">
-        <v>7654.240412000002</v>
+        <v>7122.203312000001</v>
       </c>
       <c r="N72">
-        <v>-6050.240412000002</v>
+        <v>-5518.203312000001</v>
       </c>
       <c r="O72">
-        <v>-1560.962026296</v>
+        <v>-1423.696454496</v>
       </c>
       <c r="P72">
-        <v>-4489.278385704001</v>
+        <v>-4094.506857504001</v>
       </c>
       <c r="Q72">
-        <v>-4182.878385704002</v>
+        <v>-3788.106857504001</v>
       </c>
       <c r="R72">
         <v>2.333333333333334</v>
       </c>
       <c r="S72">
-        <v>0.187193737371334</v>
+        <v>0.1866876371160242</v>
       </c>
       <c r="T72">
-        <v>3.263344890752807</v>
+        <v>3.253756053487857</v>
       </c>
       <c r="U72">
-        <v>0.2158</v>
+        <v>0.2008</v>
       </c>
       <c r="V72">
-        <v>0.05406571752713846</v>
+        <v>0.05810449124679522</v>
       </c>
       <c r="W72">
-        <v>0.2041326181576435</v>
+        <v>0.1891326181576435</v>
       </c>
       <c r="X72" t="inlineStr">
         <is>
@@ -7223,7 +7357,7 @@
         </is>
       </c>
       <c r="Y72">
-        <v>0.2095570446788312</v>
+        <v>0.2252112063829272</v>
       </c>
       <c r="Z72">
         <v>0</v>
@@ -7234,13 +7368,13 @@
         <v>0.71</v>
       </c>
       <c r="B73">
-        <v>0.2007509539217507</v>
+        <v>0.1899491238451577</v>
       </c>
       <c r="C73">
-        <v>-21601.57063285108</v>
+        <v>-20569.27704720859</v>
       </c>
       <c r="D73">
-        <v>13904.97136714893</v>
+        <v>14937.26495279141</v>
       </c>
       <c r="E73">
         <v>32116.442</v>
@@ -7267,37 +7401,37 @@
         <v>1604</v>
       </c>
       <c r="M73">
-        <v>7763.586703600002</v>
+        <v>7223.949073600001</v>
       </c>
       <c r="N73">
-        <v>-6159.586703600002</v>
+        <v>-5619.949073600001</v>
       </c>
       <c r="O73">
-        <v>-1589.173369528801</v>
+        <v>-1449.9468609888</v>
       </c>
       <c r="P73">
-        <v>-4570.413334071201</v>
+        <v>-4170.002212611201</v>
       </c>
       <c r="Q73">
-        <v>-4264.013334071202</v>
+        <v>-3863.602212611201</v>
       </c>
       <c r="R73">
         <v>2.448275862068965</v>
       </c>
       <c r="S73">
-        <v>0.1920693834875869</v>
+        <v>0.1915458314993354</v>
       </c>
       <c r="T73">
-        <v>3.375874024916696</v>
+        <v>3.365954538090886</v>
       </c>
       <c r="U73">
-        <v>0.2158</v>
+        <v>0.2008</v>
       </c>
       <c r="V73">
-        <v>0.05330422854788299</v>
+        <v>0.05728611813064318</v>
       </c>
       <c r="W73">
-        <v>0.2042969474793669</v>
+        <v>0.1892969474793668</v>
       </c>
       <c r="X73" t="inlineStr">
         <is>
@@ -7305,7 +7439,7 @@
         </is>
       </c>
       <c r="Y73">
-        <v>0.2066055370072984</v>
+        <v>0.2220392175606325</v>
       </c>
       <c r="Z73">
         <v>0</v>
@@ -7316,13 +7450,13 @@
         <v>0.72</v>
       </c>
       <c r="B74">
-        <v>0.2024509539217507</v>
+        <v>0.1914991238451577</v>
       </c>
       <c r="C74">
-        <v>-22259.17149897583</v>
+        <v>-21234.88707675469</v>
       </c>
       <c r="D74">
-        <v>13754.07250102417</v>
+        <v>14778.35692324531</v>
       </c>
       <c r="E74">
         <v>32623.144</v>
@@ -7349,37 +7483,37 @@
         <v>1604</v>
       </c>
       <c r="M74">
-        <v>7872.932995200001</v>
+        <v>7325.694835200001</v>
       </c>
       <c r="N74">
-        <v>-6268.932995200001</v>
+        <v>-5721.694835200001</v>
       </c>
       <c r="O74">
-        <v>-1617.3847127616</v>
+        <v>-1476.1972674816</v>
       </c>
       <c r="P74">
-        <v>-4651.548282438401</v>
+        <v>-4245.497567718401</v>
       </c>
       <c r="Q74">
-        <v>-4345.148282438401</v>
+        <v>-3939.097567718401</v>
       </c>
       <c r="R74">
         <v>2.571428571428571</v>
       </c>
       <c r="S74">
-        <v>0.197293290040715</v>
+        <v>0.1967510397671687</v>
       </c>
       <c r="T74">
-        <v>3.496440954378007</v>
+        <v>3.48616720016556</v>
       </c>
       <c r="U74">
-        <v>0.2158</v>
+        <v>0.2008</v>
       </c>
       <c r="V74">
-        <v>0.05256389204027351</v>
+        <v>0.05649047760105091</v>
       </c>
       <c r="W74">
-        <v>0.204456712097709</v>
+        <v>0.189456712097709</v>
       </c>
       <c r="X74" t="inlineStr">
         <is>
@@ -7387,7 +7521,7 @@
         </is>
       </c>
       <c r="Y74">
-        <v>0.2037360156599748</v>
+        <v>0.2189553395389571</v>
       </c>
       <c r="Z74">
         <v>0</v>
@@ -7398,13 +7532,13 @@
         <v>0.73</v>
       </c>
       <c r="B75">
-        <v>0.2041509539217507</v>
+        <v>0.1930491238451577</v>
       </c>
       <c r="C75">
-        <v>-22913.53237107391</v>
+        <v>-21897.15165419398</v>
       </c>
       <c r="D75">
-        <v>13606.41362892609</v>
+        <v>14622.79434580602</v>
       </c>
       <c r="E75">
         <v>33129.846</v>
@@ -7431,37 +7565,37 @@
         <v>1604</v>
       </c>
       <c r="M75">
-        <v>7982.279286800001</v>
+        <v>7427.4405968</v>
       </c>
       <c r="N75">
-        <v>-6378.279286800001</v>
+        <v>-5823.4405968</v>
       </c>
       <c r="O75">
-        <v>-1645.5960559944</v>
+        <v>-1502.4476739744</v>
       </c>
       <c r="P75">
-        <v>-4732.6832308056</v>
+        <v>-4320.992922825601</v>
       </c>
       <c r="Q75">
-        <v>-4426.2832308056</v>
+        <v>-4014.5929228256</v>
       </c>
       <c r="R75">
         <v>2.703703703703703</v>
       </c>
       <c r="S75">
-        <v>0.2029041526348155</v>
+        <v>0.2023418190178046</v>
       </c>
       <c r="T75">
-        <v>3.625938767503118</v>
+        <v>3.615284503875395</v>
       </c>
       <c r="U75">
-        <v>0.2158</v>
+        <v>0.2008</v>
       </c>
       <c r="V75">
-        <v>0.05184383872465333</v>
+        <v>0.05571663544213241</v>
       </c>
       <c r="W75">
-        <v>0.2046120996032198</v>
+        <v>0.1896120996032198</v>
       </c>
       <c r="X75" t="inlineStr">
         <is>
@@ -7469,7 +7603,7 @@
         </is>
       </c>
       <c r="Y75">
-        <v>0.2009451113358656</v>
+        <v>0.2159559513260946</v>
       </c>
       <c r="Z75">
         <v>0</v>
@@ -7480,13 +7614,13 @@
         <v>0.74</v>
       </c>
       <c r="B76">
-        <v>0.2282545953936157</v>
+        <v>0.1945991238451577</v>
       </c>
       <c r="C76">
-        <v>-25217.74522642948</v>
+        <v>-22556.17532552039</v>
       </c>
       <c r="D76">
-        <v>11808.90277357052</v>
+        <v>14470.47267447962</v>
       </c>
       <c r="E76">
         <v>33636.548</v>
@@ -7513,45 +7647,45 @@
         <v>1604</v>
       </c>
       <c r="M76">
-        <v>9216.504018400001</v>
+        <v>7529.186358400001</v>
       </c>
       <c r="N76">
-        <v>-7612.504018400001</v>
+        <v>-5925.186358400001</v>
       </c>
       <c r="O76">
-        <v>-1964.0260367472</v>
+        <v>-1528.6980804672</v>
       </c>
       <c r="P76">
-        <v>-5648.477981652801</v>
+        <v>-4396.488277932801</v>
       </c>
       <c r="Q76">
-        <v>-5342.077981652801</v>
+        <v>-4090.088277932801</v>
       </c>
       <c r="R76">
         <v>2.846153846153846</v>
       </c>
       <c r="S76">
-        <v>0.2097298564740969</v>
+        <v>0.2083626582107971</v>
       </c>
       <c r="T76">
-        <v>3.783474922666851</v>
+        <v>3.754333907870603</v>
       </c>
       <c r="U76">
-        <v>0.2458</v>
+        <v>0.2008</v>
       </c>
       <c r="V76">
-        <v>0.04490119020984726</v>
+        <v>0.05496370793615764</v>
       </c>
       <c r="W76">
-        <v>0.2347632874464196</v>
+        <v>0.1897632874464195</v>
       </c>
       <c r="X76" t="inlineStr">
         <is>
-          <t>D2/D</t>
+          <t>C2/C</t>
         </is>
       </c>
       <c r="Y76">
-        <v>0.1740356209684002</v>
+        <v>0.2130376276595257</v>
       </c>
       <c r="Z76">
         <v>0</v>
@@ -7562,13 +7696,13 @@
         <v>0.75</v>
       </c>
       <c r="B77">
-        <v>0.2302545953936157</v>
+        <v>0.1961491238451577</v>
       </c>
       <c r="C77">
-        <v>-25852.48852297047</v>
+        <v>-23212.05832552769</v>
       </c>
       <c r="D77">
-        <v>11680.86147702954</v>
+        <v>14321.29167447231</v>
       </c>
       <c r="E77">
         <v>34143.25</v>
@@ -7595,45 +7729,45 @@
         <v>1604</v>
       </c>
       <c r="M77">
-        <v>9341.051370000001</v>
+        <v>7630.93212</v>
       </c>
       <c r="N77">
-        <v>-7737.051370000001</v>
+        <v>-6026.93212</v>
       </c>
       <c r="O77">
-        <v>-1996.15925346</v>
+        <v>-1554.94848696</v>
       </c>
       <c r="P77">
-        <v>-5740.892116540001</v>
+        <v>-4471.98363304</v>
       </c>
       <c r="Q77">
-        <v>-5434.492116540001</v>
+        <v>-4165.583633040001</v>
       </c>
       <c r="R77">
         <v>3</v>
       </c>
       <c r="S77">
-        <v>0.2162870507330608</v>
+        <v>0.214865164539229</v>
       </c>
       <c r="T77">
-        <v>3.934813919573526</v>
+        <v>3.904507264185427</v>
       </c>
       <c r="U77">
-        <v>0.2458</v>
+        <v>0.2008</v>
       </c>
       <c r="V77">
-        <v>0.04430250767371596</v>
+        <v>0.05423085849700888</v>
       </c>
       <c r="W77">
-        <v>0.2349104436138006</v>
+        <v>0.1899104436138006</v>
       </c>
       <c r="X77" t="inlineStr">
         <is>
-          <t>D2/D</t>
+          <t>C2/C</t>
         </is>
       </c>
       <c r="Y77">
-        <v>0.1717151460221549</v>
+        <v>0.2101971259573987</v>
       </c>
       <c r="Z77">
         <v>0</v>
@@ -7644,13 +7778,13 @@
         <v>0.76</v>
       </c>
       <c r="B78">
-        <v>0.2322545953936157</v>
+        <v>0.1976991238451577</v>
       </c>
       <c r="C78">
-        <v>-26484.48495674262</v>
+        <v>-23864.89679777003</v>
       </c>
       <c r="D78">
-        <v>11555.56704325738</v>
+        <v>14175.15520222998</v>
       </c>
       <c r="E78">
         <v>34649.952</v>
@@ -7677,45 +7811,45 @@
         <v>1604</v>
       </c>
       <c r="M78">
-        <v>9465.598721600003</v>
+        <v>7732.677881600001</v>
       </c>
       <c r="N78">
-        <v>-7861.598721600003</v>
+        <v>-6128.677881600001</v>
       </c>
       <c r="O78">
-        <v>-2028.292470172801</v>
+        <v>-1581.1988934528</v>
       </c>
       <c r="P78">
-        <v>-5833.306251427202</v>
+        <v>-4547.478988147201</v>
       </c>
       <c r="Q78">
-        <v>-5526.906251427203</v>
+        <v>-4241.078988147201</v>
       </c>
       <c r="R78">
         <v>3.166666666666667</v>
       </c>
       <c r="S78">
-        <v>0.2233906778469384</v>
+        <v>0.2219095463950302</v>
       </c>
       <c r="T78">
-        <v>4.098764499555757</v>
+        <v>4.06719506685982</v>
       </c>
       <c r="U78">
-        <v>0.2458</v>
+        <v>0.2008</v>
       </c>
       <c r="V78">
-        <v>0.04371957994116706</v>
+        <v>0.05351729456941665</v>
       </c>
       <c r="W78">
-        <v>0.2350537272504612</v>
+        <v>0.1900537272504611</v>
       </c>
       <c r="X78" t="inlineStr">
         <is>
-          <t>D2/D</t>
+          <t>C2/C</t>
         </is>
       </c>
       <c r="Y78">
-        <v>0.1694557362060739</v>
+        <v>0.2074313743000645</v>
       </c>
       <c r="Z78">
         <v>0</v>
@@ -7726,13 +7860,13 @@
         <v>0.77</v>
       </c>
       <c r="B79">
-        <v>0.2342545953936157</v>
+        <v>0.1992491238451577</v>
       </c>
       <c r="C79">
-        <v>-27113.82198210904</v>
+        <v>-24514.78300119127</v>
       </c>
       <c r="D79">
-        <v>11432.93201789097</v>
+        <v>14031.97099880874</v>
       </c>
       <c r="E79">
         <v>35156.654</v>
@@ -7759,45 +7893,45 @@
         <v>1604</v>
       </c>
       <c r="M79">
-        <v>9590.146073200001</v>
+        <v>7834.423643200001</v>
       </c>
       <c r="N79">
-        <v>-7986.146073200001</v>
+        <v>-6230.423643200001</v>
       </c>
       <c r="O79">
-        <v>-2060.4256868856</v>
+        <v>-1607.4492999456</v>
       </c>
       <c r="P79">
-        <v>-5925.7203863144</v>
+        <v>-4622.9743432544</v>
       </c>
       <c r="Q79">
-        <v>-5619.320386314401</v>
+        <v>-4316.5743432544</v>
       </c>
       <c r="R79">
         <v>3.347826086956522</v>
       </c>
       <c r="S79">
-        <v>0.2311120116663704</v>
+        <v>0.2295664831948142</v>
       </c>
       <c r="T79">
-        <v>4.276971651710354</v>
+        <v>4.244029634984161</v>
       </c>
       <c r="U79">
-        <v>0.2458</v>
+        <v>0.2008</v>
       </c>
       <c r="V79">
-        <v>0.04315179318868437</v>
+        <v>0.05282226476981384</v>
       </c>
       <c r="W79">
-        <v>0.2351932892342214</v>
+        <v>0.1901932892342214</v>
       </c>
       <c r="X79" t="inlineStr">
         <is>
-          <t>D2/D</t>
+          <t>C2/C</t>
         </is>
       </c>
       <c r="Y79">
-        <v>0.1672550123592418</v>
+        <v>0.2047374603481157</v>
       </c>
       <c r="Z79">
         <v>0</v>
@@ -7808,13 +7942,13 @@
         <v>0.78</v>
       </c>
       <c r="B80">
-        <v>0.2362545953936157</v>
+        <v>0.2007991238451577</v>
       </c>
       <c r="C80">
-        <v>-27740.5833799331</v>
+        <v>-25161.8055043567</v>
       </c>
       <c r="D80">
-        <v>11312.8726200669</v>
+        <v>13891.6504956433</v>
       </c>
       <c r="E80">
         <v>35663.356</v>
@@ -7841,45 +7975,45 @@
         <v>1604</v>
       </c>
       <c r="M80">
-        <v>9714.693424800002</v>
+        <v>7936.169404800001</v>
       </c>
       <c r="N80">
-        <v>-8110.693424800002</v>
+        <v>-6332.169404800001</v>
       </c>
       <c r="O80">
-        <v>-2092.5589035984</v>
+        <v>-1633.6997064384</v>
       </c>
       <c r="P80">
-        <v>-6018.134521201601</v>
+        <v>-4698.4696983616</v>
       </c>
       <c r="Q80">
-        <v>-5711.734521201602</v>
+        <v>-4392.069698361601</v>
       </c>
       <c r="R80">
         <v>3.545454545454546</v>
       </c>
       <c r="S80">
-        <v>0.2395352849239328</v>
+        <v>0.2379195051582148</v>
       </c>
       <c r="T80">
-        <v>4.471379454060825</v>
+        <v>4.436940072937985</v>
       </c>
       <c r="U80">
-        <v>0.2458</v>
+        <v>0.2008</v>
       </c>
       <c r="V80">
-        <v>0.04259856507088073</v>
+        <v>0.05214505624712392</v>
       </c>
       <c r="W80">
-        <v>0.2353292727055775</v>
+        <v>0.1903292727055775</v>
       </c>
       <c r="X80" t="inlineStr">
         <is>
-          <t>D2/D</t>
+          <t>C2/C</t>
         </is>
       </c>
       <c r="Y80">
-        <v>0.1651107173289951</v>
+        <v>0.2021126211128834</v>
       </c>
       <c r="Z80">
         <v>0</v>
@@ -7890,13 +8024,13 @@
         <v>0.79</v>
       </c>
       <c r="B81">
-        <v>0.2382545953936157</v>
+        <v>0.2302651103018525</v>
       </c>
       <c r="C81">
-        <v>-28364.84944845461</v>
+        <v>-27887.524340093</v>
       </c>
       <c r="D81">
-        <v>11195.3085515454</v>
+        <v>11672.633659907</v>
       </c>
       <c r="E81">
         <v>36170.058</v>
@@ -7923,37 +8057,37 @@
         <v>1604</v>
       </c>
       <c r="M81">
-        <v>9839.240776400002</v>
+        <v>9438.946196400002</v>
       </c>
       <c r="N81">
-        <v>-8235.240776400002</v>
+        <v>-7834.946196400002</v>
       </c>
       <c r="O81">
-        <v>-2124.692120311201</v>
+        <v>-2021.416118671201</v>
       </c>
       <c r="P81">
-        <v>-6110.548656088801</v>
+        <v>-5813.530077728801</v>
       </c>
       <c r="Q81">
-        <v>-5804.148656088802</v>
+        <v>-5507.130077728802</v>
       </c>
       <c r="R81">
         <v>3.761904761904763</v>
       </c>
       <c r="S81">
-        <v>0.2487607746822153</v>
+        <v>0.248334655197629</v>
       </c>
       <c r="T81">
-        <v>4.684302285206579</v>
+        <v>4.677474715880576</v>
       </c>
       <c r="U81">
-        <v>0.2458</v>
+        <v>0.2358</v>
       </c>
       <c r="V81">
-        <v>0.04205934272821135</v>
+        <v>0.04384302986681234</v>
       </c>
       <c r="W81">
-        <v>0.2354618135574057</v>
+        <v>0.2254618135574057</v>
       </c>
       <c r="X81" t="inlineStr">
         <is>
@@ -7961,7 +8095,7 @@
         </is>
       </c>
       <c r="Y81">
-        <v>0.1630207082488812</v>
+        <v>0.1699342242899703</v>
       </c>
       <c r="Z81">
         <v>0</v>
@@ -7972,13 +8106,13 @@
         <v>0.8</v>
       </c>
       <c r="B82">
-        <v>0.2402545953936157</v>
+        <v>0.2321651103018526</v>
       </c>
       <c r="C82">
-        <v>-28986.69718238683</v>
+        <v>-28513.2293225606</v>
       </c>
       <c r="D82">
-        <v>11080.16281761318</v>
+        <v>11553.63067743941</v>
       </c>
       <c r="E82">
         <v>36676.76</v>
@@ -8005,37 +8139,37 @@
         <v>1604</v>
       </c>
       <c r="M82">
-        <v>9963.788128000002</v>
+        <v>9558.426528000002</v>
       </c>
       <c r="N82">
-        <v>-8359.788128000002</v>
+        <v>-7954.426528000002</v>
       </c>
       <c r="O82">
-        <v>-2156.825337024</v>
+        <v>-2052.242044224</v>
       </c>
       <c r="P82">
-        <v>-6202.962790976002</v>
+        <v>-5902.184483776002</v>
       </c>
       <c r="Q82">
-        <v>-5896.562790976002</v>
+        <v>-5595.784483776002</v>
       </c>
       <c r="R82">
         <v>4.000000000000001</v>
       </c>
       <c r="S82">
-        <v>0.258908813416326</v>
+        <v>0.2584613879575104</v>
       </c>
       <c r="T82">
-        <v>4.918517399466908</v>
+        <v>4.911348451674605</v>
       </c>
       <c r="U82">
-        <v>0.2458</v>
+        <v>0.2358</v>
       </c>
       <c r="V82">
-        <v>0.0415336009441087</v>
+        <v>0.04329499199347719</v>
       </c>
       <c r="W82">
-        <v>0.2355910408879381</v>
+        <v>0.2255910408879381</v>
       </c>
       <c r="X82" t="inlineStr">
         <is>
@@ -8043,7 +8177,7 @@
         </is>
       </c>
       <c r="Y82">
-        <v>0.1609829493957702</v>
+        <v>0.1678100464863457</v>
       </c>
       <c r="Z82">
         <v>0</v>
@@ -8054,13 +8188,13 @@
         <v>0.8100000000000001</v>
       </c>
       <c r="B83">
-        <v>0.2422545953936157</v>
+        <v>0.2340651103018525</v>
       </c>
       <c r="C83">
-        <v>-29606.20044107374</v>
+        <v>-29136.53231279155</v>
       </c>
       <c r="D83">
-        <v>10967.36155892628</v>
+        <v>11437.02968720846</v>
       </c>
       <c r="E83">
         <v>37183.46200000001</v>
@@ -8087,37 +8221,37 @@
         <v>1604</v>
       </c>
       <c r="M83">
-        <v>10088.3354796</v>
+        <v>9677.906859600002</v>
       </c>
       <c r="N83">
-        <v>-8484.335479600002</v>
+        <v>-8073.906859600002</v>
       </c>
       <c r="O83">
-        <v>-2188.958553736801</v>
+        <v>-2083.067969776801</v>
       </c>
       <c r="P83">
-        <v>-6295.376925863202</v>
+        <v>-5990.838889823201</v>
       </c>
       <c r="Q83">
-        <v>-5988.976925863202</v>
+        <v>-5684.438889823201</v>
       </c>
       <c r="R83">
         <v>4.263157894736843</v>
       </c>
       <c r="S83">
-        <v>0.2701250667540274</v>
+        <v>0.2696540925868531</v>
       </c>
       <c r="T83">
-        <v>5.177386736280956</v>
+        <v>5.169840475446954</v>
       </c>
       <c r="U83">
-        <v>0.2458</v>
+        <v>0.2358</v>
       </c>
       <c r="V83">
-        <v>0.04102084043862588</v>
+        <v>0.04276048591948364</v>
       </c>
       <c r="W83">
-        <v>0.2357170774201858</v>
+        <v>0.2257170774201858</v>
       </c>
       <c r="X83" t="inlineStr">
         <is>
@@ -8125,7 +8259,7 @@
         </is>
       </c>
       <c r="Y83">
-        <v>0.1589955055760693</v>
+        <v>0.1657383175173784</v>
       </c>
       <c r="Z83">
         <v>0</v>
@@ -8136,13 +8270,13 @@
         <v>0.8200000000000001</v>
       </c>
       <c r="B84">
-        <v>0.2442545953936157</v>
+        <v>0.2359651103018526</v>
       </c>
       <c r="C84">
-        <v>-30223.43010647925</v>
+        <v>-29757.50530798727</v>
       </c>
       <c r="D84">
-        <v>10856.83389352076</v>
+        <v>11322.75869201273</v>
       </c>
       <c r="E84">
         <v>37690.164</v>
@@ -8169,37 +8303,37 @@
         <v>1604</v>
       </c>
       <c r="M84">
-        <v>10212.8828312</v>
+        <v>9797.387191200001</v>
       </c>
       <c r="N84">
-        <v>-8608.882831200002</v>
+        <v>-8193.387191200001</v>
       </c>
       <c r="O84">
-        <v>-2221.091770449601</v>
+        <v>-2113.893895329601</v>
       </c>
       <c r="P84">
-        <v>-6387.791060750402</v>
+        <v>-6079.493295870401</v>
       </c>
       <c r="Q84">
-        <v>-6081.391060750402</v>
+        <v>-5773.093295870402</v>
       </c>
       <c r="R84">
         <v>4.555555555555557</v>
       </c>
       <c r="S84">
-        <v>0.2825875704625845</v>
+        <v>0.2820904310639005</v>
       </c>
       <c r="T84">
-        <v>5.46501933274101</v>
+        <v>5.457053835194007</v>
       </c>
       <c r="U84">
-        <v>0.2458</v>
+        <v>0.2358</v>
       </c>
       <c r="V84">
-        <v>0.04052058628693533</v>
+        <v>0.04223901657900214</v>
       </c>
       <c r="W84">
-        <v>0.2358400398906713</v>
+        <v>0.2258400398906713</v>
       </c>
       <c r="X84" t="inlineStr">
         <is>
@@ -8207,7 +8341,7 @@
         </is>
       </c>
       <c r="Y84">
-        <v>0.1570565359958733</v>
+        <v>0.1637171185232641</v>
       </c>
       <c r="Z84">
         <v>0</v>
@@ -8218,13 +8352,13 @@
         <v>0.8300000000000001</v>
       </c>
       <c r="B85">
-        <v>0.2462545953936157</v>
+        <v>0.2378651103018525</v>
       </c>
       <c r="C85">
-        <v>-30838.45423171866</v>
+        <v>-30376.21745642607</v>
       </c>
       <c r="D85">
-        <v>10748.51176828135</v>
+        <v>11210.74854357394</v>
       </c>
       <c r="E85">
         <v>38196.86600000001</v>
@@ -8251,37 +8385,37 @@
         <v>1604</v>
       </c>
       <c r="M85">
-        <v>10337.4301828</v>
+        <v>9916.867522800003</v>
       </c>
       <c r="N85">
-        <v>-8733.430182800003</v>
+        <v>-8312.867522800003</v>
       </c>
       <c r="O85">
-        <v>-2253.224987162401</v>
+        <v>-2144.719820882401</v>
       </c>
       <c r="P85">
-        <v>-6480.205195637602</v>
+        <v>-6168.147701917602</v>
       </c>
       <c r="Q85">
-        <v>-6173.805195637602</v>
+        <v>-5861.747701917602</v>
       </c>
       <c r="R85">
         <v>4.882352941176473</v>
       </c>
       <c r="S85">
-        <v>0.2965162510780306</v>
+        <v>0.2959898681853064</v>
       </c>
       <c r="T85">
-        <v>5.786491058196363</v>
+        <v>5.778057001970125</v>
       </c>
       <c r="U85">
-        <v>0.2458</v>
+        <v>0.2358</v>
       </c>
       <c r="V85">
-        <v>0.04003238645215297</v>
+        <v>0.04173011276479728</v>
       </c>
       <c r="W85">
-        <v>0.2359600394100608</v>
+        <v>0.2259600394100608</v>
       </c>
       <c r="X85" t="inlineStr">
         <is>
@@ -8289,7 +8423,7 @@
         </is>
       </c>
       <c r="Y85">
-        <v>0.1551642885742364</v>
+        <v>0.1617446231193693</v>
       </c>
       <c r="Z85">
         <v>0</v>
@@ -8300,13 +8434,13 @@
         <v>0.84</v>
       </c>
       <c r="B86">
-        <v>0.2482545953936157</v>
+        <v>0.2397651103018525</v>
       </c>
       <c r="C86">
-        <v>-31451.33818078613</v>
+        <v>-30992.73519699735</v>
       </c>
       <c r="D86">
-        <v>10642.32981921387</v>
+        <v>11100.93280300265</v>
       </c>
       <c r="E86">
         <v>38703.568</v>
@@ -8333,37 +8467,37 @@
         <v>1604</v>
       </c>
       <c r="M86">
-        <v>10461.9775344</v>
+        <v>10036.3478544</v>
       </c>
       <c r="N86">
-        <v>-8857.977534400001</v>
+        <v>-8432.347854400001</v>
       </c>
       <c r="O86">
-        <v>-2285.3582038752</v>
+        <v>-2175.5457464352</v>
       </c>
       <c r="P86">
-        <v>-6572.619330524801</v>
+        <v>-6256.802107964801</v>
       </c>
       <c r="Q86">
-        <v>-6266.219330524801</v>
+        <v>-5950.402107964801</v>
       </c>
       <c r="R86">
         <v>5.249999999999999</v>
       </c>
       <c r="S86">
-        <v>0.3121860167704075</v>
+        <v>0.3116267349468879</v>
       </c>
       <c r="T86">
-        <v>6.148146749333634</v>
+        <v>6.139185564593255</v>
       </c>
       <c r="U86">
-        <v>0.2458</v>
+        <v>0.2358</v>
       </c>
       <c r="V86">
-        <v>0.03955581042296068</v>
+        <v>0.04123332570807352</v>
       </c>
       <c r="W86">
-        <v>0.2360771817980363</v>
+        <v>0.2260771817980363</v>
       </c>
       <c r="X86" t="inlineStr">
         <is>
@@ -8371,7 +8505,7 @@
         </is>
       </c>
       <c r="Y86">
-        <v>0.1533170946626383</v>
+        <v>0.1598190918917578</v>
       </c>
       <c r="Z86">
         <v>0</v>
@@ -8382,13 +8516,13 @@
         <v>0.85</v>
       </c>
       <c r="B87">
-        <v>0.2502545953936157</v>
+        <v>0.2416651103018526</v>
       </c>
       <c r="C87">
-        <v>-32062.14476008136</v>
+        <v>-31607.12239061454</v>
       </c>
       <c r="D87">
-        <v>10538.22523991865</v>
+        <v>10993.24760938547</v>
       </c>
       <c r="E87">
         <v>39210.27</v>
@@ -8415,37 +8549,37 @@
         <v>1604</v>
       </c>
       <c r="M87">
-        <v>10586.524886</v>
+        <v>10155.828186</v>
       </c>
       <c r="N87">
-        <v>-8982.524886000003</v>
+        <v>-8551.828186000002</v>
       </c>
       <c r="O87">
-        <v>-2317.491420588001</v>
+        <v>-2206.371671988001</v>
       </c>
       <c r="P87">
-        <v>-6665.033465412002</v>
+        <v>-6345.456514012001</v>
       </c>
       <c r="Q87">
-        <v>-6358.633465412002</v>
+        <v>-6039.056514012002</v>
       </c>
       <c r="R87">
         <v>5.666666666666666</v>
       </c>
       <c r="S87">
-        <v>0.3299450845551014</v>
+        <v>0.3293485172766805</v>
       </c>
       <c r="T87">
-        <v>6.55802319928921</v>
+        <v>6.548464602232805</v>
       </c>
       <c r="U87">
-        <v>0.2458</v>
+        <v>0.2358</v>
       </c>
       <c r="V87">
-        <v>0.03909044794739643</v>
+        <v>0.04074822775856676</v>
       </c>
       <c r="W87">
-        <v>0.23619156789453</v>
+        <v>0.22619156789453</v>
       </c>
       <c r="X87" t="inlineStr">
         <is>
@@ -8453,7 +8587,7 @@
         </is>
       </c>
       <c r="Y87">
-        <v>0.1515133641371954</v>
+        <v>0.1579388672812665</v>
       </c>
       <c r="Z87">
         <v>0</v>
@@ -8464,13 +8598,13 @@
         <v>0.86</v>
       </c>
       <c r="B88">
-        <v>0.2522545953936157</v>
+        <v>0.2435651103018525</v>
       </c>
       <c r="C88">
-        <v>-32670.93434229116</v>
+        <v>-32219.44044405263</v>
       </c>
       <c r="D88">
-        <v>10436.13765770884</v>
+        <v>10887.63155594738</v>
       </c>
       <c r="E88">
         <v>39716.972</v>
@@ -8497,37 +8631,37 @@
         <v>1604</v>
       </c>
       <c r="M88">
-        <v>10711.0722376</v>
+        <v>10275.3085176</v>
       </c>
       <c r="N88">
-        <v>-9107.072237600001</v>
+        <v>-8671.3085176</v>
       </c>
       <c r="O88">
-        <v>-2349.6246373008</v>
+        <v>-2237.1975975408</v>
       </c>
       <c r="P88">
-        <v>-6757.447600299201</v>
+        <v>-6434.1109200592</v>
       </c>
       <c r="Q88">
-        <v>-6451.047600299202</v>
+        <v>-6127.7109200592</v>
       </c>
       <c r="R88">
         <v>6.142857142857142</v>
       </c>
       <c r="S88">
-        <v>0.3502411620233228</v>
+        <v>0.3496019827964433</v>
       </c>
       <c r="T88">
-        <v>7.026453427809868</v>
+        <v>7.016212073820863</v>
       </c>
       <c r="U88">
-        <v>0.2458</v>
+        <v>0.2358</v>
       </c>
       <c r="V88">
-        <v>0.03863590785498484</v>
+        <v>0.04027441115672296</v>
       </c>
       <c r="W88">
-        <v>0.2363032938492448</v>
+        <v>0.2263032938492447</v>
       </c>
       <c r="X88" t="inlineStr">
         <is>
@@ -8535,7 +8669,7 @@
         </is>
       </c>
       <c r="Y88">
-        <v>0.1497515808332746</v>
+        <v>0.1561023688245077</v>
       </c>
       <c r="Z88">
         <v>0</v>
@@ -8546,13 +8680,13 @@
         <v>0.87</v>
       </c>
       <c r="B89">
-        <v>0.2542545953936157</v>
+        <v>0.2454651103018525</v>
       </c>
       <c r="C89">
-        <v>-33277.7649831398</v>
+        <v>-32829.74842671544</v>
       </c>
       <c r="D89">
-        <v>10336.0090168602</v>
+        <v>10784.02557328457</v>
       </c>
       <c r="E89">
         <v>40223.674</v>
@@ -8579,37 +8713,37 @@
         <v>1604</v>
       </c>
       <c r="M89">
-        <v>10835.6195892</v>
+        <v>10394.7888492</v>
       </c>
       <c r="N89">
-        <v>-9231.619589200001</v>
+        <v>-8790.7888492</v>
       </c>
       <c r="O89">
-        <v>-2381.757854013601</v>
+        <v>-2268.0235230936</v>
       </c>
       <c r="P89">
-        <v>-6849.861735186401</v>
+        <v>-6522.765326106401</v>
       </c>
       <c r="Q89">
-        <v>-6543.461735186402</v>
+        <v>-6216.365326106401</v>
       </c>
       <c r="R89">
         <v>6.692307692307692</v>
       </c>
       <c r="S89">
-        <v>0.3736597129481938</v>
+        <v>0.3729713660884775</v>
       </c>
       <c r="T89">
-        <v>7.566949845333703</v>
+        <v>7.555920694884006</v>
       </c>
       <c r="U89">
-        <v>0.2458</v>
+        <v>0.2358</v>
       </c>
       <c r="V89">
-        <v>0.03819181696009996</v>
+        <v>0.03981148689055374</v>
       </c>
       <c r="W89">
-        <v>0.2364124513912075</v>
+        <v>0.2264124513912074</v>
       </c>
       <c r="X89" t="inlineStr">
         <is>
@@ -8617,7 +8751,7 @@
         </is>
       </c>
       <c r="Y89">
-        <v>0.1480302982949611</v>
+        <v>0.1543080887230766</v>
       </c>
       <c r="Z89">
         <v>0</v>
@@ -8628,13 +8762,13 @@
         <v>0.88</v>
       </c>
       <c r="B90">
-        <v>0.2562545953936157</v>
+        <v>0.2473651103018525</v>
       </c>
       <c r="C90">
-        <v>-33882.69253148223</v>
+        <v>-33438.10318079851</v>
       </c>
       <c r="D90">
-        <v>10237.78346851777</v>
+        <v>10682.3728192015</v>
       </c>
       <c r="E90">
         <v>40730.376</v>
@@ -8661,37 +8795,37 @@
         <v>1604</v>
       </c>
       <c r="M90">
-        <v>10960.1669408</v>
+        <v>10514.2691808</v>
       </c>
       <c r="N90">
-        <v>-9356.166940800002</v>
+        <v>-8910.269180800002</v>
       </c>
       <c r="O90">
-        <v>-2413.8910707264</v>
+        <v>-2298.849448646401</v>
       </c>
       <c r="P90">
-        <v>-6942.275870073601</v>
+        <v>-6611.419732153601</v>
       </c>
       <c r="Q90">
-        <v>-6635.875870073602</v>
+        <v>-6305.019732153602</v>
       </c>
       <c r="R90">
         <v>7.333333333333334</v>
       </c>
       <c r="S90">
-        <v>0.4009813556938767</v>
+        <v>0.4002356465958506</v>
       </c>
       <c r="T90">
-        <v>8.197528999111514</v>
+        <v>8.185580752791006</v>
       </c>
       <c r="U90">
-        <v>0.2458</v>
+        <v>0.2358</v>
       </c>
       <c r="V90">
-        <v>0.03775781904009883</v>
+        <v>0.03935908363043381</v>
       </c>
       <c r="W90">
-        <v>0.2365191280799437</v>
+        <v>0.2265191280799437</v>
       </c>
       <c r="X90" t="inlineStr">
         <is>
@@ -8699,7 +8833,7 @@
         </is>
       </c>
       <c r="Y90">
-        <v>0.1463481358143366</v>
+        <v>0.1525545877148597</v>
       </c>
       <c r="Z90">
         <v>0</v>
@@ -8710,13 +8844,13 @@
         <v>0.89</v>
       </c>
       <c r="B91">
-        <v>0.2582545953936157</v>
+        <v>0.2492651103018525</v>
       </c>
       <c r="C91">
-        <v>-34485.77073317888</v>
+        <v>-34044.55942527988</v>
       </c>
       <c r="D91">
-        <v>10141.40726682112</v>
+        <v>10582.61857472013</v>
       </c>
       <c r="E91">
         <v>41237.078</v>
@@ -8743,37 +8877,37 @@
         <v>1604</v>
       </c>
       <c r="M91">
-        <v>11084.7142924</v>
+        <v>10633.7495124</v>
       </c>
       <c r="N91">
-        <v>-9480.714292400002</v>
+        <v>-9029.749512400002</v>
       </c>
       <c r="O91">
-        <v>-2446.024287439201</v>
+        <v>-2329.675374199201</v>
       </c>
       <c r="P91">
-        <v>-7034.690004960801</v>
+        <v>-6700.074138200801</v>
       </c>
       <c r="Q91">
-        <v>-6728.290004960802</v>
+        <v>-6393.674138200801</v>
       </c>
       <c r="R91">
         <v>8.090909090909092</v>
       </c>
       <c r="S91">
-        <v>0.4332705698478655</v>
+        <v>0.4324570690136552</v>
       </c>
       <c r="T91">
-        <v>8.94275890812165</v>
+        <v>8.92972445759019</v>
       </c>
       <c r="U91">
-        <v>0.2458</v>
+        <v>0.2358</v>
       </c>
       <c r="V91">
-        <v>0.03733357388234491</v>
+        <v>0.03891684673570983</v>
       </c>
       <c r="W91">
-        <v>0.2366234075397196</v>
+        <v>0.2266234075397196</v>
       </c>
       <c r="X91" t="inlineStr">
         <is>
@@ -8781,7 +8915,7 @@
         </is>
       </c>
       <c r="Y91">
-        <v>0.144703774737771</v>
+        <v>0.1508404912236815</v>
       </c>
       <c r="Z91">
         <v>0</v>
@@ -8792,13 +8926,13 @@
         <v>0.9</v>
       </c>
       <c r="B92">
-        <v>0.2602545953936157</v>
+        <v>0.2511651103018526</v>
       </c>
       <c r="C92">
-        <v>-35087.05132915821</v>
+        <v>-34649.16985413821</v>
       </c>
       <c r="D92">
-        <v>10046.8286708418</v>
+        <v>10484.7101458618</v>
       </c>
       <c r="E92">
         <v>41743.78000000001</v>
@@ -8825,37 +8959,37 @@
         <v>1604</v>
       </c>
       <c r="M92">
-        <v>11209.261644</v>
+        <v>10753.229844</v>
       </c>
       <c r="N92">
-        <v>-9605.261644000002</v>
+        <v>-9149.229844000001</v>
       </c>
       <c r="O92">
-        <v>-2478.157504152</v>
+        <v>-2360.501299752</v>
       </c>
       <c r="P92">
-        <v>-7127.104139848001</v>
+        <v>-6788.728544248001</v>
       </c>
       <c r="Q92">
-        <v>-6820.704139848001</v>
+        <v>-6482.328544248001</v>
       </c>
       <c r="R92">
         <v>9.000000000000002</v>
       </c>
       <c r="S92">
-        <v>0.4720176268326521</v>
+        <v>0.4711227759150208</v>
       </c>
       <c r="T92">
-        <v>9.837034798933816</v>
+        <v>9.822696903349211</v>
       </c>
       <c r="U92">
-        <v>0.2458</v>
+        <v>0.2358</v>
       </c>
       <c r="V92">
-        <v>0.0369187563947633</v>
+        <v>0.03848443732753528</v>
       </c>
       <c r="W92">
-        <v>0.2367253696781672</v>
+        <v>0.2267253696781672</v>
       </c>
       <c r="X92" t="inlineStr">
         <is>
@@ -8863,7 +8997,7 @@
         </is>
       </c>
       <c r="Y92">
-        <v>0.1430959550184624</v>
+        <v>0.1491644857656406</v>
       </c>
       <c r="Z92">
         <v>0</v>
@@ -8874,13 +9008,13 @@
         <v>0.91</v>
       </c>
       <c r="B93">
-        <v>0.2622545953936157</v>
+        <v>0.2530651103018525</v>
       </c>
       <c r="C93">
-        <v>-35686.58414804262</v>
+        <v>-35251.98522916849</v>
       </c>
       <c r="D93">
-        <v>9953.997851957385</v>
+        <v>10388.59677083151</v>
       </c>
       <c r="E93">
         <v>42250.482</v>
@@ -8907,37 +9041,37 @@
         <v>1604</v>
       </c>
       <c r="M93">
-        <v>11333.8089956</v>
+        <v>10872.7101756</v>
       </c>
       <c r="N93">
-        <v>-9729.808995600002</v>
+        <v>-9268.710175600001</v>
       </c>
       <c r="O93">
-        <v>-2510.290720864801</v>
+        <v>-2391.3272253048</v>
       </c>
       <c r="P93">
-        <v>-7219.518274735201</v>
+        <v>-6877.382950295201</v>
       </c>
       <c r="Q93">
-        <v>-6913.118274735201</v>
+        <v>-6570.982950295202</v>
       </c>
       <c r="R93">
         <v>10.11111111111111</v>
       </c>
       <c r="S93">
-        <v>0.519375140925169</v>
+        <v>0.5183808621278009</v>
       </c>
       <c r="T93">
-        <v>10.93003866548202</v>
+        <v>10.91410767038801</v>
       </c>
       <c r="U93">
-        <v>0.2458</v>
+        <v>0.2358</v>
       </c>
       <c r="V93">
-        <v>0.03651305577504062</v>
+        <v>0.03806153142283709</v>
       </c>
       <c r="W93">
-        <v>0.236825090890495</v>
+        <v>0.226825090890495</v>
       </c>
       <c r="X93" t="inlineStr">
         <is>
@@ -8945,7 +9079,7 @@
         </is>
       </c>
       <c r="Y93">
-        <v>0.1415234719962815</v>
+        <v>0.1475253155923918</v>
       </c>
       <c r="Z93">
         <v>0</v>
@@ -8956,13 +9090,13 @@
         <v>0.92</v>
       </c>
       <c r="B94">
-        <v>0.2642545953936157</v>
+        <v>0.2549651103018525</v>
       </c>
       <c r="C94">
-        <v>-36284.41719368643</v>
+        <v>-35853.05446773947</v>
       </c>
       <c r="D94">
-        <v>9862.866806313577</v>
+        <v>10294.22953226053</v>
       </c>
       <c r="E94">
         <v>42757.184</v>
@@ -8989,37 +9123,37 @@
         <v>1604</v>
       </c>
       <c r="M94">
-        <v>11458.3563472</v>
+        <v>10992.1905072</v>
       </c>
       <c r="N94">
-        <v>-9854.356347200002</v>
+        <v>-9388.190507200001</v>
       </c>
       <c r="O94">
-        <v>-2542.423937577601</v>
+        <v>-2422.1531508576</v>
       </c>
       <c r="P94">
-        <v>-7311.932409622402</v>
+        <v>-6966.0373563424</v>
       </c>
       <c r="Q94">
-        <v>-7005.532409622402</v>
+        <v>-6659.6373563424</v>
       </c>
       <c r="R94">
         <v>11.50000000000001</v>
       </c>
       <c r="S94">
-        <v>0.5785720335408153</v>
+        <v>0.5774534698937761</v>
       </c>
       <c r="T94">
-        <v>12.29629349866728</v>
+        <v>12.27837112918652</v>
       </c>
       <c r="U94">
-        <v>0.2458</v>
+        <v>0.2358</v>
       </c>
       <c r="V94">
-        <v>0.03611617473400758</v>
+        <v>0.03764781912476278</v>
       </c>
       <c r="W94">
-        <v>0.236922644250381</v>
+        <v>0.2269226442503809</v>
       </c>
       <c r="X94" t="inlineStr">
         <is>
@@ -9027,7 +9161,7 @@
         </is>
       </c>
       <c r="Y94">
-        <v>0.1399851733876263</v>
+        <v>0.1459217795533441</v>
       </c>
       <c r="Z94">
         <v>0</v>
@@ -9038,13 +9172,13 @@
         <v>0.93</v>
       </c>
       <c r="B95">
-        <v>0.2662545953936157</v>
+        <v>0.2568651103018526</v>
       </c>
       <c r="C95">
-        <v>-36880.5967279488</v>
+        <v>-36452.42472581076</v>
       </c>
       <c r="D95">
-        <v>9773.389272051214</v>
+        <v>10201.56127418925</v>
       </c>
       <c r="E95">
         <v>43263.88600000001</v>
@@ -9071,37 +9205,37 @@
         <v>1604</v>
       </c>
       <c r="M95">
-        <v>11582.9036988</v>
+        <v>11111.6708388</v>
       </c>
       <c r="N95">
-        <v>-9978.903698800003</v>
+        <v>-9507.670838800002</v>
       </c>
       <c r="O95">
-        <v>-2574.557154290401</v>
+        <v>-2452.979076410401</v>
       </c>
       <c r="P95">
-        <v>-7404.346544509602</v>
+        <v>-7054.691762389602</v>
       </c>
       <c r="Q95">
-        <v>-7097.946544509602</v>
+        <v>-6748.291762389602</v>
       </c>
       <c r="R95">
         <v>13.2857142857143</v>
       </c>
       <c r="S95">
-        <v>0.6546823240466462</v>
+        <v>0.653403965592887</v>
       </c>
       <c r="T95">
-        <v>14.05290685561975</v>
+        <v>14.03242414764174</v>
       </c>
       <c r="U95">
-        <v>0.2458</v>
+        <v>0.2358</v>
       </c>
       <c r="V95">
-        <v>0.03572782876912577</v>
+        <v>0.03724300386535671</v>
       </c>
       <c r="W95">
-        <v>0.2370180996885489</v>
+        <v>0.2270180996885489</v>
       </c>
       <c r="X95" t="inlineStr">
         <is>
@@ -9109,7 +9243,7 @@
         </is>
       </c>
       <c r="Y95">
-        <v>0.1384799564694797</v>
+        <v>0.1443527281602973</v>
       </c>
       <c r="Z95">
         <v>0</v>
@@ -9120,13 +9254,13 @@
         <v>0.9400000000000001</v>
       </c>
       <c r="B96">
-        <v>0.2682545953936157</v>
+        <v>0.2587651103018526</v>
       </c>
       <c r="C96">
-        <v>-37475.16734900162</v>
+        <v>-37050.14147650624</v>
       </c>
       <c r="D96">
-        <v>9685.520650998385</v>
+        <v>10110.54652349377</v>
       </c>
       <c r="E96">
         <v>43770.588</v>
@@ -9153,37 +9287,37 @@
         <v>1604</v>
       </c>
       <c r="M96">
-        <v>11707.4510504</v>
+        <v>11231.1511704</v>
       </c>
       <c r="N96">
-        <v>-10103.4510504</v>
+        <v>-9627.151170400002</v>
       </c>
       <c r="O96">
-        <v>-2606.690371003201</v>
+        <v>-2483.805001963201</v>
       </c>
       <c r="P96">
-        <v>-7496.760679396803</v>
+        <v>-7143.346168436801</v>
       </c>
       <c r="Q96">
-        <v>-7190.360679396803</v>
+        <v>-6836.946168436802</v>
       </c>
       <c r="R96">
         <v>15.66666666666668</v>
       </c>
       <c r="S96">
-        <v>0.7561627113877538</v>
+        <v>0.7546712931917017</v>
       </c>
       <c r="T96">
-        <v>16.39505799822304</v>
+        <v>16.37116150558203</v>
       </c>
       <c r="U96">
-        <v>0.2458</v>
+        <v>0.2358</v>
       </c>
       <c r="V96">
-        <v>0.03534774548434784</v>
+        <v>0.03684680169657633</v>
       </c>
       <c r="W96">
-        <v>0.2371115241599473</v>
+        <v>0.2271115241599473</v>
       </c>
       <c r="X96" t="inlineStr">
         <is>
@@ -9191,7 +9325,7 @@
         </is>
       </c>
       <c r="Y96">
-        <v>0.1370067654432087</v>
+        <v>0.1428170608394431</v>
       </c>
       <c r="Z96">
         <v>0</v>
@@ -9202,13 +9336,13 @@
         <v>0.9500000000000001</v>
       </c>
       <c r="B97">
-        <v>0.2702545953936157</v>
+        <v>0.2606651103018526</v>
       </c>
       <c r="C97">
-        <v>-38068.17206545093</v>
+        <v>-37646.24858451867</v>
       </c>
       <c r="D97">
-        <v>9599.217934549088</v>
+        <v>10021.14141548134</v>
       </c>
       <c r="E97">
         <v>44277.29000000001</v>
@@ -9235,37 +9369,37 @@
         <v>1604</v>
       </c>
       <c r="M97">
-        <v>11831.998402</v>
+        <v>11350.631502</v>
       </c>
       <c r="N97">
-        <v>-10227.998402</v>
+        <v>-9746.631502000002</v>
       </c>
       <c r="O97">
-        <v>-2638.823587716001</v>
+        <v>-2514.630927516001</v>
       </c>
       <c r="P97">
-        <v>-7589.174814284002</v>
+        <v>-7232.000574484002</v>
       </c>
       <c r="Q97">
-        <v>-7282.774814284003</v>
+        <v>-6925.600574484002</v>
       </c>
       <c r="R97">
         <v>19.00000000000003</v>
       </c>
       <c r="S97">
-        <v>0.8982352536653051</v>
+        <v>0.8964455518300425</v>
       </c>
       <c r="T97">
-        <v>19.67406959786766</v>
+        <v>19.64539380669844</v>
       </c>
       <c r="U97">
-        <v>0.2458</v>
+        <v>0.2358</v>
       </c>
       <c r="V97">
-        <v>0.03497566395293365</v>
+        <v>0.03645894062608605</v>
       </c>
       <c r="W97">
-        <v>0.2372029818003689</v>
+        <v>0.2272029818003689</v>
       </c>
       <c r="X97" t="inlineStr">
         <is>
@@ -9273,7 +9407,7 @@
         </is>
       </c>
       <c r="Y97">
-        <v>0.1355645889648591</v>
+        <v>0.1413137233569227</v>
       </c>
       <c r="Z97">
         <v>0</v>
@@ -9284,13 +9418,13 @@
         <v>0.96</v>
       </c>
       <c r="B98">
-        <v>0.2722545953936156</v>
+        <v>0.2625651103018525</v>
       </c>
       <c r="C98">
-        <v>-38659.65236653032</v>
+        <v>-38240.78837660106</v>
       </c>
       <c r="D98">
-        <v>9514.439633469674</v>
+        <v>9933.303623398935</v>
       </c>
       <c r="E98">
         <v>44783.992</v>
@@ -9317,37 +9451,37 @@
         <v>1604</v>
       </c>
       <c r="M98">
-        <v>11956.5457536</v>
+        <v>11470.1118336</v>
       </c>
       <c r="N98">
-        <v>-10352.5457536</v>
+        <v>-9866.1118336</v>
       </c>
       <c r="O98">
-        <v>-2670.9568044288</v>
+        <v>-2545.4568530688</v>
       </c>
       <c r="P98">
-        <v>-7681.588949171201</v>
+        <v>-7320.6549805312</v>
       </c>
       <c r="Q98">
-        <v>-7375.188949171201</v>
+        <v>-7014.2549805312</v>
       </c>
       <c r="R98">
         <v>23.99999999999998</v>
       </c>
       <c r="S98">
-        <v>1.111344067081629</v>
+        <v>1.109106939787551</v>
       </c>
       <c r="T98">
-        <v>24.59258699733451</v>
+        <v>24.556742258373</v>
       </c>
       <c r="U98">
-        <v>0.2458</v>
+        <v>0.2358</v>
       </c>
       <c r="V98">
-        <v>0.0346113341200906</v>
+        <v>0.03607915999456433</v>
       </c>
       <c r="W98">
-        <v>0.2372925340732817</v>
+        <v>0.2272925340732817</v>
       </c>
       <c r="X98" t="inlineStr">
         <is>
@@ -9355,7 +9489,7 @@
         </is>
       </c>
       <c r="Y98">
-        <v>0.1341524578298084</v>
+        <v>0.1398417054052881</v>
       </c>
       <c r="Z98">
         <v>0</v>
@@ -9366,13 +9500,13 @@
         <v>0.97</v>
       </c>
       <c r="B99">
-        <v>0.2742545953936157</v>
+        <v>0.2644651103018525</v>
       </c>
       <c r="C99">
-        <v>-39249.64828860774</v>
+        <v>-38833.80170838328</v>
       </c>
       <c r="D99">
-        <v>9431.14571139227</v>
+        <v>9846.992291616723</v>
       </c>
       <c r="E99">
         <v>45290.694</v>
@@ -9399,37 +9533,37 @@
         <v>1604</v>
       </c>
       <c r="M99">
-        <v>12081.0931052</v>
+        <v>11589.5921652</v>
       </c>
       <c r="N99">
-        <v>-10477.0931052</v>
+        <v>-9985.592165200002</v>
       </c>
       <c r="O99">
-        <v>-2703.090021141601</v>
+        <v>-2576.2827786216</v>
       </c>
       <c r="P99">
-        <v>-7774.0030840584</v>
+        <v>-7409.309386578401</v>
       </c>
       <c r="Q99">
-        <v>-7467.603084058401</v>
+        <v>-7102.909386578402</v>
       </c>
       <c r="R99">
         <v>32.33333333333331</v>
       </c>
       <c r="S99">
-        <v>1.466525422775505</v>
+        <v>1.463542586383401</v>
       </c>
       <c r="T99">
-        <v>32.79011599644602</v>
+        <v>32.742323011164</v>
       </c>
       <c r="U99">
-        <v>0.2458</v>
+        <v>0.2358</v>
       </c>
       <c r="V99">
-        <v>0.03425451624256388</v>
+        <v>0.03570720989152758</v>
       </c>
       <c r="W99">
-        <v>0.2373802399075778</v>
+        <v>0.2273802399075778</v>
       </c>
       <c r="X99" t="inlineStr">
         <is>
@@ -9437,7 +9571,7 @@
         </is>
       </c>
       <c r="Y99">
-        <v>0.1327694428006352</v>
+        <v>0.1384000383392542</v>
       </c>
       <c r="Z99">
         <v>0</v>
@@ -9448,13 +9582,13 @@
         <v>0.98</v>
       </c>
       <c r="B100">
-        <v>0.2762545953936156</v>
+        <v>0.2663651103018526</v>
       </c>
       <c r="C100">
-        <v>-39838.19847822863</v>
+        <v>-39425.32802773491</v>
       </c>
       <c r="D100">
-        <v>9349.297521771376</v>
+        <v>9762.167972265092</v>
       </c>
       <c r="E100">
         <v>45797.396</v>
@@ -9481,37 +9615,37 @@
         <v>1604</v>
       </c>
       <c r="M100">
-        <v>12205.6404568</v>
+        <v>11709.0724968</v>
       </c>
       <c r="N100">
-        <v>-10601.6404568</v>
+        <v>-10105.0724968</v>
       </c>
       <c r="O100">
-        <v>-2735.2232378544</v>
+        <v>-2607.1087041744</v>
       </c>
       <c r="P100">
-        <v>-7866.417218945601</v>
+        <v>-7497.963792625601</v>
       </c>
       <c r="Q100">
-        <v>-7560.017218945602</v>
+        <v>-7191.563792625601</v>
       </c>
       <c r="R100">
         <v>48.99999999999996</v>
       </c>
       <c r="S100">
-        <v>2.176888134163258</v>
+        <v>2.172413879575102</v>
       </c>
       <c r="T100">
-        <v>49.18517399466903</v>
+        <v>49.11348451674601</v>
       </c>
       <c r="U100">
-        <v>0.2458</v>
+        <v>0.2358</v>
       </c>
       <c r="V100">
-        <v>0.03390498036253772</v>
+        <v>0.03534285060692016</v>
       </c>
       <c r="W100">
-        <v>0.2374661558268882</v>
+        <v>0.2274661558268883</v>
       </c>
       <c r="X100" t="inlineStr">
         <is>
@@ -9519,7 +9653,7 @@
         </is>
       </c>
       <c r="Y100">
-        <v>0.1314146525679757</v>
+        <v>0.1369877930500781</v>
       </c>
       <c r="Z100">
         <v>0</v>
@@ -9530,13 +9664,13 @@
         <v>0.99</v>
       </c>
       <c r="B101">
-        <v>0.2782545953936157</v>
+        <v>0.2682651103018525</v>
       </c>
       <c r="C101">
-        <v>-40425.34025190521</v>
+        <v>-40015.4054348814</v>
       </c>
       <c r="D101">
-        <v>9268.857748094797</v>
+        <v>9678.792565118611</v>
       </c>
       <c r="E101">
         <v>46304.09800000001</v>
@@ -9563,37 +9697,37 @@
         <v>1604</v>
       </c>
       <c r="M101">
-        <v>12330.1878084</v>
+        <v>11828.5528284</v>
       </c>
       <c r="N101">
-        <v>-10726.1878084</v>
+        <v>-10224.5528284</v>
       </c>
       <c r="O101">
-        <v>-2767.356454567201</v>
+        <v>-2637.934629727201</v>
       </c>
       <c r="P101">
-        <v>-7958.831353832801</v>
+        <v>-7586.618198672802</v>
       </c>
       <c r="Q101">
-        <v>-7652.431353832802</v>
+        <v>-7280.218198672803</v>
       </c>
       <c r="R101">
         <v>98.99999999999991</v>
       </c>
       <c r="S101">
-        <v>4.307976268326516</v>
+        <v>4.299027759150203</v>
       </c>
       <c r="T101">
-        <v>98.37034798933806</v>
+        <v>98.226969033492</v>
       </c>
       <c r="U101">
-        <v>0.2458</v>
+        <v>0.2358</v>
       </c>
       <c r="V101">
-        <v>0.03356250581342118</v>
+        <v>0.03498585211594116</v>
       </c>
       <c r="W101">
-        <v>0.2375503360710611</v>
+        <v>0.2275503360710611</v>
       </c>
       <c r="X101" t="inlineStr">
         <is>
@@ -9601,7 +9735,7 @@
         </is>
       </c>
       <c r="Y101">
-        <v>0.1300872318349658</v>
+        <v>0.1356040779687642</v>
       </c>
       <c r="Z101">
         <v>0</v>

--- a/research/traditional_assets/database/data/netherlands/netherlands_entertainment.xlsx
+++ b/research/traditional_assets/database/data/netherlands/netherlands_entertainment.xlsx
@@ -1406,7 +1406,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:Z101"/>
+  <dimension ref="A1:Z100"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -1543,22 +1543,22 @@
     </row>
     <row r="2">
       <c r="A2">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="B2">
-        <v>0.08985827989162551</v>
+        <v>0.08965983552950513</v>
       </c>
       <c r="C2">
-        <v>49340.7870595104</v>
+        <v>49055.20470025494</v>
       </c>
       <c r="D2">
-        <v>48871.48705951039</v>
+        <v>49092.60670025494</v>
       </c>
       <c r="E2">
-        <v>-3859.4</v>
+        <v>-3352.698</v>
       </c>
       <c r="F2">
-        <v>0</v>
+        <v>506.7020000000001</v>
       </c>
       <c r="G2">
         <v>469.3</v>
@@ -1579,28 +1579,28 @@
         <v>1604</v>
       </c>
       <c r="M2">
-        <v>0</v>
+        <v>25.4871106</v>
       </c>
       <c r="N2">
-        <v>1604</v>
+        <v>1578.5128894</v>
       </c>
       <c r="O2">
-        <v>413.832</v>
+        <v>407.2563254652</v>
       </c>
       <c r="P2">
-        <v>1190.168</v>
+        <v>1171.2565639348</v>
       </c>
       <c r="Q2">
-        <v>1496.568</v>
+        <v>1477.6565639348</v>
       </c>
       <c r="R2">
-        <v>0</v>
+        <v>0.0101010101010101</v>
       </c>
       <c r="S2">
-        <v>0.08985827989162551</v>
+        <v>0.09018849447424759</v>
       </c>
       <c r="T2">
-        <v>1.017512237681883</v>
+        <v>1.025138440513801</v>
       </c>
       <c r="U2">
         <v>0.0503</v>
@@ -1617,7 +1617,7 @@
         </is>
       </c>
       <c r="Y2">
-        <v>10000000</v>
+        <v>62.93377170811979</v>
       </c>
       <c r="Z2">
         <v>0</v>
@@ -1625,22 +1625,22 @@
     </row>
     <row r="3">
       <c r="A3">
-        <v>0.01</v>
+        <v>0.02</v>
       </c>
       <c r="B3">
-        <v>0.08965983552950513</v>
+        <v>0.08946139116738472</v>
       </c>
       <c r="C3">
-        <v>49055.20470025494</v>
+        <v>48771.63235235676</v>
       </c>
       <c r="D3">
-        <v>49092.60670025494</v>
+        <v>49315.73635235676</v>
       </c>
       <c r="E3">
-        <v>-3352.698</v>
+        <v>-2845.996</v>
       </c>
       <c r="F3">
-        <v>506.7020000000001</v>
+        <v>1013.404</v>
       </c>
       <c r="G3">
         <v>469.3</v>
@@ -1661,28 +1661,28 @@
         <v>1604</v>
       </c>
       <c r="M3">
-        <v>25.4871106</v>
+        <v>50.9742212</v>
       </c>
       <c r="N3">
-        <v>1578.5128894</v>
+        <v>1553.0257788</v>
       </c>
       <c r="O3">
-        <v>407.2563254652</v>
+        <v>400.6806509304</v>
       </c>
       <c r="P3">
-        <v>1171.2565639348</v>
+        <v>1152.3451278696</v>
       </c>
       <c r="Q3">
-        <v>1477.6565639348</v>
+        <v>1458.7451278696</v>
       </c>
       <c r="R3">
-        <v>0.0101010101010101</v>
+        <v>0.02040816326530612</v>
       </c>
       <c r="S3">
-        <v>0.09018849447424759</v>
+        <v>0.09052544812998442</v>
       </c>
       <c r="T3">
-        <v>1.025138440513801</v>
+        <v>1.032920280138208</v>
       </c>
       <c r="U3">
         <v>0.0503</v>
@@ -1699,7 +1699,7 @@
         </is>
       </c>
       <c r="Y3">
-        <v>62.93377170811979</v>
+        <v>31.46688585405989</v>
       </c>
       <c r="Z3">
         <v>0</v>
@@ -1707,22 +1707,22 @@
     </row>
     <row r="4">
       <c r="A4">
-        <v>0.02</v>
+        <v>0.03</v>
       </c>
       <c r="B4">
-        <v>0.08946139116738472</v>
+        <v>0.08926294680526432</v>
       </c>
       <c r="C4">
-        <v>48771.63235235676</v>
+        <v>48490.09754791736</v>
       </c>
       <c r="D4">
-        <v>49315.73635235676</v>
+        <v>49540.90354791736</v>
       </c>
       <c r="E4">
-        <v>-2845.996</v>
+        <v>-2339.294</v>
       </c>
       <c r="F4">
-        <v>1013.404</v>
+        <v>1520.106</v>
       </c>
       <c r="G4">
         <v>469.3</v>
@@ -1743,28 +1743,28 @@
         <v>1604</v>
       </c>
       <c r="M4">
-        <v>50.9742212</v>
+        <v>76.4613318</v>
       </c>
       <c r="N4">
-        <v>1553.0257788</v>
+        <v>1527.5386682</v>
       </c>
       <c r="O4">
-        <v>400.6806509304</v>
+        <v>394.1049763956</v>
       </c>
       <c r="P4">
-        <v>1152.3451278696</v>
+        <v>1133.4336918044</v>
       </c>
       <c r="Q4">
-        <v>1458.7451278696</v>
+        <v>1439.8336918044</v>
       </c>
       <c r="R4">
-        <v>0.02040816326530612</v>
+        <v>0.03092783505154639</v>
       </c>
       <c r="S4">
-        <v>0.09052544812998442</v>
+        <v>0.09086934928377766</v>
       </c>
       <c r="T4">
-        <v>1.032920280138208</v>
+        <v>1.040862570064149</v>
       </c>
       <c r="U4">
         <v>0.0503</v>
@@ -1781,7 +1781,7 @@
         </is>
       </c>
       <c r="Y4">
-        <v>31.46688585405989</v>
+        <v>20.9779239027066</v>
       </c>
       <c r="Z4">
         <v>0</v>
@@ -1789,22 +1789,22 @@
     </row>
     <row r="5">
       <c r="A5">
-        <v>0.03</v>
+        <v>0.04</v>
       </c>
       <c r="B5">
-        <v>0.08926294680526432</v>
+        <v>0.08906450244314394</v>
       </c>
       <c r="C5">
-        <v>48490.09754791736</v>
+        <v>48210.62832417207</v>
       </c>
       <c r="D5">
-        <v>49540.90354791736</v>
+        <v>49768.13632417206</v>
       </c>
       <c r="E5">
-        <v>-2339.294</v>
+        <v>-1832.592</v>
       </c>
       <c r="F5">
-        <v>1520.106</v>
+        <v>2026.808</v>
       </c>
       <c r="G5">
         <v>469.3</v>
@@ -1825,28 +1825,28 @@
         <v>1604</v>
       </c>
       <c r="M5">
-        <v>76.4613318</v>
+        <v>101.9484424</v>
       </c>
       <c r="N5">
-        <v>1527.5386682</v>
+        <v>1502.0515576</v>
       </c>
       <c r="O5">
-        <v>394.1049763956</v>
+        <v>387.5293018608</v>
       </c>
       <c r="P5">
-        <v>1133.4336918044</v>
+        <v>1114.5222557392</v>
       </c>
       <c r="Q5">
-        <v>1439.8336918044</v>
+        <v>1420.9222557392</v>
       </c>
       <c r="R5">
-        <v>0.03092783505154639</v>
+        <v>0.04166666666666667</v>
       </c>
       <c r="S5">
-        <v>0.09086934928377766</v>
+        <v>0.09122041504494161</v>
       </c>
       <c r="T5">
-        <v>1.040862570064149</v>
+        <v>1.048970324363548</v>
       </c>
       <c r="U5">
         <v>0.0503</v>
@@ -1863,7 +1863,7 @@
         </is>
       </c>
       <c r="Y5">
-        <v>20.9779239027066</v>
+        <v>15.73344292702995</v>
       </c>
       <c r="Z5">
         <v>0</v>
@@ -1871,22 +1871,22 @@
     </row>
     <row r="6">
       <c r="A6">
-        <v>0.04</v>
+        <v>0.05</v>
       </c>
       <c r="B6">
-        <v>0.08906450244314394</v>
+        <v>0.08886605808102353</v>
       </c>
       <c r="C6">
-        <v>48210.62832417207</v>
+        <v>47933.25323512805</v>
       </c>
       <c r="D6">
-        <v>49768.13632417206</v>
+        <v>49997.46323512805</v>
       </c>
       <c r="E6">
-        <v>-1832.592</v>
+        <v>-1325.89</v>
       </c>
       <c r="F6">
-        <v>2026.808</v>
+        <v>2533.51</v>
       </c>
       <c r="G6">
         <v>469.3</v>
@@ -1907,28 +1907,28 @@
         <v>1604</v>
       </c>
       <c r="M6">
-        <v>101.9484424</v>
+        <v>127.435553</v>
       </c>
       <c r="N6">
-        <v>1502.0515576</v>
+        <v>1476.564447</v>
       </c>
       <c r="O6">
-        <v>387.5293018608</v>
+        <v>380.953627326</v>
       </c>
       <c r="P6">
-        <v>1114.5222557392</v>
+        <v>1095.610819674</v>
       </c>
       <c r="Q6">
-        <v>1420.9222557392</v>
+        <v>1402.010819674</v>
       </c>
       <c r="R6">
-        <v>0.04166666666666667</v>
+        <v>0.05263157894736843</v>
       </c>
       <c r="S6">
-        <v>0.09122041504494161</v>
+        <v>0.09157887166423531</v>
       </c>
       <c r="T6">
-        <v>1.048970324363548</v>
+        <v>1.057248768227144</v>
       </c>
       <c r="U6">
         <v>0.0503</v>
@@ -1945,7 +1945,7 @@
         </is>
       </c>
       <c r="Y6">
-        <v>15.73344292702995</v>
+        <v>12.58675434162396</v>
       </c>
       <c r="Z6">
         <v>0</v>
@@ -1953,22 +1953,22 @@
     </row>
     <row r="7">
       <c r="A7">
-        <v>0.05</v>
+        <v>0.06</v>
       </c>
       <c r="B7">
-        <v>0.08886605808102353</v>
+        <v>0.08866761371890315</v>
       </c>
       <c r="C7">
-        <v>47933.25323512805</v>
+        <v>47658.00136352549</v>
       </c>
       <c r="D7">
-        <v>49997.46323512805</v>
+        <v>50228.91336352549</v>
       </c>
       <c r="E7">
-        <v>-1325.89</v>
+        <v>-819.1879999999996</v>
       </c>
       <c r="F7">
-        <v>2533.51</v>
+        <v>3040.212</v>
       </c>
       <c r="G7">
         <v>469.3</v>
@@ -1989,28 +1989,28 @@
         <v>1604</v>
       </c>
       <c r="M7">
-        <v>127.435553</v>
+        <v>152.9226636</v>
       </c>
       <c r="N7">
-        <v>1476.564447</v>
+        <v>1451.0773364</v>
       </c>
       <c r="O7">
-        <v>380.953627326</v>
+        <v>374.3779527912</v>
       </c>
       <c r="P7">
-        <v>1095.610819674</v>
+        <v>1076.6993836088</v>
       </c>
       <c r="Q7">
-        <v>1402.010819674</v>
+        <v>1383.0993836088</v>
       </c>
       <c r="R7">
-        <v>0.05263157894736843</v>
+        <v>0.06382978723404256</v>
       </c>
       <c r="S7">
-        <v>0.09157887166423531</v>
+        <v>0.09194495502010974</v>
       </c>
       <c r="T7">
-        <v>1.057248768227144</v>
+        <v>1.06570334919422</v>
       </c>
       <c r="U7">
         <v>0.0503</v>
@@ -2027,7 +2027,7 @@
         </is>
       </c>
       <c r="Y7">
-        <v>12.58675434162396</v>
+        <v>10.4889619513533</v>
       </c>
       <c r="Z7">
         <v>0</v>
@@ -2035,22 +2035,22 @@
     </row>
     <row r="8">
       <c r="A8">
-        <v>0.06</v>
+        <v>0.06999999999999999</v>
       </c>
       <c r="B8">
-        <v>0.08866761371890315</v>
+        <v>0.08846916935678276</v>
       </c>
       <c r="C8">
-        <v>47658.00136352549</v>
+        <v>47384.90233313289</v>
       </c>
       <c r="D8">
-        <v>50228.91336352549</v>
+        <v>50462.51633313288</v>
       </c>
       <c r="E8">
-        <v>-819.1880000000001</v>
+        <v>-312.4860000000003</v>
       </c>
       <c r="F8">
-        <v>3040.212</v>
+        <v>3546.914</v>
       </c>
       <c r="G8">
         <v>469.3</v>
@@ -2071,28 +2071,28 @@
         <v>1604</v>
       </c>
       <c r="M8">
-        <v>152.9226636</v>
+        <v>178.4097742</v>
       </c>
       <c r="N8">
-        <v>1451.0773364</v>
+        <v>1425.5902258</v>
       </c>
       <c r="O8">
-        <v>374.3779527912</v>
+        <v>367.8022782564</v>
       </c>
       <c r="P8">
-        <v>1076.6993836088</v>
+        <v>1057.7879475436</v>
       </c>
       <c r="Q8">
-        <v>1383.0993836088</v>
+        <v>1364.1879475436</v>
       </c>
       <c r="R8">
-        <v>0.06382978723404255</v>
+        <v>0.07526881720430106</v>
       </c>
       <c r="S8">
-        <v>0.09194495502010974</v>
+        <v>0.09231891113632554</v>
       </c>
       <c r="T8">
-        <v>1.06570334919422</v>
+        <v>1.074339749106826</v>
       </c>
       <c r="U8">
         <v>0.0503</v>
@@ -2109,7 +2109,7 @@
         </is>
       </c>
       <c r="Y8">
-        <v>10.4889619513533</v>
+        <v>8.990538815445685</v>
       </c>
       <c r="Z8">
         <v>0</v>
@@ -2117,22 +2117,22 @@
     </row>
     <row r="9">
       <c r="A9">
-        <v>0.07000000000000001</v>
+        <v>0.08</v>
       </c>
       <c r="B9">
-        <v>0.08846916935678274</v>
+        <v>0.08835976499466237</v>
       </c>
       <c r="C9">
-        <v>47384.90233313291</v>
+        <v>47007.91955059351</v>
       </c>
       <c r="D9">
-        <v>50462.5163331329</v>
+        <v>50592.23555059351</v>
       </c>
       <c r="E9">
-        <v>-312.4859999999994</v>
+        <v>194.2160000000003</v>
       </c>
       <c r="F9">
-        <v>3546.914000000001</v>
+        <v>4053.616</v>
       </c>
       <c r="G9">
         <v>469.3</v>
@@ -2153,45 +2153,45 @@
         <v>1604</v>
       </c>
       <c r="M9">
-        <v>178.4097742</v>
+        <v>209.9773088</v>
       </c>
       <c r="N9">
-        <v>1425.5902258</v>
+        <v>1394.0226912</v>
       </c>
       <c r="O9">
-        <v>367.8022782564</v>
+        <v>359.6578543296</v>
       </c>
       <c r="P9">
-        <v>1057.7879475436</v>
+        <v>1034.3648368704</v>
       </c>
       <c r="Q9">
-        <v>1364.1879475436</v>
+        <v>1340.7648368704</v>
       </c>
       <c r="R9">
-        <v>0.07526881720430109</v>
+        <v>0.08695652173913043</v>
       </c>
       <c r="S9">
-        <v>0.09231891113632554</v>
+        <v>0.09270099673332866</v>
       </c>
       <c r="T9">
-        <v>1.074339749106826</v>
+        <v>1.083163896843618</v>
       </c>
       <c r="U9">
-        <v>0.0503</v>
+        <v>0.0518</v>
       </c>
       <c r="V9">
         <v>0.258</v>
       </c>
       <c r="W9">
-        <v>0.0373226</v>
+        <v>0.0384356</v>
       </c>
       <c r="X9" t="inlineStr">
         <is>
-          <t>Aaa/AAA</t>
+          <t>Aa2/AA</t>
         </is>
       </c>
       <c r="Y9">
-        <v>8.990538815445685</v>
+        <v>7.638920648934423</v>
       </c>
       <c r="Z9">
         <v>0</v>
@@ -2199,22 +2199,22 @@
     </row>
     <row r="10">
       <c r="A10">
-        <v>0.08</v>
+        <v>0.09</v>
       </c>
       <c r="B10">
-        <v>0.08835976499466237</v>
+        <v>0.08817245063254198</v>
       </c>
       <c r="C10">
-        <v>47007.91955059351</v>
+        <v>46724.86881902231</v>
       </c>
       <c r="D10">
-        <v>50592.23555059351</v>
+        <v>50815.88681902231</v>
       </c>
       <c r="E10">
-        <v>194.2160000000003</v>
+        <v>700.9180000000001</v>
       </c>
       <c r="F10">
-        <v>4053.616</v>
+        <v>4560.318</v>
       </c>
       <c r="G10">
         <v>469.3</v>
@@ -2235,28 +2235,28 @@
         <v>1604</v>
       </c>
       <c r="M10">
-        <v>209.9773088</v>
+        <v>236.2244724</v>
       </c>
       <c r="N10">
-        <v>1394.0226912</v>
+        <v>1367.7755276</v>
       </c>
       <c r="O10">
-        <v>359.6578543296</v>
+        <v>352.8860861208</v>
       </c>
       <c r="P10">
-        <v>1034.3648368704</v>
+        <v>1014.8894414792</v>
       </c>
       <c r="Q10">
-        <v>1340.7648368704</v>
+        <v>1321.2894414792</v>
       </c>
       <c r="R10">
-        <v>0.08695652173913043</v>
+        <v>0.0989010989010989</v>
       </c>
       <c r="S10">
-        <v>0.09270099673332866</v>
+        <v>0.09309147981598019</v>
       </c>
       <c r="T10">
-        <v>1.083163896843618</v>
+        <v>1.092181981893307</v>
       </c>
       <c r="U10">
         <v>0.0518</v>
@@ -2273,7 +2273,7 @@
         </is>
       </c>
       <c r="Y10">
-        <v>7.638920648934423</v>
+        <v>6.790151687941711</v>
       </c>
       <c r="Z10">
         <v>0</v>
@@ -2281,22 +2281,22 @@
     </row>
     <row r="11">
       <c r="A11">
-        <v>0.09</v>
+        <v>0.09999999999999999</v>
       </c>
       <c r="B11">
-        <v>0.08817245063254198</v>
+        <v>0.08811127627042156</v>
       </c>
       <c r="C11">
-        <v>46724.86881902231</v>
+        <v>46291.63729157126</v>
       </c>
       <c r="D11">
-        <v>50815.88681902231</v>
+        <v>50889.35729157125</v>
       </c>
       <c r="E11">
-        <v>700.9180000000001</v>
+        <v>1207.62</v>
       </c>
       <c r="F11">
-        <v>4560.318</v>
+        <v>5067.02</v>
       </c>
       <c r="G11">
         <v>469.3</v>
@@ -2317,45 +2317,45 @@
         <v>1604</v>
       </c>
       <c r="M11">
-        <v>236.2244724</v>
+        <v>271.08557</v>
       </c>
       <c r="N11">
-        <v>1367.7755276</v>
+        <v>1332.91443</v>
       </c>
       <c r="O11">
-        <v>352.8860861208</v>
+        <v>343.89192294</v>
       </c>
       <c r="P11">
-        <v>1014.8894414792</v>
+        <v>989.02250706</v>
       </c>
       <c r="Q11">
-        <v>1321.2894414792</v>
+        <v>1295.42250706</v>
       </c>
       <c r="R11">
-        <v>0.0989010989010989</v>
+        <v>0.1111111111111111</v>
       </c>
       <c r="S11">
-        <v>0.09309147981598019</v>
+        <v>0.09349064030046841</v>
       </c>
       <c r="T11">
-        <v>1.092181981893307</v>
+        <v>1.101400468832989</v>
       </c>
       <c r="U11">
-        <v>0.0518</v>
+        <v>0.0535</v>
       </c>
       <c r="V11">
         <v>0.258</v>
       </c>
       <c r="W11">
-        <v>0.0384356</v>
+        <v>0.039697</v>
       </c>
       <c r="X11" t="inlineStr">
         <is>
-          <t>Aa2/AA</t>
+          <t>A1/A+</t>
         </is>
       </c>
       <c r="Y11">
-        <v>6.790151687941711</v>
+        <v>5.91695087274472</v>
       </c>
       <c r="Z11">
         <v>0</v>
@@ -2363,22 +2363,22 @@
     </row>
     <row r="12">
       <c r="A12">
-        <v>0.1</v>
+        <v>0.11</v>
       </c>
       <c r="B12">
-        <v>0.08811127627042156</v>
+        <v>0.08800187190830119</v>
       </c>
       <c r="C12">
-        <v>46291.63729157126</v>
+        <v>45916.86113801942</v>
       </c>
       <c r="D12">
-        <v>50889.35729157125</v>
+        <v>51021.28313801942</v>
       </c>
       <c r="E12">
-        <v>1207.62</v>
+        <v>1714.322000000001</v>
       </c>
       <c r="F12">
-        <v>5067.02</v>
+        <v>5573.722000000001</v>
       </c>
       <c r="G12">
         <v>469.3</v>
@@ -2399,45 +2399,45 @@
         <v>1604</v>
       </c>
       <c r="M12">
-        <v>271.08557</v>
+        <v>302.6531046000001</v>
       </c>
       <c r="N12">
-        <v>1332.91443</v>
+        <v>1301.3468954</v>
       </c>
       <c r="O12">
-        <v>343.89192294</v>
+        <v>335.7474990132</v>
       </c>
       <c r="P12">
-        <v>989.02250706</v>
+        <v>965.5993963868</v>
       </c>
       <c r="Q12">
-        <v>1295.42250706</v>
+        <v>1271.9993963868</v>
       </c>
       <c r="R12">
-        <v>0.1111111111111111</v>
+        <v>0.1235955056179775</v>
       </c>
       <c r="S12">
-        <v>0.09349064030046841</v>
+        <v>0.09389877068348448</v>
       </c>
       <c r="T12">
-        <v>1.101400468832989</v>
+        <v>1.110826112782551</v>
       </c>
       <c r="U12">
-        <v>0.0535</v>
+        <v>0.0543</v>
       </c>
       <c r="V12">
         <v>0.258</v>
       </c>
       <c r="W12">
-        <v>0.039697</v>
+        <v>0.0402906</v>
       </c>
       <c r="X12" t="inlineStr">
         <is>
-          <t>A1/A+</t>
+          <t>A2/A</t>
         </is>
       </c>
       <c r="Y12">
-        <v>5.91695087274472</v>
+        <v>5.299796947795789</v>
       </c>
       <c r="Z12">
         <v>0</v>
@@ -2445,22 +2445,22 @@
     </row>
     <row r="13">
       <c r="A13">
-        <v>0.11</v>
+        <v>0.12</v>
       </c>
       <c r="B13">
-        <v>0.08800187190830119</v>
+        <v>0.0878331075461808</v>
       </c>
       <c r="C13">
-        <v>45916.86113801942</v>
+        <v>45615.01133206412</v>
       </c>
       <c r="D13">
-        <v>51021.28313801942</v>
+        <v>51226.13533206411</v>
       </c>
       <c r="E13">
-        <v>1714.322000000001</v>
+        <v>2221.024</v>
       </c>
       <c r="F13">
-        <v>5573.722000000001</v>
+        <v>6080.424</v>
       </c>
       <c r="G13">
         <v>469.3</v>
@@ -2481,28 +2481,28 @@
         <v>1604</v>
       </c>
       <c r="M13">
-        <v>302.6531046000001</v>
+        <v>330.1670232</v>
       </c>
       <c r="N13">
-        <v>1301.3468954</v>
+        <v>1273.8329768</v>
       </c>
       <c r="O13">
-        <v>335.7474990132</v>
+        <v>328.6489080144</v>
       </c>
       <c r="P13">
-        <v>965.5993963868</v>
+        <v>945.1840687855999</v>
       </c>
       <c r="Q13">
-        <v>1271.9993963868</v>
+        <v>1251.5840687856</v>
       </c>
       <c r="R13">
-        <v>0.1235955056179775</v>
+        <v>0.1363636363636364</v>
       </c>
       <c r="S13">
-        <v>0.09389877068348448</v>
+        <v>0.09431617675702364</v>
       </c>
       <c r="T13">
-        <v>1.110826112782551</v>
+        <v>1.120465975912786</v>
       </c>
       <c r="U13">
         <v>0.0543</v>
@@ -2519,7 +2519,7 @@
         </is>
       </c>
       <c r="Y13">
-        <v>5.299796947795789</v>
+        <v>4.85814720214614</v>
       </c>
       <c r="Z13">
         <v>0</v>
@@ -2527,22 +2527,22 @@
     </row>
     <row r="14">
       <c r="A14">
-        <v>0.12</v>
+        <v>0.13</v>
       </c>
       <c r="B14">
-        <v>0.0878331075461808</v>
+        <v>0.0876643431840604</v>
       </c>
       <c r="C14">
-        <v>45615.01133206412</v>
+        <v>45314.81313448136</v>
       </c>
       <c r="D14">
-        <v>51226.13533206411</v>
+        <v>51432.63913448136</v>
       </c>
       <c r="E14">
-        <v>2221.024</v>
+        <v>2727.726000000001</v>
       </c>
       <c r="F14">
-        <v>6080.424</v>
+        <v>6587.126000000001</v>
       </c>
       <c r="G14">
         <v>469.3</v>
@@ -2563,28 +2563,28 @@
         <v>1604</v>
       </c>
       <c r="M14">
-        <v>330.1670232</v>
+        <v>357.6809418000001</v>
       </c>
       <c r="N14">
-        <v>1273.8329768</v>
+        <v>1246.3190582</v>
       </c>
       <c r="O14">
-        <v>328.6489080144</v>
+        <v>321.5503170156</v>
       </c>
       <c r="P14">
-        <v>945.1840687855999</v>
+        <v>924.7687411843999</v>
       </c>
       <c r="Q14">
-        <v>1251.5840687856</v>
+        <v>1231.1687411844</v>
       </c>
       <c r="R14">
-        <v>0.1363636363636364</v>
+        <v>0.1494252873563219</v>
       </c>
       <c r="S14">
-        <v>0.09431617675702364</v>
+        <v>0.09474317837248322</v>
       </c>
       <c r="T14">
-        <v>1.120465975912786</v>
+        <v>1.130327445091991</v>
       </c>
       <c r="U14">
         <v>0.0543</v>
@@ -2601,7 +2601,7 @@
         </is>
       </c>
       <c r="Y14">
-        <v>4.85814720214614</v>
+        <v>4.484443571211822</v>
       </c>
       <c r="Z14">
         <v>0</v>
@@ -2609,22 +2609,22 @@
     </row>
     <row r="15">
       <c r="A15">
-        <v>0.13</v>
+        <v>0.14</v>
       </c>
       <c r="B15">
-        <v>0.0876643431840604</v>
+        <v>0.08759945882194001</v>
       </c>
       <c r="C15">
-        <v>45314.81313448136</v>
+        <v>44887.94886627175</v>
       </c>
       <c r="D15">
-        <v>51432.63913448136</v>
+        <v>51512.47686627175</v>
       </c>
       <c r="E15">
-        <v>2727.726000000001</v>
+        <v>3234.428000000001</v>
       </c>
       <c r="F15">
-        <v>6587.126000000001</v>
+        <v>7093.828000000001</v>
       </c>
       <c r="G15">
         <v>469.3</v>
@@ -2645,45 +2645,45 @@
         <v>1604</v>
       </c>
       <c r="M15">
-        <v>357.6809418000001</v>
+        <v>392.2886884000001</v>
       </c>
       <c r="N15">
-        <v>1246.3190582</v>
+        <v>1211.7113116</v>
       </c>
       <c r="O15">
-        <v>321.5503170156</v>
+        <v>312.6215183928</v>
       </c>
       <c r="P15">
-        <v>924.7687411843999</v>
+        <v>899.0897932072</v>
       </c>
       <c r="Q15">
-        <v>1231.1687411844</v>
+        <v>1205.4897932072</v>
       </c>
       <c r="R15">
-        <v>0.1494252873563219</v>
+        <v>0.1627906976744186</v>
       </c>
       <c r="S15">
-        <v>0.09474317837248322</v>
+        <v>0.09518011025806977</v>
       </c>
       <c r="T15">
-        <v>1.130327445091991</v>
+        <v>1.140418250763736</v>
       </c>
       <c r="U15">
-        <v>0.0543</v>
+        <v>0.0553</v>
       </c>
       <c r="V15">
         <v>0.258</v>
       </c>
       <c r="W15">
-        <v>0.0402906</v>
+        <v>0.0410326</v>
       </c>
       <c r="X15" t="inlineStr">
         <is>
-          <t>A2/A</t>
+          <t>A3/A-</t>
         </is>
       </c>
       <c r="Y15">
-        <v>4.484443571211822</v>
+        <v>4.088825519140306</v>
       </c>
       <c r="Z15">
         <v>0</v>
@@ -2691,22 +2691,22 @@
     </row>
     <row r="16">
       <c r="A16">
-        <v>0.14</v>
+        <v>0.15</v>
       </c>
       <c r="B16">
-        <v>0.08759945882194001</v>
+        <v>0.0874381144598196</v>
       </c>
       <c r="C16">
-        <v>44887.94886627175</v>
+        <v>44580.85359268227</v>
       </c>
       <c r="D16">
-        <v>51512.47686627175</v>
+        <v>51712.08359268226</v>
       </c>
       <c r="E16">
-        <v>3234.428000000001</v>
+        <v>3741.130000000001</v>
       </c>
       <c r="F16">
-        <v>7093.828000000001</v>
+        <v>7600.530000000002</v>
       </c>
       <c r="G16">
         <v>469.3</v>
@@ -2727,28 +2727,28 @@
         <v>1604</v>
       </c>
       <c r="M16">
-        <v>392.2886884000001</v>
+        <v>420.3093090000001</v>
       </c>
       <c r="N16">
-        <v>1211.7113116</v>
+        <v>1183.690691</v>
       </c>
       <c r="O16">
-        <v>312.6215183928</v>
+        <v>305.392198278</v>
       </c>
       <c r="P16">
-        <v>899.0897932072</v>
+        <v>878.2984927219998</v>
       </c>
       <c r="Q16">
-        <v>1205.4897932072</v>
+        <v>1184.698492722</v>
       </c>
       <c r="R16">
-        <v>0.1627906976744186</v>
+        <v>0.1764705882352942</v>
       </c>
       <c r="S16">
-        <v>0.09518011025806977</v>
+        <v>0.09562732289390542</v>
       </c>
       <c r="T16">
-        <v>1.140418250763736</v>
+        <v>1.150746487157169</v>
       </c>
       <c r="U16">
         <v>0.0553</v>
@@ -2765,7 +2765,7 @@
         </is>
       </c>
       <c r="Y16">
-        <v>4.088825519140306</v>
+        <v>3.816237151197619</v>
       </c>
       <c r="Z16">
         <v>0</v>
@@ -2773,22 +2773,22 @@
     </row>
     <row r="17">
       <c r="A17">
-        <v>0.15</v>
+        <v>0.16</v>
       </c>
       <c r="B17">
-        <v>0.0874381144598196</v>
+        <v>0.08727677009769921</v>
       </c>
       <c r="C17">
-        <v>44580.85359268227</v>
+        <v>44275.31125679121</v>
       </c>
       <c r="D17">
-        <v>51712.08359268226</v>
+        <v>51913.24325679121</v>
       </c>
       <c r="E17">
-        <v>3741.130000000001</v>
+        <v>4247.832</v>
       </c>
       <c r="F17">
-        <v>7600.530000000001</v>
+        <v>8107.232000000001</v>
       </c>
       <c r="G17">
         <v>469.3</v>
@@ -2809,28 +2809,28 @@
         <v>1604</v>
       </c>
       <c r="M17">
-        <v>420.309309</v>
+        <v>448.3299296000001</v>
       </c>
       <c r="N17">
-        <v>1183.690691</v>
+        <v>1155.6700704</v>
       </c>
       <c r="O17">
-        <v>305.392198278</v>
+        <v>298.1628781632</v>
       </c>
       <c r="P17">
-        <v>878.298492722</v>
+        <v>857.5071922367999</v>
       </c>
       <c r="Q17">
-        <v>1184.698492722</v>
+        <v>1163.9071922368</v>
       </c>
       <c r="R17">
-        <v>0.1764705882352941</v>
+        <v>0.1904761904761905</v>
       </c>
       <c r="S17">
-        <v>0.09562732289390542</v>
+        <v>0.09608518344964193</v>
       </c>
       <c r="T17">
-        <v>1.150746487157169</v>
+        <v>1.161320633940922</v>
       </c>
       <c r="U17">
         <v>0.0553</v>
@@ -2847,7 +2847,7 @@
         </is>
       </c>
       <c r="Y17">
-        <v>3.816237151197619</v>
+        <v>3.577722329247768</v>
       </c>
       <c r="Z17">
         <v>0</v>
@@ -2855,22 +2855,22 @@
     </row>
     <row r="18">
       <c r="A18">
-        <v>0.16</v>
+        <v>0.17</v>
       </c>
       <c r="B18">
-        <v>0.08727677009769921</v>
+        <v>0.08711542573557882</v>
       </c>
       <c r="C18">
-        <v>44275.31125679121</v>
+        <v>43971.34005212355</v>
       </c>
       <c r="D18">
-        <v>51913.24325679121</v>
+        <v>52115.97405212354</v>
       </c>
       <c r="E18">
-        <v>4247.832</v>
+        <v>4754.534000000001</v>
       </c>
       <c r="F18">
-        <v>8107.232000000001</v>
+        <v>8613.934000000001</v>
       </c>
       <c r="G18">
         <v>469.3</v>
@@ -2891,28 +2891,28 @@
         <v>1604</v>
       </c>
       <c r="M18">
-        <v>448.3299296000001</v>
+        <v>476.3505502000001</v>
       </c>
       <c r="N18">
-        <v>1155.6700704</v>
+        <v>1127.6494498</v>
       </c>
       <c r="O18">
-        <v>298.1628781632</v>
+        <v>290.9335580484</v>
       </c>
       <c r="P18">
-        <v>857.5071922367999</v>
+        <v>836.7158917515999</v>
       </c>
       <c r="Q18">
-        <v>1163.9071922368</v>
+        <v>1143.1158917516</v>
       </c>
       <c r="R18">
-        <v>0.1904761904761905</v>
+        <v>0.2048192771084338</v>
       </c>
       <c r="S18">
-        <v>0.09608518344964193</v>
+        <v>0.096554076789854</v>
       </c>
       <c r="T18">
-        <v>1.161320633940922</v>
+        <v>1.172149579442356</v>
       </c>
       <c r="U18">
         <v>0.0553</v>
@@ -2929,7 +2929,7 @@
         </is>
       </c>
       <c r="Y18">
-        <v>3.577722329247768</v>
+        <v>3.367268074586134</v>
       </c>
       <c r="Z18">
         <v>0</v>
@@ -2937,22 +2937,22 @@
     </row>
     <row r="19">
       <c r="A19">
-        <v>0.17</v>
+        <v>0.18</v>
       </c>
       <c r="B19">
-        <v>0.08711542573557882</v>
+        <v>0.08695408137345842</v>
       </c>
       <c r="C19">
-        <v>43971.34005212355</v>
+        <v>43668.95845751464</v>
       </c>
       <c r="D19">
-        <v>52115.97405212354</v>
+        <v>52320.29445751464</v>
       </c>
       <c r="E19">
-        <v>4754.534000000001</v>
+        <v>5261.236000000003</v>
       </c>
       <c r="F19">
-        <v>8613.934000000001</v>
+        <v>9120.636000000002</v>
       </c>
       <c r="G19">
         <v>469.3</v>
@@ -2973,28 +2973,28 @@
         <v>1604</v>
       </c>
       <c r="M19">
-        <v>476.3505502000001</v>
+        <v>504.3711708000001</v>
       </c>
       <c r="N19">
-        <v>1127.6494498</v>
+        <v>1099.6288292</v>
       </c>
       <c r="O19">
-        <v>290.9335580484</v>
+        <v>283.7042379336</v>
       </c>
       <c r="P19">
-        <v>836.7158917515999</v>
+        <v>815.9245912663999</v>
       </c>
       <c r="Q19">
-        <v>1143.1158917516</v>
+        <v>1122.3245912664</v>
       </c>
       <c r="R19">
-        <v>0.2048192771084338</v>
+        <v>0.2195121951219512</v>
       </c>
       <c r="S19">
-        <v>0.096554076789854</v>
+        <v>0.09703440655299808</v>
       </c>
       <c r="T19">
-        <v>1.172149579442356</v>
+        <v>1.183242645565775</v>
       </c>
       <c r="U19">
         <v>0.0553</v>
@@ -3011,7 +3011,7 @@
         </is>
       </c>
       <c r="Y19">
-        <v>3.367268074586134</v>
+        <v>3.180197625998016</v>
       </c>
       <c r="Z19">
         <v>0</v>
@@ -3019,22 +3019,22 @@
     </row>
     <row r="20">
       <c r="A20">
-        <v>0.18</v>
+        <v>0.19</v>
       </c>
       <c r="B20">
-        <v>0.08695408137345843</v>
+        <v>0.08679273701133805</v>
       </c>
       <c r="C20">
-        <v>43668.95845751463</v>
+        <v>43368.18524272512</v>
       </c>
       <c r="D20">
-        <v>52320.29445751462</v>
+        <v>52526.22324272512</v>
       </c>
       <c r="E20">
-        <v>5261.236000000001</v>
+        <v>5767.938000000002</v>
       </c>
       <c r="F20">
-        <v>9120.636</v>
+        <v>9627.338000000002</v>
       </c>
       <c r="G20">
         <v>469.3</v>
@@ -3055,28 +3055,28 @@
         <v>1604</v>
       </c>
       <c r="M20">
-        <v>504.3711708</v>
+        <v>532.3917914000001</v>
       </c>
       <c r="N20">
-        <v>1099.6288292</v>
+        <v>1071.6082086</v>
       </c>
       <c r="O20">
-        <v>283.7042379336</v>
+        <v>276.4749178188</v>
       </c>
       <c r="P20">
-        <v>815.9245912663999</v>
+        <v>795.1332907811999</v>
       </c>
       <c r="Q20">
-        <v>1122.3245912664</v>
+        <v>1101.5332907812</v>
       </c>
       <c r="R20">
-        <v>0.2195121951219512</v>
+        <v>0.2345679012345679</v>
       </c>
       <c r="S20">
-        <v>0.09703440655299808</v>
+        <v>0.09752659631029387</v>
       </c>
       <c r="T20">
-        <v>1.183242645565775</v>
+        <v>1.19460961455644</v>
       </c>
       <c r="U20">
         <v>0.0553</v>
@@ -3093,7 +3093,7 @@
         </is>
       </c>
       <c r="Y20">
-        <v>3.180197625998016</v>
+        <v>3.012818803577067</v>
       </c>
       <c r="Z20">
         <v>0</v>
@@ -3101,22 +3101,22 @@
     </row>
     <row r="21">
       <c r="A21">
-        <v>0.19</v>
+        <v>0.2</v>
       </c>
       <c r="B21">
-        <v>0.08679273701133805</v>
+        <v>0.08700239264921765</v>
       </c>
       <c r="C21">
-        <v>43368.18524272512</v>
+        <v>42594.20704512379</v>
       </c>
       <c r="D21">
-        <v>52526.22324272512</v>
+        <v>52258.94704512379</v>
       </c>
       <c r="E21">
-        <v>5767.938000000002</v>
+        <v>6274.640000000001</v>
       </c>
       <c r="F21">
-        <v>9627.338000000002</v>
+        <v>10134.04</v>
       </c>
       <c r="G21">
         <v>469.3</v>
@@ -3137,45 +3137,45 @@
         <v>1604</v>
       </c>
       <c r="M21">
-        <v>532.3917914000001</v>
+        <v>585.7475120000001</v>
       </c>
       <c r="N21">
-        <v>1071.6082086</v>
+        <v>1018.252488</v>
       </c>
       <c r="O21">
-        <v>276.4749178188</v>
+        <v>262.709141904</v>
       </c>
       <c r="P21">
-        <v>795.1332907811999</v>
+        <v>755.5433460959998</v>
       </c>
       <c r="Q21">
-        <v>1101.5332907812</v>
+        <v>1061.943346096</v>
       </c>
       <c r="R21">
-        <v>0.2345679012345679</v>
+        <v>0.25</v>
       </c>
       <c r="S21">
-        <v>0.09752659631029387</v>
+        <v>0.09803109081152205</v>
       </c>
       <c r="T21">
-        <v>1.19460961455644</v>
+        <v>1.206260757771872</v>
       </c>
       <c r="U21">
-        <v>0.0553</v>
+        <v>0.0578</v>
       </c>
       <c r="V21">
         <v>0.258</v>
       </c>
       <c r="W21">
-        <v>0.0410326</v>
+        <v>0.0428876</v>
       </c>
       <c r="X21" t="inlineStr">
         <is>
-          <t>A3/A-</t>
+          <t>Baa2/BBB</t>
         </is>
       </c>
       <c r="Y21">
-        <v>3.012818803577067</v>
+        <v>2.738381243009018</v>
       </c>
       <c r="Z21">
         <v>0</v>
@@ -3183,22 +3183,22 @@
     </row>
     <row r="22">
       <c r="A22">
-        <v>0.2</v>
+        <v>0.21</v>
       </c>
       <c r="B22">
-        <v>0.08700239264921765</v>
+        <v>0.08685959828709726</v>
       </c>
       <c r="C22">
-        <v>42594.20704512379</v>
+        <v>42269.24776350633</v>
       </c>
       <c r="D22">
-        <v>52258.94704512379</v>
+        <v>52440.68976350633</v>
       </c>
       <c r="E22">
-        <v>6274.640000000001</v>
+        <v>6781.342000000002</v>
       </c>
       <c r="F22">
-        <v>10134.04</v>
+        <v>10640.742</v>
       </c>
       <c r="G22">
         <v>469.3</v>
@@ -3219,28 +3219,28 @@
         <v>1604</v>
       </c>
       <c r="M22">
-        <v>585.7475120000001</v>
+        <v>615.0348876000002</v>
       </c>
       <c r="N22">
-        <v>1018.252488</v>
+        <v>988.9651123999998</v>
       </c>
       <c r="O22">
-        <v>262.709141904</v>
+        <v>255.1529989992</v>
       </c>
       <c r="P22">
-        <v>755.5433460959998</v>
+        <v>733.8121134007999</v>
       </c>
       <c r="Q22">
-        <v>1061.943346096</v>
+        <v>1040.2121134008</v>
       </c>
       <c r="R22">
-        <v>0.25</v>
+        <v>0.2658227848101266</v>
       </c>
       <c r="S22">
-        <v>0.09803109081152205</v>
+        <v>0.09854835732543957</v>
       </c>
       <c r="T22">
-        <v>1.206260757771872</v>
+        <v>1.218206866638327</v>
       </c>
       <c r="U22">
         <v>0.0578</v>
@@ -3257,7 +3257,7 @@
         </is>
       </c>
       <c r="Y22">
-        <v>2.738381243009018</v>
+        <v>2.607982136199064</v>
       </c>
       <c r="Z22">
         <v>0</v>
@@ -3265,22 +3265,22 @@
     </row>
     <row r="23">
       <c r="A23">
-        <v>0.21</v>
+        <v>0.22</v>
       </c>
       <c r="B23">
-        <v>0.08685959828709724</v>
+        <v>0.08728814392497684</v>
       </c>
       <c r="C23">
-        <v>42269.24776350634</v>
+        <v>41220.86742556511</v>
       </c>
       <c r="D23">
-        <v>52440.68976350634</v>
+        <v>51899.01142556511</v>
       </c>
       <c r="E23">
-        <v>6781.342000000001</v>
+        <v>7288.044000000002</v>
       </c>
       <c r="F23">
-        <v>10640.742</v>
+        <v>11147.444</v>
       </c>
       <c r="G23">
         <v>469.3</v>
@@ -3301,45 +3301,45 @@
         <v>1604</v>
       </c>
       <c r="M23">
-        <v>615.0348876</v>
+        <v>683.3383172000001</v>
       </c>
       <c r="N23">
-        <v>988.9651124</v>
+        <v>920.6616827999999</v>
       </c>
       <c r="O23">
-        <v>255.1529989992</v>
+        <v>237.5307141624</v>
       </c>
       <c r="P23">
-        <v>733.8121134007999</v>
+        <v>683.1309686375998</v>
       </c>
       <c r="Q23">
-        <v>1040.2121134008</v>
+        <v>989.5309686375998</v>
       </c>
       <c r="R23">
-        <v>0.2658227848101266</v>
+        <v>0.282051282051282</v>
       </c>
       <c r="S23">
-        <v>0.09854835732543954</v>
+        <v>0.09907888708330365</v>
       </c>
       <c r="T23">
-        <v>1.218206866638327</v>
+        <v>1.230459285988537</v>
       </c>
       <c r="U23">
-        <v>0.0578</v>
+        <v>0.0613</v>
       </c>
       <c r="V23">
         <v>0.258</v>
       </c>
       <c r="W23">
-        <v>0.0428876</v>
+        <v>0.0454846</v>
       </c>
       <c r="X23" t="inlineStr">
         <is>
-          <t>Baa2/BBB</t>
+          <t>Ba1/BB+</t>
         </is>
       </c>
       <c r="Y23">
-        <v>2.607982136199065</v>
+        <v>2.347299953224399</v>
       </c>
       <c r="Z23">
         <v>0</v>
@@ -3347,22 +3347,22 @@
     </row>
     <row r="24">
       <c r="A24">
-        <v>0.22</v>
+        <v>0.23</v>
       </c>
       <c r="B24">
-        <v>0.08728814392497684</v>
+        <v>0.08764916756285646</v>
       </c>
       <c r="C24">
-        <v>41220.86742556511</v>
+        <v>40266.44397736496</v>
       </c>
       <c r="D24">
-        <v>51899.01142556511</v>
+        <v>51451.28997736496</v>
       </c>
       <c r="E24">
-        <v>7288.044000000002</v>
+        <v>7794.746000000001</v>
       </c>
       <c r="F24">
-        <v>11147.444</v>
+        <v>11654.146</v>
       </c>
       <c r="G24">
         <v>469.3</v>
@@ -3383,45 +3383,45 @@
         <v>1604</v>
       </c>
       <c r="M24">
-        <v>683.3383172000001</v>
+        <v>747.0307586000001</v>
       </c>
       <c r="N24">
-        <v>920.6616827999999</v>
+        <v>856.9692413999999</v>
       </c>
       <c r="O24">
-        <v>237.5307141624</v>
+        <v>221.0980642812</v>
       </c>
       <c r="P24">
-        <v>683.1309686375998</v>
+        <v>635.8711771187999</v>
       </c>
       <c r="Q24">
-        <v>989.5309686375998</v>
+        <v>942.2711771187999</v>
       </c>
       <c r="R24">
-        <v>0.282051282051282</v>
+        <v>0.2987012987012987</v>
       </c>
       <c r="S24">
-        <v>0.09907888708330365</v>
+        <v>0.09962319683487852</v>
       </c>
       <c r="T24">
-        <v>1.230459285988537</v>
+        <v>1.243029949997194</v>
       </c>
       <c r="U24">
-        <v>0.0613</v>
+        <v>0.0641</v>
       </c>
       <c r="V24">
         <v>0.258</v>
       </c>
       <c r="W24">
-        <v>0.0454846</v>
+        <v>0.04756220000000001</v>
       </c>
       <c r="X24" t="inlineStr">
         <is>
-          <t>Ba1/BB+</t>
+          <t>Ba2/BB</t>
         </is>
       </c>
       <c r="Y24">
-        <v>2.347299953224399</v>
+        <v>2.147167277296632</v>
       </c>
       <c r="Z24">
         <v>0</v>
@@ -3429,22 +3429,22 @@
     </row>
     <row r="25">
       <c r="A25">
-        <v>0.23</v>
+        <v>0.24</v>
       </c>
       <c r="B25">
-        <v>0.08764916756285646</v>
+        <v>0.08755311920073608</v>
       </c>
       <c r="C25">
-        <v>40266.44397736496</v>
+        <v>39878.09989231612</v>
       </c>
       <c r="D25">
-        <v>51451.28997736496</v>
+        <v>51569.64789231612</v>
       </c>
       <c r="E25">
-        <v>7794.746000000001</v>
+        <v>8301.448000000002</v>
       </c>
       <c r="F25">
-        <v>11654.146</v>
+        <v>12160.848</v>
       </c>
       <c r="G25">
         <v>469.3</v>
@@ -3465,28 +3465,28 @@
         <v>1604</v>
       </c>
       <c r="M25">
-        <v>747.0307586000001</v>
+        <v>779.5103568000002</v>
       </c>
       <c r="N25">
-        <v>856.9692413999999</v>
+        <v>824.4896431999998</v>
       </c>
       <c r="O25">
-        <v>221.0980642812</v>
+        <v>212.7183279456</v>
       </c>
       <c r="P25">
-        <v>635.8711771187999</v>
+        <v>611.7713152543998</v>
       </c>
       <c r="Q25">
-        <v>942.2711771187999</v>
+        <v>918.1713152543998</v>
       </c>
       <c r="R25">
-        <v>0.2987012987012987</v>
+        <v>0.3157894736842106</v>
       </c>
       <c r="S25">
-        <v>0.09962319683487852</v>
+        <v>0.1001818305272843</v>
       </c>
       <c r="T25">
-        <v>1.243029949997194</v>
+        <v>1.255931420953448</v>
       </c>
       <c r="U25">
         <v>0.0641</v>
@@ -3503,7 +3503,7 @@
         </is>
       </c>
       <c r="Y25">
-        <v>2.147167277296632</v>
+        <v>2.057701974075939</v>
       </c>
       <c r="Z25">
         <v>0</v>
@@ -3511,22 +3511,22 @@
     </row>
     <row r="26">
       <c r="A26">
-        <v>0.24</v>
+        <v>0.25</v>
       </c>
       <c r="B26">
-        <v>0.08755311920073608</v>
+        <v>0.08890397083861568</v>
       </c>
       <c r="C26">
-        <v>39878.09989231612</v>
+        <v>37755.23720074011</v>
       </c>
       <c r="D26">
-        <v>51569.64789231612</v>
+        <v>49953.48720074011</v>
       </c>
       <c r="E26">
-        <v>8301.448</v>
+        <v>8808.150000000001</v>
       </c>
       <c r="F26">
-        <v>12160.848</v>
+        <v>12667.55</v>
       </c>
       <c r="G26">
         <v>469.3</v>
@@ -3547,45 +3547,45 @@
         <v>1604</v>
       </c>
       <c r="M26">
-        <v>779.5103568000001</v>
+        <v>910.7968450000002</v>
       </c>
       <c r="N26">
-        <v>824.4896431999999</v>
+        <v>693.2031549999998</v>
       </c>
       <c r="O26">
-        <v>212.7183279456</v>
+        <v>178.8464139899999</v>
       </c>
       <c r="P26">
-        <v>611.7713152544</v>
+        <v>514.3567410099998</v>
       </c>
       <c r="Q26">
-        <v>918.1713152543999</v>
+        <v>820.7567410099998</v>
       </c>
       <c r="R26">
-        <v>0.3157894736842105</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="S26">
-        <v>0.1001818305272843</v>
+        <v>0.1007553611181542</v>
       </c>
       <c r="T26">
-        <v>1.255931420953448</v>
+        <v>1.269176931135202</v>
       </c>
       <c r="U26">
-        <v>0.0641</v>
+        <v>0.07190000000000001</v>
       </c>
       <c r="V26">
         <v>0.258</v>
       </c>
       <c r="W26">
-        <v>0.04756220000000001</v>
+        <v>0.0533498</v>
       </c>
       <c r="X26" t="inlineStr">
         <is>
-          <t>Ba2/BB</t>
+          <t>B1/B+</t>
         </is>
       </c>
       <c r="Y26">
-        <v>2.05770197407594</v>
+        <v>1.761095252805799</v>
       </c>
       <c r="Z26">
         <v>0</v>
@@ -3593,22 +3593,22 @@
     </row>
     <row r="27">
       <c r="A27">
-        <v>0.25</v>
+        <v>0.26</v>
       </c>
       <c r="B27">
-        <v>0.08890397083861568</v>
+        <v>0.08961818647649528</v>
       </c>
       <c r="C27">
-        <v>37755.23720074011</v>
+        <v>36434.31707364977</v>
       </c>
       <c r="D27">
-        <v>49953.48720074011</v>
+        <v>49139.26907364977</v>
       </c>
       <c r="E27">
-        <v>8808.150000000001</v>
+        <v>9314.852000000003</v>
       </c>
       <c r="F27">
-        <v>12667.55</v>
+        <v>13174.252</v>
       </c>
       <c r="G27">
         <v>469.3</v>
@@ -3629,45 +3629,45 @@
         <v>1604</v>
       </c>
       <c r="M27">
-        <v>910.7968450000002</v>
+        <v>998.6083016000002</v>
       </c>
       <c r="N27">
-        <v>693.2031549999998</v>
+        <v>605.3916983999998</v>
       </c>
       <c r="O27">
-        <v>178.8464139899999</v>
+        <v>156.1910581872</v>
       </c>
       <c r="P27">
-        <v>514.3567410099998</v>
+        <v>449.2006402127998</v>
       </c>
       <c r="Q27">
-        <v>820.7567410099998</v>
+        <v>755.6006402127998</v>
       </c>
       <c r="R27">
-        <v>0.3333333333333333</v>
+        <v>0.3513513513513514</v>
       </c>
       <c r="S27">
-        <v>0.1007553611181542</v>
+        <v>0.1013443925358044</v>
       </c>
       <c r="T27">
-        <v>1.269176931135202</v>
+        <v>1.282780428078624</v>
       </c>
       <c r="U27">
-        <v>0.07190000000000001</v>
+        <v>0.07580000000000001</v>
       </c>
       <c r="V27">
         <v>0.258</v>
       </c>
       <c r="W27">
-        <v>0.0533498</v>
+        <v>0.0562436</v>
       </c>
       <c r="X27" t="inlineStr">
         <is>
-          <t>B1/B+</t>
+          <t>B2/B</t>
         </is>
       </c>
       <c r="Y27">
-        <v>1.761095252805799</v>
+        <v>1.606235395229564</v>
       </c>
       <c r="Z27">
         <v>0</v>
@@ -3675,22 +3675,22 @@
     </row>
     <row r="28">
       <c r="A28">
-        <v>0.26</v>
+        <v>0.27</v>
       </c>
       <c r="B28">
-        <v>0.08961818647649528</v>
+        <v>0.08960895211437488</v>
       </c>
       <c r="C28">
-        <v>36434.31707364977</v>
+        <v>35937.97299784237</v>
       </c>
       <c r="D28">
-        <v>49139.26907364977</v>
+        <v>49149.62699784237</v>
       </c>
       <c r="E28">
-        <v>9314.852000000003</v>
+        <v>9821.554000000002</v>
       </c>
       <c r="F28">
-        <v>13174.252</v>
+        <v>13680.954</v>
       </c>
       <c r="G28">
         <v>469.3</v>
@@ -3711,28 +3711,28 @@
         <v>1604</v>
       </c>
       <c r="M28">
-        <v>998.6083016000002</v>
+        <v>1037.0163132</v>
       </c>
       <c r="N28">
-        <v>605.3916983999998</v>
+        <v>566.9836867999998</v>
       </c>
       <c r="O28">
-        <v>156.1910581872</v>
+        <v>146.2817911943999</v>
       </c>
       <c r="P28">
-        <v>449.2006402127998</v>
+        <v>420.7018956055998</v>
       </c>
       <c r="Q28">
-        <v>755.6006402127998</v>
+        <v>727.1018956055998</v>
       </c>
       <c r="R28">
-        <v>0.3513513513513514</v>
+        <v>0.3698630136986302</v>
       </c>
       <c r="S28">
-        <v>0.1013443925358044</v>
+        <v>0.1019495618005135</v>
       </c>
       <c r="T28">
-        <v>1.282780428078624</v>
+        <v>1.296756623568442</v>
       </c>
       <c r="U28">
         <v>0.07580000000000001</v>
@@ -3749,7 +3749,7 @@
         </is>
       </c>
       <c r="Y28">
-        <v>1.606235395229564</v>
+        <v>1.546745195406247</v>
       </c>
       <c r="Z28">
         <v>0</v>
@@ -3757,22 +3757,22 @@
     </row>
     <row r="29">
       <c r="A29">
-        <v>0.27</v>
+        <v>0.28</v>
       </c>
       <c r="B29">
-        <v>0.08960895211437488</v>
+        <v>0.09254990975225449</v>
       </c>
       <c r="C29">
-        <v>35937.97299784237</v>
+        <v>32339.35121266529</v>
       </c>
       <c r="D29">
-        <v>49149.62699784237</v>
+        <v>46057.70721266529</v>
       </c>
       <c r="E29">
-        <v>9821.554000000002</v>
+        <v>10328.256</v>
       </c>
       <c r="F29">
-        <v>13680.954</v>
+        <v>14187.656</v>
       </c>
       <c r="G29">
         <v>469.3</v>
@@ -3793,45 +3793,45 @@
         <v>1604</v>
       </c>
       <c r="M29">
-        <v>1037.0163132</v>
+        <v>1276.88904</v>
       </c>
       <c r="N29">
-        <v>566.9836867999998</v>
+        <v>327.1109599999997</v>
       </c>
       <c r="O29">
-        <v>146.2817911943999</v>
+        <v>84.39462767999994</v>
       </c>
       <c r="P29">
-        <v>420.7018956055998</v>
+        <v>242.7163323199998</v>
       </c>
       <c r="Q29">
-        <v>727.1018956055998</v>
+        <v>549.1163323199999</v>
       </c>
       <c r="R29">
-        <v>0.3698630136986302</v>
+        <v>0.388888888888889</v>
       </c>
       <c r="S29">
-        <v>0.1019495618005135</v>
+        <v>0.1025715413225757</v>
       </c>
       <c r="T29">
-        <v>1.296756623568442</v>
+        <v>1.311121046710755</v>
       </c>
       <c r="U29">
-        <v>0.07580000000000001</v>
+        <v>0.09</v>
       </c>
       <c r="V29">
         <v>0.258</v>
       </c>
       <c r="W29">
-        <v>0.0562436</v>
+        <v>0.06677999999999999</v>
       </c>
       <c r="X29" t="inlineStr">
         <is>
-          <t>B2/B</t>
+          <t>B3/B-</t>
         </is>
       </c>
       <c r="Y29">
-        <v>1.546745195406247</v>
+        <v>1.256178062269216</v>
       </c>
       <c r="Z29">
         <v>0</v>
@@ -3839,22 +3839,22 @@
     </row>
     <row r="30">
       <c r="A30">
-        <v>0.28</v>
+        <v>0.29</v>
       </c>
       <c r="B30">
-        <v>0.09254990975225449</v>
+        <v>0.09976912151960576</v>
       </c>
       <c r="C30">
-        <v>32339.35121266529</v>
+        <v>25671.7125043273</v>
       </c>
       <c r="D30">
-        <v>46057.70721266529</v>
+        <v>39896.7705043273</v>
       </c>
       <c r="E30">
-        <v>10328.256</v>
+        <v>10834.958</v>
       </c>
       <c r="F30">
-        <v>14187.656</v>
+        <v>14694.358</v>
       </c>
       <c r="G30">
         <v>469.3</v>
@@ -3875,45 +3875,45 @@
         <v>1604</v>
       </c>
       <c r="M30">
-        <v>1276.88904</v>
+        <v>1742.750858800001</v>
       </c>
       <c r="N30">
-        <v>327.1109599999997</v>
+        <v>-138.7508588000005</v>
       </c>
       <c r="O30">
-        <v>84.39462767999994</v>
+        <v>-35.79772157040014</v>
       </c>
       <c r="P30">
-        <v>242.7163323199998</v>
+        <v>-102.9531372296004</v>
       </c>
       <c r="Q30">
-        <v>549.1163323199999</v>
+        <v>203.4468627703996</v>
       </c>
       <c r="R30">
-        <v>0.388888888888889</v>
+        <v>0.4084507042253522</v>
       </c>
       <c r="S30">
-        <v>0.1025715413225757</v>
+        <v>0.1035806884637399</v>
       </c>
       <c r="T30">
-        <v>1.311121046710755</v>
+        <v>1.33442698530577</v>
       </c>
       <c r="U30">
-        <v>0.09</v>
+        <v>0.1186</v>
       </c>
       <c r="V30">
-        <v>0.258</v>
+        <v>0.2374590710487159</v>
       </c>
       <c r="W30">
-        <v>0.06677999999999999</v>
+        <v>0.09043735417362231</v>
       </c>
       <c r="X30" t="inlineStr">
         <is>
-          <t>B3/B-</t>
+          <t>Caa/CCC</t>
         </is>
       </c>
       <c r="Y30">
-        <v>1.256178062269216</v>
+        <v>0.9203839963128524</v>
       </c>
       <c r="Z30">
         <v>0</v>
@@ -3921,22 +3921,22 @@
     </row>
     <row r="31">
       <c r="A31">
-        <v>0.29</v>
+        <v>0.3</v>
       </c>
       <c r="B31">
-        <v>0.09976912151960576</v>
+        <v>0.1004971215196058</v>
       </c>
       <c r="C31">
-        <v>25671.7125043273</v>
+        <v>24633.99811975895</v>
       </c>
       <c r="D31">
-        <v>39896.7705043273</v>
+        <v>39365.75811975895</v>
       </c>
       <c r="E31">
-        <v>10834.958</v>
+        <v>11341.66</v>
       </c>
       <c r="F31">
-        <v>14694.358</v>
+        <v>15201.06</v>
       </c>
       <c r="G31">
         <v>469.3</v>
@@ -3957,37 +3957,37 @@
         <v>1604</v>
       </c>
       <c r="M31">
-        <v>1742.7508588</v>
+        <v>1802.845716</v>
       </c>
       <c r="N31">
-        <v>-138.7508588000003</v>
+        <v>-198.8457160000003</v>
       </c>
       <c r="O31">
-        <v>-35.79772157040008</v>
+        <v>-51.30219472800007</v>
       </c>
       <c r="P31">
-        <v>-102.9531372296002</v>
+        <v>-147.5435212720002</v>
       </c>
       <c r="Q31">
-        <v>203.4468627703998</v>
+        <v>158.8564787279998</v>
       </c>
       <c r="R31">
-        <v>0.4084507042253521</v>
+        <v>0.4285714285714286</v>
       </c>
       <c r="S31">
-        <v>0.1035806884637399</v>
+        <v>0.1044061268703647</v>
       </c>
       <c r="T31">
-        <v>1.33442698530577</v>
+        <v>1.353490227952996</v>
       </c>
       <c r="U31">
         <v>0.1186</v>
       </c>
       <c r="V31">
-        <v>0.2374590710487159</v>
+        <v>0.2295437686804254</v>
       </c>
       <c r="W31">
-        <v>0.09043735417362231</v>
+        <v>0.09137610903450157</v>
       </c>
       <c r="X31" t="inlineStr">
         <is>
@@ -3995,7 +3995,7 @@
         </is>
       </c>
       <c r="Y31">
-        <v>0.9203839963128525</v>
+        <v>0.8897045297690908</v>
       </c>
       <c r="Z31">
         <v>0</v>
@@ -4003,22 +4003,22 @@
     </row>
     <row r="32">
       <c r="A32">
-        <v>0.3</v>
+        <v>0.31</v>
       </c>
       <c r="B32">
-        <v>0.1004971215196058</v>
+        <v>0.1012251215196058</v>
       </c>
       <c r="C32">
-        <v>24633.99811975895</v>
+        <v>23610.23325863294</v>
       </c>
       <c r="D32">
-        <v>39365.75811975895</v>
+        <v>38848.69525863294</v>
       </c>
       <c r="E32">
-        <v>11341.66</v>
+        <v>11848.362</v>
       </c>
       <c r="F32">
-        <v>15201.06</v>
+        <v>15707.762</v>
       </c>
       <c r="G32">
         <v>469.3</v>
@@ -4039,37 +4039,37 @@
         <v>1604</v>
       </c>
       <c r="M32">
-        <v>1802.845716</v>
+        <v>1862.9405732</v>
       </c>
       <c r="N32">
-        <v>-198.8457160000003</v>
+        <v>-258.9405732000002</v>
       </c>
       <c r="O32">
-        <v>-51.30219472800007</v>
+        <v>-66.80666788560006</v>
       </c>
       <c r="P32">
-        <v>-147.5435212720002</v>
+        <v>-192.1339053144002</v>
       </c>
       <c r="Q32">
-        <v>158.8564787279998</v>
+        <v>114.2660946855998</v>
       </c>
       <c r="R32">
-        <v>0.4285714285714286</v>
+        <v>0.4492753623188406</v>
       </c>
       <c r="S32">
-        <v>0.1044061268703647</v>
+        <v>0.1052554910279062</v>
       </c>
       <c r="T32">
-        <v>1.353490227952996</v>
+        <v>1.373106028358112</v>
       </c>
       <c r="U32">
         <v>0.1186</v>
       </c>
       <c r="V32">
-        <v>0.2295437686804254</v>
+        <v>0.2221391309810569</v>
       </c>
       <c r="W32">
-        <v>0.09137610903450157</v>
+        <v>0.09225429906564667</v>
       </c>
       <c r="X32" t="inlineStr">
         <is>
@@ -4077,7 +4077,7 @@
         </is>
       </c>
       <c r="Y32">
-        <v>0.8897045297690908</v>
+        <v>0.8610043836475072</v>
       </c>
       <c r="Z32">
         <v>0</v>
@@ -4085,22 +4085,22 @@
     </row>
     <row r="33">
       <c r="A33">
-        <v>0.31</v>
+        <v>0.32</v>
       </c>
       <c r="B33">
-        <v>0.1012251215196058</v>
+        <v>0.1019531215196058</v>
       </c>
       <c r="C33">
-        <v>23610.23325863294</v>
+        <v>22599.87537303074</v>
       </c>
       <c r="D33">
-        <v>38848.69525863294</v>
+        <v>38345.03937303074</v>
       </c>
       <c r="E33">
-        <v>11848.362</v>
+        <v>12355.064</v>
       </c>
       <c r="F33">
-        <v>15707.762</v>
+        <v>16214.464</v>
       </c>
       <c r="G33">
         <v>469.3</v>
@@ -4121,37 +4121,37 @@
         <v>1604</v>
       </c>
       <c r="M33">
-        <v>1862.9405732</v>
+        <v>1923.0354304</v>
       </c>
       <c r="N33">
-        <v>-258.9405732000002</v>
+        <v>-319.0354304000005</v>
       </c>
       <c r="O33">
-        <v>-66.80666788560006</v>
+        <v>-82.31114104320012</v>
       </c>
       <c r="P33">
-        <v>-192.1339053144002</v>
+        <v>-236.7242893568003</v>
       </c>
       <c r="Q33">
-        <v>114.2660946855998</v>
+        <v>69.67571064319964</v>
       </c>
       <c r="R33">
-        <v>0.4492753623188406</v>
+        <v>0.4705882352941177</v>
       </c>
       <c r="S33">
-        <v>0.1052554910279062</v>
+        <v>0.106129836484199</v>
       </c>
       <c r="T33">
-        <v>1.373106028358112</v>
+        <v>1.39329876406926</v>
       </c>
       <c r="U33">
         <v>0.1186</v>
       </c>
       <c r="V33">
-        <v>0.2221391309810569</v>
+        <v>0.2151972831378988</v>
       </c>
       <c r="W33">
-        <v>0.09225429906564667</v>
+        <v>0.09307760221984522</v>
       </c>
       <c r="X33" t="inlineStr">
         <is>
@@ -4159,7 +4159,7 @@
         </is>
       </c>
       <c r="Y33">
-        <v>0.8610043836475072</v>
+        <v>0.8340979966585225</v>
       </c>
       <c r="Z33">
         <v>0</v>
@@ -4167,22 +4167,22 @@
     </row>
     <row r="34">
       <c r="A34">
-        <v>0.32</v>
+        <v>0.33</v>
       </c>
       <c r="B34">
-        <v>0.1019531215196058</v>
+        <v>0.1026811215196058</v>
       </c>
       <c r="C34">
-        <v>22599.87537303074</v>
+        <v>21602.4096904978</v>
       </c>
       <c r="D34">
-        <v>38345.03937303074</v>
+        <v>37854.27569049779</v>
       </c>
       <c r="E34">
-        <v>12355.064</v>
+        <v>12861.766</v>
       </c>
       <c r="F34">
-        <v>16214.464</v>
+        <v>16721.166</v>
       </c>
       <c r="G34">
         <v>469.3</v>
@@ -4203,37 +4203,37 @@
         <v>1604</v>
       </c>
       <c r="M34">
-        <v>1923.0354304</v>
+        <v>1983.1302876</v>
       </c>
       <c r="N34">
-        <v>-319.0354304000005</v>
+        <v>-379.1302876000002</v>
       </c>
       <c r="O34">
-        <v>-82.31114104320012</v>
+        <v>-97.81561420080006</v>
       </c>
       <c r="P34">
-        <v>-236.7242893568003</v>
+        <v>-281.3146733992002</v>
       </c>
       <c r="Q34">
-        <v>69.67571064319964</v>
+        <v>25.08532660079982</v>
       </c>
       <c r="R34">
-        <v>0.4705882352941177</v>
+        <v>0.4925373134328359</v>
       </c>
       <c r="S34">
-        <v>0.106129836484199</v>
+        <v>0.1070302818048587</v>
       </c>
       <c r="T34">
-        <v>1.39329876406926</v>
+        <v>1.414094268010593</v>
       </c>
       <c r="U34">
         <v>0.1186</v>
       </c>
       <c r="V34">
-        <v>0.2151972831378988</v>
+        <v>0.2086761533458413</v>
       </c>
       <c r="W34">
-        <v>0.09307760221984522</v>
+        <v>0.09385100821318322</v>
       </c>
       <c r="X34" t="inlineStr">
         <is>
@@ -4241,7 +4241,7 @@
         </is>
       </c>
       <c r="Y34">
-        <v>0.8340979966585225</v>
+        <v>0.8088222997900826</v>
       </c>
       <c r="Z34">
         <v>0</v>
@@ -4249,22 +4249,22 @@
     </row>
     <row r="35">
       <c r="A35">
-        <v>0.33</v>
+        <v>0.34</v>
       </c>
       <c r="B35">
-        <v>0.1026811215196058</v>
+        <v>0.1325991238451577</v>
       </c>
       <c r="C35">
-        <v>21602.4096904978</v>
+        <v>8048.060917464394</v>
       </c>
       <c r="D35">
-        <v>37854.27569049779</v>
+        <v>24806.6289174644</v>
       </c>
       <c r="E35">
-        <v>12861.766</v>
+        <v>13368.468</v>
       </c>
       <c r="F35">
-        <v>16721.166</v>
+        <v>17227.868</v>
       </c>
       <c r="G35">
         <v>469.3</v>
@@ -4285,45 +4285,45 @@
         <v>1604</v>
       </c>
       <c r="M35">
-        <v>1983.1302876</v>
+        <v>3459.355894400001</v>
       </c>
       <c r="N35">
-        <v>-379.1302876000002</v>
+        <v>-1855.355894400001</v>
       </c>
       <c r="O35">
-        <v>-97.81561420080006</v>
+        <v>-478.6818207552001</v>
       </c>
       <c r="P35">
-        <v>-281.3146733992002</v>
+        <v>-1376.674073644801</v>
       </c>
       <c r="Q35">
-        <v>25.08532660079982</v>
+        <v>-1070.2740736448</v>
       </c>
       <c r="R35">
-        <v>0.4925373134328359</v>
+        <v>0.5151515151515152</v>
       </c>
       <c r="S35">
-        <v>0.1070302818048587</v>
+        <v>0.1098398350527383</v>
       </c>
       <c r="T35">
-        <v>1.414094268010593</v>
+        <v>1.478980024312662</v>
       </c>
       <c r="U35">
-        <v>0.1186</v>
+        <v>0.2008</v>
       </c>
       <c r="V35">
-        <v>0.2086761533458413</v>
+        <v>0.1196268937434019</v>
       </c>
       <c r="W35">
-        <v>0.09385100821318322</v>
+        <v>0.1767789197363249</v>
       </c>
       <c r="X35" t="inlineStr">
         <is>
-          <t>Caa/CCC</t>
+          <t>C2/C</t>
         </is>
       </c>
       <c r="Y35">
-        <v>0.8088222997900826</v>
+        <v>0.4636701307883796</v>
       </c>
       <c r="Z35">
         <v>0</v>
@@ -4331,22 +4331,22 @@
     </row>
     <row r="36">
       <c r="A36">
-        <v>0.34</v>
+        <v>0.35</v>
       </c>
       <c r="B36">
-        <v>0.1325991238451577</v>
+        <v>0.1341491238451577</v>
       </c>
       <c r="C36">
-        <v>8048.060917464394</v>
+        <v>7106.150585467141</v>
       </c>
       <c r="D36">
-        <v>24806.6289174644</v>
+        <v>24371.42058546715</v>
       </c>
       <c r="E36">
-        <v>13368.468</v>
+        <v>13875.17</v>
       </c>
       <c r="F36">
-        <v>17227.868</v>
+        <v>17734.57</v>
       </c>
       <c r="G36">
         <v>469.3</v>
@@ -4367,37 +4367,37 @@
         <v>1604</v>
       </c>
       <c r="M36">
-        <v>3459.355894400001</v>
+        <v>3561.101656000001</v>
       </c>
       <c r="N36">
-        <v>-1855.355894400001</v>
+        <v>-1957.101656000001</v>
       </c>
       <c r="O36">
-        <v>-478.6818207552001</v>
+        <v>-504.9322272480002</v>
       </c>
       <c r="P36">
-        <v>-1376.674073644801</v>
+        <v>-1452.169428752001</v>
       </c>
       <c r="Q36">
-        <v>-1070.2740736448</v>
+        <v>-1145.769428752001</v>
       </c>
       <c r="R36">
-        <v>0.5151515151515152</v>
+        <v>0.5384615384615385</v>
       </c>
       <c r="S36">
-        <v>0.1098398350527383</v>
+        <v>0.1108250632843188</v>
       </c>
       <c r="T36">
-        <v>1.478980024312662</v>
+        <v>1.501733563148241</v>
       </c>
       <c r="U36">
         <v>0.2008</v>
       </c>
       <c r="V36">
-        <v>0.1196268937434019</v>
+        <v>0.1162089824935904</v>
       </c>
       <c r="W36">
-        <v>0.1767789197363249</v>
+        <v>0.177465236315287</v>
       </c>
       <c r="X36" t="inlineStr">
         <is>
@@ -4405,7 +4405,7 @@
         </is>
       </c>
       <c r="Y36">
-        <v>0.4636701307883796</v>
+        <v>0.4504224127658544</v>
       </c>
       <c r="Z36">
         <v>0</v>
@@ -4413,22 +4413,22 @@
     </row>
     <row r="37">
       <c r="A37">
-        <v>0.35</v>
+        <v>0.36</v>
       </c>
       <c r="B37">
-        <v>0.1341491238451577</v>
+        <v>0.1356991238451577</v>
       </c>
       <c r="C37">
-        <v>7106.150585467141</v>
+        <v>6179.247583591539</v>
       </c>
       <c r="D37">
-        <v>24371.42058546715</v>
+        <v>23951.21958359154</v>
       </c>
       <c r="E37">
-        <v>13875.17</v>
+        <v>14381.872</v>
       </c>
       <c r="F37">
-        <v>17734.57</v>
+        <v>18241.272</v>
       </c>
       <c r="G37">
         <v>469.3</v>
@@ -4449,37 +4449,37 @@
         <v>1604</v>
       </c>
       <c r="M37">
-        <v>3561.101656000001</v>
+        <v>3662.847417600001</v>
       </c>
       <c r="N37">
-        <v>-1957.101656000001</v>
+        <v>-2058.847417600001</v>
       </c>
       <c r="O37">
-        <v>-504.9322272480002</v>
+        <v>-531.1826337408003</v>
       </c>
       <c r="P37">
-        <v>-1452.169428752001</v>
+        <v>-1527.664783859201</v>
       </c>
       <c r="Q37">
-        <v>-1145.769428752001</v>
+        <v>-1221.264783859201</v>
       </c>
       <c r="R37">
-        <v>0.5384615384615385</v>
+        <v>0.5625000000000001</v>
       </c>
       <c r="S37">
-        <v>0.1108250632843188</v>
+        <v>0.1118410798981363</v>
       </c>
       <c r="T37">
-        <v>1.501733563148241</v>
+        <v>1.525198150072433</v>
       </c>
       <c r="U37">
         <v>0.2008</v>
       </c>
       <c r="V37">
-        <v>0.1162089824935904</v>
+        <v>0.1129809552021018</v>
       </c>
       <c r="W37">
-        <v>0.177465236315287</v>
+        <v>0.178113424195418</v>
       </c>
       <c r="X37" t="inlineStr">
         <is>
@@ -4487,7 +4487,7 @@
         </is>
       </c>
       <c r="Y37">
-        <v>0.4504224127658544</v>
+        <v>0.437910679077914</v>
       </c>
       <c r="Z37">
         <v>0</v>
@@ -4495,22 +4495,22 @@
     </row>
     <row r="38">
       <c r="A38">
-        <v>0.36</v>
+        <v>0.37</v>
       </c>
       <c r="B38">
-        <v>0.1356991238451577</v>
+        <v>0.1372491238451577</v>
       </c>
       <c r="C38">
-        <v>6179.247583591543</v>
+        <v>5266.588819944176</v>
       </c>
       <c r="D38">
-        <v>23951.21958359154</v>
+        <v>23545.26281994418</v>
       </c>
       <c r="E38">
-        <v>14381.872</v>
+        <v>14888.574</v>
       </c>
       <c r="F38">
-        <v>18241.272</v>
+        <v>18747.974</v>
       </c>
       <c r="G38">
         <v>469.3</v>
@@ -4531,37 +4531,37 @@
         <v>1604</v>
       </c>
       <c r="M38">
-        <v>3662.8474176</v>
+        <v>3764.593179200001</v>
       </c>
       <c r="N38">
-        <v>-2058.8474176</v>
+        <v>-2160.593179200001</v>
       </c>
       <c r="O38">
-        <v>-531.1826337408002</v>
+        <v>-557.4330402336002</v>
       </c>
       <c r="P38">
-        <v>-1527.6647838592</v>
+        <v>-1603.1601389664</v>
       </c>
       <c r="Q38">
-        <v>-1221.2647838592</v>
+        <v>-1296.760138966401</v>
       </c>
       <c r="R38">
-        <v>0.5625</v>
+        <v>0.5873015873015873</v>
       </c>
       <c r="S38">
-        <v>0.1118410798981363</v>
+        <v>0.1128893510076306</v>
       </c>
       <c r="T38">
-        <v>1.525198150072432</v>
+        <v>1.549407644518027</v>
       </c>
       <c r="U38">
         <v>0.2008</v>
       </c>
       <c r="V38">
-        <v>0.1129809552021018</v>
+        <v>0.1099274158723153</v>
       </c>
       <c r="W38">
-        <v>0.178113424195418</v>
+        <v>0.1787265748928391</v>
       </c>
       <c r="X38" t="inlineStr">
         <is>
@@ -4569,7 +4569,7 @@
         </is>
       </c>
       <c r="Y38">
-        <v>0.437910679077914</v>
+        <v>0.4260752553190514</v>
       </c>
       <c r="Z38">
         <v>0</v>
@@ -4577,22 +4577,22 @@
     </row>
     <row r="39">
       <c r="A39">
-        <v>0.37</v>
+        <v>0.38</v>
       </c>
       <c r="B39">
-        <v>0.1372491238451577</v>
+        <v>0.1387991238451577</v>
       </c>
       <c r="C39">
-        <v>5266.588819944176</v>
+        <v>4367.462075903819</v>
       </c>
       <c r="D39">
-        <v>23545.26281994418</v>
+        <v>23152.83807590382</v>
       </c>
       <c r="E39">
-        <v>14888.574</v>
+        <v>15395.276</v>
       </c>
       <c r="F39">
-        <v>18747.974</v>
+        <v>19254.676</v>
       </c>
       <c r="G39">
         <v>469.3</v>
@@ -4613,37 +4613,37 @@
         <v>1604</v>
       </c>
       <c r="M39">
-        <v>3764.593179200001</v>
+        <v>3866.338940800001</v>
       </c>
       <c r="N39">
-        <v>-2160.593179200001</v>
+        <v>-2262.338940800001</v>
       </c>
       <c r="O39">
-        <v>-557.4330402336002</v>
+        <v>-583.6834467264002</v>
       </c>
       <c r="P39">
-        <v>-1603.1601389664</v>
+        <v>-1678.6554940736</v>
       </c>
       <c r="Q39">
-        <v>-1296.760138966401</v>
+        <v>-1372.2554940736</v>
       </c>
       <c r="R39">
-        <v>0.5873015873015873</v>
+        <v>0.6129032258064516</v>
       </c>
       <c r="S39">
-        <v>0.1128893510076306</v>
+        <v>0.1139714373142053</v>
       </c>
       <c r="T39">
-        <v>1.549407644518027</v>
+        <v>1.57439809039735</v>
       </c>
       <c r="U39">
         <v>0.2008</v>
       </c>
       <c r="V39">
-        <v>0.1099274158723153</v>
+        <v>0.1070345891388333</v>
       </c>
       <c r="W39">
-        <v>0.1787265748928391</v>
+        <v>0.1793074545009223</v>
       </c>
       <c r="X39" t="inlineStr">
         <is>
@@ -4651,7 +4651,7 @@
         </is>
       </c>
       <c r="Y39">
-        <v>0.4260752553190514</v>
+        <v>0.4148627486001291</v>
       </c>
       <c r="Z39">
         <v>0</v>
@@ -4659,22 +4659,22 @@
     </row>
     <row r="40">
       <c r="A40">
-        <v>0.38</v>
+        <v>0.39</v>
       </c>
       <c r="B40">
-        <v>0.1387991238451577</v>
+        <v>0.1403491238451577</v>
       </c>
       <c r="C40">
-        <v>4367.462075903819</v>
+        <v>3481.201836142427</v>
       </c>
       <c r="D40">
-        <v>23152.83807590382</v>
+        <v>22773.27983614243</v>
       </c>
       <c r="E40">
-        <v>15395.276</v>
+        <v>15901.978</v>
       </c>
       <c r="F40">
-        <v>19254.676</v>
+        <v>19761.378</v>
       </c>
       <c r="G40">
         <v>469.3</v>
@@ -4695,37 +4695,37 @@
         <v>1604</v>
       </c>
       <c r="M40">
-        <v>3866.338940800001</v>
+        <v>3968.0847024</v>
       </c>
       <c r="N40">
-        <v>-2262.338940800001</v>
+        <v>-2364.0847024</v>
       </c>
       <c r="O40">
-        <v>-583.6834467264002</v>
+        <v>-609.9338532192002</v>
       </c>
       <c r="P40">
-        <v>-1678.6554940736</v>
+        <v>-1754.1508491808</v>
       </c>
       <c r="Q40">
-        <v>-1372.2554940736</v>
+        <v>-1447.7508491808</v>
       </c>
       <c r="R40">
-        <v>0.6129032258064516</v>
+        <v>0.639344262295082</v>
       </c>
       <c r="S40">
-        <v>0.1139714373142053</v>
+        <v>0.1150890018603397</v>
       </c>
       <c r="T40">
-        <v>1.57439809039735</v>
+        <v>1.600207895157962</v>
       </c>
       <c r="U40">
         <v>0.2008</v>
       </c>
       <c r="V40">
-        <v>0.1070345891388333</v>
+        <v>0.1042901124942478</v>
       </c>
       <c r="W40">
-        <v>0.1793074545009223</v>
+        <v>0.179858545411155</v>
       </c>
       <c r="X40" t="inlineStr">
         <is>
@@ -4733,7 +4733,7 @@
         </is>
       </c>
       <c r="Y40">
-        <v>0.4148627486001291</v>
+        <v>0.4042252422257668</v>
       </c>
       <c r="Z40">
         <v>0</v>
@@ -4741,22 +4741,22 @@
     </row>
     <row r="41">
       <c r="A41">
-        <v>0.39</v>
+        <v>0.4</v>
       </c>
       <c r="B41">
-        <v>0.1403491238451577</v>
+        <v>0.1418991238451577</v>
       </c>
       <c r="C41">
-        <v>3481.201836142427</v>
+        <v>2607.185522196156</v>
       </c>
       <c r="D41">
-        <v>22773.27983614243</v>
+        <v>22405.96552219616</v>
       </c>
       <c r="E41">
-        <v>15901.978</v>
+        <v>16408.68</v>
       </c>
       <c r="F41">
-        <v>19761.378</v>
+        <v>20268.08</v>
       </c>
       <c r="G41">
         <v>469.3</v>
@@ -4777,37 +4777,37 @@
         <v>1604</v>
       </c>
       <c r="M41">
-        <v>3968.0847024</v>
+        <v>4069.830464000001</v>
       </c>
       <c r="N41">
-        <v>-2364.0847024</v>
+        <v>-2465.830464000001</v>
       </c>
       <c r="O41">
-        <v>-609.9338532192002</v>
+        <v>-636.1842597120002</v>
       </c>
       <c r="P41">
-        <v>-1754.1508491808</v>
+        <v>-1829.646204288</v>
       </c>
       <c r="Q41">
-        <v>-1447.7508491808</v>
+        <v>-1523.246204288</v>
       </c>
       <c r="R41">
-        <v>0.639344262295082</v>
+        <v>0.6666666666666667</v>
       </c>
       <c r="S41">
-        <v>0.1150890018603397</v>
+        <v>0.1162438185580121</v>
       </c>
       <c r="T41">
-        <v>1.600207895157962</v>
+        <v>1.626878026743928</v>
       </c>
       <c r="U41">
         <v>0.2008</v>
       </c>
       <c r="V41">
-        <v>0.1042901124942478</v>
+        <v>0.1016828596818916</v>
       </c>
       <c r="W41">
-        <v>0.179858545411155</v>
+        <v>0.1803820817758762</v>
       </c>
       <c r="X41" t="inlineStr">
         <is>
@@ -4815,7 +4815,7 @@
         </is>
       </c>
       <c r="Y41">
-        <v>0.4042252422257668</v>
+        <v>0.3941196111701226</v>
       </c>
       <c r="Z41">
         <v>0</v>
@@ -4823,22 +4823,22 @@
     </row>
     <row r="42">
       <c r="A42">
-        <v>0.4</v>
+        <v>0.41</v>
       </c>
       <c r="B42">
-        <v>0.1418991238451577</v>
+        <v>0.1434491238451577</v>
       </c>
       <c r="C42">
-        <v>2607.185522196156</v>
+        <v>1744.830084747256</v>
       </c>
       <c r="D42">
-        <v>22405.96552219616</v>
+        <v>22050.31208474726</v>
       </c>
       <c r="E42">
-        <v>16408.68</v>
+        <v>16915.382</v>
       </c>
       <c r="F42">
-        <v>20268.08</v>
+        <v>20774.782</v>
       </c>
       <c r="G42">
         <v>469.3</v>
@@ -4859,37 +4859,37 @@
         <v>1604</v>
       </c>
       <c r="M42">
-        <v>4069.830464000001</v>
+        <v>4171.576225600001</v>
       </c>
       <c r="N42">
-        <v>-2465.830464000001</v>
+        <v>-2567.576225600001</v>
       </c>
       <c r="O42">
-        <v>-636.1842597120002</v>
+        <v>-662.4346662048002</v>
       </c>
       <c r="P42">
-        <v>-1829.646204288</v>
+        <v>-1905.141559395201</v>
       </c>
       <c r="Q42">
-        <v>-1523.246204288</v>
+        <v>-1598.741559395201</v>
       </c>
       <c r="R42">
-        <v>0.6666666666666667</v>
+        <v>0.6949152542372882</v>
       </c>
       <c r="S42">
-        <v>0.1162438185580121</v>
+        <v>0.1174377815844191</v>
       </c>
       <c r="T42">
-        <v>1.626878026743928</v>
+        <v>1.654452230587045</v>
       </c>
       <c r="U42">
         <v>0.2008</v>
       </c>
       <c r="V42">
-        <v>0.1016828596818916</v>
+        <v>0.09920278993355282</v>
       </c>
       <c r="W42">
-        <v>0.1803820817758762</v>
+        <v>0.1808800797813426</v>
       </c>
       <c r="X42" t="inlineStr">
         <is>
@@ -4897,7 +4897,7 @@
         </is>
       </c>
       <c r="Y42">
-        <v>0.3941196111701226</v>
+        <v>0.3845069377269489</v>
       </c>
       <c r="Z42">
         <v>0</v>
@@ -4905,22 +4905,22 @@
     </row>
     <row r="43">
       <c r="A43">
-        <v>0.41</v>
+        <v>0.42</v>
       </c>
       <c r="B43">
-        <v>0.1434491238451577</v>
+        <v>0.1449991238451577</v>
       </c>
       <c r="C43">
-        <v>1744.830084747256</v>
+        <v>893.5889153821336</v>
       </c>
       <c r="D43">
-        <v>22050.31208474726</v>
+        <v>21705.77291538214</v>
       </c>
       <c r="E43">
-        <v>16915.382</v>
+        <v>17422.084</v>
       </c>
       <c r="F43">
-        <v>20774.782</v>
+        <v>21281.484</v>
       </c>
       <c r="G43">
         <v>469.3</v>
@@ -4941,37 +4941,37 @@
         <v>1604</v>
       </c>
       <c r="M43">
-        <v>4171.576225600001</v>
+        <v>4273.321987200001</v>
       </c>
       <c r="N43">
-        <v>-2567.576225600001</v>
+        <v>-2669.321987200001</v>
       </c>
       <c r="O43">
-        <v>-662.4346662048002</v>
+        <v>-688.6850726976003</v>
       </c>
       <c r="P43">
-        <v>-1905.141559395201</v>
+        <v>-1980.6369145024</v>
       </c>
       <c r="Q43">
-        <v>-1598.741559395201</v>
+        <v>-1674.2369145024</v>
       </c>
       <c r="R43">
-        <v>0.6949152542372882</v>
+        <v>0.7241379310344829</v>
       </c>
       <c r="S43">
-        <v>0.1174377815844191</v>
+        <v>0.1186729157496677</v>
       </c>
       <c r="T43">
-        <v>1.654452230587045</v>
+        <v>1.682977269045443</v>
       </c>
       <c r="U43">
         <v>0.2008</v>
       </c>
       <c r="V43">
-        <v>0.09920278993355282</v>
+        <v>0.09684081874465869</v>
       </c>
       <c r="W43">
-        <v>0.1808800797813426</v>
+        <v>0.1813543635960725</v>
       </c>
       <c r="X43" t="inlineStr">
         <is>
@@ -4979,7 +4979,7 @@
         </is>
       </c>
       <c r="Y43">
-        <v>0.3845069377269489</v>
+        <v>0.375352010638212</v>
       </c>
       <c r="Z43">
         <v>0</v>
@@ -4987,22 +4987,22 @@
     </row>
     <row r="44">
       <c r="A44">
-        <v>0.42</v>
+        <v>0.43</v>
       </c>
       <c r="B44">
-        <v>0.1449991238451577</v>
+        <v>0.1465491238451577</v>
       </c>
       <c r="C44">
-        <v>893.5889153821408</v>
+        <v>52.9490434205909</v>
       </c>
       <c r="D44">
-        <v>21705.77291538214</v>
+        <v>21371.83504342059</v>
       </c>
       <c r="E44">
-        <v>17422.084</v>
+        <v>17928.786</v>
       </c>
       <c r="F44">
-        <v>21281.484</v>
+        <v>21788.186</v>
       </c>
       <c r="G44">
         <v>469.3</v>
@@ -5023,37 +5023,37 @@
         <v>1604</v>
       </c>
       <c r="M44">
-        <v>4273.3219872</v>
+        <v>4375.0677488</v>
       </c>
       <c r="N44">
-        <v>-2669.3219872</v>
+        <v>-2771.0677488</v>
       </c>
       <c r="O44">
-        <v>-688.6850726976</v>
+        <v>-714.9354791904001</v>
       </c>
       <c r="P44">
-        <v>-1980.6369145024</v>
+        <v>-2056.1322696096</v>
       </c>
       <c r="Q44">
-        <v>-1674.2369145024</v>
+        <v>-1749.7322696096</v>
       </c>
       <c r="R44">
-        <v>0.7241379310344827</v>
+        <v>0.7543859649122806</v>
       </c>
       <c r="S44">
-        <v>0.1186729157496677</v>
+        <v>0.1199513879558022</v>
       </c>
       <c r="T44">
-        <v>1.682977269045443</v>
+        <v>1.71250318604624</v>
       </c>
       <c r="U44">
         <v>0.2008</v>
       </c>
       <c r="V44">
-        <v>0.09684081874465873</v>
+        <v>0.09458870668082944</v>
       </c>
       <c r="W44">
-        <v>0.1813543635960725</v>
+        <v>0.1818065876984895</v>
       </c>
       <c r="X44" t="inlineStr">
         <is>
@@ -5061,7 +5061,7 @@
         </is>
       </c>
       <c r="Y44">
-        <v>0.3753520106382121</v>
+        <v>0.366622894111742</v>
       </c>
       <c r="Z44">
         <v>0</v>
@@ -5069,22 +5069,22 @@
     </row>
     <row r="45">
       <c r="A45">
-        <v>0.43</v>
+        <v>0.44</v>
       </c>
       <c r="B45">
-        <v>0.1465491238451577</v>
+        <v>0.1480991238451577</v>
       </c>
       <c r="C45">
-        <v>52.9490434205909</v>
+        <v>-777.5714124191945</v>
       </c>
       <c r="D45">
-        <v>21371.83504342059</v>
+        <v>21048.01658758081</v>
       </c>
       <c r="E45">
-        <v>17928.786</v>
+        <v>18435.488</v>
       </c>
       <c r="F45">
-        <v>21788.186</v>
+        <v>22294.888</v>
       </c>
       <c r="G45">
         <v>469.3</v>
@@ -5105,37 +5105,37 @@
         <v>1604</v>
       </c>
       <c r="M45">
-        <v>4375.0677488</v>
+        <v>4476.8135104</v>
       </c>
       <c r="N45">
-        <v>-2771.0677488</v>
+        <v>-2872.8135104</v>
       </c>
       <c r="O45">
-        <v>-714.9354791904001</v>
+        <v>-741.1858856832001</v>
       </c>
       <c r="P45">
-        <v>-2056.1322696096</v>
+        <v>-2131.6276247168</v>
       </c>
       <c r="Q45">
-        <v>-1749.7322696096</v>
+        <v>-1825.2276247168</v>
       </c>
       <c r="R45">
-        <v>0.7543859649122806</v>
+        <v>0.7857142857142857</v>
       </c>
       <c r="S45">
-        <v>0.1199513879558022</v>
+        <v>0.1212755198835844</v>
       </c>
       <c r="T45">
-        <v>1.71250318604624</v>
+        <v>1.74308360008278</v>
       </c>
       <c r="U45">
         <v>0.2008</v>
       </c>
       <c r="V45">
-        <v>0.09458870668082944</v>
+        <v>0.09243896334717423</v>
       </c>
       <c r="W45">
-        <v>0.1818065876984895</v>
+        <v>0.1822382561598874</v>
       </c>
       <c r="X45" t="inlineStr">
         <is>
@@ -5143,7 +5143,7 @@
         </is>
       </c>
       <c r="Y45">
-        <v>0.366622894111742</v>
+        <v>0.3582905556092024</v>
       </c>
       <c r="Z45">
         <v>0</v>
@@ -5151,22 +5151,22 @@
     </row>
     <row r="46">
       <c r="A46">
-        <v>0.44</v>
+        <v>0.45</v>
       </c>
       <c r="B46">
-        <v>0.1480991238451577</v>
+        <v>0.1496491238451577</v>
       </c>
       <c r="C46">
-        <v>-777.5714124191945</v>
+        <v>-1598.425564144563</v>
       </c>
       <c r="D46">
-        <v>21048.01658758081</v>
+        <v>20733.86443585544</v>
       </c>
       <c r="E46">
-        <v>18435.488</v>
+        <v>18942.19</v>
       </c>
       <c r="F46">
-        <v>22294.888</v>
+        <v>22801.59</v>
       </c>
       <c r="G46">
         <v>469.3</v>
@@ -5187,37 +5187,37 @@
         <v>1604</v>
       </c>
       <c r="M46">
-        <v>4476.8135104</v>
+        <v>4578.559272000001</v>
       </c>
       <c r="N46">
-        <v>-2872.8135104</v>
+        <v>-2974.559272000001</v>
       </c>
       <c r="O46">
-        <v>-741.1858856832001</v>
+        <v>-767.4362921760004</v>
       </c>
       <c r="P46">
-        <v>-2131.6276247168</v>
+        <v>-2207.122979824001</v>
       </c>
       <c r="Q46">
-        <v>-1825.2276247168</v>
+        <v>-1900.722979824001</v>
       </c>
       <c r="R46">
-        <v>0.7857142857142857</v>
+        <v>0.8181818181818181</v>
       </c>
       <c r="S46">
-        <v>0.1212755198835844</v>
+        <v>0.1226478020632859</v>
       </c>
       <c r="T46">
-        <v>1.74308360008278</v>
+        <v>1.774776029175194</v>
       </c>
       <c r="U46">
         <v>0.2008</v>
       </c>
       <c r="V46">
-        <v>0.09243896334717423</v>
+        <v>0.09038476416168144</v>
       </c>
       <c r="W46">
-        <v>0.1822382561598874</v>
+        <v>0.1826507393563344</v>
       </c>
       <c r="X46" t="inlineStr">
         <is>
@@ -5225,7 +5225,7 @@
         </is>
       </c>
       <c r="Y46">
-        <v>0.3582905556092024</v>
+        <v>0.3503285432623312</v>
       </c>
       <c r="Z46">
         <v>0</v>
@@ -5233,22 +5233,22 @@
     </row>
     <row r="47">
       <c r="A47">
-        <v>0.45</v>
+        <v>0.46</v>
       </c>
       <c r="B47">
-        <v>0.1496491238451577</v>
+        <v>0.1511991238451577</v>
       </c>
       <c r="C47">
-        <v>-1598.425564144563</v>
+        <v>-2410.039869893793</v>
       </c>
       <c r="D47">
-        <v>20733.86443585544</v>
+        <v>20428.95213010621</v>
       </c>
       <c r="E47">
-        <v>18942.19</v>
+        <v>19448.892</v>
       </c>
       <c r="F47">
-        <v>22801.59</v>
+        <v>23308.292</v>
       </c>
       <c r="G47">
         <v>469.3</v>
@@ -5269,37 +5269,37 @@
         <v>1604</v>
       </c>
       <c r="M47">
-        <v>4578.559272000001</v>
+        <v>4680.305033600001</v>
       </c>
       <c r="N47">
-        <v>-2974.559272000001</v>
+        <v>-3076.305033600001</v>
       </c>
       <c r="O47">
-        <v>-767.4362921760004</v>
+        <v>-793.6866986688002</v>
       </c>
       <c r="P47">
-        <v>-2207.122979824001</v>
+        <v>-2282.6183349312</v>
       </c>
       <c r="Q47">
-        <v>-1900.722979824001</v>
+        <v>-1976.2183349312</v>
       </c>
       <c r="R47">
-        <v>0.8181818181818181</v>
+        <v>0.8518518518518519</v>
       </c>
       <c r="S47">
-        <v>0.1226478020632859</v>
+        <v>0.1240709095089023</v>
       </c>
       <c r="T47">
-        <v>1.774776029175194</v>
+        <v>1.807642251937698</v>
       </c>
       <c r="U47">
         <v>0.2008</v>
       </c>
       <c r="V47">
-        <v>0.09038476416168144</v>
+        <v>0.0884198779842536</v>
       </c>
       <c r="W47">
-        <v>0.1826507393563344</v>
+        <v>0.1830452885007619</v>
       </c>
       <c r="X47" t="inlineStr">
         <is>
@@ -5307,7 +5307,7 @@
         </is>
       </c>
       <c r="Y47">
-        <v>0.3503285432623312</v>
+        <v>0.3427127053653241</v>
       </c>
       <c r="Z47">
         <v>0</v>
@@ -5315,22 +5315,22 @@
     </row>
     <row r="48">
       <c r="A48">
-        <v>0.46</v>
+        <v>0.47</v>
       </c>
       <c r="B48">
-        <v>0.1511991238451577</v>
+        <v>0.1527491238451577</v>
       </c>
       <c r="C48">
-        <v>-2410.039869893793</v>
+        <v>-3212.816065391733</v>
       </c>
       <c r="D48">
-        <v>20428.95213010621</v>
+        <v>20132.87793460827</v>
       </c>
       <c r="E48">
-        <v>19448.892</v>
+        <v>19955.594</v>
       </c>
       <c r="F48">
-        <v>23308.292</v>
+        <v>23814.994</v>
       </c>
       <c r="G48">
         <v>469.3</v>
@@ -5351,37 +5351,37 @@
         <v>1604</v>
       </c>
       <c r="M48">
-        <v>4680.305033600001</v>
+        <v>4782.050795200001</v>
       </c>
       <c r="N48">
-        <v>-3076.305033600001</v>
+        <v>-3178.050795200001</v>
       </c>
       <c r="O48">
-        <v>-793.6866986688002</v>
+        <v>-819.9371051616002</v>
       </c>
       <c r="P48">
-        <v>-2282.6183349312</v>
+        <v>-2358.1136900384</v>
       </c>
       <c r="Q48">
-        <v>-1976.2183349312</v>
+        <v>-2051.7136900384</v>
       </c>
       <c r="R48">
-        <v>0.8518518518518519</v>
+        <v>0.8867924528301887</v>
       </c>
       <c r="S48">
-        <v>0.1240709095089023</v>
+        <v>0.1255477191222778</v>
       </c>
       <c r="T48">
-        <v>1.807642251937698</v>
+        <v>1.841748709521428</v>
       </c>
       <c r="U48">
         <v>0.2008</v>
       </c>
       <c r="V48">
-        <v>0.0884198779842536</v>
+        <v>0.08653860398458862</v>
       </c>
       <c r="W48">
-        <v>0.1830452885007619</v>
+        <v>0.1834230483198946</v>
       </c>
       <c r="X48" t="inlineStr">
         <is>
@@ -5389,7 +5389,7 @@
         </is>
       </c>
       <c r="Y48">
-        <v>0.3427127053653241</v>
+        <v>0.3354209456767001</v>
       </c>
       <c r="Z48">
         <v>0</v>
@@ -5397,22 +5397,22 @@
     </row>
     <row r="49">
       <c r="A49">
-        <v>0.47</v>
+        <v>0.48</v>
       </c>
       <c r="B49">
-        <v>0.1527491238451577</v>
+        <v>0.1542991238451577</v>
       </c>
       <c r="C49">
-        <v>-3212.816065391733</v>
+        <v>-4007.132929850715</v>
       </c>
       <c r="D49">
-        <v>20132.87793460827</v>
+        <v>19845.26307014929</v>
       </c>
       <c r="E49">
-        <v>19955.594</v>
+        <v>20462.296</v>
       </c>
       <c r="F49">
-        <v>23814.994</v>
+        <v>24321.696</v>
       </c>
       <c r="G49">
         <v>469.3</v>
@@ -5433,37 +5433,37 @@
         <v>1604</v>
       </c>
       <c r="M49">
-        <v>4782.050795200001</v>
+        <v>4883.796556800001</v>
       </c>
       <c r="N49">
-        <v>-3178.050795200001</v>
+        <v>-3279.796556800001</v>
       </c>
       <c r="O49">
-        <v>-819.9371051616002</v>
+        <v>-846.1875116544003</v>
       </c>
       <c r="P49">
-        <v>-2358.1136900384</v>
+        <v>-2433.609045145601</v>
       </c>
       <c r="Q49">
-        <v>-2051.7136900384</v>
+        <v>-2127.209045145601</v>
       </c>
       <c r="R49">
-        <v>0.8867924528301887</v>
+        <v>0.9230769230769231</v>
       </c>
       <c r="S49">
-        <v>0.1255477191222778</v>
+        <v>0.1270813291053986</v>
       </c>
       <c r="T49">
-        <v>1.841748709521428</v>
+        <v>1.877166953935302</v>
       </c>
       <c r="U49">
         <v>0.2008</v>
       </c>
       <c r="V49">
-        <v>0.08653860398458862</v>
+        <v>0.08473571640157636</v>
       </c>
       <c r="W49">
-        <v>0.1834230483198946</v>
+        <v>0.1837850681465635</v>
       </c>
       <c r="X49" t="inlineStr">
         <is>
@@ -5471,7 +5471,7 @@
         </is>
       </c>
       <c r="Y49">
-        <v>0.3354209456767001</v>
+        <v>0.3284330093084356</v>
       </c>
       <c r="Z49">
         <v>0</v>
@@ -5479,22 +5479,22 @@
     </row>
     <row r="50">
       <c r="A50">
-        <v>0.48</v>
+        <v>0.49</v>
       </c>
       <c r="B50">
-        <v>0.1542991238451577</v>
+        <v>0.1558491238451577</v>
       </c>
       <c r="C50">
-        <v>-4007.132929850704</v>
+        <v>-4793.34790263922</v>
       </c>
       <c r="D50">
-        <v>19845.2630701493</v>
+        <v>19565.75009736078</v>
       </c>
       <c r="E50">
-        <v>20462.296</v>
+        <v>20968.998</v>
       </c>
       <c r="F50">
-        <v>24321.696</v>
+        <v>24828.398</v>
       </c>
       <c r="G50">
         <v>469.3</v>
@@ -5515,37 +5515,37 @@
         <v>1604</v>
       </c>
       <c r="M50">
-        <v>4883.7965568</v>
+        <v>4985.5423184</v>
       </c>
       <c r="N50">
-        <v>-3279.7965568</v>
+        <v>-3381.5423184</v>
       </c>
       <c r="O50">
-        <v>-846.1875116544001</v>
+        <v>-872.4379181472001</v>
       </c>
       <c r="P50">
-        <v>-2433.6090451456</v>
+        <v>-2509.1044002528</v>
       </c>
       <c r="Q50">
-        <v>-2127.2090451456</v>
+        <v>-2202.7044002528</v>
       </c>
       <c r="R50">
-        <v>0.923076923076923</v>
+        <v>0.9607843137254901</v>
       </c>
       <c r="S50">
-        <v>0.1270813291053985</v>
+        <v>0.1286750806564848</v>
       </c>
       <c r="T50">
-        <v>1.877166953935302</v>
+        <v>1.913974149110503</v>
       </c>
       <c r="U50">
         <v>0.2008</v>
       </c>
       <c r="V50">
-        <v>0.08473571640157637</v>
+        <v>0.08300641606685033</v>
       </c>
       <c r="W50">
-        <v>0.1837850681465635</v>
+        <v>0.1841323116537765</v>
       </c>
       <c r="X50" t="inlineStr">
         <is>
@@ -5553,7 +5553,7 @@
         </is>
       </c>
       <c r="Y50">
-        <v>0.3284330093084356</v>
+        <v>0.3217302948327532</v>
       </c>
       <c r="Z50">
         <v>0</v>
@@ -5561,22 +5561,22 @@
     </row>
     <row r="51">
       <c r="A51">
-        <v>0.49</v>
+        <v>0.5</v>
       </c>
       <c r="B51">
-        <v>0.1558491238451577</v>
+        <v>0.1573991238451577</v>
       </c>
       <c r="C51">
-        <v>-4793.34790263922</v>
+        <v>-5571.798565227182</v>
       </c>
       <c r="D51">
-        <v>19565.75009736078</v>
+        <v>19294.00143477282</v>
       </c>
       <c r="E51">
-        <v>20968.998</v>
+        <v>21475.7</v>
       </c>
       <c r="F51">
-        <v>24828.398</v>
+        <v>25335.1</v>
       </c>
       <c r="G51">
         <v>469.3</v>
@@ -5597,37 +5597,37 @@
         <v>1604</v>
       </c>
       <c r="M51">
-        <v>4985.5423184</v>
+        <v>5087.28808</v>
       </c>
       <c r="N51">
-        <v>-3381.5423184</v>
+        <v>-3483.28808</v>
       </c>
       <c r="O51">
-        <v>-872.4379181472001</v>
+        <v>-898.6883246400001</v>
       </c>
       <c r="P51">
-        <v>-2509.1044002528</v>
+        <v>-2584.59975536</v>
       </c>
       <c r="Q51">
-        <v>-2202.7044002528</v>
+        <v>-2278.19975536</v>
       </c>
       <c r="R51">
-        <v>0.9607843137254901</v>
+        <v>1</v>
       </c>
       <c r="S51">
-        <v>0.1286750806564848</v>
+        <v>0.1303325822696145</v>
       </c>
       <c r="T51">
-        <v>1.913974149110503</v>
+        <v>1.952253632092714</v>
       </c>
       <c r="U51">
         <v>0.2008</v>
       </c>
       <c r="V51">
-        <v>0.08300641606685033</v>
+        <v>0.08134628774551331</v>
       </c>
       <c r="W51">
-        <v>0.1841323116537765</v>
+        <v>0.1844656654207009</v>
       </c>
       <c r="X51" t="inlineStr">
         <is>
@@ -5635,7 +5635,7 @@
         </is>
       </c>
       <c r="Y51">
-        <v>0.3217302948327532</v>
+        <v>0.3152956889360982</v>
       </c>
       <c r="Z51">
         <v>0</v>
@@ -5643,22 +5643,22 @@
     </row>
     <row r="52">
       <c r="A52">
-        <v>0.5</v>
+        <v>0.51</v>
       </c>
       <c r="B52">
-        <v>0.1573991238451577</v>
+        <v>0.1589491238451577</v>
       </c>
       <c r="C52">
-        <v>-5571.798565227182</v>
+        <v>-6342.804001326462</v>
       </c>
       <c r="D52">
-        <v>19294.00143477282</v>
+        <v>19029.69799867354</v>
       </c>
       <c r="E52">
-        <v>21475.7</v>
+        <v>21982.402</v>
       </c>
       <c r="F52">
-        <v>25335.1</v>
+        <v>25841.802</v>
       </c>
       <c r="G52">
         <v>469.3</v>
@@ -5679,37 +5679,37 @@
         <v>1604</v>
       </c>
       <c r="M52">
-        <v>5087.28808</v>
+        <v>5189.0338416</v>
       </c>
       <c r="N52">
-        <v>-3483.28808</v>
+        <v>-3585.0338416</v>
       </c>
       <c r="O52">
-        <v>-898.6883246400001</v>
+        <v>-924.9387311328002</v>
       </c>
       <c r="P52">
-        <v>-2584.59975536</v>
+        <v>-2660.0951104672</v>
       </c>
       <c r="Q52">
-        <v>-2278.19975536</v>
+        <v>-2353.6951104672</v>
       </c>
       <c r="R52">
-        <v>1</v>
+        <v>1.040816326530612</v>
       </c>
       <c r="S52">
-        <v>0.1303325822696145</v>
+        <v>0.1320577370098107</v>
       </c>
       <c r="T52">
-        <v>1.952253632092714</v>
+        <v>1.992095542951749</v>
       </c>
       <c r="U52">
         <v>0.2008</v>
       </c>
       <c r="V52">
-        <v>0.08134628774551331</v>
+        <v>0.07975126249560129</v>
       </c>
       <c r="W52">
-        <v>0.1844656654207009</v>
+        <v>0.1847859464908833</v>
       </c>
       <c r="X52" t="inlineStr">
         <is>
@@ -5717,7 +5717,7 @@
         </is>
       </c>
       <c r="Y52">
-        <v>0.3152956889360982</v>
+        <v>0.3091134205255864</v>
       </c>
       <c r="Z52">
         <v>0</v>
@@ -5725,22 +5725,22 @@
     </row>
     <row r="53">
       <c r="A53">
-        <v>0.51</v>
+        <v>0.52</v>
       </c>
       <c r="B53">
-        <v>0.1589491238451577</v>
+        <v>0.1604991238451577</v>
       </c>
       <c r="C53">
-        <v>-6342.804001326462</v>
+        <v>-7106.666046748982</v>
       </c>
       <c r="D53">
-        <v>19029.69799867354</v>
+        <v>18772.53795325102</v>
       </c>
       <c r="E53">
-        <v>21982.402</v>
+        <v>22489.104</v>
       </c>
       <c r="F53">
-        <v>25841.802</v>
+        <v>26348.504</v>
       </c>
       <c r="G53">
         <v>469.3</v>
@@ -5761,37 +5761,37 @@
         <v>1604</v>
       </c>
       <c r="M53">
-        <v>5189.0338416</v>
+        <v>5290.779603200001</v>
       </c>
       <c r="N53">
-        <v>-3585.0338416</v>
+        <v>-3686.779603200001</v>
       </c>
       <c r="O53">
-        <v>-924.9387311328002</v>
+        <v>-951.1891376256004</v>
       </c>
       <c r="P53">
-        <v>-2660.0951104672</v>
+        <v>-2735.590465574401</v>
       </c>
       <c r="Q53">
-        <v>-2353.6951104672</v>
+        <v>-2429.190465574401</v>
       </c>
       <c r="R53">
-        <v>1.040816326530612</v>
+        <v>1.083333333333333</v>
       </c>
       <c r="S53">
-        <v>0.1320577370098107</v>
+        <v>0.1338547731975151</v>
       </c>
       <c r="T53">
-        <v>1.992095542951749</v>
+        <v>2.03359753342991</v>
       </c>
       <c r="U53">
         <v>0.2008</v>
       </c>
       <c r="V53">
-        <v>0.07975126249560129</v>
+        <v>0.07821758437068586</v>
       </c>
       <c r="W53">
-        <v>0.1847859464908833</v>
+        <v>0.1850939090583663</v>
       </c>
       <c r="X53" t="inlineStr">
         <is>
@@ -5799,7 +5799,7 @@
         </is>
       </c>
       <c r="Y53">
-        <v>0.3091134205255864</v>
+        <v>0.303168931669325</v>
       </c>
       <c r="Z53">
         <v>0</v>
@@ -5807,22 +5807,22 @@
     </row>
     <row r="54">
       <c r="A54">
-        <v>0.52</v>
+        <v>0.53</v>
       </c>
       <c r="B54">
-        <v>0.1604991238451577</v>
+        <v>0.1620491238451577</v>
       </c>
       <c r="C54">
-        <v>-7106.666046748982</v>
+        <v>-7863.670439275367</v>
       </c>
       <c r="D54">
-        <v>18772.53795325102</v>
+        <v>18522.23556072464</v>
       </c>
       <c r="E54">
-        <v>22489.104</v>
+        <v>22995.806</v>
       </c>
       <c r="F54">
-        <v>26348.504</v>
+        <v>26855.206</v>
       </c>
       <c r="G54">
         <v>469.3</v>
@@ -5843,37 +5843,37 @@
         <v>1604</v>
       </c>
       <c r="M54">
-        <v>5290.779603200001</v>
+        <v>5392.525364800001</v>
       </c>
       <c r="N54">
-        <v>-3686.779603200001</v>
+        <v>-3788.525364800001</v>
       </c>
       <c r="O54">
-        <v>-951.1891376256004</v>
+        <v>-977.4395441184002</v>
       </c>
       <c r="P54">
-        <v>-2735.590465574401</v>
+        <v>-2811.085820681601</v>
       </c>
       <c r="Q54">
-        <v>-2429.190465574401</v>
+        <v>-2504.6858206816</v>
       </c>
       <c r="R54">
-        <v>1.083333333333333</v>
+        <v>1.127659574468085</v>
       </c>
       <c r="S54">
-        <v>0.1338547731975151</v>
+        <v>0.1357282790102282</v>
       </c>
       <c r="T54">
-        <v>2.03359753342991</v>
+        <v>2.076865566056078</v>
       </c>
       <c r="U54">
         <v>0.2008</v>
       </c>
       <c r="V54">
-        <v>0.07821758437068586</v>
+        <v>0.0767417808919937</v>
       </c>
       <c r="W54">
-        <v>0.1850939090583663</v>
+        <v>0.1853902503968877</v>
       </c>
       <c r="X54" t="inlineStr">
         <is>
@@ -5881,7 +5881,7 @@
         </is>
       </c>
       <c r="Y54">
-        <v>0.303168931669325</v>
+        <v>0.2974487631472623</v>
       </c>
       <c r="Z54">
         <v>0</v>
@@ -5889,22 +5889,22 @@
     </row>
     <row r="55">
       <c r="A55">
-        <v>0.53</v>
+        <v>0.54</v>
       </c>
       <c r="B55">
-        <v>0.1620491238451577</v>
+        <v>0.1635991238451577</v>
       </c>
       <c r="C55">
-        <v>-7863.670439275367</v>
+        <v>-8614.08787774383</v>
       </c>
       <c r="D55">
-        <v>18522.23556072464</v>
+        <v>18278.52012225617</v>
       </c>
       <c r="E55">
-        <v>22995.806</v>
+        <v>23502.508</v>
       </c>
       <c r="F55">
-        <v>26855.206</v>
+        <v>27361.908</v>
       </c>
       <c r="G55">
         <v>469.3</v>
@@ -5925,37 +5925,37 @@
         <v>1604</v>
       </c>
       <c r="M55">
-        <v>5392.525364800001</v>
+        <v>5494.271126400001</v>
       </c>
       <c r="N55">
-        <v>-3788.525364800001</v>
+        <v>-3890.271126400001</v>
       </c>
       <c r="O55">
-        <v>-977.4395441184002</v>
+        <v>-1003.6899506112</v>
       </c>
       <c r="P55">
-        <v>-2811.085820681601</v>
+        <v>-2886.5811757888</v>
       </c>
       <c r="Q55">
-        <v>-2504.6858206816</v>
+        <v>-2580.1811757888</v>
       </c>
       <c r="R55">
-        <v>1.127659574468085</v>
+        <v>1.173913043478261</v>
       </c>
       <c r="S55">
-        <v>0.1357282790102282</v>
+        <v>0.1376832415974071</v>
       </c>
       <c r="T55">
-        <v>2.076865566056078</v>
+        <v>2.12201481749208</v>
       </c>
       <c r="U55">
         <v>0.2008</v>
       </c>
       <c r="V55">
-        <v>0.0767417808919937</v>
+        <v>0.07532063680140122</v>
       </c>
       <c r="W55">
-        <v>0.1853902503968877</v>
+        <v>0.1856756161302786</v>
       </c>
       <c r="X55" t="inlineStr">
         <is>
@@ -5963,7 +5963,7 @@
         </is>
       </c>
       <c r="Y55">
-        <v>0.2974487631472623</v>
+        <v>0.2919404527186094</v>
       </c>
       <c r="Z55">
         <v>0</v>
@@ -5971,22 +5971,22 @@
     </row>
     <row r="56">
       <c r="A56">
-        <v>0.54</v>
+        <v>0.55</v>
       </c>
       <c r="B56">
-        <v>0.1635991238451577</v>
+        <v>0.1651491238451577</v>
       </c>
       <c r="C56">
-        <v>-8614.08787774383</v>
+        <v>-9358.174998612034</v>
       </c>
       <c r="D56">
-        <v>18278.52012225617</v>
+        <v>18041.13500138797</v>
       </c>
       <c r="E56">
-        <v>23502.508</v>
+        <v>24009.21</v>
       </c>
       <c r="F56">
-        <v>27361.908</v>
+        <v>27868.61</v>
       </c>
       <c r="G56">
         <v>469.3</v>
@@ -6007,37 +6007,37 @@
         <v>1604</v>
       </c>
       <c r="M56">
-        <v>5494.271126400001</v>
+        <v>5596.016888000001</v>
       </c>
       <c r="N56">
-        <v>-3890.271126400001</v>
+        <v>-3992.016888000001</v>
       </c>
       <c r="O56">
-        <v>-1003.6899506112</v>
+        <v>-1029.940357104</v>
       </c>
       <c r="P56">
-        <v>-2886.5811757888</v>
+        <v>-2962.076530896001</v>
       </c>
       <c r="Q56">
-        <v>-2580.1811757888</v>
+        <v>-2655.676530896001</v>
       </c>
       <c r="R56">
-        <v>1.173913043478261</v>
+        <v>1.222222222222223</v>
       </c>
       <c r="S56">
-        <v>0.1376832415974071</v>
+        <v>0.1397250914106828</v>
       </c>
       <c r="T56">
-        <v>2.12201481749208</v>
+        <v>2.169170702325238</v>
       </c>
       <c r="U56">
         <v>0.2008</v>
       </c>
       <c r="V56">
-        <v>0.07532063680140122</v>
+        <v>0.07395117067773938</v>
       </c>
       <c r="W56">
-        <v>0.1856756161302786</v>
+        <v>0.1859506049279099</v>
       </c>
       <c r="X56" t="inlineStr">
         <is>
@@ -6045,7 +6045,7 @@
         </is>
       </c>
       <c r="Y56">
-        <v>0.2919404527186094</v>
+        <v>0.2866324444873619</v>
       </c>
       <c r="Z56">
         <v>0</v>
@@ -6053,22 +6053,22 @@
     </row>
     <row r="57">
       <c r="A57">
-        <v>0.55</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="B57">
-        <v>0.1651491238451577</v>
+        <v>0.1666991238451577</v>
       </c>
       <c r="C57">
-        <v>-9358.174998612034</v>
+        <v>-10096.17527739829</v>
       </c>
       <c r="D57">
-        <v>18041.13500138797</v>
+        <v>17809.83672260172</v>
       </c>
       <c r="E57">
-        <v>24009.21</v>
+        <v>24515.912</v>
       </c>
       <c r="F57">
-        <v>27868.61</v>
+        <v>28375.31200000001</v>
       </c>
       <c r="G57">
         <v>469.3</v>
@@ -6089,37 +6089,37 @@
         <v>1604</v>
       </c>
       <c r="M57">
-        <v>5596.016888000001</v>
+        <v>5697.762649600001</v>
       </c>
       <c r="N57">
-        <v>-3992.016888000001</v>
+        <v>-4093.762649600001</v>
       </c>
       <c r="O57">
-        <v>-1029.940357104</v>
+        <v>-1056.1907635968</v>
       </c>
       <c r="P57">
-        <v>-2962.076530896001</v>
+        <v>-3037.571886003201</v>
       </c>
       <c r="Q57">
-        <v>-2655.676530896001</v>
+        <v>-2731.171886003201</v>
       </c>
       <c r="R57">
-        <v>1.222222222222223</v>
+        <v>1.272727272727273</v>
       </c>
       <c r="S57">
-        <v>0.1397250914106828</v>
+        <v>0.1418597525791074</v>
       </c>
       <c r="T57">
-        <v>2.169170702325238</v>
+        <v>2.218470036468993</v>
       </c>
       <c r="U57">
         <v>0.2008</v>
       </c>
       <c r="V57">
-        <v>0.07395117067773938</v>
+        <v>0.07263061405849403</v>
       </c>
       <c r="W57">
-        <v>0.1859506049279099</v>
+        <v>0.1862157726970544</v>
       </c>
       <c r="X57" t="inlineStr">
         <is>
@@ -6127,7 +6127,7 @@
         </is>
       </c>
       <c r="Y57">
-        <v>0.2866324444873619</v>
+        <v>0.281514007978659</v>
       </c>
       <c r="Z57">
         <v>0</v>
@@ -6135,22 +6135,22 @@
     </row>
     <row r="58">
       <c r="A58">
-        <v>0.5600000000000001</v>
+        <v>0.5700000000000001</v>
       </c>
       <c r="B58">
-        <v>0.1666991238451577</v>
+        <v>0.1682491238451577</v>
       </c>
       <c r="C58">
-        <v>-10096.17527739829</v>
+        <v>-10828.31986165835</v>
       </c>
       <c r="D58">
-        <v>17809.83672260172</v>
+        <v>17584.39413834165</v>
       </c>
       <c r="E58">
-        <v>24515.912</v>
+        <v>25022.61400000001</v>
       </c>
       <c r="F58">
-        <v>28375.31200000001</v>
+        <v>28882.01400000001</v>
       </c>
       <c r="G58">
         <v>469.3</v>
@@ -6171,37 +6171,37 @@
         <v>1604</v>
       </c>
       <c r="M58">
-        <v>5697.762649600001</v>
+        <v>5799.508411200001</v>
       </c>
       <c r="N58">
-        <v>-4093.762649600001</v>
+        <v>-4195.508411200001</v>
       </c>
       <c r="O58">
-        <v>-1056.1907635968</v>
+        <v>-1082.4411700896</v>
       </c>
       <c r="P58">
-        <v>-3037.571886003201</v>
+        <v>-3113.067241110401</v>
       </c>
       <c r="Q58">
-        <v>-2731.171886003201</v>
+        <v>-2806.667241110401</v>
       </c>
       <c r="R58">
-        <v>1.272727272727273</v>
+        <v>1.325581395348838</v>
       </c>
       <c r="S58">
-        <v>0.1418597525791074</v>
+        <v>0.1440937003135052</v>
       </c>
       <c r="T58">
-        <v>2.218470036468993</v>
+        <v>2.270062362898504</v>
       </c>
       <c r="U58">
         <v>0.2008</v>
       </c>
       <c r="V58">
-        <v>0.07263061405849403</v>
+        <v>0.0713563927592222</v>
       </c>
       <c r="W58">
-        <v>0.1862157726970544</v>
+        <v>0.1864716363339482</v>
       </c>
       <c r="X58" t="inlineStr">
         <is>
@@ -6209,7 +6209,7 @@
         </is>
       </c>
       <c r="Y58">
-        <v>0.281514007978659</v>
+        <v>0.2765751657334193</v>
       </c>
       <c r="Z58">
         <v>0</v>
@@ -6217,22 +6217,22 @@
     </row>
     <row r="59">
       <c r="A59">
-        <v>0.5700000000000001</v>
+        <v>0.5800000000000001</v>
       </c>
       <c r="B59">
-        <v>0.1682491238451577</v>
+        <v>0.1697991238451577</v>
       </c>
       <c r="C59">
-        <v>-10828.31986165835</v>
+        <v>-11554.82834148853</v>
       </c>
       <c r="D59">
-        <v>17584.39413834165</v>
+        <v>17364.58765851148</v>
       </c>
       <c r="E59">
-        <v>25022.61400000001</v>
+        <v>25529.31600000001</v>
       </c>
       <c r="F59">
-        <v>28882.01400000001</v>
+        <v>29388.71600000001</v>
       </c>
       <c r="G59">
         <v>469.3</v>
@@ -6253,37 +6253,37 @@
         <v>1604</v>
       </c>
       <c r="M59">
-        <v>5799.508411200001</v>
+        <v>5901.254172800001</v>
       </c>
       <c r="N59">
-        <v>-4195.508411200001</v>
+        <v>-4297.254172800001</v>
       </c>
       <c r="O59">
-        <v>-1082.4411700896</v>
+        <v>-1108.6915765824</v>
       </c>
       <c r="P59">
-        <v>-3113.067241110401</v>
+        <v>-3188.562596217601</v>
       </c>
       <c r="Q59">
-        <v>-2806.667241110401</v>
+        <v>-2882.162596217601</v>
       </c>
       <c r="R59">
-        <v>1.325581395348838</v>
+        <v>1.380952380952381</v>
       </c>
       <c r="S59">
-        <v>0.1440937003135052</v>
+        <v>0.1464340265114459</v>
       </c>
       <c r="T59">
-        <v>2.270062362898504</v>
+        <v>2.324111466777041</v>
       </c>
       <c r="U59">
         <v>0.2008</v>
       </c>
       <c r="V59">
-        <v>0.0713563927592222</v>
+        <v>0.0701261101254425</v>
       </c>
       <c r="W59">
-        <v>0.1864716363339482</v>
+        <v>0.1867186770868112</v>
       </c>
       <c r="X59" t="inlineStr">
         <is>
@@ -6291,7 +6291,7 @@
         </is>
       </c>
       <c r="Y59">
-        <v>0.2765751657334193</v>
+        <v>0.271806628393188</v>
       </c>
       <c r="Z59">
         <v>0</v>
@@ -6299,22 +6299,22 @@
     </row>
     <row r="60">
       <c r="A60">
-        <v>0.58</v>
+        <v>0.59</v>
       </c>
       <c r="B60">
-        <v>0.1697991238451577</v>
+        <v>0.1713491238451577</v>
       </c>
       <c r="C60">
-        <v>-11554.82834148852</v>
+        <v>-12275.90946295406</v>
       </c>
       <c r="D60">
-        <v>17364.58765851149</v>
+        <v>17150.20853704595</v>
       </c>
       <c r="E60">
-        <v>25529.316</v>
+        <v>26036.018</v>
       </c>
       <c r="F60">
-        <v>29388.716</v>
+        <v>29895.418</v>
       </c>
       <c r="G60">
         <v>469.3</v>
@@ -6335,37 +6335,37 @@
         <v>1604</v>
       </c>
       <c r="M60">
-        <v>5901.254172800001</v>
+        <v>6002.999934400001</v>
       </c>
       <c r="N60">
-        <v>-4297.254172800001</v>
+        <v>-4398.999934400001</v>
       </c>
       <c r="O60">
-        <v>-1108.6915765824</v>
+        <v>-1134.9419830752</v>
       </c>
       <c r="P60">
-        <v>-3188.5625962176</v>
+        <v>-3264.0579513248</v>
       </c>
       <c r="Q60">
-        <v>-2882.1625962176</v>
+        <v>-2957.6579513248</v>
       </c>
       <c r="R60">
-        <v>1.380952380952381</v>
+        <v>1.439024390243902</v>
       </c>
       <c r="S60">
-        <v>0.1464340265114458</v>
+        <v>0.1488885149629445</v>
       </c>
       <c r="T60">
-        <v>2.32411146677704</v>
+        <v>2.380797112308187</v>
       </c>
       <c r="U60">
         <v>0.2008</v>
       </c>
       <c r="V60">
-        <v>0.07012611012544251</v>
+        <v>0.06893753198772315</v>
       </c>
       <c r="W60">
-        <v>0.1867186770868112</v>
+        <v>0.1869573435768652</v>
       </c>
       <c r="X60" t="inlineStr">
         <is>
@@ -6373,7 +6373,7 @@
         </is>
       </c>
       <c r="Y60">
-        <v>0.271806628393188</v>
+        <v>0.2671997363865238</v>
       </c>
       <c r="Z60">
         <v>0</v>
@@ -6381,22 +6381,22 @@
     </row>
     <row r="61">
       <c r="A61">
-        <v>0.59</v>
+        <v>0.6</v>
       </c>
       <c r="B61">
-        <v>0.1713491238451577</v>
+        <v>0.1728991238451577</v>
       </c>
       <c r="C61">
-        <v>-12275.90946295406</v>
+        <v>-12991.76178931513</v>
       </c>
       <c r="D61">
-        <v>17150.20853704595</v>
+        <v>16941.05821068487</v>
       </c>
       <c r="E61">
-        <v>26036.018</v>
+        <v>26542.72</v>
       </c>
       <c r="F61">
-        <v>29895.418</v>
+        <v>30402.12</v>
       </c>
       <c r="G61">
         <v>469.3</v>
@@ -6417,37 +6417,37 @@
         <v>1604</v>
       </c>
       <c r="M61">
-        <v>6002.999934400001</v>
+        <v>6104.745696000001</v>
       </c>
       <c r="N61">
-        <v>-4398.999934400001</v>
+        <v>-4500.745696000001</v>
       </c>
       <c r="O61">
-        <v>-1134.9419830752</v>
+        <v>-1161.192389568</v>
       </c>
       <c r="P61">
-        <v>-3264.0579513248</v>
+        <v>-3339.553306432001</v>
       </c>
       <c r="Q61">
-        <v>-2957.6579513248</v>
+        <v>-3033.153306432001</v>
       </c>
       <c r="R61">
-        <v>1.439024390243902</v>
+        <v>1.5</v>
       </c>
       <c r="S61">
-        <v>0.1488885149629445</v>
+        <v>0.1514657278370181</v>
       </c>
       <c r="T61">
-        <v>2.380797112308187</v>
+        <v>2.440317040115892</v>
       </c>
       <c r="U61">
         <v>0.2008</v>
       </c>
       <c r="V61">
-        <v>0.06893753198772315</v>
+        <v>0.0677885731212611</v>
       </c>
       <c r="W61">
-        <v>0.1869573435768652</v>
+        <v>0.1871880545172508</v>
       </c>
       <c r="X61" t="inlineStr">
         <is>
@@ -6455,7 +6455,7 @@
         </is>
       </c>
       <c r="Y61">
-        <v>0.2671997363865238</v>
+        <v>0.2627464074467484</v>
       </c>
       <c r="Z61">
         <v>0</v>
@@ -6463,22 +6463,22 @@
     </row>
     <row r="62">
       <c r="A62">
-        <v>0.6</v>
+        <v>0.61</v>
       </c>
       <c r="B62">
-        <v>0.1728991238451577</v>
+        <v>0.1744491238451577</v>
       </c>
       <c r="C62">
-        <v>-12991.76178931513</v>
+        <v>-13702.574314453</v>
       </c>
       <c r="D62">
-        <v>16941.05821068487</v>
+        <v>16736.94768554701</v>
       </c>
       <c r="E62">
-        <v>26542.72</v>
+        <v>27049.422</v>
       </c>
       <c r="F62">
-        <v>30402.12</v>
+        <v>30908.822</v>
       </c>
       <c r="G62">
         <v>469.3</v>
@@ -6499,37 +6499,37 @@
         <v>1604</v>
       </c>
       <c r="M62">
-        <v>6104.745696000001</v>
+        <v>6206.491457600001</v>
       </c>
       <c r="N62">
-        <v>-4500.745696000001</v>
+        <v>-4602.491457600001</v>
       </c>
       <c r="O62">
-        <v>-1161.192389568</v>
+        <v>-1187.4427960608</v>
       </c>
       <c r="P62">
-        <v>-3339.553306432001</v>
+        <v>-3415.048661539201</v>
       </c>
       <c r="Q62">
-        <v>-3033.153306432001</v>
+        <v>-3108.648661539201</v>
       </c>
       <c r="R62">
-        <v>1.5</v>
+        <v>1.564102564102564</v>
       </c>
       <c r="S62">
-        <v>0.1514657278370181</v>
+        <v>0.1541751054738648</v>
       </c>
       <c r="T62">
-        <v>2.440317040115892</v>
+        <v>2.502889271913736</v>
       </c>
       <c r="U62">
         <v>0.2008</v>
       </c>
       <c r="V62">
-        <v>0.0677885731212611</v>
+        <v>0.06667728503730599</v>
       </c>
       <c r="W62">
-        <v>0.1871880545172508</v>
+        <v>0.187411201164509</v>
       </c>
       <c r="X62" t="inlineStr">
         <is>
@@ -6537,7 +6537,7 @@
         </is>
       </c>
       <c r="Y62">
-        <v>0.2627464074467484</v>
+        <v>0.2584390892918836</v>
       </c>
       <c r="Z62">
         <v>0</v>
@@ -6545,22 +6545,22 @@
     </row>
     <row r="63">
       <c r="A63">
-        <v>0.61</v>
+        <v>0.62</v>
       </c>
       <c r="B63">
-        <v>0.1744491238451577</v>
+        <v>0.1759991238451577</v>
       </c>
       <c r="C63">
-        <v>-13702.574314453</v>
+        <v>-14408.52703247972</v>
       </c>
       <c r="D63">
-        <v>16736.94768554701</v>
+        <v>16537.69696752028</v>
       </c>
       <c r="E63">
-        <v>27049.422</v>
+        <v>27556.124</v>
       </c>
       <c r="F63">
-        <v>30908.822</v>
+        <v>31415.524</v>
       </c>
       <c r="G63">
         <v>469.3</v>
@@ -6581,37 +6581,37 @@
         <v>1604</v>
       </c>
       <c r="M63">
-        <v>6206.491457600001</v>
+        <v>6308.2372192</v>
       </c>
       <c r="N63">
-        <v>-4602.491457600001</v>
+        <v>-4704.2372192</v>
       </c>
       <c r="O63">
-        <v>-1187.4427960608</v>
+        <v>-1213.6932025536</v>
       </c>
       <c r="P63">
-        <v>-3415.048661539201</v>
+        <v>-3490.5440166464</v>
       </c>
       <c r="Q63">
-        <v>-3108.648661539201</v>
+        <v>-3184.1440166464</v>
       </c>
       <c r="R63">
-        <v>1.564102564102564</v>
+        <v>1.631578947368421</v>
       </c>
       <c r="S63">
-        <v>0.1541751054738648</v>
+        <v>0.1570270819337033</v>
       </c>
       <c r="T63">
-        <v>2.502889271913736</v>
+        <v>2.56875477906936</v>
       </c>
       <c r="U63">
         <v>0.2008</v>
       </c>
       <c r="V63">
-        <v>0.06667728503730599</v>
+        <v>0.06560184495605913</v>
       </c>
       <c r="W63">
-        <v>0.187411201164509</v>
+        <v>0.1876271495328233</v>
       </c>
       <c r="X63" t="inlineStr">
         <is>
@@ -6619,7 +6619,7 @@
         </is>
       </c>
       <c r="Y63">
-        <v>0.2584390892918836</v>
+        <v>0.2542707168839501</v>
       </c>
       <c r="Z63">
         <v>0</v>
@@ -6627,22 +6627,22 @@
     </row>
     <row r="64">
       <c r="A64">
-        <v>0.62</v>
+        <v>0.63</v>
       </c>
       <c r="B64">
-        <v>0.1759991238451577</v>
+        <v>0.1775491238451577</v>
       </c>
       <c r="C64">
-        <v>-14408.52703247972</v>
+        <v>-15109.79146713988</v>
       </c>
       <c r="D64">
-        <v>16537.69696752028</v>
+        <v>16343.13453286013</v>
       </c>
       <c r="E64">
-        <v>27556.124</v>
+        <v>28062.826</v>
       </c>
       <c r="F64">
-        <v>31415.524</v>
+        <v>31922.226</v>
       </c>
       <c r="G64">
         <v>469.3</v>
@@ -6663,37 +6663,37 @@
         <v>1604</v>
       </c>
       <c r="M64">
-        <v>6308.2372192</v>
+        <v>6409.9829808</v>
       </c>
       <c r="N64">
-        <v>-4704.2372192</v>
+        <v>-4805.9829808</v>
       </c>
       <c r="O64">
-        <v>-1213.6932025536</v>
+        <v>-1239.9436090464</v>
       </c>
       <c r="P64">
-        <v>-3490.5440166464</v>
+        <v>-3566.0393717536</v>
       </c>
       <c r="Q64">
-        <v>-3184.1440166464</v>
+        <v>-3259.6393717536</v>
       </c>
       <c r="R64">
-        <v>1.631578947368421</v>
+        <v>1.702702702702703</v>
       </c>
       <c r="S64">
-        <v>0.1570270819337033</v>
+        <v>0.1600332192832628</v>
       </c>
       <c r="T64">
-        <v>2.56875477906936</v>
+        <v>2.638180583909072</v>
       </c>
       <c r="U64">
         <v>0.2008</v>
       </c>
       <c r="V64">
-        <v>0.06560184495605913</v>
+        <v>0.06456054582977247</v>
       </c>
       <c r="W64">
-        <v>0.1876271495328233</v>
+        <v>0.1878362423973817</v>
       </c>
       <c r="X64" t="inlineStr">
         <is>
@@ -6701,7 +6701,7 @@
         </is>
       </c>
       <c r="Y64">
-        <v>0.2542707168839501</v>
+        <v>0.250234673758808</v>
       </c>
       <c r="Z64">
         <v>0</v>
@@ -6709,22 +6709,22 @@
     </row>
     <row r="65">
       <c r="A65">
-        <v>0.63</v>
+        <v>0.64</v>
       </c>
       <c r="B65">
-        <v>0.1775491238451577</v>
+        <v>0.1790991238451577</v>
       </c>
       <c r="C65">
-        <v>-15109.79146713988</v>
+        <v>-15806.53116427702</v>
       </c>
       <c r="D65">
-        <v>16343.13453286013</v>
+        <v>16153.09683572298</v>
       </c>
       <c r="E65">
-        <v>28062.826</v>
+        <v>28569.528</v>
       </c>
       <c r="F65">
-        <v>31922.226</v>
+        <v>32428.928</v>
       </c>
       <c r="G65">
         <v>469.3</v>
@@ -6745,37 +6745,37 @@
         <v>1604</v>
       </c>
       <c r="M65">
-        <v>6409.9829808</v>
+        <v>6511.728742400001</v>
       </c>
       <c r="N65">
-        <v>-4805.9829808</v>
+        <v>-4907.728742400001</v>
       </c>
       <c r="O65">
-        <v>-1239.9436090464</v>
+        <v>-1266.1940155392</v>
       </c>
       <c r="P65">
-        <v>-3566.0393717536</v>
+        <v>-3641.5347268608</v>
       </c>
       <c r="Q65">
-        <v>-3259.6393717536</v>
+        <v>-3335.1347268608</v>
       </c>
       <c r="R65">
-        <v>1.702702702702703</v>
+        <v>1.777777777777778</v>
       </c>
       <c r="S65">
-        <v>0.1600332192832628</v>
+        <v>0.1632063642633535</v>
       </c>
       <c r="T65">
-        <v>2.638180583909072</v>
+        <v>2.711463377906547</v>
       </c>
       <c r="U65">
         <v>0.2008</v>
       </c>
       <c r="V65">
-        <v>0.06456054582977247</v>
+        <v>0.06355178730118229</v>
       </c>
       <c r="W65">
-        <v>0.1878362423973817</v>
+        <v>0.1880388011099226</v>
       </c>
       <c r="X65" t="inlineStr">
         <is>
@@ -6783,7 +6783,7 @@
         </is>
       </c>
       <c r="Y65">
-        <v>0.250234673758808</v>
+        <v>0.2463247569813266</v>
       </c>
       <c r="Z65">
         <v>0</v>
@@ -6791,22 +6791,22 @@
     </row>
     <row r="66">
       <c r="A66">
-        <v>0.64</v>
+        <v>0.65</v>
       </c>
       <c r="B66">
-        <v>0.1790991238451577</v>
+        <v>0.1806491238451577</v>
       </c>
       <c r="C66">
-        <v>-15806.53116427702</v>
+        <v>-16498.90215033674</v>
       </c>
       <c r="D66">
-        <v>16153.09683572298</v>
+        <v>15967.42784966327</v>
       </c>
       <c r="E66">
-        <v>28569.528</v>
+        <v>29076.23</v>
       </c>
       <c r="F66">
-        <v>32428.928</v>
+        <v>32935.63</v>
       </c>
       <c r="G66">
         <v>469.3</v>
@@ -6827,37 +6827,37 @@
         <v>1604</v>
       </c>
       <c r="M66">
-        <v>6511.728742400001</v>
+        <v>6613.474504000001</v>
       </c>
       <c r="N66">
-        <v>-4907.728742400001</v>
+        <v>-5009.474504000001</v>
       </c>
       <c r="O66">
-        <v>-1266.1940155392</v>
+        <v>-1292.444422032</v>
       </c>
       <c r="P66">
-        <v>-3641.5347268608</v>
+        <v>-3717.030081968001</v>
       </c>
       <c r="Q66">
-        <v>-3335.1347268608</v>
+        <v>-3410.630081968</v>
       </c>
       <c r="R66">
-        <v>1.777777777777778</v>
+        <v>1.857142857142857</v>
       </c>
       <c r="S66">
-        <v>0.1632063642633535</v>
+        <v>0.166560831813735</v>
       </c>
       <c r="T66">
-        <v>2.711463377906547</v>
+        <v>2.788933760132448</v>
       </c>
       <c r="U66">
         <v>0.2008</v>
       </c>
       <c r="V66">
-        <v>0.06355178730118229</v>
+        <v>0.0625740674965487</v>
       </c>
       <c r="W66">
-        <v>0.1880388011099226</v>
+        <v>0.188235127246693</v>
       </c>
       <c r="X66" t="inlineStr">
         <is>
@@ -6865,7 +6865,7 @@
         </is>
       </c>
       <c r="Y66">
-        <v>0.2463247569813266</v>
+        <v>0.2425351453354601</v>
       </c>
       <c r="Z66">
         <v>0</v>
@@ -6873,22 +6873,22 @@
     </row>
     <row r="67">
       <c r="A67">
-        <v>0.65</v>
+        <v>0.66</v>
       </c>
       <c r="B67">
-        <v>0.1806491238451577</v>
+        <v>0.1821991238451577</v>
       </c>
       <c r="C67">
-        <v>-16498.90215033674</v>
+        <v>-17187.05335960786</v>
       </c>
       <c r="D67">
-        <v>15967.42784966327</v>
+        <v>15785.97864039214</v>
       </c>
       <c r="E67">
-        <v>29076.23</v>
+        <v>29582.932</v>
       </c>
       <c r="F67">
-        <v>32935.63</v>
+        <v>33442.332</v>
       </c>
       <c r="G67">
         <v>469.3</v>
@@ -6909,37 +6909,37 @@
         <v>1604</v>
       </c>
       <c r="M67">
-        <v>6613.474504000001</v>
+        <v>6715.220265600001</v>
       </c>
       <c r="N67">
-        <v>-5009.474504000001</v>
+        <v>-5111.220265600001</v>
       </c>
       <c r="O67">
-        <v>-1292.444422032</v>
+        <v>-1318.6948285248</v>
       </c>
       <c r="P67">
-        <v>-3717.030081968001</v>
+        <v>-3792.525437075201</v>
       </c>
       <c r="Q67">
-        <v>-3410.630081968</v>
+        <v>-3486.125437075201</v>
       </c>
       <c r="R67">
-        <v>1.857142857142857</v>
+        <v>1.941176470588236</v>
       </c>
       <c r="S67">
-        <v>0.166560831813735</v>
+        <v>0.1701126209847272</v>
       </c>
       <c r="T67">
-        <v>2.788933760132448</v>
+        <v>2.870961223665755</v>
       </c>
       <c r="U67">
         <v>0.2008</v>
       </c>
       <c r="V67">
-        <v>0.0625740674965487</v>
+        <v>0.06162597556478281</v>
       </c>
       <c r="W67">
-        <v>0.188235127246693</v>
+        <v>0.1884255041065916</v>
       </c>
       <c r="X67" t="inlineStr">
         <is>
@@ -6947,7 +6947,7 @@
         </is>
       </c>
       <c r="Y67">
-        <v>0.2425351453354601</v>
+        <v>0.2388603704061349</v>
       </c>
       <c r="Z67">
         <v>0</v>
@@ -6955,22 +6955,22 @@
     </row>
     <row r="68">
       <c r="A68">
-        <v>0.66</v>
+        <v>0.67</v>
       </c>
       <c r="B68">
-        <v>0.1821991238451577</v>
+        <v>0.1837491238451577</v>
       </c>
       <c r="C68">
-        <v>-17187.05335960786</v>
+        <v>-17871.12703266084</v>
       </c>
       <c r="D68">
-        <v>15785.97864039214</v>
+        <v>15608.60696733917</v>
       </c>
       <c r="E68">
-        <v>29582.932</v>
+        <v>30089.63400000001</v>
       </c>
       <c r="F68">
-        <v>33442.332</v>
+        <v>33949.03400000001</v>
       </c>
       <c r="G68">
         <v>469.3</v>
@@ -6991,37 +6991,37 @@
         <v>1604</v>
       </c>
       <c r="M68">
-        <v>6715.220265600001</v>
+        <v>6816.966027200002</v>
       </c>
       <c r="N68">
-        <v>-5111.220265600001</v>
+        <v>-5212.966027200002</v>
       </c>
       <c r="O68">
-        <v>-1318.6948285248</v>
+        <v>-1344.9452350176</v>
       </c>
       <c r="P68">
-        <v>-3792.525437075201</v>
+        <v>-3868.020792182401</v>
       </c>
       <c r="Q68">
-        <v>-3486.125437075201</v>
+        <v>-3561.620792182401</v>
       </c>
       <c r="R68">
-        <v>1.941176470588236</v>
+        <v>2.030303030303031</v>
       </c>
       <c r="S68">
-        <v>0.1701126209847272</v>
+        <v>0.1738796701054765</v>
       </c>
       <c r="T68">
-        <v>2.870961223665755</v>
+        <v>2.957960048625324</v>
       </c>
       <c r="U68">
         <v>0.2008</v>
       </c>
       <c r="V68">
-        <v>0.06162597556478281</v>
+        <v>0.06070618488471142</v>
       </c>
       <c r="W68">
-        <v>0.1884255041065916</v>
+        <v>0.1886101980751499</v>
       </c>
       <c r="X68" t="inlineStr">
         <is>
@@ -7029,7 +7029,7 @@
         </is>
       </c>
       <c r="Y68">
-        <v>0.2388603704061349</v>
+        <v>0.2352952902508194</v>
       </c>
       <c r="Z68">
         <v>0</v>
@@ -7037,22 +7037,22 @@
     </row>
     <row r="69">
       <c r="A69">
-        <v>0.67</v>
+        <v>0.68</v>
       </c>
       <c r="B69">
-        <v>0.1837491238451577</v>
+        <v>0.1852991238451577</v>
       </c>
       <c r="C69">
-        <v>-17871.12703266084</v>
+        <v>-18551.25908822327</v>
       </c>
       <c r="D69">
-        <v>15608.60696733917</v>
+        <v>15435.17691177674</v>
       </c>
       <c r="E69">
-        <v>30089.63400000001</v>
+        <v>30596.336</v>
       </c>
       <c r="F69">
-        <v>33949.03400000001</v>
+        <v>34455.736</v>
       </c>
       <c r="G69">
         <v>469.3</v>
@@ -7073,37 +7073,37 @@
         <v>1604</v>
       </c>
       <c r="M69">
-        <v>6816.966027200002</v>
+        <v>6918.711788800001</v>
       </c>
       <c r="N69">
-        <v>-5212.966027200002</v>
+        <v>-5314.711788800001</v>
       </c>
       <c r="O69">
-        <v>-1344.9452350176</v>
+        <v>-1371.1956415104</v>
       </c>
       <c r="P69">
-        <v>-3868.020792182401</v>
+        <v>-3943.516147289601</v>
       </c>
       <c r="Q69">
-        <v>-3561.620792182401</v>
+        <v>-3637.116147289601</v>
       </c>
       <c r="R69">
-        <v>2.030303030303031</v>
+        <v>2.125</v>
       </c>
       <c r="S69">
-        <v>0.1738796701054765</v>
+        <v>0.1778821597962727</v>
       </c>
       <c r="T69">
-        <v>2.957960048625324</v>
+        <v>3.050396300144866</v>
       </c>
       <c r="U69">
         <v>0.2008</v>
       </c>
       <c r="V69">
-        <v>0.06070618488471142</v>
+        <v>0.05981344687170096</v>
       </c>
       <c r="W69">
-        <v>0.1886101980751499</v>
+        <v>0.1887894598681625</v>
       </c>
       <c r="X69" t="inlineStr">
         <is>
@@ -7111,7 +7111,7 @@
         </is>
       </c>
       <c r="Y69">
-        <v>0.2352952902508194</v>
+        <v>0.2318350653941897</v>
       </c>
       <c r="Z69">
         <v>0</v>
@@ -7119,22 +7119,22 @@
     </row>
     <row r="70">
       <c r="A70">
-        <v>0.68</v>
+        <v>0.6900000000000001</v>
       </c>
       <c r="B70">
-        <v>0.1852991238451577</v>
+        <v>0.1868491238451577</v>
       </c>
       <c r="C70">
-        <v>-18551.25908822327</v>
+        <v>-19227.57947053607</v>
       </c>
       <c r="D70">
-        <v>15435.17691177674</v>
+        <v>15265.55852946394</v>
       </c>
       <c r="E70">
-        <v>30596.336</v>
+        <v>31103.03800000001</v>
       </c>
       <c r="F70">
-        <v>34455.736</v>
+        <v>34962.43800000001</v>
       </c>
       <c r="G70">
         <v>469.3</v>
@@ -7155,37 +7155,37 @@
         <v>1604</v>
       </c>
       <c r="M70">
-        <v>6918.711788800001</v>
+        <v>7020.457550400002</v>
       </c>
       <c r="N70">
-        <v>-5314.711788800001</v>
+        <v>-5416.457550400002</v>
       </c>
       <c r="O70">
-        <v>-1371.1956415104</v>
+        <v>-1397.446048003201</v>
       </c>
       <c r="P70">
-        <v>-3943.516147289601</v>
+        <v>-4019.011502396802</v>
       </c>
       <c r="Q70">
-        <v>-3637.116147289601</v>
+        <v>-3712.611502396802</v>
       </c>
       <c r="R70">
-        <v>2.125</v>
+        <v>2.225806451612904</v>
       </c>
       <c r="S70">
-        <v>0.1778821597962727</v>
+        <v>0.1821428746284105</v>
       </c>
       <c r="T70">
-        <v>3.050396300144866</v>
+        <v>3.1487961807947</v>
       </c>
       <c r="U70">
         <v>0.2008</v>
       </c>
       <c r="V70">
-        <v>0.05981344687170096</v>
+        <v>0.05894658532283573</v>
       </c>
       <c r="W70">
-        <v>0.1887894598681625</v>
+        <v>0.1889635256671746</v>
       </c>
       <c r="X70" t="inlineStr">
         <is>
@@ -7193,7 +7193,7 @@
         </is>
       </c>
       <c r="Y70">
-        <v>0.2318350653941897</v>
+        <v>0.2284751369102159</v>
       </c>
       <c r="Z70">
         <v>0</v>
@@ -7201,22 +7201,22 @@
     </row>
     <row r="71">
       <c r="A71">
-        <v>0.6900000000000001</v>
+        <v>0.7000000000000001</v>
       </c>
       <c r="B71">
-        <v>0.1868491238451577</v>
+        <v>0.1883991238451577</v>
       </c>
       <c r="C71">
-        <v>-19227.57947053607</v>
+        <v>-19900.21247405585</v>
       </c>
       <c r="D71">
-        <v>15265.55852946394</v>
+        <v>15099.62752594416</v>
       </c>
       <c r="E71">
-        <v>31103.03800000001</v>
+        <v>31609.74000000001</v>
       </c>
       <c r="F71">
-        <v>34962.43800000001</v>
+        <v>35469.14000000001</v>
       </c>
       <c r="G71">
         <v>469.3</v>
@@ -7237,37 +7237,37 @@
         <v>1604</v>
       </c>
       <c r="M71">
-        <v>7020.457550400002</v>
+        <v>7122.203312000001</v>
       </c>
       <c r="N71">
-        <v>-5416.457550400002</v>
+        <v>-5518.203312000001</v>
       </c>
       <c r="O71">
-        <v>-1397.446048003201</v>
+        <v>-1423.696454496</v>
       </c>
       <c r="P71">
-        <v>-4019.011502396802</v>
+        <v>-4094.506857504001</v>
       </c>
       <c r="Q71">
-        <v>-3712.611502396802</v>
+        <v>-3788.106857504001</v>
       </c>
       <c r="R71">
-        <v>2.225806451612904</v>
+        <v>2.333333333333334</v>
       </c>
       <c r="S71">
-        <v>0.1821428746284105</v>
+        <v>0.1866876371160242</v>
       </c>
       <c r="T71">
-        <v>3.1487961807947</v>
+        <v>3.253756053487857</v>
       </c>
       <c r="U71">
         <v>0.2008</v>
       </c>
       <c r="V71">
-        <v>0.05894658532283573</v>
+        <v>0.05810449124679522</v>
       </c>
       <c r="W71">
-        <v>0.1889635256671746</v>
+        <v>0.1891326181576435</v>
       </c>
       <c r="X71" t="inlineStr">
         <is>
@@ -7275,7 +7275,7 @@
         </is>
       </c>
       <c r="Y71">
-        <v>0.2284751369102159</v>
+        <v>0.2252112063829272</v>
       </c>
       <c r="Z71">
         <v>0</v>
@@ -7283,22 +7283,22 @@
     </row>
     <row r="72">
       <c r="A72">
-        <v>0.7000000000000001</v>
+        <v>0.7100000000000001</v>
       </c>
       <c r="B72">
-        <v>0.1883991238451577</v>
+        <v>0.1899491238451577</v>
       </c>
       <c r="C72">
-        <v>-19900.21247405585</v>
+        <v>-20569.2770472086</v>
       </c>
       <c r="D72">
-        <v>15099.62752594416</v>
+        <v>14937.26495279141</v>
       </c>
       <c r="E72">
-        <v>31609.74000000001</v>
+        <v>32116.442</v>
       </c>
       <c r="F72">
-        <v>35469.14000000001</v>
+        <v>35975.842</v>
       </c>
       <c r="G72">
         <v>469.3</v>
@@ -7319,37 +7319,37 @@
         <v>1604</v>
       </c>
       <c r="M72">
-        <v>7122.203312000001</v>
+        <v>7223.949073600001</v>
       </c>
       <c r="N72">
-        <v>-5518.203312000001</v>
+        <v>-5619.949073600001</v>
       </c>
       <c r="O72">
-        <v>-1423.696454496</v>
+        <v>-1449.9468609888</v>
       </c>
       <c r="P72">
-        <v>-4094.506857504001</v>
+        <v>-4170.002212611201</v>
       </c>
       <c r="Q72">
-        <v>-3788.106857504001</v>
+        <v>-3863.602212611201</v>
       </c>
       <c r="R72">
-        <v>2.333333333333334</v>
+        <v>2.448275862068967</v>
       </c>
       <c r="S72">
-        <v>0.1866876371160242</v>
+        <v>0.1915458314993354</v>
       </c>
       <c r="T72">
-        <v>3.253756053487857</v>
+        <v>3.365954538090886</v>
       </c>
       <c r="U72">
         <v>0.2008</v>
       </c>
       <c r="V72">
-        <v>0.05810449124679522</v>
+        <v>0.05728611813064318</v>
       </c>
       <c r="W72">
-        <v>0.1891326181576435</v>
+        <v>0.1892969474793668</v>
       </c>
       <c r="X72" t="inlineStr">
         <is>
@@ -7357,7 +7357,7 @@
         </is>
       </c>
       <c r="Y72">
-        <v>0.2252112063829272</v>
+        <v>0.2220392175606325</v>
       </c>
       <c r="Z72">
         <v>0</v>
@@ -7365,22 +7365,22 @@
     </row>
     <row r="73">
       <c r="A73">
-        <v>0.71</v>
+        <v>0.72</v>
       </c>
       <c r="B73">
-        <v>0.1899491238451577</v>
+        <v>0.1914991238451577</v>
       </c>
       <c r="C73">
-        <v>-20569.27704720859</v>
+        <v>-21234.88707675469</v>
       </c>
       <c r="D73">
-        <v>14937.26495279141</v>
+        <v>14778.35692324531</v>
       </c>
       <c r="E73">
-        <v>32116.442</v>
+        <v>32623.144</v>
       </c>
       <c r="F73">
-        <v>35975.842</v>
+        <v>36482.544</v>
       </c>
       <c r="G73">
         <v>469.3</v>
@@ -7401,37 +7401,37 @@
         <v>1604</v>
       </c>
       <c r="M73">
-        <v>7223.949073600001</v>
+        <v>7325.694835200001</v>
       </c>
       <c r="N73">
-        <v>-5619.949073600001</v>
+        <v>-5721.694835200001</v>
       </c>
       <c r="O73">
-        <v>-1449.9468609888</v>
+        <v>-1476.1972674816</v>
       </c>
       <c r="P73">
-        <v>-4170.002212611201</v>
+        <v>-4245.497567718401</v>
       </c>
       <c r="Q73">
-        <v>-3863.602212611201</v>
+        <v>-3939.097567718401</v>
       </c>
       <c r="R73">
-        <v>2.448275862068965</v>
+        <v>2.571428571428571</v>
       </c>
       <c r="S73">
-        <v>0.1915458314993354</v>
+        <v>0.1967510397671687</v>
       </c>
       <c r="T73">
-        <v>3.365954538090886</v>
+        <v>3.48616720016556</v>
       </c>
       <c r="U73">
         <v>0.2008</v>
       </c>
       <c r="V73">
-        <v>0.05728611813064318</v>
+        <v>0.05649047760105091</v>
       </c>
       <c r="W73">
-        <v>0.1892969474793668</v>
+        <v>0.189456712097709</v>
       </c>
       <c r="X73" t="inlineStr">
         <is>
@@ -7439,7 +7439,7 @@
         </is>
       </c>
       <c r="Y73">
-        <v>0.2220392175606325</v>
+        <v>0.2189553395389571</v>
       </c>
       <c r="Z73">
         <v>0</v>
@@ -7447,22 +7447,22 @@
     </row>
     <row r="74">
       <c r="A74">
-        <v>0.72</v>
+        <v>0.73</v>
       </c>
       <c r="B74">
-        <v>0.1914991238451577</v>
+        <v>0.1930491238451577</v>
       </c>
       <c r="C74">
-        <v>-21234.88707675469</v>
+        <v>-21897.15165419398</v>
       </c>
       <c r="D74">
-        <v>14778.35692324531</v>
+        <v>14622.79434580602</v>
       </c>
       <c r="E74">
-        <v>32623.144</v>
+        <v>33129.846</v>
       </c>
       <c r="F74">
-        <v>36482.544</v>
+        <v>36989.246</v>
       </c>
       <c r="G74">
         <v>469.3</v>
@@ -7483,37 +7483,37 @@
         <v>1604</v>
       </c>
       <c r="M74">
-        <v>7325.694835200001</v>
+        <v>7427.4405968</v>
       </c>
       <c r="N74">
-        <v>-5721.694835200001</v>
+        <v>-5823.4405968</v>
       </c>
       <c r="O74">
-        <v>-1476.1972674816</v>
+        <v>-1502.4476739744</v>
       </c>
       <c r="P74">
-        <v>-4245.497567718401</v>
+        <v>-4320.992922825601</v>
       </c>
       <c r="Q74">
-        <v>-3939.097567718401</v>
+        <v>-4014.5929228256</v>
       </c>
       <c r="R74">
-        <v>2.571428571428571</v>
+        <v>2.703703703703703</v>
       </c>
       <c r="S74">
-        <v>0.1967510397671687</v>
+        <v>0.2023418190178046</v>
       </c>
       <c r="T74">
-        <v>3.48616720016556</v>
+        <v>3.615284503875395</v>
       </c>
       <c r="U74">
         <v>0.2008</v>
       </c>
       <c r="V74">
-        <v>0.05649047760105091</v>
+        <v>0.05571663544213241</v>
       </c>
       <c r="W74">
-        <v>0.189456712097709</v>
+        <v>0.1896120996032198</v>
       </c>
       <c r="X74" t="inlineStr">
         <is>
@@ -7521,7 +7521,7 @@
         </is>
       </c>
       <c r="Y74">
-        <v>0.2189553395389571</v>
+        <v>0.2159559513260946</v>
       </c>
       <c r="Z74">
         <v>0</v>
@@ -7529,22 +7529,22 @@
     </row>
     <row r="75">
       <c r="A75">
-        <v>0.73</v>
+        <v>0.74</v>
       </c>
       <c r="B75">
-        <v>0.1930491238451577</v>
+        <v>0.1945991238451577</v>
       </c>
       <c r="C75">
-        <v>-21897.15165419398</v>
+        <v>-22556.17532552039</v>
       </c>
       <c r="D75">
-        <v>14622.79434580602</v>
+        <v>14470.47267447962</v>
       </c>
       <c r="E75">
-        <v>33129.846</v>
+        <v>33636.548</v>
       </c>
       <c r="F75">
-        <v>36989.246</v>
+        <v>37495.948</v>
       </c>
       <c r="G75">
         <v>469.3</v>
@@ -7565,37 +7565,37 @@
         <v>1604</v>
       </c>
       <c r="M75">
-        <v>7427.4405968</v>
+        <v>7529.186358400001</v>
       </c>
       <c r="N75">
-        <v>-5823.4405968</v>
+        <v>-5925.186358400001</v>
       </c>
       <c r="O75">
-        <v>-1502.4476739744</v>
+        <v>-1528.6980804672</v>
       </c>
       <c r="P75">
-        <v>-4320.992922825601</v>
+        <v>-4396.488277932801</v>
       </c>
       <c r="Q75">
-        <v>-4014.5929228256</v>
+        <v>-4090.088277932801</v>
       </c>
       <c r="R75">
-        <v>2.703703703703703</v>
+        <v>2.846153846153846</v>
       </c>
       <c r="S75">
-        <v>0.2023418190178046</v>
+        <v>0.2083626582107971</v>
       </c>
       <c r="T75">
-        <v>3.615284503875395</v>
+        <v>3.754333907870603</v>
       </c>
       <c r="U75">
         <v>0.2008</v>
       </c>
       <c r="V75">
-        <v>0.05571663544213241</v>
+        <v>0.05496370793615764</v>
       </c>
       <c r="W75">
-        <v>0.1896120996032198</v>
+        <v>0.1897632874464195</v>
       </c>
       <c r="X75" t="inlineStr">
         <is>
@@ -7603,7 +7603,7 @@
         </is>
       </c>
       <c r="Y75">
-        <v>0.2159559513260946</v>
+        <v>0.2130376276595257</v>
       </c>
       <c r="Z75">
         <v>0</v>
@@ -7611,22 +7611,22 @@
     </row>
     <row r="76">
       <c r="A76">
-        <v>0.74</v>
+        <v>0.75</v>
       </c>
       <c r="B76">
-        <v>0.1945991238451577</v>
+        <v>0.1961491238451577</v>
       </c>
       <c r="C76">
-        <v>-22556.17532552039</v>
+        <v>-23212.05832552769</v>
       </c>
       <c r="D76">
-        <v>14470.47267447962</v>
+        <v>14321.29167447231</v>
       </c>
       <c r="E76">
-        <v>33636.548</v>
+        <v>34143.25</v>
       </c>
       <c r="F76">
-        <v>37495.948</v>
+        <v>38002.65</v>
       </c>
       <c r="G76">
         <v>469.3</v>
@@ -7647,37 +7647,37 @@
         <v>1604</v>
       </c>
       <c r="M76">
-        <v>7529.186358400001</v>
+        <v>7630.93212</v>
       </c>
       <c r="N76">
-        <v>-5925.186358400001</v>
+        <v>-6026.93212</v>
       </c>
       <c r="O76">
-        <v>-1528.6980804672</v>
+        <v>-1554.94848696</v>
       </c>
       <c r="P76">
-        <v>-4396.488277932801</v>
+        <v>-4471.98363304</v>
       </c>
       <c r="Q76">
-        <v>-4090.088277932801</v>
+        <v>-4165.583633040001</v>
       </c>
       <c r="R76">
-        <v>2.846153846153846</v>
+        <v>3</v>
       </c>
       <c r="S76">
-        <v>0.2083626582107971</v>
+        <v>0.214865164539229</v>
       </c>
       <c r="T76">
-        <v>3.754333907870603</v>
+        <v>3.904507264185427</v>
       </c>
       <c r="U76">
         <v>0.2008</v>
       </c>
       <c r="V76">
-        <v>0.05496370793615764</v>
+        <v>0.05423085849700888</v>
       </c>
       <c r="W76">
-        <v>0.1897632874464195</v>
+        <v>0.1899104436138006</v>
       </c>
       <c r="X76" t="inlineStr">
         <is>
@@ -7685,7 +7685,7 @@
         </is>
       </c>
       <c r="Y76">
-        <v>0.2130376276595257</v>
+        <v>0.2101971259573987</v>
       </c>
       <c r="Z76">
         <v>0</v>
@@ -7693,22 +7693,22 @@
     </row>
     <row r="77">
       <c r="A77">
-        <v>0.75</v>
+        <v>0.76</v>
       </c>
       <c r="B77">
-        <v>0.1961491238451577</v>
+        <v>0.1976991238451577</v>
       </c>
       <c r="C77">
-        <v>-23212.05832552769</v>
+        <v>-23864.89679777003</v>
       </c>
       <c r="D77">
-        <v>14321.29167447231</v>
+        <v>14175.15520222998</v>
       </c>
       <c r="E77">
-        <v>34143.25</v>
+        <v>34649.952</v>
       </c>
       <c r="F77">
-        <v>38002.65</v>
+        <v>38509.35200000001</v>
       </c>
       <c r="G77">
         <v>469.3</v>
@@ -7729,37 +7729,37 @@
         <v>1604</v>
       </c>
       <c r="M77">
-        <v>7630.93212</v>
+        <v>7732.677881600001</v>
       </c>
       <c r="N77">
-        <v>-6026.93212</v>
+        <v>-6128.677881600001</v>
       </c>
       <c r="O77">
-        <v>-1554.94848696</v>
+        <v>-1581.1988934528</v>
       </c>
       <c r="P77">
-        <v>-4471.98363304</v>
+        <v>-4547.478988147201</v>
       </c>
       <c r="Q77">
-        <v>-4165.583633040001</v>
+        <v>-4241.078988147201</v>
       </c>
       <c r="R77">
-        <v>3</v>
+        <v>3.166666666666667</v>
       </c>
       <c r="S77">
-        <v>0.214865164539229</v>
+        <v>0.2219095463950302</v>
       </c>
       <c r="T77">
-        <v>3.904507264185427</v>
+        <v>4.06719506685982</v>
       </c>
       <c r="U77">
         <v>0.2008</v>
       </c>
       <c r="V77">
-        <v>0.05423085849700888</v>
+        <v>0.05351729456941665</v>
       </c>
       <c r="W77">
-        <v>0.1899104436138006</v>
+        <v>0.1900537272504611</v>
       </c>
       <c r="X77" t="inlineStr">
         <is>
@@ -7767,7 +7767,7 @@
         </is>
       </c>
       <c r="Y77">
-        <v>0.2101971259573987</v>
+        <v>0.2074313743000645</v>
       </c>
       <c r="Z77">
         <v>0</v>
@@ -7775,22 +7775,22 @@
     </row>
     <row r="78">
       <c r="A78">
-        <v>0.76</v>
+        <v>0.77</v>
       </c>
       <c r="B78">
-        <v>0.1976991238451577</v>
+        <v>0.1992491238451577</v>
       </c>
       <c r="C78">
-        <v>-23864.89679777003</v>
+        <v>-24514.78300119127</v>
       </c>
       <c r="D78">
-        <v>14175.15520222998</v>
+        <v>14031.97099880874</v>
       </c>
       <c r="E78">
-        <v>34649.952</v>
+        <v>35156.654</v>
       </c>
       <c r="F78">
-        <v>38509.35200000001</v>
+        <v>39016.054</v>
       </c>
       <c r="G78">
         <v>469.3</v>
@@ -7811,37 +7811,37 @@
         <v>1604</v>
       </c>
       <c r="M78">
-        <v>7732.677881600001</v>
+        <v>7834.423643200001</v>
       </c>
       <c r="N78">
-        <v>-6128.677881600001</v>
+        <v>-6230.423643200001</v>
       </c>
       <c r="O78">
-        <v>-1581.1988934528</v>
+        <v>-1607.4492999456</v>
       </c>
       <c r="P78">
-        <v>-4547.478988147201</v>
+        <v>-4622.9743432544</v>
       </c>
       <c r="Q78">
-        <v>-4241.078988147201</v>
+        <v>-4316.5743432544</v>
       </c>
       <c r="R78">
-        <v>3.166666666666667</v>
+        <v>3.347826086956522</v>
       </c>
       <c r="S78">
-        <v>0.2219095463950302</v>
+        <v>0.2295664831948142</v>
       </c>
       <c r="T78">
-        <v>4.06719506685982</v>
+        <v>4.244029634984161</v>
       </c>
       <c r="U78">
         <v>0.2008</v>
       </c>
       <c r="V78">
-        <v>0.05351729456941665</v>
+        <v>0.05282226476981384</v>
       </c>
       <c r="W78">
-        <v>0.1900537272504611</v>
+        <v>0.1901932892342214</v>
       </c>
       <c r="X78" t="inlineStr">
         <is>
@@ -7849,7 +7849,7 @@
         </is>
       </c>
       <c r="Y78">
-        <v>0.2074313743000645</v>
+        <v>0.2047374603481157</v>
       </c>
       <c r="Z78">
         <v>0</v>
@@ -7857,22 +7857,22 @@
     </row>
     <row r="79">
       <c r="A79">
-        <v>0.77</v>
+        <v>0.78</v>
       </c>
       <c r="B79">
-        <v>0.1992491238451577</v>
+        <v>0.2007991238451577</v>
       </c>
       <c r="C79">
-        <v>-24514.78300119127</v>
+        <v>-25161.8055043567</v>
       </c>
       <c r="D79">
-        <v>14031.97099880874</v>
+        <v>13891.6504956433</v>
       </c>
       <c r="E79">
-        <v>35156.654</v>
+        <v>35663.356</v>
       </c>
       <c r="F79">
-        <v>39016.054</v>
+        <v>39522.756</v>
       </c>
       <c r="G79">
         <v>469.3</v>
@@ -7893,37 +7893,37 @@
         <v>1604</v>
       </c>
       <c r="M79">
-        <v>7834.423643200001</v>
+        <v>7936.169404800001</v>
       </c>
       <c r="N79">
-        <v>-6230.423643200001</v>
+        <v>-6332.169404800001</v>
       </c>
       <c r="O79">
-        <v>-1607.4492999456</v>
+        <v>-1633.6997064384</v>
       </c>
       <c r="P79">
-        <v>-4622.9743432544</v>
+        <v>-4698.4696983616</v>
       </c>
       <c r="Q79">
-        <v>-4316.5743432544</v>
+        <v>-4392.069698361601</v>
       </c>
       <c r="R79">
-        <v>3.347826086956522</v>
+        <v>3.545454545454546</v>
       </c>
       <c r="S79">
-        <v>0.2295664831948142</v>
+        <v>0.2379195051582148</v>
       </c>
       <c r="T79">
-        <v>4.244029634984161</v>
+        <v>4.436940072937985</v>
       </c>
       <c r="U79">
         <v>0.2008</v>
       </c>
       <c r="V79">
-        <v>0.05282226476981384</v>
+        <v>0.05214505624712392</v>
       </c>
       <c r="W79">
-        <v>0.1901932892342214</v>
+        <v>0.1903292727055775</v>
       </c>
       <c r="X79" t="inlineStr">
         <is>
@@ -7931,7 +7931,7 @@
         </is>
       </c>
       <c r="Y79">
-        <v>0.2047374603481157</v>
+        <v>0.2021126211128834</v>
       </c>
       <c r="Z79">
         <v>0</v>
@@ -7939,22 +7939,22 @@
     </row>
     <row r="80">
       <c r="A80">
-        <v>0.78</v>
+        <v>0.79</v>
       </c>
       <c r="B80">
-        <v>0.2007991238451577</v>
+        <v>0.2302651103018525</v>
       </c>
       <c r="C80">
-        <v>-25161.8055043567</v>
+        <v>-27887.524340093</v>
       </c>
       <c r="D80">
-        <v>13891.6504956433</v>
+        <v>11672.633659907</v>
       </c>
       <c r="E80">
-        <v>35663.356</v>
+        <v>36170.058</v>
       </c>
       <c r="F80">
-        <v>39522.756</v>
+        <v>40029.45800000001</v>
       </c>
       <c r="G80">
         <v>469.3</v>
@@ -7975,45 +7975,45 @@
         <v>1604</v>
       </c>
       <c r="M80">
-        <v>7936.169404800001</v>
+        <v>9438.946196400002</v>
       </c>
       <c r="N80">
-        <v>-6332.169404800001</v>
+        <v>-7834.946196400002</v>
       </c>
       <c r="O80">
-        <v>-1633.6997064384</v>
+        <v>-2021.416118671201</v>
       </c>
       <c r="P80">
-        <v>-4698.4696983616</v>
+        <v>-5813.530077728801</v>
       </c>
       <c r="Q80">
-        <v>-4392.069698361601</v>
+        <v>-5507.130077728802</v>
       </c>
       <c r="R80">
-        <v>3.545454545454546</v>
+        <v>3.761904761904763</v>
       </c>
       <c r="S80">
-        <v>0.2379195051582148</v>
+        <v>0.248334655197629</v>
       </c>
       <c r="T80">
-        <v>4.436940072937985</v>
+        <v>4.677474715880576</v>
       </c>
       <c r="U80">
-        <v>0.2008</v>
+        <v>0.2358</v>
       </c>
       <c r="V80">
-        <v>0.05214505624712392</v>
+        <v>0.04384302986681234</v>
       </c>
       <c r="W80">
-        <v>0.1903292727055775</v>
+        <v>0.2254618135574057</v>
       </c>
       <c r="X80" t="inlineStr">
         <is>
-          <t>C2/C</t>
+          <t>D2/D</t>
         </is>
       </c>
       <c r="Y80">
-        <v>0.2021126211128834</v>
+        <v>0.1699342242899703</v>
       </c>
       <c r="Z80">
         <v>0</v>
@@ -8021,22 +8021,22 @@
     </row>
     <row r="81">
       <c r="A81">
-        <v>0.79</v>
+        <v>0.8</v>
       </c>
       <c r="B81">
-        <v>0.2302651103018525</v>
+        <v>0.2321651103018526</v>
       </c>
       <c r="C81">
-        <v>-27887.524340093</v>
+        <v>-28513.2293225606</v>
       </c>
       <c r="D81">
-        <v>11672.633659907</v>
+        <v>11553.63067743941</v>
       </c>
       <c r="E81">
-        <v>36170.058</v>
+        <v>36676.76</v>
       </c>
       <c r="F81">
-        <v>40029.45800000001</v>
+        <v>40536.16</v>
       </c>
       <c r="G81">
         <v>469.3</v>
@@ -8057,37 +8057,37 @@
         <v>1604</v>
       </c>
       <c r="M81">
-        <v>9438.946196400002</v>
+        <v>9558.426528000002</v>
       </c>
       <c r="N81">
-        <v>-7834.946196400002</v>
+        <v>-7954.426528000002</v>
       </c>
       <c r="O81">
-        <v>-2021.416118671201</v>
+        <v>-2052.242044224</v>
       </c>
       <c r="P81">
-        <v>-5813.530077728801</v>
+        <v>-5902.184483776002</v>
       </c>
       <c r="Q81">
-        <v>-5507.130077728802</v>
+        <v>-5595.784483776002</v>
       </c>
       <c r="R81">
-        <v>3.761904761904763</v>
+        <v>4.000000000000001</v>
       </c>
       <c r="S81">
-        <v>0.248334655197629</v>
+        <v>0.2584613879575104</v>
       </c>
       <c r="T81">
-        <v>4.677474715880576</v>
+        <v>4.911348451674605</v>
       </c>
       <c r="U81">
         <v>0.2358</v>
       </c>
       <c r="V81">
-        <v>0.04384302986681234</v>
+        <v>0.04329499199347719</v>
       </c>
       <c r="W81">
-        <v>0.2254618135574057</v>
+        <v>0.2255910408879381</v>
       </c>
       <c r="X81" t="inlineStr">
         <is>
@@ -8095,7 +8095,7 @@
         </is>
       </c>
       <c r="Y81">
-        <v>0.1699342242899703</v>
+        <v>0.1678100464863457</v>
       </c>
       <c r="Z81">
         <v>0</v>
@@ -8103,22 +8103,22 @@
     </row>
     <row r="82">
       <c r="A82">
-        <v>0.8</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="B82">
-        <v>0.2321651103018526</v>
+        <v>0.2340651103018525</v>
       </c>
       <c r="C82">
-        <v>-28513.2293225606</v>
+        <v>-29136.53231279155</v>
       </c>
       <c r="D82">
-        <v>11553.63067743941</v>
+        <v>11437.02968720846</v>
       </c>
       <c r="E82">
-        <v>36676.76</v>
+        <v>37183.46200000001</v>
       </c>
       <c r="F82">
-        <v>40536.16</v>
+        <v>41042.86200000001</v>
       </c>
       <c r="G82">
         <v>469.3</v>
@@ -8139,37 +8139,37 @@
         <v>1604</v>
       </c>
       <c r="M82">
-        <v>9558.426528000002</v>
+        <v>9677.906859600002</v>
       </c>
       <c r="N82">
-        <v>-7954.426528000002</v>
+        <v>-8073.906859600002</v>
       </c>
       <c r="O82">
-        <v>-2052.242044224</v>
+        <v>-2083.067969776801</v>
       </c>
       <c r="P82">
-        <v>-5902.184483776002</v>
+        <v>-5990.838889823201</v>
       </c>
       <c r="Q82">
-        <v>-5595.784483776002</v>
+        <v>-5684.438889823201</v>
       </c>
       <c r="R82">
-        <v>4.000000000000001</v>
+        <v>4.263157894736843</v>
       </c>
       <c r="S82">
-        <v>0.2584613879575104</v>
+        <v>0.2696540925868531</v>
       </c>
       <c r="T82">
-        <v>4.911348451674605</v>
+        <v>5.169840475446954</v>
       </c>
       <c r="U82">
         <v>0.2358</v>
       </c>
       <c r="V82">
-        <v>0.04329499199347719</v>
+        <v>0.04276048591948364</v>
       </c>
       <c r="W82">
-        <v>0.2255910408879381</v>
+        <v>0.2257170774201858</v>
       </c>
       <c r="X82" t="inlineStr">
         <is>
@@ -8177,7 +8177,7 @@
         </is>
       </c>
       <c r="Y82">
-        <v>0.1678100464863457</v>
+        <v>0.1657383175173784</v>
       </c>
       <c r="Z82">
         <v>0</v>
@@ -8185,22 +8185,22 @@
     </row>
     <row r="83">
       <c r="A83">
-        <v>0.8100000000000001</v>
+        <v>0.8200000000000001</v>
       </c>
       <c r="B83">
-        <v>0.2340651103018525</v>
+        <v>0.2359651103018526</v>
       </c>
       <c r="C83">
-        <v>-29136.53231279155</v>
+        <v>-29757.50530798727</v>
       </c>
       <c r="D83">
-        <v>11437.02968720846</v>
+        <v>11322.75869201273</v>
       </c>
       <c r="E83">
-        <v>37183.46200000001</v>
+        <v>37690.164</v>
       </c>
       <c r="F83">
-        <v>41042.86200000001</v>
+        <v>41549.56400000001</v>
       </c>
       <c r="G83">
         <v>469.3</v>
@@ -8221,37 +8221,37 @@
         <v>1604</v>
       </c>
       <c r="M83">
-        <v>9677.906859600002</v>
+        <v>9797.387191200001</v>
       </c>
       <c r="N83">
-        <v>-8073.906859600002</v>
+        <v>-8193.387191200001</v>
       </c>
       <c r="O83">
-        <v>-2083.067969776801</v>
+        <v>-2113.893895329601</v>
       </c>
       <c r="P83">
-        <v>-5990.838889823201</v>
+        <v>-6079.493295870401</v>
       </c>
       <c r="Q83">
-        <v>-5684.438889823201</v>
+        <v>-5773.093295870402</v>
       </c>
       <c r="R83">
-        <v>4.263157894736843</v>
+        <v>4.555555555555557</v>
       </c>
       <c r="S83">
-        <v>0.2696540925868531</v>
+        <v>0.2820904310639005</v>
       </c>
       <c r="T83">
-        <v>5.169840475446954</v>
+        <v>5.457053835194007</v>
       </c>
       <c r="U83">
         <v>0.2358</v>
       </c>
       <c r="V83">
-        <v>0.04276048591948364</v>
+        <v>0.04223901657900214</v>
       </c>
       <c r="W83">
-        <v>0.2257170774201858</v>
+        <v>0.2258400398906713</v>
       </c>
       <c r="X83" t="inlineStr">
         <is>
@@ -8259,7 +8259,7 @@
         </is>
       </c>
       <c r="Y83">
-        <v>0.1657383175173784</v>
+        <v>0.1637171185232641</v>
       </c>
       <c r="Z83">
         <v>0</v>
@@ -8267,22 +8267,22 @@
     </row>
     <row r="84">
       <c r="A84">
-        <v>0.8200000000000001</v>
+        <v>0.8300000000000001</v>
       </c>
       <c r="B84">
-        <v>0.2359651103018526</v>
+        <v>0.2378651103018525</v>
       </c>
       <c r="C84">
-        <v>-29757.50530798727</v>
+        <v>-30376.21745642607</v>
       </c>
       <c r="D84">
-        <v>11322.75869201273</v>
+        <v>11210.74854357394</v>
       </c>
       <c r="E84">
-        <v>37690.164</v>
+        <v>38196.86600000001</v>
       </c>
       <c r="F84">
-        <v>41549.56400000001</v>
+        <v>42056.26600000001</v>
       </c>
       <c r="G84">
         <v>469.3</v>
@@ -8303,37 +8303,37 @@
         <v>1604</v>
       </c>
       <c r="M84">
-        <v>9797.387191200001</v>
+        <v>9916.867522800003</v>
       </c>
       <c r="N84">
-        <v>-8193.387191200001</v>
+        <v>-8312.867522800003</v>
       </c>
       <c r="O84">
-        <v>-2113.893895329601</v>
+        <v>-2144.719820882401</v>
       </c>
       <c r="P84">
-        <v>-6079.493295870401</v>
+        <v>-6168.147701917602</v>
       </c>
       <c r="Q84">
-        <v>-5773.093295870402</v>
+        <v>-5861.747701917602</v>
       </c>
       <c r="R84">
-        <v>4.555555555555557</v>
+        <v>4.882352941176473</v>
       </c>
       <c r="S84">
-        <v>0.2820904310639005</v>
+        <v>0.2959898681853064</v>
       </c>
       <c r="T84">
-        <v>5.457053835194007</v>
+        <v>5.778057001970125</v>
       </c>
       <c r="U84">
         <v>0.2358</v>
       </c>
       <c r="V84">
-        <v>0.04223901657900214</v>
+        <v>0.04173011276479728</v>
       </c>
       <c r="W84">
-        <v>0.2258400398906713</v>
+        <v>0.2259600394100608</v>
       </c>
       <c r="X84" t="inlineStr">
         <is>
@@ -8341,7 +8341,7 @@
         </is>
       </c>
       <c r="Y84">
-        <v>0.1637171185232641</v>
+        <v>0.1617446231193693</v>
       </c>
       <c r="Z84">
         <v>0</v>
@@ -8349,22 +8349,22 @@
     </row>
     <row r="85">
       <c r="A85">
-        <v>0.8300000000000001</v>
+        <v>0.8400000000000001</v>
       </c>
       <c r="B85">
-        <v>0.2378651103018525</v>
+        <v>0.2397651103018526</v>
       </c>
       <c r="C85">
-        <v>-30376.21745642607</v>
+        <v>-30992.73519699735</v>
       </c>
       <c r="D85">
-        <v>11210.74854357394</v>
+        <v>11100.93280300265</v>
       </c>
       <c r="E85">
-        <v>38196.86600000001</v>
+        <v>38703.56800000001</v>
       </c>
       <c r="F85">
-        <v>42056.26600000001</v>
+        <v>42562.96800000001</v>
       </c>
       <c r="G85">
         <v>469.3</v>
@@ -8385,37 +8385,37 @@
         <v>1604</v>
       </c>
       <c r="M85">
-        <v>9916.867522800003</v>
+        <v>10036.3478544</v>
       </c>
       <c r="N85">
-        <v>-8312.867522800003</v>
+        <v>-8432.347854400003</v>
       </c>
       <c r="O85">
-        <v>-2144.719820882401</v>
+        <v>-2175.545746435201</v>
       </c>
       <c r="P85">
-        <v>-6168.147701917602</v>
+        <v>-6256.802107964802</v>
       </c>
       <c r="Q85">
-        <v>-5861.747701917602</v>
+        <v>-5950.402107964803</v>
       </c>
       <c r="R85">
-        <v>4.882352941176473</v>
+        <v>5.250000000000004</v>
       </c>
       <c r="S85">
-        <v>0.2959898681853064</v>
+        <v>0.3116267349468881</v>
       </c>
       <c r="T85">
-        <v>5.778057001970125</v>
+        <v>6.139185564593259</v>
       </c>
       <c r="U85">
         <v>0.2358</v>
       </c>
       <c r="V85">
-        <v>0.04173011276479728</v>
+        <v>0.0412333257080735</v>
       </c>
       <c r="W85">
-        <v>0.2259600394100608</v>
+        <v>0.2260771817980363</v>
       </c>
       <c r="X85" t="inlineStr">
         <is>
@@ -8423,7 +8423,7 @@
         </is>
       </c>
       <c r="Y85">
-        <v>0.1617446231193693</v>
+        <v>0.1598190918917578</v>
       </c>
       <c r="Z85">
         <v>0</v>
@@ -8431,22 +8431,22 @@
     </row>
     <row r="86">
       <c r="A86">
-        <v>0.84</v>
+        <v>0.85</v>
       </c>
       <c r="B86">
-        <v>0.2397651103018525</v>
+        <v>0.2416651103018526</v>
       </c>
       <c r="C86">
-        <v>-30992.73519699735</v>
+        <v>-31607.12239061454</v>
       </c>
       <c r="D86">
-        <v>11100.93280300265</v>
+        <v>10993.24760938547</v>
       </c>
       <c r="E86">
-        <v>38703.568</v>
+        <v>39210.27</v>
       </c>
       <c r="F86">
-        <v>42562.968</v>
+        <v>43069.67000000001</v>
       </c>
       <c r="G86">
         <v>469.3</v>
@@ -8467,37 +8467,37 @@
         <v>1604</v>
       </c>
       <c r="M86">
-        <v>10036.3478544</v>
+        <v>10155.828186</v>
       </c>
       <c r="N86">
-        <v>-8432.347854400001</v>
+        <v>-8551.828186000002</v>
       </c>
       <c r="O86">
-        <v>-2175.5457464352</v>
+        <v>-2206.371671988001</v>
       </c>
       <c r="P86">
-        <v>-6256.802107964801</v>
+        <v>-6345.456514012001</v>
       </c>
       <c r="Q86">
-        <v>-5950.402107964801</v>
+        <v>-6039.056514012002</v>
       </c>
       <c r="R86">
-        <v>5.249999999999999</v>
+        <v>5.666666666666666</v>
       </c>
       <c r="S86">
-        <v>0.3116267349468879</v>
+        <v>0.3293485172766805</v>
       </c>
       <c r="T86">
-        <v>6.139185564593255</v>
+        <v>6.548464602232805</v>
       </c>
       <c r="U86">
         <v>0.2358</v>
       </c>
       <c r="V86">
-        <v>0.04123332570807352</v>
+        <v>0.04074822775856676</v>
       </c>
       <c r="W86">
-        <v>0.2260771817980363</v>
+        <v>0.22619156789453</v>
       </c>
       <c r="X86" t="inlineStr">
         <is>
@@ -8505,7 +8505,7 @@
         </is>
       </c>
       <c r="Y86">
-        <v>0.1598190918917578</v>
+        <v>0.1579388672812665</v>
       </c>
       <c r="Z86">
         <v>0</v>
@@ -8513,22 +8513,22 @@
     </row>
     <row r="87">
       <c r="A87">
-        <v>0.85</v>
+        <v>0.86</v>
       </c>
       <c r="B87">
-        <v>0.2416651103018526</v>
+        <v>0.2435651103018525</v>
       </c>
       <c r="C87">
-        <v>-31607.12239061454</v>
+        <v>-32219.44044405263</v>
       </c>
       <c r="D87">
-        <v>10993.24760938547</v>
+        <v>10887.63155594738</v>
       </c>
       <c r="E87">
-        <v>39210.27</v>
+        <v>39716.972</v>
       </c>
       <c r="F87">
-        <v>43069.67000000001</v>
+        <v>43576.372</v>
       </c>
       <c r="G87">
         <v>469.3</v>
@@ -8549,37 +8549,37 @@
         <v>1604</v>
       </c>
       <c r="M87">
-        <v>10155.828186</v>
+        <v>10275.3085176</v>
       </c>
       <c r="N87">
-        <v>-8551.828186000002</v>
+        <v>-8671.3085176</v>
       </c>
       <c r="O87">
-        <v>-2206.371671988001</v>
+        <v>-2237.1975975408</v>
       </c>
       <c r="P87">
-        <v>-6345.456514012001</v>
+        <v>-6434.1109200592</v>
       </c>
       <c r="Q87">
-        <v>-6039.056514012002</v>
+        <v>-6127.7109200592</v>
       </c>
       <c r="R87">
-        <v>5.666666666666666</v>
+        <v>6.142857142857142</v>
       </c>
       <c r="S87">
-        <v>0.3293485172766805</v>
+        <v>0.3496019827964433</v>
       </c>
       <c r="T87">
-        <v>6.548464602232805</v>
+        <v>7.016212073820863</v>
       </c>
       <c r="U87">
         <v>0.2358</v>
       </c>
       <c r="V87">
-        <v>0.04074822775856676</v>
+        <v>0.04027441115672296</v>
       </c>
       <c r="W87">
-        <v>0.22619156789453</v>
+        <v>0.2263032938492447</v>
       </c>
       <c r="X87" t="inlineStr">
         <is>
@@ -8587,7 +8587,7 @@
         </is>
       </c>
       <c r="Y87">
-        <v>0.1579388672812665</v>
+        <v>0.1561023688245077</v>
       </c>
       <c r="Z87">
         <v>0</v>
@@ -8595,22 +8595,22 @@
     </row>
     <row r="88">
       <c r="A88">
-        <v>0.86</v>
+        <v>0.87</v>
       </c>
       <c r="B88">
-        <v>0.2435651103018525</v>
+        <v>0.2454651103018525</v>
       </c>
       <c r="C88">
-        <v>-32219.44044405263</v>
+        <v>-32829.74842671544</v>
       </c>
       <c r="D88">
-        <v>10887.63155594738</v>
+        <v>10784.02557328457</v>
       </c>
       <c r="E88">
-        <v>39716.972</v>
+        <v>40223.674</v>
       </c>
       <c r="F88">
-        <v>43576.372</v>
+        <v>44083.074</v>
       </c>
       <c r="G88">
         <v>469.3</v>
@@ -8631,37 +8631,37 @@
         <v>1604</v>
       </c>
       <c r="M88">
-        <v>10275.3085176</v>
+        <v>10394.7888492</v>
       </c>
       <c r="N88">
-        <v>-8671.3085176</v>
+        <v>-8790.7888492</v>
       </c>
       <c r="O88">
-        <v>-2237.1975975408</v>
+        <v>-2268.0235230936</v>
       </c>
       <c r="P88">
-        <v>-6434.1109200592</v>
+        <v>-6522.765326106401</v>
       </c>
       <c r="Q88">
-        <v>-6127.7109200592</v>
+        <v>-6216.365326106401</v>
       </c>
       <c r="R88">
-        <v>6.142857142857142</v>
+        <v>6.692307692307692</v>
       </c>
       <c r="S88">
-        <v>0.3496019827964433</v>
+        <v>0.3729713660884775</v>
       </c>
       <c r="T88">
-        <v>7.016212073820863</v>
+        <v>7.555920694884006</v>
       </c>
       <c r="U88">
         <v>0.2358</v>
       </c>
       <c r="V88">
-        <v>0.04027441115672296</v>
+        <v>0.03981148689055374</v>
       </c>
       <c r="W88">
-        <v>0.2263032938492447</v>
+        <v>0.2264124513912074</v>
       </c>
       <c r="X88" t="inlineStr">
         <is>
@@ -8669,7 +8669,7 @@
         </is>
       </c>
       <c r="Y88">
-        <v>0.1561023688245077</v>
+        <v>0.1543080887230766</v>
       </c>
       <c r="Z88">
         <v>0</v>
@@ -8677,22 +8677,22 @@
     </row>
     <row r="89">
       <c r="A89">
-        <v>0.87</v>
+        <v>0.88</v>
       </c>
       <c r="B89">
-        <v>0.2454651103018525</v>
+        <v>0.2473651103018525</v>
       </c>
       <c r="C89">
-        <v>-32829.74842671544</v>
+        <v>-33438.10318079851</v>
       </c>
       <c r="D89">
-        <v>10784.02557328457</v>
+        <v>10682.3728192015</v>
       </c>
       <c r="E89">
-        <v>40223.674</v>
+        <v>40730.376</v>
       </c>
       <c r="F89">
-        <v>44083.074</v>
+        <v>44589.77600000001</v>
       </c>
       <c r="G89">
         <v>469.3</v>
@@ -8713,37 +8713,37 @@
         <v>1604</v>
       </c>
       <c r="M89">
-        <v>10394.7888492</v>
+        <v>10514.2691808</v>
       </c>
       <c r="N89">
-        <v>-8790.7888492</v>
+        <v>-8910.269180800002</v>
       </c>
       <c r="O89">
-        <v>-2268.0235230936</v>
+        <v>-2298.849448646401</v>
       </c>
       <c r="P89">
-        <v>-6522.765326106401</v>
+        <v>-6611.419732153601</v>
       </c>
       <c r="Q89">
-        <v>-6216.365326106401</v>
+        <v>-6305.019732153602</v>
       </c>
       <c r="R89">
-        <v>6.692307692307692</v>
+        <v>7.333333333333334</v>
       </c>
       <c r="S89">
-        <v>0.3729713660884775</v>
+        <v>0.4002356465958506</v>
       </c>
       <c r="T89">
-        <v>7.555920694884006</v>
+        <v>8.185580752791006</v>
       </c>
       <c r="U89">
         <v>0.2358</v>
       </c>
       <c r="V89">
-        <v>0.03981148689055374</v>
+        <v>0.03935908363043381</v>
       </c>
       <c r="W89">
-        <v>0.2264124513912074</v>
+        <v>0.2265191280799437</v>
       </c>
       <c r="X89" t="inlineStr">
         <is>
@@ -8751,7 +8751,7 @@
         </is>
       </c>
       <c r="Y89">
-        <v>0.1543080887230766</v>
+        <v>0.1525545877148597</v>
       </c>
       <c r="Z89">
         <v>0</v>
@@ -8759,22 +8759,22 @@
     </row>
     <row r="90">
       <c r="A90">
-        <v>0.88</v>
+        <v>0.89</v>
       </c>
       <c r="B90">
-        <v>0.2473651103018525</v>
+        <v>0.2492651103018525</v>
       </c>
       <c r="C90">
-        <v>-33438.10318079851</v>
+        <v>-34044.55942527988</v>
       </c>
       <c r="D90">
-        <v>10682.3728192015</v>
+        <v>10582.61857472013</v>
       </c>
       <c r="E90">
-        <v>40730.376</v>
+        <v>41237.078</v>
       </c>
       <c r="F90">
-        <v>44589.77600000001</v>
+        <v>45096.478</v>
       </c>
       <c r="G90">
         <v>469.3</v>
@@ -8795,37 +8795,37 @@
         <v>1604</v>
       </c>
       <c r="M90">
-        <v>10514.2691808</v>
+        <v>10633.7495124</v>
       </c>
       <c r="N90">
-        <v>-8910.269180800002</v>
+        <v>-9029.749512400002</v>
       </c>
       <c r="O90">
-        <v>-2298.849448646401</v>
+        <v>-2329.675374199201</v>
       </c>
       <c r="P90">
-        <v>-6611.419732153601</v>
+        <v>-6700.074138200801</v>
       </c>
       <c r="Q90">
-        <v>-6305.019732153602</v>
+        <v>-6393.674138200801</v>
       </c>
       <c r="R90">
-        <v>7.333333333333334</v>
+        <v>8.090909090909092</v>
       </c>
       <c r="S90">
-        <v>0.4002356465958506</v>
+        <v>0.4324570690136552</v>
       </c>
       <c r="T90">
-        <v>8.185580752791006</v>
+        <v>8.92972445759019</v>
       </c>
       <c r="U90">
         <v>0.2358</v>
       </c>
       <c r="V90">
-        <v>0.03935908363043381</v>
+        <v>0.03891684673570983</v>
       </c>
       <c r="W90">
-        <v>0.2265191280799437</v>
+        <v>0.2266234075397196</v>
       </c>
       <c r="X90" t="inlineStr">
         <is>
@@ -8833,7 +8833,7 @@
         </is>
       </c>
       <c r="Y90">
-        <v>0.1525545877148597</v>
+        <v>0.1508404912236815</v>
       </c>
       <c r="Z90">
         <v>0</v>
@@ -8841,22 +8841,22 @@
     </row>
     <row r="91">
       <c r="A91">
-        <v>0.89</v>
+        <v>0.9</v>
       </c>
       <c r="B91">
-        <v>0.2492651103018525</v>
+        <v>0.2511651103018526</v>
       </c>
       <c r="C91">
-        <v>-34044.55942527988</v>
+        <v>-34649.16985413821</v>
       </c>
       <c r="D91">
-        <v>10582.61857472013</v>
+        <v>10484.7101458618</v>
       </c>
       <c r="E91">
-        <v>41237.078</v>
+        <v>41743.78000000001</v>
       </c>
       <c r="F91">
-        <v>45096.478</v>
+        <v>45603.18000000001</v>
       </c>
       <c r="G91">
         <v>469.3</v>
@@ -8877,37 +8877,37 @@
         <v>1604</v>
       </c>
       <c r="M91">
-        <v>10633.7495124</v>
+        <v>10753.229844</v>
       </c>
       <c r="N91">
-        <v>-9029.749512400002</v>
+        <v>-9149.229844000001</v>
       </c>
       <c r="O91">
-        <v>-2329.675374199201</v>
+        <v>-2360.501299752</v>
       </c>
       <c r="P91">
-        <v>-6700.074138200801</v>
+        <v>-6788.728544248001</v>
       </c>
       <c r="Q91">
-        <v>-6393.674138200801</v>
+        <v>-6482.328544248001</v>
       </c>
       <c r="R91">
-        <v>8.090909090909092</v>
+        <v>9.000000000000002</v>
       </c>
       <c r="S91">
-        <v>0.4324570690136552</v>
+        <v>0.4711227759150208</v>
       </c>
       <c r="T91">
-        <v>8.92972445759019</v>
+        <v>9.822696903349211</v>
       </c>
       <c r="U91">
         <v>0.2358</v>
       </c>
       <c r="V91">
-        <v>0.03891684673570983</v>
+        <v>0.03848443732753528</v>
       </c>
       <c r="W91">
-        <v>0.2266234075397196</v>
+        <v>0.2267253696781672</v>
       </c>
       <c r="X91" t="inlineStr">
         <is>
@@ -8915,7 +8915,7 @@
         </is>
       </c>
       <c r="Y91">
-        <v>0.1508404912236815</v>
+        <v>0.1491644857656406</v>
       </c>
       <c r="Z91">
         <v>0</v>
@@ -8923,22 +8923,22 @@
     </row>
     <row r="92">
       <c r="A92">
-        <v>0.9</v>
+        <v>0.91</v>
       </c>
       <c r="B92">
-        <v>0.2511651103018526</v>
+        <v>0.2530651103018525</v>
       </c>
       <c r="C92">
-        <v>-34649.16985413821</v>
+        <v>-35251.98522916849</v>
       </c>
       <c r="D92">
-        <v>10484.7101458618</v>
+        <v>10388.59677083151</v>
       </c>
       <c r="E92">
-        <v>41743.78000000001</v>
+        <v>42250.482</v>
       </c>
       <c r="F92">
-        <v>45603.18000000001</v>
+        <v>46109.88200000001</v>
       </c>
       <c r="G92">
         <v>469.3</v>
@@ -8959,37 +8959,37 @@
         <v>1604</v>
       </c>
       <c r="M92">
-        <v>10753.229844</v>
+        <v>10872.7101756</v>
       </c>
       <c r="N92">
-        <v>-9149.229844000001</v>
+        <v>-9268.710175600001</v>
       </c>
       <c r="O92">
-        <v>-2360.501299752</v>
+        <v>-2391.3272253048</v>
       </c>
       <c r="P92">
-        <v>-6788.728544248001</v>
+        <v>-6877.382950295201</v>
       </c>
       <c r="Q92">
-        <v>-6482.328544248001</v>
+        <v>-6570.982950295202</v>
       </c>
       <c r="R92">
-        <v>9.000000000000002</v>
+        <v>10.11111111111111</v>
       </c>
       <c r="S92">
-        <v>0.4711227759150208</v>
+        <v>0.5183808621278009</v>
       </c>
       <c r="T92">
-        <v>9.822696903349211</v>
+        <v>10.91410767038801</v>
       </c>
       <c r="U92">
         <v>0.2358</v>
       </c>
       <c r="V92">
-        <v>0.03848443732753528</v>
+        <v>0.03806153142283709</v>
       </c>
       <c r="W92">
-        <v>0.2267253696781672</v>
+        <v>0.226825090890495</v>
       </c>
       <c r="X92" t="inlineStr">
         <is>
@@ -8997,7 +8997,7 @@
         </is>
       </c>
       <c r="Y92">
-        <v>0.1491644857656406</v>
+        <v>0.1475253155923918</v>
       </c>
       <c r="Z92">
         <v>0</v>
@@ -9005,22 +9005,22 @@
     </row>
     <row r="93">
       <c r="A93">
-        <v>0.91</v>
+        <v>0.92</v>
       </c>
       <c r="B93">
-        <v>0.2530651103018525</v>
+        <v>0.2549651103018525</v>
       </c>
       <c r="C93">
-        <v>-35251.98522916849</v>
+        <v>-35853.05446773947</v>
       </c>
       <c r="D93">
-        <v>10388.59677083151</v>
+        <v>10294.22953226053</v>
       </c>
       <c r="E93">
-        <v>42250.482</v>
+        <v>42757.184</v>
       </c>
       <c r="F93">
-        <v>46109.88200000001</v>
+        <v>46616.584</v>
       </c>
       <c r="G93">
         <v>469.3</v>
@@ -9041,37 +9041,37 @@
         <v>1604</v>
       </c>
       <c r="M93">
-        <v>10872.7101756</v>
+        <v>10992.1905072</v>
       </c>
       <c r="N93">
-        <v>-9268.710175600001</v>
+        <v>-9388.190507200001</v>
       </c>
       <c r="O93">
-        <v>-2391.3272253048</v>
+        <v>-2422.1531508576</v>
       </c>
       <c r="P93">
-        <v>-6877.382950295201</v>
+        <v>-6966.0373563424</v>
       </c>
       <c r="Q93">
-        <v>-6570.982950295202</v>
+        <v>-6659.6373563424</v>
       </c>
       <c r="R93">
-        <v>10.11111111111111</v>
+        <v>11.50000000000001</v>
       </c>
       <c r="S93">
-        <v>0.5183808621278009</v>
+        <v>0.5774534698937761</v>
       </c>
       <c r="T93">
-        <v>10.91410767038801</v>
+        <v>12.27837112918652</v>
       </c>
       <c r="U93">
         <v>0.2358</v>
       </c>
       <c r="V93">
-        <v>0.03806153142283709</v>
+        <v>0.03764781912476278</v>
       </c>
       <c r="W93">
-        <v>0.226825090890495</v>
+        <v>0.2269226442503809</v>
       </c>
       <c r="X93" t="inlineStr">
         <is>
@@ -9079,7 +9079,7 @@
         </is>
       </c>
       <c r="Y93">
-        <v>0.1475253155923918</v>
+        <v>0.1459217795533441</v>
       </c>
       <c r="Z93">
         <v>0</v>
@@ -9087,22 +9087,22 @@
     </row>
     <row r="94">
       <c r="A94">
-        <v>0.92</v>
+        <v>0.93</v>
       </c>
       <c r="B94">
-        <v>0.2549651103018525</v>
+        <v>0.2568651103018526</v>
       </c>
       <c r="C94">
-        <v>-35853.05446773947</v>
+        <v>-36452.42472581076</v>
       </c>
       <c r="D94">
-        <v>10294.22953226053</v>
+        <v>10201.56127418925</v>
       </c>
       <c r="E94">
-        <v>42757.184</v>
+        <v>43263.88600000001</v>
       </c>
       <c r="F94">
-        <v>46616.584</v>
+        <v>47123.28600000001</v>
       </c>
       <c r="G94">
         <v>469.3</v>
@@ -9123,37 +9123,37 @@
         <v>1604</v>
       </c>
       <c r="M94">
-        <v>10992.1905072</v>
+        <v>11111.6708388</v>
       </c>
       <c r="N94">
-        <v>-9388.190507200001</v>
+        <v>-9507.670838800002</v>
       </c>
       <c r="O94">
-        <v>-2422.1531508576</v>
+        <v>-2452.979076410401</v>
       </c>
       <c r="P94">
-        <v>-6966.0373563424</v>
+        <v>-7054.691762389602</v>
       </c>
       <c r="Q94">
-        <v>-6659.6373563424</v>
+        <v>-6748.291762389602</v>
       </c>
       <c r="R94">
-        <v>11.50000000000001</v>
+        <v>13.2857142857143</v>
       </c>
       <c r="S94">
-        <v>0.5774534698937761</v>
+        <v>0.653403965592887</v>
       </c>
       <c r="T94">
-        <v>12.27837112918652</v>
+        <v>14.03242414764174</v>
       </c>
       <c r="U94">
         <v>0.2358</v>
       </c>
       <c r="V94">
-        <v>0.03764781912476278</v>
+        <v>0.03724300386535671</v>
       </c>
       <c r="W94">
-        <v>0.2269226442503809</v>
+        <v>0.2270180996885489</v>
       </c>
       <c r="X94" t="inlineStr">
         <is>
@@ -9161,7 +9161,7 @@
         </is>
       </c>
       <c r="Y94">
-        <v>0.1459217795533441</v>
+        <v>0.1443527281602973</v>
       </c>
       <c r="Z94">
         <v>0</v>
@@ -9169,22 +9169,22 @@
     </row>
     <row r="95">
       <c r="A95">
-        <v>0.93</v>
+        <v>0.9400000000000001</v>
       </c>
       <c r="B95">
-        <v>0.2568651103018526</v>
+        <v>0.2587651103018526</v>
       </c>
       <c r="C95">
-        <v>-36452.42472581076</v>
+        <v>-37050.14147650624</v>
       </c>
       <c r="D95">
-        <v>10201.56127418925</v>
+        <v>10110.54652349377</v>
       </c>
       <c r="E95">
-        <v>43263.88600000001</v>
+        <v>43770.588</v>
       </c>
       <c r="F95">
-        <v>47123.28600000001</v>
+        <v>47629.988</v>
       </c>
       <c r="G95">
         <v>469.3</v>
@@ -9205,37 +9205,37 @@
         <v>1604</v>
       </c>
       <c r="M95">
-        <v>11111.6708388</v>
+        <v>11231.1511704</v>
       </c>
       <c r="N95">
-        <v>-9507.670838800002</v>
+        <v>-9627.151170400002</v>
       </c>
       <c r="O95">
-        <v>-2452.979076410401</v>
+        <v>-2483.805001963201</v>
       </c>
       <c r="P95">
-        <v>-7054.691762389602</v>
+        <v>-7143.346168436801</v>
       </c>
       <c r="Q95">
-        <v>-6748.291762389602</v>
+        <v>-6836.946168436802</v>
       </c>
       <c r="R95">
-        <v>13.2857142857143</v>
+        <v>15.66666666666668</v>
       </c>
       <c r="S95">
-        <v>0.653403965592887</v>
+        <v>0.7546712931917017</v>
       </c>
       <c r="T95">
-        <v>14.03242414764174</v>
+        <v>16.37116150558203</v>
       </c>
       <c r="U95">
         <v>0.2358</v>
       </c>
       <c r="V95">
-        <v>0.03724300386535671</v>
+        <v>0.03684680169657633</v>
       </c>
       <c r="W95">
-        <v>0.2270180996885489</v>
+        <v>0.2271115241599473</v>
       </c>
       <c r="X95" t="inlineStr">
         <is>
@@ -9243,7 +9243,7 @@
         </is>
       </c>
       <c r="Y95">
-        <v>0.1443527281602973</v>
+        <v>0.1428170608394431</v>
       </c>
       <c r="Z95">
         <v>0</v>
@@ -9251,22 +9251,22 @@
     </row>
     <row r="96">
       <c r="A96">
-        <v>0.9400000000000001</v>
+        <v>0.9500000000000001</v>
       </c>
       <c r="B96">
-        <v>0.2587651103018526</v>
+        <v>0.2606651103018526</v>
       </c>
       <c r="C96">
-        <v>-37050.14147650624</v>
+        <v>-37646.24858451867</v>
       </c>
       <c r="D96">
-        <v>10110.54652349377</v>
+        <v>10021.14141548134</v>
       </c>
       <c r="E96">
-        <v>43770.588</v>
+        <v>44277.29000000001</v>
       </c>
       <c r="F96">
-        <v>47629.988</v>
+        <v>48136.69000000001</v>
       </c>
       <c r="G96">
         <v>469.3</v>
@@ -9287,37 +9287,37 @@
         <v>1604</v>
       </c>
       <c r="M96">
-        <v>11231.1511704</v>
+        <v>11350.631502</v>
       </c>
       <c r="N96">
-        <v>-9627.151170400002</v>
+        <v>-9746.631502000002</v>
       </c>
       <c r="O96">
-        <v>-2483.805001963201</v>
+        <v>-2514.630927516001</v>
       </c>
       <c r="P96">
-        <v>-7143.346168436801</v>
+        <v>-7232.000574484002</v>
       </c>
       <c r="Q96">
-        <v>-6836.946168436802</v>
+        <v>-6925.600574484002</v>
       </c>
       <c r="R96">
-        <v>15.66666666666668</v>
+        <v>19.00000000000003</v>
       </c>
       <c r="S96">
-        <v>0.7546712931917017</v>
+        <v>0.8964455518300425</v>
       </c>
       <c r="T96">
-        <v>16.37116150558203</v>
+        <v>19.64539380669844</v>
       </c>
       <c r="U96">
         <v>0.2358</v>
       </c>
       <c r="V96">
-        <v>0.03684680169657633</v>
+        <v>0.03645894062608605</v>
       </c>
       <c r="W96">
-        <v>0.2271115241599473</v>
+        <v>0.2272029818003689</v>
       </c>
       <c r="X96" t="inlineStr">
         <is>
@@ -9325,7 +9325,7 @@
         </is>
       </c>
       <c r="Y96">
-        <v>0.1428170608394431</v>
+        <v>0.1413137233569227</v>
       </c>
       <c r="Z96">
         <v>0</v>
@@ -9333,22 +9333,22 @@
     </row>
     <row r="97">
       <c r="A97">
-        <v>0.9500000000000001</v>
+        <v>0.9600000000000001</v>
       </c>
       <c r="B97">
-        <v>0.2606651103018526</v>
+        <v>0.2625651103018525</v>
       </c>
       <c r="C97">
-        <v>-37646.24858451867</v>
+        <v>-38240.78837660107</v>
       </c>
       <c r="D97">
-        <v>10021.14141548134</v>
+        <v>9933.303623398935</v>
       </c>
       <c r="E97">
-        <v>44277.29000000001</v>
+        <v>44783.99200000001</v>
       </c>
       <c r="F97">
-        <v>48136.69000000001</v>
+        <v>48643.39200000001</v>
       </c>
       <c r="G97">
         <v>469.3</v>
@@ -9369,37 +9369,37 @@
         <v>1604</v>
       </c>
       <c r="M97">
-        <v>11350.631502</v>
+        <v>11470.1118336</v>
       </c>
       <c r="N97">
-        <v>-9746.631502000002</v>
+        <v>-9866.111833600002</v>
       </c>
       <c r="O97">
-        <v>-2514.630927516001</v>
+        <v>-2545.456853068801</v>
       </c>
       <c r="P97">
-        <v>-7232.000574484002</v>
+        <v>-7320.654980531201</v>
       </c>
       <c r="Q97">
-        <v>-6925.600574484002</v>
+        <v>-7014.254980531201</v>
       </c>
       <c r="R97">
-        <v>19.00000000000003</v>
+        <v>24.00000000000005</v>
       </c>
       <c r="S97">
-        <v>0.8964455518300425</v>
+        <v>1.109106939787554</v>
       </c>
       <c r="T97">
-        <v>19.64539380669844</v>
+        <v>24.55674225837307</v>
       </c>
       <c r="U97">
         <v>0.2358</v>
       </c>
       <c r="V97">
-        <v>0.03645894062608605</v>
+        <v>0.03607915999456432</v>
       </c>
       <c r="W97">
-        <v>0.2272029818003689</v>
+        <v>0.2272925340732817</v>
       </c>
       <c r="X97" t="inlineStr">
         <is>
@@ -9407,7 +9407,7 @@
         </is>
       </c>
       <c r="Y97">
-        <v>0.1413137233569227</v>
+        <v>0.1398417054052881</v>
       </c>
       <c r="Z97">
         <v>0</v>
@@ -9415,22 +9415,22 @@
     </row>
     <row r="98">
       <c r="A98">
-        <v>0.96</v>
+        <v>0.97</v>
       </c>
       <c r="B98">
-        <v>0.2625651103018525</v>
+        <v>0.2644651103018525</v>
       </c>
       <c r="C98">
-        <v>-38240.78837660106</v>
+        <v>-38833.80170838328</v>
       </c>
       <c r="D98">
-        <v>9933.303623398935</v>
+        <v>9846.992291616723</v>
       </c>
       <c r="E98">
-        <v>44783.992</v>
+        <v>45290.694</v>
       </c>
       <c r="F98">
-        <v>48643.392</v>
+        <v>49150.094</v>
       </c>
       <c r="G98">
         <v>469.3</v>
@@ -9451,37 +9451,37 @@
         <v>1604</v>
       </c>
       <c r="M98">
-        <v>11470.1118336</v>
+        <v>11589.5921652</v>
       </c>
       <c r="N98">
-        <v>-9866.1118336</v>
+        <v>-9985.592165200002</v>
       </c>
       <c r="O98">
-        <v>-2545.4568530688</v>
+        <v>-2576.2827786216</v>
       </c>
       <c r="P98">
-        <v>-7320.6549805312</v>
+        <v>-7409.309386578401</v>
       </c>
       <c r="Q98">
-        <v>-7014.2549805312</v>
+        <v>-7102.909386578402</v>
       </c>
       <c r="R98">
-        <v>23.99999999999998</v>
+        <v>32.33333333333331</v>
       </c>
       <c r="S98">
-        <v>1.109106939787551</v>
+        <v>1.463542586383401</v>
       </c>
       <c r="T98">
-        <v>24.556742258373</v>
+        <v>32.742323011164</v>
       </c>
       <c r="U98">
         <v>0.2358</v>
       </c>
       <c r="V98">
-        <v>0.03607915999456433</v>
+        <v>0.03570720989152758</v>
       </c>
       <c r="W98">
-        <v>0.2272925340732817</v>
+        <v>0.2273802399075778</v>
       </c>
       <c r="X98" t="inlineStr">
         <is>
@@ -9489,7 +9489,7 @@
         </is>
       </c>
       <c r="Y98">
-        <v>0.1398417054052881</v>
+        <v>0.1384000383392542</v>
       </c>
       <c r="Z98">
         <v>0</v>
@@ -9497,22 +9497,22 @@
     </row>
     <row r="99">
       <c r="A99">
-        <v>0.97</v>
+        <v>0.98</v>
       </c>
       <c r="B99">
-        <v>0.2644651103018525</v>
+        <v>0.2663651103018526</v>
       </c>
       <c r="C99">
-        <v>-38833.80170838328</v>
+        <v>-39425.32802773491</v>
       </c>
       <c r="D99">
-        <v>9846.992291616723</v>
+        <v>9762.167972265092</v>
       </c>
       <c r="E99">
-        <v>45290.694</v>
+        <v>45797.396</v>
       </c>
       <c r="F99">
-        <v>49150.094</v>
+        <v>49656.796</v>
       </c>
       <c r="G99">
         <v>469.3</v>
@@ -9533,37 +9533,37 @@
         <v>1604</v>
       </c>
       <c r="M99">
-        <v>11589.5921652</v>
+        <v>11709.0724968</v>
       </c>
       <c r="N99">
-        <v>-9985.592165200002</v>
+        <v>-10105.0724968</v>
       </c>
       <c r="O99">
-        <v>-2576.2827786216</v>
+        <v>-2607.1087041744</v>
       </c>
       <c r="P99">
-        <v>-7409.309386578401</v>
+        <v>-7497.963792625601</v>
       </c>
       <c r="Q99">
-        <v>-7102.909386578402</v>
+        <v>-7191.563792625601</v>
       </c>
       <c r="R99">
-        <v>32.33333333333331</v>
+        <v>48.99999999999996</v>
       </c>
       <c r="S99">
-        <v>1.463542586383401</v>
+        <v>2.172413879575102</v>
       </c>
       <c r="T99">
-        <v>32.742323011164</v>
+        <v>49.11348451674601</v>
       </c>
       <c r="U99">
         <v>0.2358</v>
       </c>
       <c r="V99">
-        <v>0.03570720989152758</v>
+        <v>0.03534285060692016</v>
       </c>
       <c r="W99">
-        <v>0.2273802399075778</v>
+        <v>0.2274661558268883</v>
       </c>
       <c r="X99" t="inlineStr">
         <is>
@@ -9571,7 +9571,7 @@
         </is>
       </c>
       <c r="Y99">
-        <v>0.1384000383392542</v>
+        <v>0.1369877930500781</v>
       </c>
       <c r="Z99">
         <v>0</v>
@@ -9579,22 +9579,22 @@
     </row>
     <row r="100">
       <c r="A100">
-        <v>0.98</v>
+        <v>0.99</v>
       </c>
       <c r="B100">
-        <v>0.2663651103018526</v>
+        <v>0.2682651103018525</v>
       </c>
       <c r="C100">
-        <v>-39425.32802773491</v>
+        <v>-40015.4054348814</v>
       </c>
       <c r="D100">
-        <v>9762.167972265092</v>
+        <v>9678.792565118611</v>
       </c>
       <c r="E100">
-        <v>45797.396</v>
+        <v>46304.09800000001</v>
       </c>
       <c r="F100">
-        <v>49656.796</v>
+        <v>50163.49800000001</v>
       </c>
       <c r="G100">
         <v>469.3</v>
@@ -9615,37 +9615,37 @@
         <v>1604</v>
       </c>
       <c r="M100">
-        <v>11709.0724968</v>
+        <v>11828.5528284</v>
       </c>
       <c r="N100">
-        <v>-10105.0724968</v>
+        <v>-10224.5528284</v>
       </c>
       <c r="O100">
-        <v>-2607.1087041744</v>
+        <v>-2637.934629727201</v>
       </c>
       <c r="P100">
-        <v>-7497.963792625601</v>
+        <v>-7586.618198672802</v>
       </c>
       <c r="Q100">
-        <v>-7191.563792625601</v>
+        <v>-7280.218198672803</v>
       </c>
       <c r="R100">
-        <v>48.99999999999996</v>
+        <v>98.99999999999991</v>
       </c>
       <c r="S100">
-        <v>2.172413879575102</v>
+        <v>4.299027759150203</v>
       </c>
       <c r="T100">
-        <v>49.11348451674601</v>
+        <v>98.226969033492</v>
       </c>
       <c r="U100">
         <v>0.2358</v>
       </c>
       <c r="V100">
-        <v>0.03534285060692016</v>
+        <v>0.03498585211594116</v>
       </c>
       <c r="W100">
-        <v>0.2274661558268883</v>
+        <v>0.2275503360710611</v>
       </c>
       <c r="X100" t="inlineStr">
         <is>
@@ -9653,91 +9653,9 @@
         </is>
       </c>
       <c r="Y100">
-        <v>0.1369877930500781</v>
+        <v>0.1356040779687642</v>
       </c>
       <c r="Z100">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="101">
-      <c r="A101">
-        <v>0.99</v>
-      </c>
-      <c r="B101">
-        <v>0.2682651103018525</v>
-      </c>
-      <c r="C101">
-        <v>-40015.4054348814</v>
-      </c>
-      <c r="D101">
-        <v>9678.792565118611</v>
-      </c>
-      <c r="E101">
-        <v>46304.09800000001</v>
-      </c>
-      <c r="F101">
-        <v>50163.49800000001</v>
-      </c>
-      <c r="G101">
-        <v>469.3</v>
-      </c>
-      <c r="H101">
-        <v>46810.8</v>
-      </c>
-      <c r="I101">
-        <v>0</v>
-      </c>
-      <c r="J101">
-        <v>1910.4</v>
-      </c>
-      <c r="K101">
-        <v>306.4</v>
-      </c>
-      <c r="L101">
-        <v>1604</v>
-      </c>
-      <c r="M101">
-        <v>11828.5528284</v>
-      </c>
-      <c r="N101">
-        <v>-10224.5528284</v>
-      </c>
-      <c r="O101">
-        <v>-2637.934629727201</v>
-      </c>
-      <c r="P101">
-        <v>-7586.618198672802</v>
-      </c>
-      <c r="Q101">
-        <v>-7280.218198672803</v>
-      </c>
-      <c r="R101">
-        <v>98.99999999999991</v>
-      </c>
-      <c r="S101">
-        <v>4.299027759150203</v>
-      </c>
-      <c r="T101">
-        <v>98.226969033492</v>
-      </c>
-      <c r="U101">
-        <v>0.2358</v>
-      </c>
-      <c r="V101">
-        <v>0.03498585211594116</v>
-      </c>
-      <c r="W101">
-        <v>0.2275503360710611</v>
-      </c>
-      <c r="X101" t="inlineStr">
-        <is>
-          <t>D2/D</t>
-        </is>
-      </c>
-      <c r="Y101">
-        <v>0.1356040779687642</v>
-      </c>
-      <c r="Z101">
         <v>0</v>
       </c>
     </row>
